--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{93CA2416-F868-4B9E-987E-7C49EF6006DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD4574DA-DF9D-482B-97F5-BCF177D45CFD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6A5A26-E34F-453A-9291-39C90C96DAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="65">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -221,6 +221,18 @@
   </si>
   <si>
     <t>วริษฐ์ ยุวโชติพันธุ์</t>
+  </si>
+  <si>
+    <t>รอส่งมอบงาน</t>
+  </si>
+  <si>
+    <t>รองานโครงสร้าง</t>
+  </si>
+  <si>
+    <t>โครงสร้างจบปี 2027</t>
+  </si>
+  <si>
+    <t>รอทางโครงการเปิดฝ้า เพื่อเข้าดำเนินงาน</t>
   </si>
 </sst>
 </file>
@@ -362,7 +374,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -404,15 +416,21 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -811,7 +829,7 @@
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
@@ -821,7 +839,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
@@ -833,7 +851,7 @@
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
@@ -906,10 +924,10 @@
         <v>46189</v>
       </c>
       <c r="E6" s="4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6" s="19"/>
       <c r="H6" s="2"/>
@@ -994,7 +1012,7 @@
         <v>46213</v>
       </c>
       <c r="E10" s="4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -1148,7 +1166,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="4">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
@@ -1278,7 +1296,7 @@
         <v>46206</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
@@ -1476,6 +1494,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A1:H1"/>
@@ -1492,20 +1524,6 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F50" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1535,11 +1553,11 @@
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="16" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="28" customWidth="1"/>
+    <col min="19" max="19" width="35.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="16"/>
@@ -1562,7 +1580,7 @@
       <c r="S1" s="16"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="16"/>
@@ -1648,7 +1666,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" s="8">
         <v>0.9</v>
@@ -1690,7 +1708,9 @@
         <v>46213</v>
       </c>
       <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
+      <c r="S5" s="7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="7" t="s">
@@ -1733,14 +1753,16 @@
         <v>39</v>
       </c>
       <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
+      <c r="S6" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8">
         <v>0.9</v>
@@ -1782,7 +1804,9 @@
         <v>46204</v>
       </c>
       <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
+      <c r="S7" s="7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="7" t="s">
@@ -1874,7 +1898,9 @@
         <v>39</v>
       </c>
       <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
+      <c r="S9" s="7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
@@ -1925,7 +1951,9 @@
         <v>46199</v>
       </c>
       <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
+      <c r="S10" s="7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
@@ -1935,7 +1963,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="8">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="D11" s="9">
         <v>1156111.18</v>
@@ -2021,7 +2049,9 @@
         <v>46336</v>
       </c>
       <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
+      <c r="S12" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
@@ -2067,6 +2097,9 @@
       <c r="Q13" s="13">
         <v>46336</v>
       </c>
+      <c r="S13" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
@@ -2076,7 +2109,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="8">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D14" s="9">
         <v>1707089</v>
@@ -2113,6 +2146,9 @@
       </c>
       <c r="Q14" s="13">
         <v>46218</v>
+      </c>
+      <c r="S14" s="21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2197,6 +2233,9 @@
       </c>
       <c r="Q16" s="13">
         <v>46321</v>
+      </c>
+      <c r="S16" s="22" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -2308,14 +2347,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="16"/>
@@ -2504,28 +2543,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -2778,26 +2795,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4FF8CBE-3129-4B52-9D99-BC4B6B4C496C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EF7796D-18CF-451E-9339-CE23320C9E25}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C86DF85-F84C-4A7F-AE43-781BF74452D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2814,4 +2834,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EF7796D-18CF-451E-9339-CE23320C9E25}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4FF8CBE-3129-4B52-9D99-BC4B6B4C496C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF9501C-8403-4EAE-AA3E-3F403A0218C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19450531-0C39-4851-9A41-8E4317E8526C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="64">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>ส่งมอบงานวันที่ 15/07/2026</t>
+  </si>
+  <si>
+    <t>บ้านคุณเต้ย</t>
   </si>
 </sst>
 </file>
@@ -1523,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2305,6 +2308,42 @@
         <v>46200</v>
       </c>
       <c r="Q18" s="11">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7">
+        <f t="shared" ref="E19" si="2">O19</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7">
+        <f>D19*1</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="12">
+        <v>10</v>
+      </c>
+      <c r="J19" s="5"/>
+      <c r="K19" s="7"/>
+      <c r="N19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P19" s="9" t="e">
+        <f>'[1]Master Schedule'!C19</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q19" s="11">
         <v>46133</v>
       </c>
     </row>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19450531-0C39-4851-9A41-8E4317E8526C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="64">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -816,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
@@ -1482,8 +1482,52 @@
       </c>
       <c r="G32" s="22"/>
     </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="14">
+        <v>46091</v>
+      </c>
+      <c r="D33" s="14">
+        <v>46094</v>
+      </c>
+      <c r="E33" s="15">
+        <v>0</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="23">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="22"/>
+      <c r="B34" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="14">
+        <v>46091</v>
+      </c>
+      <c r="D34" s="14">
+        <v>46094</v>
+      </c>
+      <c r="E34" s="15">
+        <v>0</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="32">
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="G33:G34"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A1:H1"/>
@@ -2229,7 +2273,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -2270,7 +2314,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -2311,7 +2355,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -2336,15 +2380,18 @@
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="7"/>
-      <c r="N19" t="s">
-        <v>36</v>
-      </c>
-      <c r="P19" s="9" t="e">
-        <f>'[1]Master Schedule'!C19</f>
-        <v>#REF!</v>
+      <c r="N19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19" s="9">
+        <f>'Master Schedule'!C33</f>
+        <v>46091</v>
       </c>
       <c r="Q19" s="11">
-        <v>46133</v>
+        <v>46295</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9122DACE-0F09-4378-A6DC-2F6870C91495}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -362,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -422,6 +422,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1002,10 +1005,10 @@
         <v>46213</v>
       </c>
       <c r="E10" s="15">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G10" s="22"/>
       <c r="H10" s="13"/>
@@ -1156,7 +1159,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="15">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>10</v>
@@ -1203,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G19" s="23">
         <v>46336</v>
@@ -1225,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" s="22"/>
       <c r="H20" s="13"/>
@@ -1286,7 +1289,7 @@
         <v>46206</v>
       </c>
       <c r="E23" s="15">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>10</v>
@@ -1310,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24" s="22"/>
     </row>
@@ -1373,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27" s="23">
         <v>46321</v>
@@ -1394,7 +1397,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="22"/>
     </row>
@@ -1499,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" s="23">
         <v>46295</v>
@@ -1520,12 +1523,28 @@
         <v>0</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="A9:A10"/>
@@ -1542,22 +1561,6 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="G15:G16"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1700,7 +1703,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6">
         <v>0.9</v>
@@ -1714,8 +1717,8 @@
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7">
-        <f>D5*0.4</f>
-        <v>130714.54399999999</v>
+        <f>D5*0.8</f>
+        <v>261429.08799999999</v>
       </c>
       <c r="H5" s="8">
         <v>12</v>
@@ -1767,7 +1770,9 @@
         <f t="shared" ref="G6:G14" si="0">D6*0.4</f>
         <v>163839.85600000003</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
       <c r="I6" s="8"/>
       <c r="J6" s="5"/>
       <c r="K6" s="7">
@@ -1798,7 +1803,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6">
         <v>0.9</v>
@@ -1915,7 +1920,9 @@
         <f>D9*0.4</f>
         <v>252247.67999999999</v>
       </c>
-      <c r="H9" s="8"/>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
       <c r="I9" s="8"/>
       <c r="J9" s="5"/>
       <c r="K9" s="7"/>
@@ -1960,7 +1967,7 @@
         <v>135380.08000000002</v>
       </c>
       <c r="H10" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="5"/>
@@ -2012,7 +2019,7 @@
         <v>462444.47200000001</v>
       </c>
       <c r="H11" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="5"/>
@@ -2061,7 +2068,9 @@
         <f t="shared" si="0"/>
         <v>237645.6</v>
       </c>
-      <c r="H12" s="8"/>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
       <c r="I12" s="8"/>
       <c r="J12" s="5"/>
       <c r="K12" s="7">
@@ -2146,7 +2155,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D14" s="7">
         <v>1707089</v>
@@ -2161,7 +2170,7 @@
         <v>682835.60000000009</v>
       </c>
       <c r="H14" s="10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="7">
@@ -2235,7 +2244,7 @@
         <v>51</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6">
         <v>0</v>
@@ -2252,6 +2261,9 @@
         <f>D16*0.4</f>
         <v>479984.00800000003</v>
       </c>
+      <c r="H16" s="24">
+        <v>0</v>
+      </c>
       <c r="K16" s="7"/>
       <c r="M16">
         <v>34414</v>
@@ -2360,23 +2372,25 @@
         <v>63</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6">
         <v>0</v>
       </c>
-      <c r="D19" s="7"/>
+      <c r="D19" s="7">
+        <v>832813</v>
+      </c>
       <c r="E19" s="7">
         <f t="shared" ref="E19" si="2">O19</f>
         <v>0</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7">
-        <f>D19*1</f>
-        <v>0</v>
+        <f>455555</f>
+        <v>455555</v>
       </c>
       <c r="H19" s="12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="7"/>
@@ -2615,12 +2629,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2877,22 +2895,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2917,12 +2934,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9122DACE-0F09-4378-A6DC-2F6870C91495}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACA5B751-EEE6-48F6-8B14-14E47380CB1A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="64">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -362,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -413,9 +413,6 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -423,9 +420,9 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -832,28 +829,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -882,7 +879,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="18" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="13" t="s">
@@ -900,13 +897,13 @@
       <c r="F5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="20">
         <v>46213</v>
       </c>
       <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="13" t="s">
         <v>56</v>
       </c>
@@ -922,11 +919,11 @@
       <c r="F6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="18" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -944,13 +941,13 @@
       <c r="F7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="20" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="13" t="s">
         <v>56</v>
       </c>
@@ -966,11 +963,11 @@
       <c r="F8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="22"/>
+      <c r="G8" s="19"/>
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="18" t="s">
         <v>40</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -988,13 +985,13 @@
       <c r="F9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="20">
         <v>46204</v>
       </c>
       <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="13" t="s">
         <v>56</v>
       </c>
@@ -1010,11 +1007,11 @@
       <c r="F10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="22"/>
+      <c r="G10" s="19"/>
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="18" t="s">
         <v>41</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1032,13 +1029,13 @@
       <c r="F11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="20">
         <v>46171</v>
       </c>
       <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="13" t="s">
         <v>56</v>
       </c>
@@ -1054,11 +1051,11 @@
       <c r="F12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="19"/>
       <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="18" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="13" t="s">
@@ -1076,13 +1073,13 @@
       <c r="F13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="20" t="s">
         <v>39</v>
       </c>
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="13" t="s">
         <v>56</v>
       </c>
@@ -1098,11 +1095,11 @@
       <c r="F14" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="22"/>
+      <c r="G14" s="19"/>
       <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="18" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -1120,13 +1117,13 @@
       <c r="F15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="20">
         <v>46199</v>
       </c>
       <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="13" t="s">
         <v>56</v>
       </c>
@@ -1142,11 +1139,11 @@
       <c r="F16" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="22"/>
+      <c r="G16" s="19"/>
       <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B17" s="13" t="s">
@@ -1164,13 +1161,13 @@
       <c r="F17" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="20">
         <v>46305</v>
       </c>
       <c r="H17" s="13"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="13" t="s">
         <v>56</v>
       </c>
@@ -1186,11 +1183,11 @@
       <c r="F18" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="19"/>
       <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -1208,13 +1205,13 @@
       <c r="F19" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="20">
         <v>46336</v>
       </c>
       <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="13" t="s">
         <v>56</v>
       </c>
@@ -1230,11 +1227,11 @@
       <c r="F20" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="22"/>
+      <c r="G20" s="19"/>
       <c r="H20" s="13"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="18" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -1252,12 +1249,12 @@
       <c r="F21" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="20">
         <v>46336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="22"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="13" t="s">
         <v>56</v>
       </c>
@@ -1273,10 +1270,10 @@
       <c r="F22" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="22"/>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -1294,12 +1291,12 @@
       <c r="F23" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="20">
         <v>46218</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="13" t="s">
         <v>56</v>
       </c>
@@ -1315,10 +1312,10 @@
       <c r="F24" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="22"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -1336,12 +1333,12 @@
       <c r="F25" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="20">
         <v>46188</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="22"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="13" t="s">
         <v>56</v>
       </c>
@@ -1357,10 +1354,10 @@
       <c r="F26" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="22"/>
+      <c r="G26" s="19"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="18" t="s">
         <v>51</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -1378,12 +1375,12 @@
       <c r="F27" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="20">
         <v>46321</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="13" t="s">
         <v>56</v>
       </c>
@@ -1399,10 +1396,10 @@
       <c r="F28" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G28" s="22"/>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="18" t="s">
         <v>52</v>
       </c>
       <c r="B29" s="13" t="s">
@@ -1420,12 +1417,12 @@
       <c r="F29" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="20">
         <v>46139</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="22"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="13" t="s">
         <v>56</v>
       </c>
@@ -1441,10 +1438,10 @@
       <c r="F30" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="22"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="18" t="s">
         <v>54</v>
       </c>
       <c r="B31" s="13" t="s">
@@ -1462,12 +1459,12 @@
       <c r="F31" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="20">
         <v>46133</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="13" t="s">
         <v>56</v>
       </c>
@@ -1483,10 +1480,10 @@
       <c r="F32" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="22"/>
+      <c r="G32" s="19"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="18" t="s">
         <v>63</v>
       </c>
       <c r="B33" s="13" t="s">
@@ -1504,12 +1501,12 @@
       <c r="F33" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="20">
         <v>46295</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="22"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="13" t="s">
         <v>56</v>
       </c>
@@ -1525,26 +1522,10 @@
       <c r="F34" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G34" s="22"/>
+      <c r="G34" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="A9:A10"/>
@@ -1561,6 +1542,22 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="G15:G16"/>
     <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1586,7 +1583,7 @@
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="14" max="14" width="31.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="16" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
@@ -1594,50 +1591,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="19"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
     </row>
     <row r="4" spans="1:19" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1731,7 +1728,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O5" s="7">
         <v>130000</v>
@@ -1883,7 +1880,7 @@
         <v>1444</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="O8" s="7">
         <v>89000</v>
@@ -2030,8 +2027,8 @@
       <c r="M11" s="7">
         <v>46175</v>
       </c>
-      <c r="N11" s="5" t="s">
-        <v>44</v>
+      <c r="N11" t="s">
+        <v>36</v>
       </c>
       <c r="O11" s="7">
         <v>280000</v>
@@ -2080,8 +2077,8 @@
       <c r="M12" s="7">
         <v>20018</v>
       </c>
-      <c r="N12" s="5" t="s">
-        <v>36</v>
+      <c r="N12" t="s">
+        <v>48</v>
       </c>
       <c r="O12" s="7">
         <v>233247.9</v>
@@ -2130,8 +2127,8 @@
       <c r="M13">
         <v>4164</v>
       </c>
-      <c r="N13" t="s">
-        <v>48</v>
+      <c r="N13" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="O13">
         <v>120000</v>
@@ -2180,7 +2177,7 @@
         <v>20695.969999999972</v>
       </c>
       <c r="N14" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="O14">
         <v>656679.03</v>
@@ -2226,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O15">
         <v>40000</v>
@@ -2261,7 +2258,7 @@
         <f>D16*0.4</f>
         <v>479984.00800000003</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="10">
         <v>0</v>
       </c>
       <c r="K16" s="7"/>
@@ -2269,7 +2266,7 @@
         <v>34414</v>
       </c>
       <c r="N16" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="O16">
         <v>430000</v>
@@ -2313,7 +2310,7 @@
       <c r="J17" s="5"/>
       <c r="K17" s="7"/>
       <c r="N17" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="O17">
         <v>234861</v>
@@ -2353,8 +2350,8 @@
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="7"/>
-      <c r="N18" t="s">
-        <v>36</v>
+      <c r="N18" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="O18">
         <v>119980</v>
@@ -2433,18 +2430,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2545,23 +2542,41 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="17">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="4"/>
+      <c r="A15" s="3">
+        <v>46198</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4"/>
+      <c r="A16" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
-      <c r="B17" s="2"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2629,16 +2644,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2895,21 +2906,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2934,9 +2946,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACA5B751-EEE6-48F6-8B14-14E47380CB1A}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD94B2C0-B700-4246-8CD7-4B17BBBA80AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="67">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>Planning</t>
-  </si>
-  <si>
     <t>Completed</t>
   </si>
   <si>
@@ -230,16 +227,30 @@
   </si>
   <si>
     <t>บ้านคุณเต้ย</t>
+  </si>
+  <si>
+    <t>Khun Sarut's House</t>
+  </si>
+  <si>
+    <t>25-17_Ekamai 28 (K'Phong)</t>
+  </si>
+  <si>
+    <t>โครงการล่าช้า</t>
+  </si>
+  <si>
+    <t>บริษัทอีโค่คูลไคลเมท เทคโนโลยีจำกัด</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,11 +281,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10.5"/>
       <color rgb="FF16243A"/>
@@ -287,10 +293,29 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Cordia New"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cordia New"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -359,10 +384,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -376,55 +402,69 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -471,11 +511,6 @@
         <row r="8">
           <cell r="C8">
             <v>46244</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9">
-            <v>46082</v>
           </cell>
         </row>
         <row r="10">
@@ -529,6 +564,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -816,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
@@ -829,28 +868,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -879,653 +918,757 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="6">
+        <v>46084</v>
+      </c>
+      <c r="D5" s="6">
+        <v>46127</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="11">
+        <v>46213</v>
+      </c>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="10"/>
+      <c r="B6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="14">
-        <v>46084</v>
-      </c>
-      <c r="D5" s="14">
-        <v>46127</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="C6" s="6">
+        <v>46189</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46189</v>
+      </c>
+      <c r="E6" s="7">
         <v>1</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="6">
+        <v>46219</v>
+      </c>
+      <c r="D7" s="6">
+        <v>46233</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="6">
+        <v>46244</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46247</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="6">
+        <v>46082</v>
+      </c>
+      <c r="D9" s="6">
+        <v>46096</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="11">
+        <v>46204</v>
+      </c>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="6">
+        <v>46168</v>
+      </c>
+      <c r="D10" s="6">
         <v>46213</v>
       </c>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="14">
-        <v>46189</v>
-      </c>
-      <c r="D6" s="14">
-        <v>46189</v>
-      </c>
-      <c r="E6" s="15">
+      <c r="E10" s="7">
         <v>1</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="6">
+        <v>46184</v>
+      </c>
+      <c r="D11" s="6">
+        <v>46191</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="11">
+        <v>46171</v>
+      </c>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="6">
+        <v>46200</v>
+      </c>
+      <c r="D12" s="6">
+        <v>46202</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="6">
+        <v>46392</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46402</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="6">
+        <v>46042</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46042</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="6">
+        <v>46168</v>
+      </c>
+      <c r="D15" s="6">
+        <v>46188</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="11">
+        <v>46199</v>
+      </c>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="6">
+        <v>46198</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46199</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="6">
+        <v>46188</v>
+      </c>
+      <c r="D17" s="6">
+        <v>46198</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="11">
+        <v>46305</v>
+      </c>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="6">
+        <v>46296</v>
+      </c>
+      <c r="D18" s="6">
+        <v>46298</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="G18" s="10"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="6">
+        <v>46275</v>
+      </c>
+      <c r="D19" s="6">
+        <v>46290</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11">
+        <v>46336</v>
+      </c>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="14">
-        <v>46219</v>
-      </c>
-      <c r="D7" s="14">
-        <v>46233</v>
-      </c>
-      <c r="E7" s="15">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="14">
-        <v>46244</v>
-      </c>
-      <c r="D8" s="14">
+      <c r="C20" s="6">
+        <v>46327</v>
+      </c>
+      <c r="D20" s="6">
+        <v>46329</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="6">
+        <v>46240</v>
+      </c>
+      <c r="D21" s="6">
+        <v>46249</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="11">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="6">
+        <v>46327</v>
+      </c>
+      <c r="D22" s="6">
+        <v>46329</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="6">
+        <v>46190</v>
+      </c>
+      <c r="D23" s="6">
+        <v>46206</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="11">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="6">
+        <v>46209</v>
+      </c>
+      <c r="D24" s="6">
+        <v>46211</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="6">
+        <v>46185</v>
+      </c>
+      <c r="D25" s="6">
+        <v>46188</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="11">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="6">
+        <v>46185</v>
+      </c>
+      <c r="D26" s="6">
+        <v>46188</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="6">
+        <v>46234</v>
+      </c>
+      <c r="D27" s="6">
         <v>46247</v>
       </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="E27" s="7">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="11">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="14">
-        <v>46082</v>
-      </c>
-      <c r="D9" s="14">
-        <v>46096</v>
-      </c>
-      <c r="E9" s="15">
+      <c r="C28" s="6">
+        <v>46314</v>
+      </c>
+      <c r="D28" s="6">
+        <v>46316</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="6">
+        <v>46091</v>
+      </c>
+      <c r="D29" s="6">
+        <v>46100</v>
+      </c>
+      <c r="E29" s="7">
         <v>1</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="11">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="6">
+        <v>46120</v>
+      </c>
+      <c r="D30" s="6">
+        <v>46124</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="6">
+        <v>46091</v>
+      </c>
+      <c r="D31" s="6">
+        <v>46094</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="11">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="6">
+        <v>46091</v>
+      </c>
+      <c r="D32" s="6">
+        <v>46094</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="6">
+        <v>46091</v>
+      </c>
+      <c r="D33" s="6">
+        <v>46094</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="20">
-        <v>46204</v>
-      </c>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="19"/>
-      <c r="B10" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="14">
-        <v>46168</v>
-      </c>
-      <c r="D10" s="14">
-        <v>46213</v>
-      </c>
-      <c r="E10" s="15">
+      <c r="G33" s="11">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="10"/>
+      <c r="B34" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="6">
+        <v>46091</v>
+      </c>
+      <c r="D34" s="6">
+        <v>46094</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="6">
+        <v>45723</v>
+      </c>
+      <c r="D35" s="6">
+        <v>45729</v>
+      </c>
+      <c r="E35" s="7">
         <v>1</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F35" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="G35" s="11">
+        <v>45737</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="10"/>
+      <c r="B36" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="14">
-        <v>46184</v>
-      </c>
-      <c r="D11" s="14">
-        <v>46191</v>
-      </c>
-      <c r="E11" s="15">
+      <c r="C36" s="6">
+        <v>45729</v>
+      </c>
+      <c r="D36" s="6">
+        <v>45732</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="6">
+        <v>45723</v>
+      </c>
+      <c r="D37" s="6">
+        <v>45729</v>
+      </c>
+      <c r="E37" s="7">
         <v>1</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="20">
-        <v>46171</v>
-      </c>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="19"/>
-      <c r="B12" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="14">
-        <v>46200</v>
-      </c>
-      <c r="D12" s="14">
-        <v>46202</v>
-      </c>
-      <c r="E12" s="15">
-        <v>1</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="F37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="11">
+        <v>45737</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
+      <c r="B38" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="16">
-        <v>46392</v>
-      </c>
-      <c r="D13" s="16">
-        <v>46402</v>
-      </c>
-      <c r="E13" s="15">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="16">
-        <v>46042</v>
-      </c>
-      <c r="D14" s="16">
-        <v>46042</v>
-      </c>
-      <c r="E14" s="15">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="19"/>
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="14">
-        <v>46168</v>
-      </c>
-      <c r="D15" s="14">
-        <v>46188</v>
-      </c>
-      <c r="E15" s="15">
-        <v>1</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="20">
-        <v>46199</v>
-      </c>
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="14">
-        <v>46198</v>
-      </c>
-      <c r="D16" s="14">
-        <v>46199</v>
-      </c>
-      <c r="E16" s="15">
-        <v>1</v>
-      </c>
-      <c r="F16" s="13" t="s">
+      <c r="C38" s="6">
+        <v>45729</v>
+      </c>
+      <c r="D38" s="6">
+        <v>45732</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="14">
-        <v>46188</v>
-      </c>
-      <c r="D17" s="14">
-        <v>46198</v>
-      </c>
-      <c r="E17" s="15">
-        <v>1</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="20">
-        <v>46305</v>
-      </c>
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="14">
-        <v>46296</v>
-      </c>
-      <c r="D18" s="14">
-        <v>46298</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0.4</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="14">
-        <v>46275</v>
-      </c>
-      <c r="D19" s="14">
-        <v>46290</v>
-      </c>
-      <c r="E19" s="15">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="20">
-        <v>46336</v>
-      </c>
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="19"/>
-      <c r="B20" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="14">
-        <v>46327</v>
-      </c>
-      <c r="D20" s="14">
-        <v>46329</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="14">
-        <v>46240</v>
-      </c>
-      <c r="D21" s="14">
-        <v>46249</v>
-      </c>
-      <c r="E21" s="15">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="20">
-        <v>46336</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="19"/>
-      <c r="B22" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="14">
-        <v>46327</v>
-      </c>
-      <c r="D22" s="14">
-        <v>46329</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="14">
-        <v>46190</v>
-      </c>
-      <c r="D23" s="14">
-        <v>46206</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="20">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="19"/>
-      <c r="B24" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="14">
-        <v>46209</v>
-      </c>
-      <c r="D24" s="14">
-        <v>46211</v>
-      </c>
-      <c r="E24" s="15">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="14">
-        <v>46185</v>
-      </c>
-      <c r="D25" s="14">
-        <v>46188</v>
-      </c>
-      <c r="E25" s="15">
-        <v>1</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="20">
-        <v>46188</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="14">
-        <v>46185</v>
-      </c>
-      <c r="D26" s="14">
-        <v>46188</v>
-      </c>
-      <c r="E26" s="15">
-        <v>1</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="19"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="14">
-        <v>46234</v>
-      </c>
-      <c r="D27" s="14">
-        <v>46247</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="20">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="19"/>
-      <c r="B28" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="14">
-        <v>46314</v>
-      </c>
-      <c r="D28" s="14">
-        <v>46316</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="19"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="14">
-        <v>46091</v>
-      </c>
-      <c r="D29" s="14">
-        <v>46100</v>
-      </c>
-      <c r="E29" s="15">
-        <v>1</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="20">
-        <v>46139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="14">
-        <v>46120</v>
-      </c>
-      <c r="D30" s="14">
-        <v>46124</v>
-      </c>
-      <c r="E30" s="15">
-        <v>1</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="19"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="14">
-        <v>46091</v>
-      </c>
-      <c r="D31" s="14">
-        <v>46094</v>
-      </c>
-      <c r="E31" s="15">
-        <v>1</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="20">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="19"/>
-      <c r="B32" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="14">
-        <v>46091</v>
-      </c>
-      <c r="D32" s="14">
-        <v>46094</v>
-      </c>
-      <c r="E32" s="15">
-        <v>1</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="19"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="14">
-        <v>46091</v>
-      </c>
-      <c r="D33" s="14">
-        <v>46094</v>
-      </c>
-      <c r="E33" s="15">
-        <v>0</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="20">
-        <v>46295</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="19"/>
-      <c r="B34" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="14">
-        <v>46091</v>
-      </c>
-      <c r="D34" s="14">
-        <v>46094</v>
-      </c>
-      <c r="E34" s="15">
-        <v>0</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="19"/>
+      <c r="G38" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="36">
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="A9:A10"/>
@@ -1542,22 +1685,6 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="G15:G16"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1570,10 +1697,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="37.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="15" customWidth="1"/>
@@ -1591,50 +1718,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
     </row>
     <row r="4" spans="1:19" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1644,43 +1771,43 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>4</v>
@@ -1689,728 +1816,1024 @@
         <v>5</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="16">
         <v>0.9</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="17">
         <v>326786.36</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="17">
         <f>O5</f>
         <v>130000</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17">
         <f>D5*0.8</f>
         <v>261429.08799999999</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="18">
         <v>12</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="7">
+      <c r="I5" s="18"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="17">
         <v>5198</v>
       </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" s="7">
+      <c r="L5" s="17"/>
+      <c r="M5" s="17">
+        <v>0</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="17">
         <v>130000</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="19">
         <f>'[1]Master Schedule'!C5</f>
         <v>46084</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="Q5" s="19">
         <v>46106</v>
       </c>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="R5" s="15"/>
+      <c r="S5" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0</v>
+      </c>
+      <c r="D6" s="17">
         <v>409599.64</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="17">
         <f>O6*0.3</f>
         <v>41833.799999999996</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7">
+      <c r="F6" s="17"/>
+      <c r="G6" s="17">
         <f t="shared" ref="G6:G14" si="0">D6*0.4</f>
         <v>163839.85600000003</v>
       </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="7">
+      <c r="H6" s="18">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="17">
         <v>6972.5</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" s="7">
+      <c r="L6" s="17"/>
+      <c r="M6" s="17">
+        <v>0</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="17">
         <v>139446</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="19">
         <f>'[1]Master Schedule'!C6</f>
         <v>46189</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q6" s="19">
+        <v>46264</v>
+      </c>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="16">
         <v>0.9</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="17">
         <v>576317.9</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="17">
         <f t="shared" ref="E7:E18" si="1">O7</f>
         <v>280000</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7">
+      <c r="F7" s="17">
+        <v>603</v>
+      </c>
+      <c r="G7" s="17">
         <f>D7*0.9</f>
         <v>518686.11000000004</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="18">
         <v>20</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="7">
+      <c r="I7" s="18"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="17">
         <v>12045</v>
       </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" s="7">
+      <c r="L7" s="17"/>
+      <c r="M7" s="17">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="17">
         <v>280000</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="19">
         <f>'[1]Master Schedule'!C7</f>
         <v>46219</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="Q7" s="19">
         <v>46102</v>
       </c>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="6">
+      <c r="R7" s="15"/>
+      <c r="S7" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="16">
         <v>1</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="17">
         <v>322961.08</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="17">
         <f t="shared" si="1"/>
         <v>89000</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7">
+      <c r="F8" s="17">
+        <v>715</v>
+      </c>
+      <c r="G8" s="17">
         <f>D8*1</f>
         <v>322961.08</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="18">
         <v>7</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="7">
+      <c r="I8" s="18"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="17">
         <v>24166</v>
       </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7">
+      <c r="L8" s="17"/>
+      <c r="M8" s="17">
         <v>1444</v>
       </c>
-      <c r="N8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O8" s="7">
+      <c r="N8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="O8" s="17">
         <v>89000</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="19">
         <f>'[1]Master Schedule'!C8</f>
         <v>46244</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="Q8" s="19">
         <v>46171</v>
       </c>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+    </row>
+    <row r="9" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="16">
+        <v>0</v>
+      </c>
+      <c r="D9" s="17">
         <v>630619.19999999995</v>
       </c>
-      <c r="E9" s="7" t="str">
+      <c r="E9" s="17" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17">
         <f>D9*0.4</f>
         <v>252247.67999999999</v>
       </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" s="9">
-        <f>'[1]Master Schedule'!C9</f>
-        <v>46082</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="H9" s="18">
+        <v>0</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15"/>
+      <c r="O9" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="19">
+        <v>46388</v>
+      </c>
+      <c r="Q9" s="19">
+        <v>46447</v>
+      </c>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="16">
         <v>1</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="17">
         <v>338450.2</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="17">
         <f>O10*0.8</f>
         <v>110400</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7">
+      <c r="F10" s="17">
+        <v>370</v>
+      </c>
+      <c r="G10" s="17">
         <f>D10*0.4</f>
         <v>135380.08000000002</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="18">
         <v>10</v>
       </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="7">
+      <c r="I10" s="18"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="17">
         <v>5783</v>
       </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7">
+      <c r="L10" s="17"/>
+      <c r="M10" s="17">
         <v>787</v>
       </c>
-      <c r="N10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="7">
+      <c r="N10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="O10" s="17">
         <v>138000</v>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="19">
         <f>'[1]Master Schedule'!C10</f>
         <v>46168</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="Q10" s="19">
         <v>46199</v>
       </c>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="R10" s="15"/>
+      <c r="S10" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C11" s="16">
+        <v>0.7</v>
+      </c>
+      <c r="D11" s="17">
         <v>1156111.18</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="17">
         <f>O11*0.3</f>
         <v>84000</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7">
+      <c r="F11" s="17">
+        <v>840</v>
+      </c>
+      <c r="G11" s="17">
         <f t="shared" si="0"/>
         <v>462444.47200000001</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="18">
         <v>10</v>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="7">
+      <c r="I11" s="18"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="17">
         <v>26094</v>
       </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7">
+      <c r="L11" s="17"/>
+      <c r="M11" s="17">
         <v>46175</v>
       </c>
-      <c r="N11" t="s">
-        <v>36</v>
-      </c>
-      <c r="O11" s="7">
+      <c r="N11" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" s="17">
         <v>280000</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="19">
         <f>'[1]Master Schedule'!C11</f>
         <v>46184</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q11" s="19">
         <v>46305</v>
       </c>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+    </row>
+    <row r="12" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="16">
+        <v>0</v>
+      </c>
+      <c r="D12" s="17">
         <v>594114</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="17">
         <f>O12*0</f>
         <v>0</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7">
+      <c r="F12" s="17"/>
+      <c r="G12" s="17">
         <f t="shared" si="0"/>
         <v>237645.6</v>
       </c>
-      <c r="H12" s="8">
-        <v>0</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="7">
+      <c r="H12" s="18">
+        <v>0</v>
+      </c>
+      <c r="I12" s="18"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="17">
         <v>20261</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7">
+      <c r="L12" s="17"/>
+      <c r="M12" s="17">
         <v>20018</v>
       </c>
-      <c r="N12" t="s">
-        <v>48</v>
-      </c>
-      <c r="O12" s="7">
+      <c r="N12" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="O12" s="17">
         <v>233247.9</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="19">
         <f>'[1]Master Schedule'!C12</f>
         <v>46200</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="19">
         <v>46336</v>
       </c>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="R12" s="15"/>
+      <c r="S12" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="16">
+        <v>0</v>
+      </c>
+      <c r="D13" s="17">
         <v>327102.8</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="17">
         <f>O13*0.3</f>
         <v>36000</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7">
+      <c r="F13" s="17"/>
+      <c r="G13" s="17">
         <f t="shared" si="0"/>
         <v>130841.12</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="20">
         <v>3</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="7">
+      <c r="J13" s="15"/>
+      <c r="K13" s="17">
         <v>14327</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="25">
         <v>4164</v>
       </c>
-      <c r="N13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13">
+      <c r="N13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="25">
         <v>120000</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="19">
         <f>'[1]Master Schedule'!C13</f>
         <v>46392</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="26">
         <v>46336</v>
       </c>
-      <c r="S13" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="S13" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="16">
         <v>0.5</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="17">
         <v>1707089</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="17">
         <f>O14*0.3</f>
         <v>197003.709</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7">
+      <c r="F14" s="17">
+        <v>215</v>
+      </c>
+      <c r="G14" s="17">
         <f t="shared" si="0"/>
         <v>682835.60000000009</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="20">
         <v>10</v>
       </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="7">
+      <c r="J14" s="15"/>
+      <c r="K14" s="17">
         <v>54190</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="25">
         <v>20695.969999999972</v>
       </c>
-      <c r="N14" t="s">
-        <v>48</v>
-      </c>
-      <c r="O14">
+      <c r="N14" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="O14" s="25">
         <v>656679.03</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="19">
         <f>'[1]Master Schedule'!C14</f>
         <v>46042</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="26">
         <v>46218</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="6">
+    <row r="15" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="16">
         <v>1</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="17">
         <v>80000</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="17">
         <f>O15</f>
         <v>40000</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7">
+      <c r="F15" s="17">
+        <v>489</v>
+      </c>
+      <c r="G15" s="17">
         <f>D15*1</f>
         <v>80000</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="20">
         <v>4</v>
       </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="7">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>36</v>
-      </c>
-      <c r="O15">
+      <c r="J15" s="15"/>
+      <c r="K15" s="17">
+        <v>0</v>
+      </c>
+      <c r="M15" s="25">
+        <v>0</v>
+      </c>
+      <c r="N15" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="O15" s="25">
         <v>40000</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="19">
         <f>'[1]Master Schedule'!C15</f>
         <v>46168</v>
       </c>
-      <c r="Q15" s="11">
+      <c r="Q15" s="26">
         <v>46188</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="5" t="s">
+    <row r="16" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" s="16">
+        <v>0</v>
+      </c>
+      <c r="D16" s="17">
         <v>1199960.02</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="17">
         <f>O16*0</f>
         <v>0</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7">
+      <c r="F16" s="17"/>
+      <c r="G16" s="17">
         <f>D16*0.4</f>
         <v>479984.00800000003</v>
       </c>
-      <c r="H16" s="10">
-        <v>0</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="M16">
+      <c r="H16" s="20">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>27535</v>
+      </c>
+      <c r="M16" s="25">
         <v>34414</v>
       </c>
-      <c r="N16" t="s">
-        <v>53</v>
-      </c>
-      <c r="O16">
+      <c r="N16" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="O16" s="25">
         <v>430000</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="19">
         <f>'[1]Master Schedule'!C16</f>
         <v>46198</v>
       </c>
-      <c r="Q16" s="11">
+      <c r="Q16" s="26">
         <v>46321</v>
       </c>
-      <c r="S16" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="S16" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="16">
         <v>1</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="17">
         <v>600000</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="17">
         <f>O17</f>
         <v>234861</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7">
+      <c r="F17" s="17">
+        <v>735</v>
+      </c>
+      <c r="G17" s="17">
         <f>D17*1</f>
         <v>600000</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="21">
         <v>10</v>
       </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="7"/>
-      <c r="N17" t="s">
-        <v>36</v>
-      </c>
-      <c r="O17">
+      <c r="J17" s="15"/>
+      <c r="K17" s="17">
+        <v>10000</v>
+      </c>
+      <c r="M17" s="25">
+        <v>0</v>
+      </c>
+      <c r="N17" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" s="25">
         <v>234861</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="19">
         <f>'[1]Master Schedule'!C17</f>
         <v>46188</v>
       </c>
-      <c r="Q17" s="11">
+      <c r="Q17" s="26">
         <v>46139</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="6">
+    <row r="18" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="16">
         <v>1</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="17">
         <v>317648</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="17">
         <f t="shared" si="1"/>
         <v>119980</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7">
+      <c r="F18" s="17"/>
+      <c r="G18" s="17">
         <f>D18*1</f>
         <v>317648</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="21">
         <v>10</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="7"/>
-      <c r="N18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O18">
+      <c r="J18" s="15"/>
+      <c r="K18" s="17">
+        <v>8760</v>
+      </c>
+      <c r="M18" s="25">
+        <v>0</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="25">
         <v>119980</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="19">
         <f>'[1]Master Schedule'!C18</f>
         <v>46200</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="Q18" s="26">
         <v>46133</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="5" t="s">
+    <row r="19" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="6">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="C19" s="16">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17">
         <v>832813</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="17">
         <f t="shared" ref="E19" si="2">O19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7">
+      <c r="F19" s="17">
+        <v>630</v>
+      </c>
+      <c r="G19" s="17">
         <f>455555</f>
         <v>455555</v>
       </c>
-      <c r="H19" s="12">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="7"/>
-      <c r="N19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="P19" s="9">
+      <c r="H19" s="21">
+        <v>0</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="17">
+        <v>35070</v>
+      </c>
+      <c r="M19" s="25">
+        <v>0</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P19" s="19">
         <f>'Master Schedule'!C33</f>
         <v>46091</v>
       </c>
-      <c r="Q19" s="11">
+      <c r="Q19" s="26">
         <v>46295</v>
       </c>
-      <c r="S19" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
+      <c r="S19" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="D20" s="24">
+        <v>341236.34</v>
+      </c>
+      <c r="E20" s="28">
+        <f>O20*0.3</f>
+        <v>71744.399999999994</v>
+      </c>
+      <c r="F20" s="23">
+        <v>255</v>
+      </c>
+      <c r="G20" s="29">
+        <f>D20*0.9</f>
+        <v>307112.70600000001</v>
+      </c>
+      <c r="H20" s="25">
+        <v>3</v>
+      </c>
+      <c r="K20" s="25">
+        <v>0</v>
+      </c>
+      <c r="M20" s="25">
+        <v>0</v>
+      </c>
+      <c r="N20" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="O20" s="25">
+        <v>239148</v>
+      </c>
+      <c r="P20" s="19">
+        <v>45717</v>
+      </c>
+      <c r="Q20" s="19">
+        <v>45737</v>
+      </c>
+      <c r="S20" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="D21" s="23">
+        <v>666700</v>
+      </c>
+      <c r="E21" s="28">
+        <f>O21*0.65</f>
+        <v>145747.55000000002</v>
+      </c>
+      <c r="H21" s="25">
+        <v>3</v>
+      </c>
+      <c r="K21" s="25">
+        <v>0</v>
+      </c>
+      <c r="M21" s="25">
+        <v>0</v>
+      </c>
+      <c r="N21" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="O21" s="25">
+        <v>224227</v>
+      </c>
+      <c r="P21" s="19">
+        <v>45717</v>
+      </c>
+      <c r="Q21" s="19">
+        <v>45737</v>
+      </c>
+      <c r="S21" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="33" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="34" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="35" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="36" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="37" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="38" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="39" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="40" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="41" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="42" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="43" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="44" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="45" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="46" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="47" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="48" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="49" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="50" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="51" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="52" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="53" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="54" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="55" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="56" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="57" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="58" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="59" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="60" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="61" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="62" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="63" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="64" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="65" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="66" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="67" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="68" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="69" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="70" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="71" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="72" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="73" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="74" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="75" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="76" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="77" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="78" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="79" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="80" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="81" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="82" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="83" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="84" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="85" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="86" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="87" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="88" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="89" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="90" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="91" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="92" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="93" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="94" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="95" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="96" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="97" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="98" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="99" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="100" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="101" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="102" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="103" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="104" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="105" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="106" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="107" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="108" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="109" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="110" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="111" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="112" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="113" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="114" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="115" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="116" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="117" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="118" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="119" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="120" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="121" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="122" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="123" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="124" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="125" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="126" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="127" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="128" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="129" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="130" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="131" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="132" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="133" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="134" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="135" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="136" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="137" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="138" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="139" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="140" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="141" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="142" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="143" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="144" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="145" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="146" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="147" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="148" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="149" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="150" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="151" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="152" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="153" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="154" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="155" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="156" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="157" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="158" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="159" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="160" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="161" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="162" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="163" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="164" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="165" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="166" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="167" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="168" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="169" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="170" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="171" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="172" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="173" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="174" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="175" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="176" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="177" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="178" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="179" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="180" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="181" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="182" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="183" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="184" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="185" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="186" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="187" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="188" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="B5:B39" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -2430,125 +2853,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="6">
         <v>46185</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
-        <v>46189</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
-        <v>46183</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C10" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
-        <v>46185</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="17">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
         <v>46190</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="17">
+      <c r="B12" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
-        <v>46190</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="17">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
-        <v>46192</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="17">
-        <v>3</v>
-      </c>
-    </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
+      <c r="A14" s="6">
         <v>46197</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="17">
+      <c r="B14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="8">
         <v>3</v>
       </c>
     </row>
@@ -2556,8 +2979,8 @@
       <c r="A15" s="3">
         <v>46198</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>57</v>
+      <c r="B15" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C15" s="4">
         <v>6</v>
@@ -2567,8 +2990,8 @@
       <c r="A16" s="3">
         <v>46202</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>57</v>
+      <c r="B16" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C16" s="4">
         <v>6</v>
@@ -2576,7 +2999,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
-      <c r="B17" s="13"/>
+      <c r="B17" s="5"/>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2644,12 +3067,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2906,22 +3333,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2946,12 +3372,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD94B2C0-B700-4246-8CD7-4B17BBBA80AA}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B9C9BED-86B7-48AA-A8DF-73E02C0254B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -248,7 +248,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -388,7 +388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -414,16 +414,6 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -449,19 +439,32 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
@@ -564,10 +567,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -868,28 +867,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -918,7 +917,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -936,13 +935,13 @@
       <c r="F5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="27">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="5" t="s">
         <v>55</v>
       </c>
@@ -958,11 +957,11 @@
       <c r="F6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="29" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -980,13 +979,13 @@
       <c r="F7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="27" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="5" t="s">
         <v>55</v>
       </c>
@@ -1002,11 +1001,11 @@
       <c r="F8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="10"/>
+      <c r="G8" s="28"/>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="29" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1024,13 +1023,13 @@
       <c r="F9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="27">
         <v>46204</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
+      <c r="A10" s="28"/>
       <c r="B10" s="5" t="s">
         <v>55</v>
       </c>
@@ -1046,11 +1045,11 @@
       <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="28"/>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="29" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1068,13 +1067,13 @@
       <c r="F11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="27">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="5" t="s">
         <v>55</v>
       </c>
@@ -1090,11 +1089,11 @@
       <c r="F12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="10"/>
+      <c r="G12" s="28"/>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="29" t="s">
         <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1112,13 +1111,13 @@
       <c r="F13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="27" t="s">
         <v>38</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="5" t="s">
         <v>55</v>
       </c>
@@ -1134,11 +1133,11 @@
       <c r="F14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="10"/>
+      <c r="G14" s="28"/>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="29" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1156,13 +1155,13 @@
       <c r="F15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="27">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
+      <c r="A16" s="28"/>
       <c r="B16" s="5" t="s">
         <v>55</v>
       </c>
@@ -1178,11 +1177,11 @@
       <c r="F16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="29" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1200,13 +1199,13 @@
       <c r="F17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="27">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
+      <c r="A18" s="28"/>
       <c r="B18" s="5" t="s">
         <v>55</v>
       </c>
@@ -1222,11 +1221,11 @@
       <c r="F18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="10"/>
+      <c r="G18" s="28"/>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="29" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1244,13 +1243,13 @@
       <c r="F19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="27">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
+      <c r="A20" s="28"/>
       <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
@@ -1266,11 +1265,11 @@
       <c r="F20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="28"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="29" t="s">
         <v>46</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1288,12 +1287,12 @@
       <c r="F21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="27">
         <v>46336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
+      <c r="A22" s="28"/>
       <c r="B22" s="5" t="s">
         <v>55</v>
       </c>
@@ -1309,10 +1308,10 @@
       <c r="F22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="10"/>
+      <c r="G22" s="28"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="29" t="s">
         <v>48</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1330,12 +1329,12 @@
       <c r="F23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="27">
         <v>46218</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
+      <c r="A24" s="28"/>
       <c r="B24" s="5" t="s">
         <v>55</v>
       </c>
@@ -1351,10 +1350,10 @@
       <c r="F24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="10"/>
+      <c r="G24" s="28"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="29" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1372,12 +1371,12 @@
       <c r="F25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="27">
         <v>46188</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
+      <c r="A26" s="28"/>
       <c r="B26" s="5" t="s">
         <v>55</v>
       </c>
@@ -1393,10 +1392,10 @@
       <c r="F26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G26" s="10"/>
+      <c r="G26" s="28"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="29" t="s">
         <v>50</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1414,12 +1413,12 @@
       <c r="F27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="27">
         <v>46321</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
+      <c r="A28" s="28"/>
       <c r="B28" s="5" t="s">
         <v>55</v>
       </c>
@@ -1435,10 +1434,10 @@
       <c r="F28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G28" s="10"/>
+      <c r="G28" s="28"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="29" t="s">
         <v>51</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1456,12 +1455,12 @@
       <c r="F29" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="27">
         <v>46139</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="10"/>
+      <c r="A30" s="28"/>
       <c r="B30" s="5" t="s">
         <v>55</v>
       </c>
@@ -1477,10 +1476,10 @@
       <c r="F30" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="10"/>
+      <c r="G30" s="28"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="29" t="s">
         <v>53</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1498,12 +1497,12 @@
       <c r="F31" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="27">
         <v>46133</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="10"/>
+      <c r="A32" s="28"/>
       <c r="B32" s="5" t="s">
         <v>55</v>
       </c>
@@ -1519,10 +1518,10 @@
       <c r="F32" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="10"/>
+      <c r="G32" s="28"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="29" t="s">
         <v>62</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1540,12 +1539,12 @@
       <c r="F33" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="27">
         <v>46295</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="10"/>
+      <c r="A34" s="28"/>
       <c r="B34" s="5" t="s">
         <v>55</v>
       </c>
@@ -1561,10 +1560,10 @@
       <c r="F34" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G34" s="10"/>
+      <c r="G34" s="28"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="29" t="s">
         <v>63</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1582,12 +1581,12 @@
       <c r="F35" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="27">
         <v>45737</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="10"/>
+      <c r="A36" s="28"/>
       <c r="B36" s="5" t="s">
         <v>55</v>
       </c>
@@ -1603,10 +1602,10 @@
       <c r="F36" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G36" s="10"/>
+      <c r="G36" s="28"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="29" t="s">
         <v>64</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1624,12 +1623,12 @@
       <c r="F37" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="27">
         <v>45737</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
+      <c r="A38" s="28"/>
       <c r="B38" s="5" t="s">
         <v>55</v>
       </c>
@@ -1645,12 +1644,10 @@
       <c r="F38" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G38" s="10"/>
+      <c r="G38" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="G35:G36"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="G37:G38"/>
     <mergeCell ref="A23:A24"/>
@@ -1663,16 +1660,14 @@
     <mergeCell ref="G27:G28"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="G33:G34"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="G33:G34"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="G35:G36"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="G11:G12"/>
@@ -1685,6 +1680,10 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="G15:G16"/>
     <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A17:A18"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1718,50 +1717,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
     </row>
     <row r="4" spans="1:19" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1822,1012 +1821,1013 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="10">
         <v>0.9</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="11">
         <v>326786.36</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="11">
         <f>O5</f>
         <v>130000</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17">
+      <c r="F5" s="11"/>
+      <c r="G5" s="11">
         <f>D5*0.8</f>
         <v>261429.08799999999</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="12">
         <v>12</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="17">
+      <c r="I5" s="12"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="11">
         <v>5198</v>
       </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17">
-        <v>0</v>
-      </c>
-      <c r="N5" s="15" t="s">
+      <c r="L5" s="11"/>
+      <c r="M5" s="11">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="30">
         <v>130000</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="13">
         <f>'[1]Master Schedule'!C5</f>
         <v>46084</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="13">
         <v>46106</v>
       </c>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15" t="s">
+      <c r="R5" s="9"/>
+      <c r="S5" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="16">
-        <v>0</v>
-      </c>
-      <c r="D6" s="17">
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11">
         <v>409599.64</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="11">
         <f>O6*0.3</f>
         <v>41833.799999999996</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17">
+      <c r="F6" s="11"/>
+      <c r="G6" s="11">
         <f t="shared" ref="G6:G14" si="0">D6*0.4</f>
         <v>163839.85600000003</v>
       </c>
-      <c r="H6" s="18">
-        <v>0</v>
-      </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="17">
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="11">
         <v>6972.5</v>
       </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17">
-        <v>0</v>
-      </c>
-      <c r="N6" s="15" t="s">
+      <c r="L6" s="11"/>
+      <c r="M6" s="11">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="30">
         <v>139446</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="13">
         <f>'[1]Master Schedule'!C6</f>
         <v>46189</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="Q6" s="13">
         <v>46264</v>
       </c>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15" t="s">
+      <c r="R6" s="9"/>
+      <c r="S6" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="10">
         <v>0.9</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="11">
         <v>576317.9</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="11">
         <f t="shared" ref="E7:E18" si="1">O7</f>
         <v>280000</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="11">
         <v>603</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="11">
         <f>D7*0.9</f>
         <v>518686.11000000004</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="12">
         <v>20</v>
       </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="17">
+      <c r="I7" s="12"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="11">
         <v>12045</v>
       </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17">
-        <v>0</v>
-      </c>
-      <c r="N7" s="15" t="s">
+      <c r="L7" s="11"/>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="30">
         <v>280000</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="13">
         <f>'[1]Master Schedule'!C7</f>
         <v>46219</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="13">
         <v>46102</v>
       </c>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15" t="s">
+      <c r="R7" s="9"/>
+      <c r="S7" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="11">
         <v>322961.08</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="11">
         <f t="shared" si="1"/>
         <v>89000</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="11">
         <v>715</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="11">
         <f>D8*1</f>
         <v>322961.08</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="12">
         <v>7</v>
       </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="17">
+      <c r="I8" s="12"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="11">
         <v>24166</v>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17">
+      <c r="L8" s="11"/>
+      <c r="M8" s="11">
         <v>1444</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="30">
         <v>89000</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="13">
         <f>'[1]Master Schedule'!C8</f>
         <v>46244</v>
       </c>
-      <c r="Q8" s="19">
+      <c r="Q8" s="13">
         <v>46171</v>
       </c>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-    </row>
-    <row r="9" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="15" t="s">
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+    </row>
+    <row r="9" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="16">
-        <v>0</v>
-      </c>
-      <c r="D9" s="17">
+      <c r="C9" s="10">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11">
         <v>630619.19999999995</v>
       </c>
-      <c r="E9" s="17" t="str">
+      <c r="E9" s="11" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17">
+      <c r="F9" s="11"/>
+      <c r="G9" s="11">
         <f>D9*0.4</f>
         <v>252247.67999999999</v>
       </c>
-      <c r="H9" s="18">
-        <v>0</v>
-      </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17">
-        <v>0</v>
-      </c>
-      <c r="N9" s="15"/>
-      <c r="O9" s="17" t="s">
+      <c r="H9" s="12">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9"/>
+      <c r="O9" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="13">
         <v>46388</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="13">
         <v>46447</v>
       </c>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-    </row>
-    <row r="10" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="25" t="s">
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+    </row>
+    <row r="10" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="16">
-        <v>1</v>
-      </c>
-      <c r="D10" s="17">
+      <c r="C10" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="D10" s="11">
         <v>338450.2</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="11">
         <f>O10*0.8</f>
         <v>110400</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="11">
         <v>370</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="11">
         <f>D10*0.4</f>
         <v>135380.08000000002</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="12">
         <v>10</v>
       </c>
-      <c r="I10" s="18"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="17">
+      <c r="I10" s="12"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="11">
         <v>5783</v>
       </c>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17">
+      <c r="L10" s="11"/>
+      <c r="M10" s="11">
         <v>787</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="N10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="30">
         <v>138000</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="13">
         <f>'[1]Master Schedule'!C10</f>
         <v>46168</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="Q10" s="13">
         <v>46199</v>
       </c>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15" t="s">
+      <c r="R10" s="9"/>
+      <c r="S10" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="25" t="s">
+    <row r="11" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="10">
         <v>0.7</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="11">
         <v>1156111.18</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="11">
         <f>O11*0.3</f>
         <v>84000</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="11">
         <v>840</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="11">
         <f t="shared" si="0"/>
         <v>462444.47200000001</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="12">
         <v>10</v>
       </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="17">
+      <c r="I11" s="12"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="11">
         <v>26094</v>
       </c>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17">
+      <c r="L11" s="11"/>
+      <c r="M11" s="11">
         <v>46175</v>
       </c>
-      <c r="N11" s="25" t="s">
+      <c r="N11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="30">
         <v>280000</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="13">
         <f>'[1]Master Schedule'!C11</f>
         <v>46184</v>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="13">
         <v>46305</v>
       </c>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-    </row>
-    <row r="12" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="25" t="s">
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+    </row>
+    <row r="12" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="16">
-        <v>0</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="C12" s="10">
+        <v>0</v>
+      </c>
+      <c r="D12" s="11">
         <v>594114</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="11">
         <f>O12*0</f>
         <v>0</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17">
+      <c r="F12" s="11"/>
+      <c r="G12" s="11">
         <f t="shared" si="0"/>
         <v>237645.6</v>
       </c>
-      <c r="H12" s="18">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="17">
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="11">
         <v>20261</v>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17">
+      <c r="L12" s="11"/>
+      <c r="M12" s="11">
         <v>20018</v>
       </c>
-      <c r="N12" s="25" t="s">
+      <c r="N12" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="O12" s="17">
+      <c r="O12" s="30">
         <v>233247.9</v>
       </c>
-      <c r="P12" s="19">
+      <c r="P12" s="13">
         <f>'[1]Master Schedule'!C12</f>
         <v>46200</v>
       </c>
-      <c r="Q12" s="19">
+      <c r="Q12" s="13">
         <v>46336</v>
       </c>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15" t="s">
+      <c r="R12" s="9"/>
+      <c r="S12" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="25" t="s">
+    <row r="13" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="16">
-        <v>0</v>
-      </c>
-      <c r="D13" s="17">
+      <c r="C13" s="10">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11">
         <v>327102.8</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="11">
         <f>O13*0.3</f>
         <v>36000</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17">
+      <c r="F13" s="11"/>
+      <c r="G13" s="11">
         <f t="shared" si="0"/>
         <v>130841.12</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="14">
         <v>3</v>
       </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="17">
+      <c r="J13" s="9"/>
+      <c r="K13" s="11">
         <v>14327</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="19">
         <v>4164</v>
       </c>
-      <c r="N13" s="15" t="s">
+      <c r="N13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O13" s="25">
+      <c r="O13" s="31">
         <v>120000</v>
       </c>
-      <c r="P13" s="19">
+      <c r="P13" s="13">
         <f>'[1]Master Schedule'!C13</f>
         <v>46392</v>
       </c>
-      <c r="Q13" s="26">
+      <c r="Q13" s="20">
         <v>46336</v>
       </c>
-      <c r="S13" s="15" t="s">
+      <c r="S13" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="25" t="s">
+    <row r="14" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="10">
         <v>0.5</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="11">
         <v>1707089</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="11">
         <f>O14*0.3</f>
         <v>197003.709</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="11">
         <v>215</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="11">
         <f t="shared" si="0"/>
         <v>682835.60000000009</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="14">
         <v>10</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="17">
+      <c r="J14" s="9"/>
+      <c r="K14" s="11">
         <v>54190</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="19">
         <v>20695.969999999972</v>
       </c>
-      <c r="N14" s="25" t="s">
+      <c r="N14" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="O14" s="25">
+      <c r="O14" s="31">
         <v>656679.03</v>
       </c>
-      <c r="P14" s="19">
+      <c r="P14" s="13">
         <f>'[1]Master Schedule'!C14</f>
         <v>46042</v>
       </c>
-      <c r="Q14" s="26">
+      <c r="Q14" s="20">
         <v>46218</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="25" t="s">
+    <row r="15" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="10">
         <v>1</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="11">
         <v>80000</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="11">
         <f>O15</f>
         <v>40000</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="11">
         <v>489</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="11">
         <f>D15*1</f>
         <v>80000</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="14">
         <v>4</v>
       </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="M15" s="25">
-        <v>0</v>
-      </c>
-      <c r="N15" s="25" t="s">
+      <c r="J15" s="9"/>
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="19">
+        <v>0</v>
+      </c>
+      <c r="N15" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="O15" s="25">
+      <c r="O15" s="31">
         <v>40000</v>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="13">
         <f>'[1]Master Schedule'!C15</f>
         <v>46168</v>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="20">
         <v>46188</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="25" t="s">
+    <row r="16" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="16">
-        <v>0</v>
-      </c>
-      <c r="D16" s="17">
+      <c r="C16" s="10">
+        <v>0</v>
+      </c>
+      <c r="D16" s="11">
         <v>1199960.02</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="11">
         <f>O16*0</f>
         <v>0</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17">
+      <c r="F16" s="11"/>
+      <c r="G16" s="11">
         <f>D16*0.4</f>
         <v>479984.00800000003</v>
       </c>
-      <c r="H16" s="20">
-        <v>0</v>
-      </c>
-      <c r="K16" s="17">
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="K16" s="11">
         <v>27535</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="19">
         <v>34414</v>
       </c>
-      <c r="N16" s="25" t="s">
+      <c r="N16" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="25">
+      <c r="O16" s="31">
         <v>430000</v>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="13">
         <f>'[1]Master Schedule'!C16</f>
         <v>46198</v>
       </c>
-      <c r="Q16" s="26">
+      <c r="Q16" s="20">
         <v>46321</v>
       </c>
-      <c r="S16" s="15" t="s">
+      <c r="S16" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="25" t="s">
+    <row r="17" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="10">
         <v>1</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="11">
         <v>600000</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="11">
         <f>O17</f>
         <v>234861</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="11">
         <v>735</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="11">
         <f>D17*1</f>
         <v>600000</v>
       </c>
-      <c r="H17" s="21">
+      <c r="H17" s="15">
         <v>10</v>
       </c>
-      <c r="J17" s="15"/>
-      <c r="K17" s="17">
+      <c r="J17" s="9"/>
+      <c r="K17" s="11">
         <v>10000</v>
       </c>
-      <c r="M17" s="25">
-        <v>0</v>
-      </c>
-      <c r="N17" s="25" t="s">
+      <c r="M17" s="19">
+        <v>0</v>
+      </c>
+      <c r="N17" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="31">
         <v>234861</v>
       </c>
-      <c r="P17" s="19">
+      <c r="P17" s="13">
         <f>'[1]Master Schedule'!C17</f>
         <v>46188</v>
       </c>
-      <c r="Q17" s="26">
+      <c r="Q17" s="20">
         <v>46139</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="25" t="s">
+    <row r="18" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="10">
         <v>1</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="11">
         <v>317648</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="11">
         <f t="shared" si="1"/>
         <v>119980</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17">
+      <c r="F18" s="11"/>
+      <c r="G18" s="11">
         <f>D18*1</f>
         <v>317648</v>
       </c>
-      <c r="H18" s="21">
+      <c r="H18" s="15">
         <v>10</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="17">
+      <c r="J18" s="9"/>
+      <c r="K18" s="11">
         <v>8760</v>
       </c>
-      <c r="M18" s="25">
-        <v>0</v>
-      </c>
-      <c r="N18" s="15" t="s">
+      <c r="M18" s="19">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O18" s="31">
         <v>119980</v>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="13">
         <f>'[1]Master Schedule'!C18</f>
         <v>46200</v>
       </c>
-      <c r="Q18" s="26">
+      <c r="Q18" s="20">
         <v>46133</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="25" t="s">
+    <row r="19" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="16">
-        <v>0</v>
-      </c>
-      <c r="D19" s="17">
+      <c r="C19" s="10">
+        <v>0</v>
+      </c>
+      <c r="D19" s="11">
         <v>832813</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="11">
         <f t="shared" ref="E19" si="2">O19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="11">
         <v>630</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="11">
         <f>455555</f>
         <v>455555</v>
       </c>
-      <c r="H19" s="21">
-        <v>0</v>
-      </c>
-      <c r="J19" s="15"/>
-      <c r="K19" s="17">
+      <c r="H19" s="15">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="11">
         <v>35070</v>
       </c>
-      <c r="M19" s="25">
-        <v>0</v>
-      </c>
-      <c r="N19" s="15" t="s">
+      <c r="M19" s="19">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="P19" s="19">
+      <c r="O19" s="31"/>
+      <c r="P19" s="13">
         <f>'Master Schedule'!C33</f>
         <v>46091</v>
       </c>
-      <c r="Q19" s="26">
+      <c r="Q19" s="20">
         <v>46295</v>
       </c>
-      <c r="S19" s="15" t="s">
+      <c r="S19" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="25" t="s">
+    <row r="20" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="10">
         <v>0.9</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="18">
         <v>341236.34</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="22">
         <f>O20*0.3</f>
         <v>71744.399999999994</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="17">
         <v>255</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="23">
         <f>D20*0.9</f>
         <v>307112.70600000001</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="19">
         <v>3</v>
       </c>
-      <c r="K20" s="25">
-        <v>0</v>
-      </c>
-      <c r="M20" s="25">
-        <v>0</v>
-      </c>
-      <c r="N20" s="25" t="s">
+      <c r="K20" s="19">
+        <v>0</v>
+      </c>
+      <c r="M20" s="19">
+        <v>0</v>
+      </c>
+      <c r="N20" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="O20" s="25">
+      <c r="O20" s="31">
         <v>239148</v>
       </c>
-      <c r="P20" s="19">
+      <c r="P20" s="13">
         <v>45717</v>
       </c>
-      <c r="Q20" s="19">
+      <c r="Q20" s="13">
         <v>45737</v>
       </c>
-      <c r="S20" s="15" t="s">
+      <c r="S20" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="25" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="30" t="s">
+    <row r="21" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="10">
         <v>0.9</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="17">
         <v>666700</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="22">
         <f>O21*0.65</f>
         <v>145747.55000000002</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="19">
         <v>3</v>
       </c>
-      <c r="K21" s="25">
-        <v>0</v>
-      </c>
-      <c r="M21" s="25">
-        <v>0</v>
-      </c>
-      <c r="N21" s="25" t="s">
+      <c r="K21" s="19">
+        <v>0</v>
+      </c>
+      <c r="M21" s="19">
+        <v>0</v>
+      </c>
+      <c r="N21" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="O21" s="25">
+      <c r="O21" s="31">
         <v>224227</v>
       </c>
-      <c r="P21" s="19">
+      <c r="P21" s="13">
         <v>45717</v>
       </c>
-      <c r="Q21" s="19">
+      <c r="Q21" s="13">
         <v>45737</v>
       </c>
-      <c r="S21" s="15" t="s">
+      <c r="S21" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:19" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="33" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="34" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="35" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="36" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="37" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="38" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="39" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="40" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="41" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="42" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="43" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="44" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="45" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="46" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="47" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="48" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="49" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="50" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="51" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="52" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="53" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="54" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="55" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="56" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="57" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="58" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="59" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="60" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="61" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="62" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="63" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="64" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="65" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="66" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="67" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="68" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="69" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="70" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="71" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="72" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="73" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="74" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="75" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="76" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="77" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="78" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="79" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="80" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="81" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="82" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="83" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="84" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="85" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="86" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="87" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="88" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="89" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="90" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="91" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="92" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="93" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="94" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="95" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="96" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="97" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="98" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="99" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="100" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="101" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="102" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="103" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="104" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="105" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="106" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="107" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="108" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="109" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="110" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="111" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="112" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="113" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="114" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="115" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="116" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="117" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="118" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="119" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="120" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="121" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="122" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="123" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="124" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="125" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="126" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="127" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="128" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="129" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="130" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="131" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="132" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="133" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="134" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="135" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="136" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="137" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="138" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="139" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="140" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="141" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="142" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="143" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="144" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="145" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="146" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="147" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="148" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="149" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="150" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="151" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="152" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="153" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="154" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="155" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="156" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="157" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="158" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="159" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="160" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="161" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="162" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="163" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="164" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="165" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="166" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="167" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="168" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="169" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="170" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="171" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="172" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="173" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="174" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="175" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="176" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="177" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="178" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="179" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="180" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="181" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="182" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="183" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="184" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="185" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="186" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="187" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="188" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="33" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="34" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="35" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="36" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="37" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="38" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="39" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="40" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="41" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="42" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="43" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="44" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="45" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="46" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="47" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="48" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="49" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="50" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="51" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="52" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="53" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="54" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="55" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="56" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="57" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="58" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="59" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="60" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="61" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="62" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="63" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="64" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="65" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="66" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="67" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="68" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="69" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="70" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="71" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="72" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="73" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="74" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="75" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="76" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="77" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="78" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="79" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="80" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="81" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="82" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="83" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="84" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="85" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="86" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="87" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="88" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="89" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="90" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="91" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="92" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="93" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="94" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="95" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="96" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="97" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="98" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="99" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="100" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="101" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="102" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="103" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="104" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="105" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="106" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="107" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="108" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="109" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="110" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="111" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="112" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="113" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="114" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="115" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="116" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="117" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="118" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="119" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="120" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="121" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="122" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="123" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="124" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="125" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="126" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="127" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="128" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="129" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="130" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="131" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="132" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="133" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="134" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="135" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="136" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="137" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="138" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="139" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="140" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="141" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="142" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="143" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="144" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="145" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="146" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="147" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="148" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="149" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="150" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="151" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="152" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="153" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="154" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="155" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="156" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="157" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="158" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="159" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="160" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="161" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="162" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="163" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="164" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="165" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="166" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="167" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="168" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="169" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="170" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="171" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="172" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="173" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="174" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="175" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="176" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="177" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="178" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="179" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="180" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="181" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="182" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="183" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="184" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="185" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="186" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="187" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="188" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
@@ -2853,18 +2853,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3067,19 +3067,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -3332,7 +3319,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3341,18 +3328,20 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3371,10 +3360,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{41D1AEA8-9C20-47A1-A739-0B1E1E53F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B9C9BED-86B7-48AA-A8DF-73E02C0254B0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,11 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191028" calcOnSave="0"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="66">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -70,13 +73,73 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>Sukhumvit 77 Prawet Residence</t>
+  </si>
+  <si>
+    <t>Frist Fix</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Second Fix</t>
+  </si>
+  <si>
+    <t>หมู่บ้านมัณฑนา</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>สำนักงานบริษัท เอส.บี.-ซีร่า จำกัดพระราม2</t>
+  </si>
+  <si>
+    <t>Ventier courtyard ชั้น 3</t>
+  </si>
+  <si>
+    <t>บ้านคุณยู้เขาใหญ่</t>
+  </si>
+  <si>
+    <t>บ้านคุณอิสระ</t>
+  </si>
+  <si>
+    <t>S’rin House</t>
+  </si>
+  <si>
     <t>Construction</t>
   </si>
   <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>On Hold</t>
+    <t>บ้านคุณปุกกี้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">บ้านบางบอน5ซอย7 </t>
+  </si>
+  <si>
+    <t>PhanasonSamutprakhan Residence</t>
+  </si>
+  <si>
+    <t>P'Gummy @Sildrom Residence FL.21</t>
+  </si>
+  <si>
+    <t>HUAY KWANG RESIDENCE</t>
+  </si>
+  <si>
+    <t>Granpix</t>
+  </si>
+  <si>
+    <t>บ้านคุณอู BUGAAN พัฒนาการ</t>
+  </si>
+  <si>
+    <t>บ้านคุณเต้ย</t>
+  </si>
+  <si>
+    <t>Khun Sarut's House</t>
+  </si>
+  <si>
+    <t>25-17_Ekamai 28 (K'Phong)</t>
   </si>
   <si>
     <t>SUMMARY REPORT</t>
@@ -127,6 +190,33 @@
     <t>Project Manager</t>
   </si>
   <si>
+    <t>บริษัทเอ.เอ็น.เอ็นจิเนียริ่งจํากัด</t>
+  </si>
+  <si>
+    <t xml:space="preserve">รอลูกค้าคอนเฟิมวันส่งมอบงาน </t>
+  </si>
+  <si>
+    <t>รองานโครงสร้าง</t>
+  </si>
+  <si>
+    <t>ส่งมอบงานวันที่ 15/07/2026</t>
+  </si>
+  <si>
+    <t>นายคธาชัย จันทร์ศรี</t>
+  </si>
+  <si>
+    <t>บริษัท เคบีเอส ซีสเต็ม จํากัด</t>
+  </si>
+  <si>
+    <t>บริษัท สามที เอ็นจิเนียริ่ง  จำกัด</t>
+  </si>
+  <si>
+    <t>บริษัท อาร์ทอพ แอร์ ซัพพลาย จำกัด</t>
+  </si>
+  <si>
+    <t>โครงการล่าช้า</t>
+  </si>
+  <si>
     <t>SITE VISIT LOG</t>
   </si>
   <si>
@@ -142,72 +232,6 @@
     <t>Site Visit Hours</t>
   </si>
   <si>
-    <t>Sukhumvit 77 Prawet Residence</t>
-  </si>
-  <si>
-    <t>บริษัท เคบีเอส ซีสเต็ม จํากัด</t>
-  </si>
-  <si>
-    <t>หมู่บ้านมัณฑนา</t>
-  </si>
-  <si>
-    <t>บริษัทเอ.เอ็น.เอ็นจิเนียริ่งจํากัด</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>สำนักงานบริษัท เอส.บี.-ซีร่า จำกัดพระราม2</t>
-  </si>
-  <si>
-    <t>Ventier courtyard ชั้น 3</t>
-  </si>
-  <si>
-    <t>บ้านคุณยู้เขาใหญ่</t>
-  </si>
-  <si>
-    <t>บ้านคุณอิสระ</t>
-  </si>
-  <si>
-    <t>นายคธาชัย จันทร์ศรี</t>
-  </si>
-  <si>
-    <t>S’rin House</t>
-  </si>
-  <si>
-    <t>บ้านคุณปุกกี้</t>
-  </si>
-  <si>
-    <t xml:space="preserve">บ้านบางบอน5ซอย7 </t>
-  </si>
-  <si>
-    <t>บริษัท สามที เอ็นจิเนียริ่ง  จำกัด</t>
-  </si>
-  <si>
-    <t>PhanasonSamutprakhan Residence</t>
-  </si>
-  <si>
-    <t>P'Gummy @Sildrom Residence FL.21</t>
-  </si>
-  <si>
-    <t>HUAY KWANG RESIDENCE</t>
-  </si>
-  <si>
-    <t>Granpix</t>
-  </si>
-  <si>
-    <t>บริษัท อาร์ทอพ แอร์ ซัพพลาย จำกัด</t>
-  </si>
-  <si>
-    <t>บ้านคุณอู BUGAAN พัฒนาการ</t>
-  </si>
-  <si>
-    <t>Frist Fix</t>
-  </si>
-  <si>
-    <t>Second Fix</t>
-  </si>
-  <si>
     <t>ฤทธิพร บุตรนิตย์</t>
   </si>
   <si>
@@ -215,30 +239,6 @@
   </si>
   <si>
     <t>วริษฐ์ ยุวโชติพันธุ์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">รอลูกค้าคอนเฟิมวันส่งมอบงาน </t>
-  </si>
-  <si>
-    <t>รองานโครงสร้าง</t>
-  </si>
-  <si>
-    <t>ส่งมอบงานวันที่ 15/07/2026</t>
-  </si>
-  <si>
-    <t>บ้านคุณเต้ย</t>
-  </si>
-  <si>
-    <t>Khun Sarut's House</t>
-  </si>
-  <si>
-    <t>25-17_Ekamai 28 (K'Phong)</t>
-  </si>
-  <si>
-    <t>โครงการล่าช้า</t>
-  </si>
-  <si>
-    <t>บริษัทอีโค่คูลไคลเมท เทคโนโลยีจำกัด</t>
   </si>
 </sst>
 </file>
@@ -451,9 +451,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -461,10 +465,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
@@ -857,7 +857,7 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
@@ -870,25 +870,25 @@
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -917,11 +917,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
-        <v>34</v>
+      <c r="A5" s="31" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6">
         <v>46084</v>
@@ -933,17 +933,17 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="27">
+        <v>12</v>
+      </c>
+      <c r="G5" s="29">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
+      <c r="A6" s="30"/>
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6">
         <v>46189</v>
@@ -955,17 +955,17 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="30"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C7" s="6">
         <v>46219</v>
@@ -977,17 +977,17 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>38</v>
+        <v>15</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>16</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
+      <c r="A8" s="30"/>
       <c r="B8" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6">
         <v>46244</v>
@@ -999,17 +999,17 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="28"/>
+        <v>15</v>
+      </c>
+      <c r="G8" s="30"/>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="29" t="s">
-        <v>39</v>
+      <c r="A9" s="31" t="s">
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6">
         <v>46082</v>
@@ -1021,17 +1021,17 @@
         <v>1</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="27">
+        <v>12</v>
+      </c>
+      <c r="G9" s="29">
         <v>46204</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
+      <c r="A10" s="30"/>
       <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6">
         <v>46168</v>
@@ -1043,17 +1043,17 @@
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C11" s="6">
         <v>46184</v>
@@ -1065,17 +1065,17 @@
         <v>1</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="27">
+        <v>12</v>
+      </c>
+      <c r="G11" s="29">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
+      <c r="A12" s="30"/>
       <c r="B12" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C12" s="6">
         <v>46200</v>
@@ -1087,17 +1087,17 @@
         <v>1</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C13" s="6">
         <v>46392</v>
@@ -1109,17 +1109,17 @@
         <v>0</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>38</v>
+        <v>15</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>16</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
+      <c r="A14" s="30"/>
       <c r="B14" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C14" s="6">
         <v>46042</v>
@@ -1131,17 +1131,17 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="28"/>
+        <v>15</v>
+      </c>
+      <c r="G14" s="30"/>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="29" t="s">
-        <v>42</v>
+      <c r="A15" s="31" t="s">
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C15" s="6">
         <v>46168</v>
@@ -1153,17 +1153,17 @@
         <v>1</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="27">
+        <v>12</v>
+      </c>
+      <c r="G15" s="29">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C16" s="6">
         <v>46198</v>
@@ -1175,17 +1175,17 @@
         <v>1</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="30"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C17" s="6">
         <v>46188</v>
@@ -1197,17 +1197,17 @@
         <v>1</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="27">
+        <v>12</v>
+      </c>
+      <c r="G17" s="29">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C18" s="6">
         <v>46296</v>
@@ -1219,17 +1219,17 @@
         <v>0.4</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="28"/>
+        <v>22</v>
+      </c>
+      <c r="G18" s="30"/>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="29" t="s">
-        <v>45</v>
+      <c r="A19" s="31" t="s">
+        <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C19" s="6">
         <v>46275</v>
@@ -1241,17 +1241,17 @@
         <v>0</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="27">
+        <v>15</v>
+      </c>
+      <c r="G19" s="29">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C20" s="6">
         <v>46327</v>
@@ -1263,17 +1263,17 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="28"/>
+        <v>15</v>
+      </c>
+      <c r="G20" s="30"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
-        <v>46</v>
+      <c r="A21" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C21" s="6">
         <v>46240</v>
@@ -1285,16 +1285,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="27">
+        <v>15</v>
+      </c>
+      <c r="G21" s="29">
         <v>46336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
+      <c r="A22" s="30"/>
       <c r="B22" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C22" s="6">
         <v>46327</v>
@@ -1306,16 +1306,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="28"/>
+        <v>15</v>
+      </c>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
-        <v>48</v>
+      <c r="A23" s="31" t="s">
+        <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C23" s="6">
         <v>46190</v>
@@ -1327,16 +1327,16 @@
         <v>0.5</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="27">
+        <v>22</v>
+      </c>
+      <c r="G23" s="29">
         <v>46218</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
+      <c r="A24" s="30"/>
       <c r="B24" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C24" s="6">
         <v>46209</v>
@@ -1348,16 +1348,16 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="28"/>
+        <v>22</v>
+      </c>
+      <c r="G24" s="30"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="29" t="s">
-        <v>49</v>
+      <c r="A25" s="31" t="s">
+        <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
         <v>46185</v>
@@ -1369,16 +1369,16 @@
         <v>1</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="27">
+        <v>12</v>
+      </c>
+      <c r="G25" s="29">
         <v>46188</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
+      <c r="A26" s="30"/>
       <c r="B26" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C26" s="6">
         <v>46185</v>
@@ -1390,16 +1390,16 @@
         <v>1</v>
       </c>
       <c r="F26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="30"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="G26" s="28"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C27" s="6">
         <v>46234</v>
@@ -1411,16 +1411,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="27">
+        <v>22</v>
+      </c>
+      <c r="G27" s="29">
         <v>46321</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
+      <c r="A28" s="30"/>
       <c r="B28" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C28" s="6">
         <v>46314</v>
@@ -1432,16 +1432,16 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="28"/>
+        <v>22</v>
+      </c>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="29" t="s">
-        <v>51</v>
+      <c r="A29" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C29" s="6">
         <v>46091</v>
@@ -1453,16 +1453,16 @@
         <v>1</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="27">
+        <v>12</v>
+      </c>
+      <c r="G29" s="29">
         <v>46139</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
+      <c r="A30" s="30"/>
       <c r="B30" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C30" s="6">
         <v>46120</v>
@@ -1474,16 +1474,16 @@
         <v>1</v>
       </c>
       <c r="F30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="30"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="G30" s="28"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C31" s="6">
         <v>46091</v>
@@ -1495,16 +1495,16 @@
         <v>1</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="27">
+        <v>12</v>
+      </c>
+      <c r="G31" s="29">
         <v>46133</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C32" s="6">
         <v>46091</v>
@@ -1516,16 +1516,16 @@
         <v>1</v>
       </c>
       <c r="F32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="30"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="G32" s="28"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C33" s="6">
         <v>46091</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="27">
+        <v>22</v>
+      </c>
+      <c r="G33" s="29">
         <v>46295</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="28"/>
+      <c r="A34" s="30"/>
       <c r="B34" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C34" s="6">
         <v>46091</v>
@@ -1558,16 +1558,16 @@
         <v>0</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="28"/>
+        <v>22</v>
+      </c>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="29" t="s">
-        <v>63</v>
+      <c r="A35" s="31" t="s">
+        <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C35" s="6">
         <v>45723</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="27">
+        <v>22</v>
+      </c>
+      <c r="G35" s="29">
         <v>45737</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
+      <c r="A36" s="30"/>
       <c r="B36" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C36" s="6">
         <v>45729</v>
@@ -1600,16 +1600,16 @@
         <v>0.9</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="28"/>
+        <v>22</v>
+      </c>
+      <c r="G36" s="30"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="29" t="s">
-        <v>64</v>
+      <c r="A37" s="31" t="s">
+        <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C37" s="6">
         <v>45723</v>
@@ -1621,16 +1621,16 @@
         <v>1</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="27">
+        <v>22</v>
+      </c>
+      <c r="G37" s="29">
         <v>45737</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
+      <c r="A38" s="30"/>
       <c r="B38" s="5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C38" s="6">
         <v>45729</v>
@@ -1642,9 +1642,9 @@
         <v>0.9</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="28"/>
+        <v>22</v>
+      </c>
+      <c r="G38" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -1699,7 +1699,7 @@
   <dimension ref="A1:S188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="15" customWidth="1"/>
@@ -1718,49 +1718,49 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
+        <v>33</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
+      <c r="A2" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
     </row>
     <row r="4" spans="1:19" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1770,43 +1770,43 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>4</v>
@@ -1815,7 +1815,7 @@
         <v>5</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>9</v>
@@ -1823,10 +1823,10 @@
     </row>
     <row r="5" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="9" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C5" s="10">
         <v>0.9</v>
@@ -1856,9 +1856,9 @@
         <v>0</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="30">
+        <v>49</v>
+      </c>
+      <c r="O5" s="24">
         <v>130000</v>
       </c>
       <c r="P5" s="13">
@@ -1870,15 +1870,15 @@
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="9" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -1908,9 +1908,9 @@
         <v>0</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O6" s="30">
+        <v>49</v>
+      </c>
+      <c r="O6" s="24">
         <v>139446</v>
       </c>
       <c r="P6" s="13">
@@ -1922,15 +1922,15 @@
       </c>
       <c r="R6" s="9"/>
       <c r="S6" s="9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="9" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C7" s="10">
         <v>0.9</v>
@@ -1962,9 +1962,9 @@
         <v>0</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O7" s="30">
+        <v>49</v>
+      </c>
+      <c r="O7" s="24">
         <v>280000</v>
       </c>
       <c r="P7" s="13">
@@ -1976,15 +1976,15 @@
       </c>
       <c r="R7" s="9"/>
       <c r="S7" s="9" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="9" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
@@ -2016,9 +2016,9 @@
         <v>1444</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O8" s="30">
+        <v>53</v>
+      </c>
+      <c r="O8" s="24">
         <v>89000</v>
       </c>
       <c r="P8" s="13">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="9" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="9" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
@@ -2064,8 +2064,8 @@
         <v>0</v>
       </c>
       <c r="N9" s="9"/>
-      <c r="O9" s="30" t="s">
-        <v>38</v>
+      <c r="O9" s="24" t="s">
+        <v>16</v>
       </c>
       <c r="P9" s="13">
         <v>46388</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="10" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="19" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C10" s="10">
         <v>0.9</v>
@@ -2113,9 +2113,9 @@
         <v>787</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O10" s="30">
+        <v>53</v>
+      </c>
+      <c r="O10" s="24">
         <v>138000</v>
       </c>
       <c r="P10" s="13">
@@ -2127,15 +2127,15 @@
       </c>
       <c r="R10" s="9"/>
       <c r="S10" s="9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="19" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C11" s="10">
         <v>0.7</v>
@@ -2167,9 +2167,9 @@
         <v>46175</v>
       </c>
       <c r="N11" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="O11" s="30">
+        <v>54</v>
+      </c>
+      <c r="O11" s="24">
         <v>280000</v>
       </c>
       <c r="P11" s="13">
@@ -2184,10 +2184,10 @@
     </row>
     <row r="12" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="19" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C12" s="10">
         <v>0</v>
@@ -2217,9 +2217,9 @@
         <v>20018</v>
       </c>
       <c r="N12" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="O12" s="30">
+        <v>55</v>
+      </c>
+      <c r="O12" s="24">
         <v>233247.9</v>
       </c>
       <c r="P12" s="13">
@@ -2231,15 +2231,15 @@
       </c>
       <c r="R12" s="9"/>
       <c r="S12" s="9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="19" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13" s="10">
         <v>0</v>
@@ -2267,9 +2267,9 @@
         <v>4164</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" s="31">
+        <v>49</v>
+      </c>
+      <c r="O13" s="25">
         <v>120000</v>
       </c>
       <c r="P13" s="13">
@@ -2280,15 +2280,15 @@
         <v>46336</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="19" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C14" s="10">
         <v>0.5</v>
@@ -2318,9 +2318,9 @@
         <v>20695.969999999972</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="O14" s="31">
+        <v>55</v>
+      </c>
+      <c r="O14" s="25">
         <v>656679.03</v>
       </c>
       <c r="P14" s="13">
@@ -2333,10 +2333,10 @@
     </row>
     <row r="15" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="19" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="10">
         <v>1</v>
@@ -2366,9 +2366,9 @@
         <v>0</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="O15" s="31">
+        <v>54</v>
+      </c>
+      <c r="O15" s="25">
         <v>40000</v>
       </c>
       <c r="P15" s="13">
@@ -2381,10 +2381,10 @@
     </row>
     <row r="16" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="19" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C16" s="10">
         <v>0</v>
@@ -2411,9 +2411,9 @@
         <v>34414</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="O16" s="31">
+        <v>56</v>
+      </c>
+      <c r="O16" s="25">
         <v>430000</v>
       </c>
       <c r="P16" s="13">
@@ -2424,15 +2424,15 @@
         <v>46321</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="19" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="10">
         <v>1</v>
@@ -2462,9 +2462,9 @@
         <v>0</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="O17" s="31">
+        <v>54</v>
+      </c>
+      <c r="O17" s="25">
         <v>234861</v>
       </c>
       <c r="P17" s="13">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="18" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="19" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="10">
         <v>1</v>
@@ -2508,9 +2508,9 @@
         <v>0</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O18" s="31">
+        <v>53</v>
+      </c>
+      <c r="O18" s="25">
         <v>119980</v>
       </c>
       <c r="P18" s="13">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="19" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -2556,9 +2556,9 @@
         <v>0</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O19" s="31"/>
+        <v>53</v>
+      </c>
+      <c r="O19" s="25"/>
       <c r="P19" s="13">
         <f>'Master Schedule'!C33</f>
         <v>46091</v>
@@ -2567,15 +2567,15 @@
         <v>46295</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="19" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C20" s="10">
         <v>0.9</v>
@@ -2603,10 +2603,7 @@
       <c r="M20" s="19">
         <v>0</v>
       </c>
-      <c r="N20" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="O20" s="31">
+      <c r="O20" s="25">
         <v>239148</v>
       </c>
       <c r="P20" s="13">
@@ -2616,15 +2613,15 @@
         <v>45737</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="19" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C21" s="10">
         <v>0.9</v>
@@ -2636,6 +2633,10 @@
         <f>O21*0.65</f>
         <v>145747.55000000002</v>
       </c>
+      <c r="G21" s="19">
+        <f>D21*0.75</f>
+        <v>500025</v>
+      </c>
       <c r="H21" s="19">
         <v>3</v>
       </c>
@@ -2645,10 +2646,7 @@
       <c r="M21" s="19">
         <v>0</v>
       </c>
-      <c r="N21" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="O21" s="31">
+      <c r="O21" s="25">
         <v>224227</v>
       </c>
       <c r="P21" s="13">
@@ -2658,7 +2656,7 @@
         <v>45737</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
@@ -2854,27 +2852,27 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+        <v>58</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="A2" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2892,7 +2890,7 @@
         <v>46185</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C7" s="8">
         <v>4</v>
@@ -2903,7 +2901,7 @@
         <v>46189</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C8" s="8">
         <v>4</v>
@@ -2914,7 +2912,7 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C9" s="8">
         <v>3</v>
@@ -2925,7 +2923,7 @@
         <v>46185</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C10" s="8">
         <v>2.5</v>
@@ -2936,7 +2934,7 @@
         <v>46190</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C11" s="8">
         <v>3</v>
@@ -2947,7 +2945,7 @@
         <v>46190</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C12" s="8">
         <v>3</v>
@@ -2958,7 +2956,7 @@
         <v>46192</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C13" s="8">
         <v>3</v>
@@ -2969,7 +2967,7 @@
         <v>46197</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C14" s="8">
         <v>3</v>
@@ -2980,7 +2978,7 @@
         <v>46198</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C15" s="4">
         <v>6</v>
@@ -2991,21 +2989,33 @@
         <v>46202</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C16" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="4"/>
+      <c r="A17" s="3">
+        <v>46205</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="4"/>
+      <c r="A18" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
@@ -3067,6 +3077,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -3319,7 +3342,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3328,20 +3351,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3360,21 +3381,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BBA398E-E399-4599-8FB3-812CFAEB6628}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191028" calcOnSave="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="69">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t>วริษฐ์ ยุวโชติพันธุ์</t>
+  </si>
+  <si>
+    <t>รอลูกค้าคอนเฟิมวันส่งงาน Frist fix</t>
+  </si>
+  <si>
+    <t>รอลูกค้าคอนเฟิมวันส่งงาน Frist fix 07/10/2026</t>
+  </si>
+  <si>
+    <t>ส่งมอบงานวันเสาร์ ที่ 07/04/2026</t>
   </si>
 </sst>
 </file>
@@ -250,7 +259,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,22 +272,26 @@
       <sz val="14"/>
       <color rgb="FF16243A"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF5B6B7C"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -316,6 +329,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cordia New"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -388,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -457,13 +476,16 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -879,7 +901,7 @@
       <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="27"/>
@@ -917,7 +939,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="30" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -935,13 +957,13 @@
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="28">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="30"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
@@ -957,11 +979,11 @@
       <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="30" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -979,13 +1001,13 @@
       <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="30"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
@@ -1001,11 +1023,11 @@
       <c r="F8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="29"/>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="30" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1023,13 +1045,13 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>46204</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="30"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
@@ -1045,11 +1067,11 @@
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="29"/>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1067,13 +1089,13 @@
       <c r="F11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="28">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="30"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1089,11 +1111,11 @@
       <c r="F12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="30" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1111,13 +1133,13 @@
       <c r="F13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="28" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1133,11 +1155,11 @@
       <c r="F14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="30"/>
+      <c r="G14" s="29"/>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="30" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1155,13 +1177,13 @@
       <c r="F15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="30"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
@@ -1177,11 +1199,11 @@
       <c r="F16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="30"/>
+      <c r="G16" s="29"/>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="30" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1199,13 +1221,13 @@
       <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="28">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="30"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
@@ -1221,11 +1243,11 @@
       <c r="F18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="29"/>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="30" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1243,13 +1265,13 @@
       <c r="F19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="28">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="30"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="5" t="s">
         <v>13</v>
       </c>
@@ -1265,11 +1287,11 @@
       <c r="F20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="30"/>
+      <c r="G20" s="29"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="30" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1287,12 +1309,12 @@
       <c r="F21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="28">
         <v>46336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="30"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="5" t="s">
         <v>13</v>
       </c>
@@ -1308,10 +1330,10 @@
       <c r="F22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="30"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="30" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1329,12 +1351,12 @@
       <c r="F23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="28">
         <v>46218</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="30"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="5" t="s">
         <v>13</v>
       </c>
@@ -1350,10 +1372,10 @@
       <c r="F24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="30"/>
+      <c r="G24" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1371,12 +1393,12 @@
       <c r="F25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="28">
         <v>46188</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="30"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="5" t="s">
         <v>13</v>
       </c>
@@ -1392,10 +1414,10 @@
       <c r="F26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="30"/>
+      <c r="G26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="30" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1413,12 +1435,12 @@
       <c r="F27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="28">
         <v>46321</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="30"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="5" t="s">
         <v>13</v>
       </c>
@@ -1434,10 +1456,10 @@
       <c r="F28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="30"/>
+      <c r="G28" s="29"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="30" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1455,12 +1477,12 @@
       <c r="F29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="29">
+      <c r="G29" s="28">
         <v>46139</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="30"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="5" t="s">
         <v>13</v>
       </c>
@@ -1476,10 +1498,10 @@
       <c r="F30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="30"/>
+      <c r="G30" s="29"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="30" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1497,12 +1519,12 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="28">
         <v>46133</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="30"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="5" t="s">
         <v>13</v>
       </c>
@@ -1518,10 +1540,10 @@
       <c r="F32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="30"/>
+      <c r="G32" s="29"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="30" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1539,12 +1561,12 @@
       <c r="F33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="28">
         <v>46295</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="30"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="5" t="s">
         <v>13</v>
       </c>
@@ -1560,10 +1582,10 @@
       <c r="F34" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="30"/>
+      <c r="G34" s="29"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="30" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1581,12 +1603,12 @@
       <c r="F35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="28">
         <v>45737</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="30"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="5" t="s">
         <v>13</v>
       </c>
@@ -1602,10 +1624,10 @@
       <c r="F36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="30"/>
+      <c r="G36" s="29"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="30" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1623,12 +1645,12 @@
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="28">
         <v>45737</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="30"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
@@ -1644,7 +1666,7 @@
       <c r="F38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="30"/>
+      <c r="G38" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -1740,7 +1762,7 @@
       <c r="S1" s="27"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="31" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="27"/>
@@ -2126,8 +2148,8 @@
         <v>46199</v>
       </c>
       <c r="R10" s="9"/>
-      <c r="S10" s="9" t="s">
-        <v>50</v>
+      <c r="S10" s="32" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2180,7 +2202,9 @@
         <v>46305</v>
       </c>
       <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
+      <c r="S11" s="32" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="19" t="s">
@@ -2329,6 +2353,9 @@
       </c>
       <c r="Q14" s="20">
         <v>46218</v>
+      </c>
+      <c r="S14" s="32" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2858,7 +2885,7 @@
       <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="31" t="s">
         <v>59</v>
       </c>
       <c r="B2" s="27"/>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BBA398E-E399-4599-8FB3-812CFAEB6628}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF6D03B4-0554-400D-B876-6234A4233EA5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,18 +474,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -889,28 +889,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -957,13 +957,13 @@
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="32">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="29"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
@@ -979,7 +979,7 @@
       <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="29"/>
+      <c r="G6" s="31"/>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1001,13 +1001,13 @@
       <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="32" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
@@ -1023,7 +1023,7 @@
       <c r="F8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="29"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1045,13 +1045,13 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="32">
         <v>46204</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
@@ -1067,7 +1067,7 @@
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="29"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -1089,13 +1089,13 @@
       <c r="F11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="32">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="29"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1111,7 +1111,7 @@
       <c r="F12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="29"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1133,13 +1133,13 @@
       <c r="F13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="32" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1155,7 +1155,7 @@
       <c r="F14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="29"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1177,13 +1177,13 @@
       <c r="F15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="32">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="29"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
@@ -1199,7 +1199,7 @@
       <c r="F16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="29"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1221,13 +1221,13 @@
       <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="32">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="29"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
@@ -1243,7 +1243,7 @@
       <c r="F18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="29"/>
+      <c r="G18" s="31"/>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1265,13 +1265,13 @@
       <c r="F19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="32">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="29"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="5" t="s">
         <v>13</v>
       </c>
@@ -1287,7 +1287,7 @@
       <c r="F20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="29"/>
+      <c r="G20" s="31"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -1309,12 +1309,12 @@
       <c r="F21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="32">
         <v>46336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="29"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="5" t="s">
         <v>13</v>
       </c>
@@ -1330,7 +1330,7 @@
       <c r="F22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="29"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="30" t="s">
@@ -1351,12 +1351,12 @@
       <c r="F23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="32">
         <v>46218</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="29"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="5" t="s">
         <v>13</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="F24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="29"/>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
@@ -1393,12 +1393,12 @@
       <c r="F25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="32">
         <v>46188</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="29"/>
+      <c r="A26" s="31"/>
       <c r="B26" s="5" t="s">
         <v>13</v>
       </c>
@@ -1414,7 +1414,7 @@
       <c r="F26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="29"/>
+      <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="30" t="s">
@@ -1435,12 +1435,12 @@
       <c r="F27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="32">
         <v>46321</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="29"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="5" t="s">
         <v>13</v>
       </c>
@@ -1456,7 +1456,7 @@
       <c r="F28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="29"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
@@ -1477,12 +1477,12 @@
       <c r="F29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="32">
         <v>46139</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="29"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="5" t="s">
         <v>13</v>
       </c>
@@ -1498,7 +1498,7 @@
       <c r="F30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="29"/>
+      <c r="G30" s="31"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
@@ -1519,12 +1519,12 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="32">
         <v>46133</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="29"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="5" t="s">
         <v>13</v>
       </c>
@@ -1540,7 +1540,7 @@
       <c r="F32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="29"/>
+      <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
@@ -1561,12 +1561,12 @@
       <c r="F33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="32">
         <v>46295</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="29"/>
+      <c r="A34" s="31"/>
       <c r="B34" s="5" t="s">
         <v>13</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="F34" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="29"/>
+      <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="30" t="s">
@@ -1603,12 +1603,12 @@
       <c r="F35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="32">
         <v>45737</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="29"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="5" t="s">
         <v>13</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="F36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="29"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="30" t="s">
@@ -1645,12 +1645,12 @@
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="28">
+      <c r="G37" s="32">
         <v>45737</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="29"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
@@ -1666,30 +1666,10 @@
       <c r="F38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="29"/>
+      <c r="G38" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="G35:G36"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="G11:G12"/>
@@ -1706,6 +1686,26 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="G33:G34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1739,50 +1739,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
     </row>
     <row r="4" spans="1:19" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2148,7 +2148,7 @@
         <v>46199</v>
       </c>
       <c r="R10" s="9"/>
-      <c r="S10" s="32" t="s">
+      <c r="S10" s="26" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v>46305</v>
       </c>
       <c r="R11" s="9"/>
-      <c r="S11" s="32" t="s">
+      <c r="S11" s="26" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       <c r="Q14" s="20">
         <v>46218</v>
       </c>
-      <c r="S14" s="32" t="s">
+      <c r="S14" s="26" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2607,9 +2607,7 @@
       <c r="C20" s="10">
         <v>0.9</v>
       </c>
-      <c r="D20" s="18">
-        <v>341236.34</v>
-      </c>
+      <c r="D20" s="18"/>
       <c r="E20" s="22">
         <f>O20*0.3</f>
         <v>71744.399999999994</v>
@@ -2619,7 +2617,7 @@
       </c>
       <c r="G20" s="23">
         <f>D20*0.9</f>
-        <v>307112.70600000001</v>
+        <v>0</v>
       </c>
       <c r="H20" s="19">
         <v>3</v>
@@ -2653,16 +2651,14 @@
       <c r="C21" s="10">
         <v>0.9</v>
       </c>
-      <c r="D21" s="17">
-        <v>666700</v>
-      </c>
+      <c r="D21" s="17"/>
       <c r="E21" s="22">
         <f>O21*0.65</f>
         <v>145747.55000000002</v>
       </c>
       <c r="G21" s="19">
         <f>D21*0.75</f>
-        <v>500025</v>
+        <v>0</v>
       </c>
       <c r="H21" s="19">
         <v>3</v>
@@ -2878,18 +2874,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3104,19 +3100,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -3369,6 +3352,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3379,17 +3375,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3408,6 +3393,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF6D03B4-0554-400D-B876-6234A4233EA5}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2113E06-71DE-414B-882B-9EFC72A2B594}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -480,12 +480,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -939,7 +939,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -957,7 +957,7 @@
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="30">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
@@ -983,7 +983,7 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="32" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1001,7 +1001,7 @@
       <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="30" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="5"/>
@@ -1027,7 +1027,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="32" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1045,7 +1045,7 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="30">
         <v>46204</v>
       </c>
       <c r="H9" s="5"/>
@@ -1071,7 +1071,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1089,7 +1089,7 @@
       <c r="F11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="30">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
@@ -1115,7 +1115,7 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1133,7 +1133,7 @@
       <c r="F13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="30" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="5"/>
@@ -1159,7 +1159,7 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="32" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1177,7 +1177,7 @@
       <c r="F15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="30">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
@@ -1203,7 +1203,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="32" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1221,7 +1221,7 @@
       <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="30">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
@@ -1247,7 +1247,7 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="32" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1265,7 +1265,7 @@
       <c r="F19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="30">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
@@ -1291,7 +1291,7 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="32" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1309,7 +1309,7 @@
       <c r="F21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="30">
         <v>46336</v>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       <c r="G22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="32" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1351,7 +1351,7 @@
       <c r="F23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="30">
         <v>46218</v>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="32" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1393,7 +1393,7 @@
       <c r="F25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="30">
         <v>46188</v>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="32" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1435,7 +1435,7 @@
       <c r="F27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="30">
         <v>46321</v>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="32" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1477,7 +1477,7 @@
       <c r="F29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="30">
         <v>46139</v>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       <c r="G30" s="31"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="32" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1519,7 +1519,7 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="30">
         <v>46133</v>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="32" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1561,7 +1561,7 @@
       <c r="F33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="30">
         <v>46295</v>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="32" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1603,7 +1603,7 @@
       <c r="F35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="30">
         <v>45737</v>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="32" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1645,7 +1645,7 @@
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="30">
         <v>45737</v>
       </c>
     </row>
@@ -1670,6 +1670,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="G35:G36"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="G11:G12"/>
@@ -1686,26 +1706,6 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="G33:G34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2608,17 +2608,11 @@
         <v>0.9</v>
       </c>
       <c r="D20" s="18"/>
-      <c r="E20" s="22">
-        <f>O20*0.3</f>
-        <v>71744.399999999994</v>
-      </c>
+      <c r="E20" s="22"/>
       <c r="F20" s="17">
         <v>255</v>
       </c>
-      <c r="G20" s="23">
-        <f>D20*0.9</f>
-        <v>0</v>
-      </c>
+      <c r="G20" s="23"/>
       <c r="H20" s="19">
         <v>3</v>
       </c>
@@ -2628,9 +2622,7 @@
       <c r="M20" s="19">
         <v>0</v>
       </c>
-      <c r="O20" s="25">
-        <v>239148</v>
-      </c>
+      <c r="O20" s="25"/>
       <c r="P20" s="13">
         <v>45717</v>
       </c>
@@ -2652,14 +2644,7 @@
         <v>0.9</v>
       </c>
       <c r="D21" s="17"/>
-      <c r="E21" s="22">
-        <f>O21*0.65</f>
-        <v>145747.55000000002</v>
-      </c>
-      <c r="G21" s="19">
-        <f>D21*0.75</f>
-        <v>0</v>
-      </c>
+      <c r="E21" s="22"/>
       <c r="H21" s="19">
         <v>3</v>
       </c>
@@ -2669,9 +2654,7 @@
       <c r="M21" s="19">
         <v>0</v>
       </c>
-      <c r="O21" s="25">
-        <v>224227</v>
-      </c>
+      <c r="O21" s="25"/>
       <c r="P21" s="13">
         <v>45717</v>
       </c>
@@ -3100,6 +3083,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -3352,29 +3357,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3391,23 +3393,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2113E06-71DE-414B-882B-9EFC72A2B594}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06EED68D-93E3-4878-9BA6-AA3ACD4F9C84}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="68">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -244,10 +244,7 @@
     <t>รอลูกค้าคอนเฟิมวันส่งงาน Frist fix</t>
   </si>
   <si>
-    <t>รอลูกค้าคอนเฟิมวันส่งงาน Frist fix 07/10/2026</t>
-  </si>
-  <si>
-    <t>ส่งมอบงานวันเสาร์ ที่ 07/04/2026</t>
+    <t>ส่งงาน Frist fix 07/13/2026</t>
   </si>
 </sst>
 </file>
@@ -480,12 +477,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -939,7 +936,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="30" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -957,7 +954,7 @@
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="32">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
@@ -983,7 +980,7 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="30" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1001,7 +998,7 @@
       <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="32" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="5"/>
@@ -1027,7 +1024,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="30" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1045,7 +1042,7 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="32">
         <v>46204</v>
       </c>
       <c r="H9" s="5"/>
@@ -1071,7 +1068,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1089,7 +1086,7 @@
       <c r="F11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="32">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
@@ -1115,7 +1112,7 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="30" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1133,7 +1130,7 @@
       <c r="F13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="32" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="5"/>
@@ -1159,7 +1156,7 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="30" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1177,7 +1174,7 @@
       <c r="F15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="32">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
@@ -1203,7 +1200,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="30" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1221,7 +1218,7 @@
       <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="32">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
@@ -1247,7 +1244,7 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="30" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1265,7 +1262,7 @@
       <c r="F19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="32">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
@@ -1291,7 +1288,7 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="30" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1309,7 +1306,7 @@
       <c r="F21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="32">
         <v>46336</v>
       </c>
     </row>
@@ -1333,7 +1330,7 @@
       <c r="G22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="30" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1351,7 +1348,7 @@
       <c r="F23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="32">
         <v>46218</v>
       </c>
     </row>
@@ -1375,7 +1372,7 @@
       <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="30" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1393,7 +1390,7 @@
       <c r="F25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="32">
         <v>46188</v>
       </c>
     </row>
@@ -1417,7 +1414,7 @@
       <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="30" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1435,7 +1432,7 @@
       <c r="F27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="32">
         <v>46321</v>
       </c>
     </row>
@@ -1459,7 +1456,7 @@
       <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="30" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1477,7 +1474,7 @@
       <c r="F29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G29" s="32">
         <v>46139</v>
       </c>
     </row>
@@ -1501,7 +1498,7 @@
       <c r="G30" s="31"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="30" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1519,7 +1516,7 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="32">
         <v>46133</v>
       </c>
     </row>
@@ -1543,7 +1540,7 @@
       <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="30" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1561,7 +1558,7 @@
       <c r="F33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="32">
         <v>46295</v>
       </c>
     </row>
@@ -1585,7 +1582,7 @@
       <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="30" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1603,7 +1600,7 @@
       <c r="F35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="32">
         <v>45737</v>
       </c>
     </row>
@@ -1627,7 +1624,7 @@
       <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="30" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1645,7 +1642,7 @@
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="32">
         <v>45737</v>
       </c>
     </row>
@@ -1670,26 +1667,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="G35:G36"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="G11:G12"/>
@@ -1706,6 +1683,26 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="G33:G34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2103,10 +2100,10 @@
         <v>20</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C10" s="10">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D10" s="11">
         <v>338450.2</v>
@@ -2119,11 +2116,11 @@
         <v>370</v>
       </c>
       <c r="G10" s="11">
-        <f>D10*0.4</f>
-        <v>135380.08000000002</v>
+        <f>D10*1</f>
+        <v>338450.2</v>
       </c>
       <c r="H10" s="12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="9"/>
@@ -2148,9 +2145,7 @@
         <v>46199</v>
       </c>
       <c r="R10" s="9"/>
-      <c r="S10" s="26" t="s">
-        <v>68</v>
-      </c>
+      <c r="S10" s="26"/>
     </row>
     <row r="11" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="19" t="s">
@@ -2837,7 +2832,7 @@
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="B5:B39" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -3083,28 +3078,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -3357,10 +3330,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3377,20 +3383,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06EED68D-93E3-4878-9BA6-AA3ACD4F9C84}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689BE7B0-8029-4ECA-BC50-6BBE0E618299}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="71">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -214,9 +214,6 @@
     <t>บริษัท อาร์ทอพ แอร์ ซัพพลาย จำกัด</t>
   </si>
   <si>
-    <t>โครงการล่าช้า</t>
-  </si>
-  <si>
     <t>SITE VISIT LOG</t>
   </si>
   <si>
@@ -245,6 +242,18 @@
   </si>
   <si>
     <t>ส่งงาน Frist fix 07/13/2026</t>
+  </si>
+  <si>
+    <t>1 กันยา เริ่มเข้าไซต์</t>
+  </si>
+  <si>
+    <t>07/24/2026 เริ่มเข้าไซต์</t>
+  </si>
+  <si>
+    <t>โครงการล่าช้า เดือน 9 ส่งมอบงาน</t>
+  </si>
+  <si>
+    <t>โครงการล่าช้า/ติดกริลวันที่ 17/07/2026 กำหนดส่งงานได้ กันยา-ตุลา</t>
   </si>
 </sst>
 </file>
@@ -477,12 +486,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -936,7 +945,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -954,7 +963,7 @@
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="30">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
@@ -980,7 +989,7 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="32" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -998,7 +1007,7 @@
       <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="30" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="5"/>
@@ -1024,7 +1033,7 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="32" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1042,7 +1051,7 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="30">
         <v>46204</v>
       </c>
       <c r="H9" s="5"/>
@@ -1068,7 +1077,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1086,7 +1095,7 @@
       <c r="F11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="30">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
@@ -1112,7 +1121,7 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1130,7 +1139,7 @@
       <c r="F13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="30" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="5"/>
@@ -1156,7 +1165,7 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="32" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1174,7 +1183,7 @@
       <c r="F15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="30">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
@@ -1200,7 +1209,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="32" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1213,12 +1222,12 @@
         <v>46198</v>
       </c>
       <c r="E17" s="7">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="30">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
@@ -1244,7 +1253,7 @@
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="32" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1262,7 +1271,7 @@
       <c r="F19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="30">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
@@ -1288,7 +1297,7 @@
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="32" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1306,7 +1315,7 @@
       <c r="F21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="30">
         <v>46336</v>
       </c>
     </row>
@@ -1330,7 +1339,7 @@
       <c r="G22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="32" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1343,12 +1352,12 @@
         <v>46206</v>
       </c>
       <c r="E23" s="7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="30">
         <v>46218</v>
       </c>
     </row>
@@ -1372,7 +1381,7 @@
       <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="32" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1390,7 +1399,7 @@
       <c r="F25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="30">
         <v>46188</v>
       </c>
     </row>
@@ -1414,7 +1423,7 @@
       <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="32" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1432,7 +1441,7 @@
       <c r="F27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="30">
         <v>46321</v>
       </c>
     </row>
@@ -1456,7 +1465,7 @@
       <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="32" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1474,7 +1483,7 @@
       <c r="F29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="30">
         <v>46139</v>
       </c>
     </row>
@@ -1498,7 +1507,7 @@
       <c r="G30" s="31"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="32" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1516,7 +1525,7 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="30">
         <v>46133</v>
       </c>
     </row>
@@ -1540,7 +1549,7 @@
       <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="32" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1558,7 +1567,7 @@
       <c r="F33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="30">
         <v>46295</v>
       </c>
     </row>
@@ -1582,7 +1591,7 @@
       <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="32" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1600,7 +1609,7 @@
       <c r="F35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="30">
         <v>45737</v>
       </c>
     </row>
@@ -1624,7 +1633,7 @@
       <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="32" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1642,7 +1651,7 @@
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="30">
         <v>45737</v>
       </c>
     </row>
@@ -1667,6 +1676,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="G35:G36"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="G11:G12"/>
@@ -1683,26 +1712,6 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="G33:G34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2175,7 +2184,6 @@
         <v>10</v>
       </c>
       <c r="I11" s="12"/>
-      <c r="J11" s="9"/>
       <c r="K11" s="11">
         <v>26094</v>
       </c>
@@ -2198,7 +2206,7 @@
       </c>
       <c r="R11" s="9"/>
       <c r="S11" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2249,8 +2257,8 @@
         <v>46336</v>
       </c>
       <c r="R12" s="9"/>
-      <c r="S12" s="9" t="s">
-        <v>51</v>
+      <c r="S12" s="26" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2310,7 +2318,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D14" s="11">
         <v>1707089</v>
@@ -2350,7 +2358,7 @@
         <v>46218</v>
       </c>
       <c r="S14" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2588,8 +2596,8 @@
       <c r="Q19" s="20">
         <v>46295</v>
       </c>
-      <c r="S19" s="9" t="s">
-        <v>51</v>
+      <c r="S19" s="26" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2624,8 +2632,8 @@
       <c r="Q20" s="13">
         <v>45737</v>
       </c>
-      <c r="S20" s="9" t="s">
-        <v>57</v>
+      <c r="S20" s="26" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2656,8 +2664,8 @@
       <c r="Q21" s="13">
         <v>45737</v>
       </c>
-      <c r="S21" s="9" t="s">
-        <v>57</v>
+      <c r="S21" s="26" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
@@ -2832,7 +2840,7 @@
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="B5:B39" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -2853,27 +2861,27 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2891,7 +2899,7 @@
         <v>46185</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="8">
         <v>4</v>
@@ -2902,7 +2910,7 @@
         <v>46189</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="8">
         <v>4</v>
@@ -2913,7 +2921,7 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="8">
         <v>3</v>
@@ -2924,7 +2932,7 @@
         <v>46185</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="8">
         <v>2.5</v>
@@ -2935,7 +2943,7 @@
         <v>46190</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="8">
         <v>3</v>
@@ -2946,7 +2954,7 @@
         <v>46190</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" s="8">
         <v>3</v>
@@ -2957,7 +2965,7 @@
         <v>46192</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="8">
         <v>3</v>
@@ -2968,7 +2976,7 @@
         <v>46197</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="8">
         <v>3</v>
@@ -2979,7 +2987,7 @@
         <v>46198</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="4">
         <v>6</v>
@@ -2990,7 +2998,7 @@
         <v>46202</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="4">
         <v>6</v>
@@ -3001,7 +3009,7 @@
         <v>46205</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="4">
         <v>4</v>
@@ -3012,7 +3020,7 @@
         <v>46206</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="4">
         <v>4</v>
@@ -3331,6 +3339,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -3341,15 +3358,6 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3372,6 +3380,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3380,12 +3396,4 @@
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689BE7B0-8029-4ECA-BC50-6BBE0E618299}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3276A669-893A-4488-8791-EDE67B210EDF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="71">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -247,13 +247,13 @@
     <t>1 กันยา เริ่มเข้าไซต์</t>
   </si>
   <si>
-    <t>07/24/2026 เริ่มเข้าไซต์</t>
-  </si>
-  <si>
     <t>โครงการล่าช้า เดือน 9 ส่งมอบงาน</t>
   </si>
   <si>
     <t>โครงการล่าช้า/ติดกริลวันที่ 17/07/2026 กำหนดส่งงานได้ กันยา-ตุลา</t>
+  </si>
+  <si>
+    <t>07/24/2026 เริ่มเข้าไซต์ (Draft)</t>
   </si>
 </sst>
 </file>
@@ -413,7 +413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -439,59 +439,76 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -895,28 +912,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -945,7 +962,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -963,13 +980,13 @@
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="12">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
@@ -985,11 +1002,11 @@
       <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="13"/>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="14" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1007,13 +1024,13 @@
       <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="12" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="31"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
@@ -1029,11 +1046,11 @@
       <c r="F8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="31"/>
+      <c r="G8" s="13"/>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1051,13 +1068,13 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="30">
-        <v>46204</v>
+      <c r="G9" s="12">
+        <v>46218</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
@@ -1073,11 +1090,11 @@
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="31"/>
+      <c r="G10" s="13"/>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="14" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1095,13 +1112,13 @@
       <c r="F11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="12">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1117,11 +1134,11 @@
       <c r="F12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="31"/>
+      <c r="G12" s="13"/>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1139,13 +1156,13 @@
       <c r="F13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="12" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1161,11 +1178,11 @@
       <c r="F14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="31"/>
+      <c r="G14" s="13"/>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="14" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1183,13 +1200,13 @@
       <c r="F15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="12">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
@@ -1205,11 +1222,11 @@
       <c r="F16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="31"/>
+      <c r="G16" s="13"/>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1227,13 +1244,13 @@
       <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="12">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
+      <c r="A18" s="13"/>
       <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
@@ -1249,11 +1266,11 @@
       <c r="F18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="31"/>
+      <c r="G18" s="13"/>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="14" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1271,13 +1288,13 @@
       <c r="F19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="12">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="31"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="5" t="s">
         <v>13</v>
       </c>
@@ -1293,11 +1310,11 @@
       <c r="F20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="31"/>
+      <c r="G20" s="13"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="14" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1315,12 +1332,12 @@
       <c r="F21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="12">
         <v>46336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="31"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="5" t="s">
         <v>13</v>
       </c>
@@ -1336,10 +1353,10 @@
       <c r="F22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="31"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="14" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1352,17 +1369,17 @@
         <v>46206</v>
       </c>
       <c r="E23" s="7">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="12">
         <v>46218</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
+      <c r="A24" s="13"/>
       <c r="B24" s="5" t="s">
         <v>13</v>
       </c>
@@ -1378,10 +1395,10 @@
       <c r="F24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="31"/>
+      <c r="G24" s="13"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1399,12 +1416,12 @@
       <c r="F25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="12">
         <v>46188</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="31"/>
+      <c r="A26" s="13"/>
       <c r="B26" s="5" t="s">
         <v>13</v>
       </c>
@@ -1420,10 +1437,10 @@
       <c r="F26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="31"/>
+      <c r="G26" s="13"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="14" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1441,12 +1458,12 @@
       <c r="F27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="12">
         <v>46321</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="31"/>
+      <c r="A28" s="13"/>
       <c r="B28" s="5" t="s">
         <v>13</v>
       </c>
@@ -1462,10 +1479,10 @@
       <c r="F28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="31"/>
+      <c r="G28" s="13"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="14" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1483,12 +1500,12 @@
       <c r="F29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G29" s="12">
         <v>46139</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="31"/>
+      <c r="A30" s="13"/>
       <c r="B30" s="5" t="s">
         <v>13</v>
       </c>
@@ -1504,10 +1521,10 @@
       <c r="F30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="31"/>
+      <c r="G30" s="13"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1525,12 +1542,12 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="12">
         <v>46133</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="31"/>
+      <c r="A32" s="13"/>
       <c r="B32" s="5" t="s">
         <v>13</v>
       </c>
@@ -1546,10 +1563,10 @@
       <c r="F32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="31"/>
+      <c r="G32" s="13"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="14" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1567,12 +1584,12 @@
       <c r="F33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="12">
         <v>46295</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="31"/>
+      <c r="A34" s="13"/>
       <c r="B34" s="5" t="s">
         <v>13</v>
       </c>
@@ -1588,10 +1605,10 @@
       <c r="F34" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="31"/>
+      <c r="G34" s="13"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1609,12 +1626,12 @@
       <c r="F35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="12">
         <v>45737</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="31"/>
+      <c r="A36" s="13"/>
       <c r="B36" s="5" t="s">
         <v>13</v>
       </c>
@@ -1630,10 +1647,10 @@
       <c r="F36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="31"/>
+      <c r="G36" s="13"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="14" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1651,12 +1668,12 @@
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="12">
         <v>45737</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="31"/>
+      <c r="A38" s="13"/>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
@@ -1672,7 +1689,7 @@
       <c r="F38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="31"/>
+      <c r="G38" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -1745,50 +1762,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
     </row>
     <row r="4" spans="1:19" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1849,992 +1866,996 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="22">
         <v>0.9</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="23">
         <v>326786.36</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="23">
         <f>O5</f>
         <v>130000</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11">
+      <c r="F5" s="23"/>
+      <c r="G5" s="23">
         <f>D5*0.8</f>
         <v>261429.08799999999</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="24">
         <v>12</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="11">
+      <c r="I5" s="24"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="23">
         <v>5198</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9" t="s">
+      <c r="L5" s="23"/>
+      <c r="M5" s="23">
+        <v>0</v>
+      </c>
+      <c r="N5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="24">
+      <c r="O5" s="25">
         <v>130000</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="26">
         <f>'[1]Master Schedule'!C5</f>
         <v>46084</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="26">
         <v>46106</v>
       </c>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9" t="s">
+      <c r="R5" s="21"/>
+      <c r="S5" s="33" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="10">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11">
+      <c r="C6" s="22">
+        <v>0</v>
+      </c>
+      <c r="D6" s="23">
         <v>409599.64</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="23">
         <f>O6*0.3</f>
         <v>41833.799999999996</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11">
+      <c r="F6" s="23"/>
+      <c r="G6" s="23">
         <f t="shared" ref="G6:G14" si="0">D6*0.4</f>
         <v>163839.85600000003</v>
       </c>
-      <c r="H6" s="12">
-        <v>0</v>
-      </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="11">
+      <c r="H6" s="24">
+        <v>0</v>
+      </c>
+      <c r="I6" s="24"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="23">
         <v>6972.5</v>
       </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9" t="s">
+      <c r="L6" s="23"/>
+      <c r="M6" s="23">
+        <v>0</v>
+      </c>
+      <c r="N6" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="25">
         <v>139446</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="26">
         <f>'[1]Master Schedule'!C6</f>
         <v>46189</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="26">
         <v>46264</v>
       </c>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9" t="s">
+      <c r="R6" s="21"/>
+      <c r="S6" s="33" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="22">
         <v>0.9</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="23">
         <v>576317.9</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="23">
         <f t="shared" ref="E7:E18" si="1">O7</f>
         <v>280000</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="23">
         <v>603</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="23">
         <f>D7*0.9</f>
         <v>518686.11000000004</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="24">
         <v>20</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="11">
+      <c r="I7" s="24"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="23">
         <v>12045</v>
       </c>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11">
-        <v>0</v>
-      </c>
-      <c r="N7" s="9" t="s">
+      <c r="L7" s="23"/>
+      <c r="M7" s="23">
+        <v>0</v>
+      </c>
+      <c r="N7" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="25">
         <v>280000</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="26">
         <f>'[1]Master Schedule'!C7</f>
         <v>46219</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="Q7" s="26">
         <v>46102</v>
       </c>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9" t="s">
+      <c r="R7" s="21"/>
+      <c r="S7" s="33" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="22">
         <v>1</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="23">
         <v>322961.08</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="23">
         <f t="shared" si="1"/>
         <v>89000</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="23">
         <v>715</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="23">
         <f>D8*1</f>
         <v>322961.08</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="24">
         <v>7</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="11">
+      <c r="I8" s="24"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="23">
         <v>24166</v>
       </c>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11">
+      <c r="L8" s="23"/>
+      <c r="M8" s="23">
         <v>1444</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="N8" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="O8" s="24">
+      <c r="O8" s="25">
         <v>89000</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="26">
         <f>'[1]Master Schedule'!C8</f>
         <v>46244</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8" s="26">
         <v>46171</v>
       </c>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-    </row>
-    <row r="9" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="9" t="s">
+      <c r="R8" s="21"/>
+      <c r="S8" s="33"/>
+    </row>
+    <row r="9" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="10">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11">
+      <c r="C9" s="22">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
         <v>630619.19999999995</v>
       </c>
-      <c r="E9" s="11" t="str">
+      <c r="E9" s="23" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11">
+      <c r="F9" s="23"/>
+      <c r="G9" s="23">
         <f>D9*0.4</f>
         <v>252247.67999999999</v>
       </c>
-      <c r="H9" s="12">
-        <v>0</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="24" t="s">
+      <c r="H9" s="24">
+        <v>0</v>
+      </c>
+      <c r="I9" s="24"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23">
+        <v>0</v>
+      </c>
+      <c r="N9" s="21"/>
+      <c r="O9" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="26">
         <v>46388</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="Q9" s="26">
         <v>46447</v>
       </c>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-    </row>
-    <row r="10" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="19" t="s">
+      <c r="R9" s="21"/>
+      <c r="S9" s="33"/>
+    </row>
+    <row r="10" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="22">
         <v>1</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="23">
         <v>338450.2</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="23">
         <f>O10*0.8</f>
         <v>110400</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="23">
         <v>370</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="23">
         <f>D10*1</f>
         <v>338450.2</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="24">
         <v>12</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="11">
+      <c r="I10" s="24"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="23">
         <v>5783</v>
       </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11">
+      <c r="L10" s="23"/>
+      <c r="M10" s="23">
         <v>787</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="24">
+      <c r="O10" s="25">
         <v>138000</v>
       </c>
-      <c r="P10" s="13">
+      <c r="P10" s="26">
         <f>'[1]Master Schedule'!C10</f>
         <v>46168</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="26">
         <v>46199</v>
       </c>
-      <c r="R10" s="9"/>
-      <c r="S10" s="26"/>
-    </row>
-    <row r="11" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="19" t="s">
+      <c r="R10" s="21"/>
+      <c r="S10" s="34"/>
+    </row>
+    <row r="11" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="22">
         <v>0.7</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="23">
         <v>1156111.18</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="23">
         <f>O11*0.3</f>
         <v>84000</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="23">
         <v>840</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="23">
         <f t="shared" si="0"/>
         <v>462444.47200000001</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="24">
         <v>10</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="K11" s="11">
+      <c r="I11" s="24"/>
+      <c r="K11" s="23">
         <v>26094</v>
       </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11">
+      <c r="L11" s="23"/>
+      <c r="M11" s="23">
         <v>46175</v>
       </c>
-      <c r="N11" s="19" t="s">
+      <c r="N11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="24">
+      <c r="O11" s="25">
         <v>280000</v>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="26">
         <f>'[1]Master Schedule'!C11</f>
         <v>46184</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="26">
         <v>46305</v>
       </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="26" t="s">
+      <c r="R11" s="21"/>
+      <c r="S11" s="34" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="10">
-        <v>0</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="22">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23">
         <v>594114</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="23">
         <f>O12*0</f>
         <v>0</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11">
+      <c r="F12" s="23"/>
+      <c r="G12" s="23">
         <f t="shared" si="0"/>
         <v>237645.6</v>
       </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="11">
+      <c r="H12" s="24">
+        <v>0</v>
+      </c>
+      <c r="I12" s="24"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="23">
         <v>20261</v>
       </c>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11">
+      <c r="L12" s="23"/>
+      <c r="M12" s="23">
         <v>20018</v>
       </c>
-      <c r="N12" s="19" t="s">
+      <c r="N12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="24">
+      <c r="O12" s="25">
         <v>233247.9</v>
       </c>
-      <c r="P12" s="13">
+      <c r="P12" s="26">
         <f>'[1]Master Schedule'!C12</f>
         <v>46200</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="Q12" s="26">
         <v>46336</v>
       </c>
-      <c r="R12" s="9"/>
-      <c r="S12" s="26" t="s">
+      <c r="R12" s="21"/>
+      <c r="S12" s="34" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="19" t="s">
+    <row r="13" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="10">
-        <v>0</v>
-      </c>
-      <c r="D13" s="11">
+      <c r="C13" s="22">
+        <v>0</v>
+      </c>
+      <c r="D13" s="23">
         <v>327102.8</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="23">
         <f>O13*0.3</f>
         <v>36000</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11">
+      <c r="F13" s="23"/>
+      <c r="G13" s="23">
         <f t="shared" si="0"/>
         <v>130841.12</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="27">
         <v>3</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="11">
+      <c r="J13" s="21"/>
+      <c r="K13" s="23">
         <v>14327</v>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="16">
         <v>4164</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="O13" s="25">
+      <c r="O13" s="17">
         <v>120000</v>
       </c>
-      <c r="P13" s="13">
+      <c r="P13" s="26">
         <f>'[1]Master Schedule'!C13</f>
         <v>46392</v>
       </c>
-      <c r="Q13" s="20">
+      <c r="Q13" s="18">
         <v>46336</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="S13" s="33" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="28">
         <v>0.6</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="23">
         <v>1707089</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="23">
         <f>O14*0.3</f>
         <v>197003.709</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="23">
         <v>215</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="23">
         <f t="shared" si="0"/>
         <v>682835.60000000009</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="27">
         <v>10</v>
       </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="11">
+      <c r="J14" s="21"/>
+      <c r="K14" s="23">
         <v>54190</v>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="16">
         <v>20695.969999999972</v>
       </c>
-      <c r="N14" s="19" t="s">
+      <c r="N14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="O14" s="25">
+      <c r="O14" s="17">
         <v>656679.03</v>
       </c>
-      <c r="P14" s="13">
+      <c r="P14" s="26">
         <f>'[1]Master Schedule'!C14</f>
         <v>46042</v>
       </c>
-      <c r="Q14" s="20">
+      <c r="Q14" s="18">
         <v>46218</v>
       </c>
-      <c r="S14" s="26" t="s">
+      <c r="S14" s="34" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="19" t="s">
+    <row r="15" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="22">
         <v>1</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="23">
         <v>80000</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="23">
         <f>O15</f>
         <v>40000</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="23">
         <v>489</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="23">
         <f>D15*1</f>
         <v>80000</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="27">
         <v>4</v>
       </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="11">
-        <v>0</v>
-      </c>
-      <c r="M15" s="19">
-        <v>0</v>
-      </c>
-      <c r="N15" s="19" t="s">
+      <c r="J15" s="21"/>
+      <c r="K15" s="23">
+        <v>0</v>
+      </c>
+      <c r="M15" s="16">
+        <v>0</v>
+      </c>
+      <c r="N15" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="O15" s="25">
+      <c r="O15" s="17">
         <v>40000</v>
       </c>
-      <c r="P15" s="13">
+      <c r="P15" s="26">
         <f>'[1]Master Schedule'!C15</f>
         <v>46168</v>
       </c>
-      <c r="Q15" s="20">
+      <c r="Q15" s="18">
         <v>46188</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="19" t="s">
+      <c r="S15" s="35"/>
+    </row>
+    <row r="16" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="10">
-        <v>0</v>
-      </c>
-      <c r="D16" s="11">
+      <c r="C16" s="22">
+        <v>0</v>
+      </c>
+      <c r="D16" s="23">
         <v>1199960.02</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="23">
         <f>O16*0</f>
         <v>0</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11">
+      <c r="F16" s="23"/>
+      <c r="G16" s="23">
         <f>D16*0.4</f>
         <v>479984.00800000003</v>
       </c>
-      <c r="H16" s="14">
-        <v>0</v>
-      </c>
-      <c r="K16" s="11">
+      <c r="H16" s="27">
+        <v>0</v>
+      </c>
+      <c r="K16" s="23">
         <v>27535</v>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="16">
         <v>34414</v>
       </c>
-      <c r="N16" s="19" t="s">
+      <c r="N16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="O16" s="25">
+      <c r="O16" s="17">
         <v>430000</v>
       </c>
-      <c r="P16" s="13">
+      <c r="P16" s="26">
         <f>'[1]Master Schedule'!C16</f>
         <v>46198</v>
       </c>
-      <c r="Q16" s="20">
+      <c r="Q16" s="18">
         <v>46321</v>
       </c>
-      <c r="S16" s="9" t="s">
+      <c r="S16" s="33" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="19" t="s">
+    <row r="17" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="22">
         <v>1</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="23">
         <v>600000</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="23">
         <f>O17</f>
         <v>234861</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="23">
         <v>735</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="23">
         <f>D17*1</f>
         <v>600000</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="29">
         <v>10</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="11">
+      <c r="J17" s="21"/>
+      <c r="K17" s="23">
         <v>10000</v>
       </c>
-      <c r="M17" s="19">
-        <v>0</v>
-      </c>
-      <c r="N17" s="19" t="s">
+      <c r="M17" s="16">
+        <v>0</v>
+      </c>
+      <c r="N17" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="17">
         <v>234861</v>
       </c>
-      <c r="P17" s="13">
+      <c r="P17" s="26">
         <f>'[1]Master Schedule'!C17</f>
         <v>46188</v>
       </c>
-      <c r="Q17" s="20">
+      <c r="Q17" s="18">
         <v>46139</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="19" t="s">
+      <c r="S17" s="35"/>
+    </row>
+    <row r="18" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="22">
         <v>1</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="23">
         <v>317648</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="23">
         <f t="shared" si="1"/>
         <v>119980</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11">
+      <c r="F18" s="23"/>
+      <c r="G18" s="23">
         <f>D18*1</f>
         <v>317648</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="29">
         <v>10</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="11">
+      <c r="J18" s="21"/>
+      <c r="K18" s="23">
         <v>8760</v>
       </c>
-      <c r="M18" s="19">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9" t="s">
+      <c r="M18" s="16">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="O18" s="25">
+      <c r="O18" s="17">
         <v>119980</v>
       </c>
-      <c r="P18" s="13">
+      <c r="P18" s="26">
         <f>'[1]Master Schedule'!C18</f>
         <v>46200</v>
       </c>
-      <c r="Q18" s="20">
+      <c r="Q18" s="18">
         <v>46133</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="19" t="s">
+      <c r="S18" s="35"/>
+    </row>
+    <row r="19" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="10">
-        <v>0</v>
-      </c>
-      <c r="D19" s="11">
+      <c r="C19" s="22">
+        <v>0</v>
+      </c>
+      <c r="D19" s="23">
         <v>832813</v>
       </c>
-      <c r="E19" s="11">
-        <f t="shared" ref="E19" si="2">O19</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="11">
+      <c r="E19" s="23">
+        <f>O19*0.3</f>
+        <v>84000</v>
+      </c>
+      <c r="F19" s="23">
         <v>630</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="23">
         <f>455555</f>
         <v>455555</v>
       </c>
-      <c r="H19" s="15">
-        <v>0</v>
-      </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="11">
+      <c r="H19" s="29">
+        <v>3</v>
+      </c>
+      <c r="J19" s="21"/>
+      <c r="K19" s="23">
         <v>35070</v>
       </c>
-      <c r="M19" s="19">
-        <v>0</v>
-      </c>
-      <c r="N19" s="9" t="s">
+      <c r="M19" s="16">
+        <v>7702</v>
+      </c>
+      <c r="N19" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="O19" s="25"/>
-      <c r="P19" s="13">
+      <c r="O19" s="17">
+        <v>280000</v>
+      </c>
+      <c r="P19" s="26">
         <f>'Master Schedule'!C33</f>
         <v>46091</v>
       </c>
-      <c r="Q19" s="20">
+      <c r="Q19" s="18">
         <v>46295</v>
       </c>
-      <c r="S19" s="26" t="s">
+      <c r="S19" s="34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="22">
+        <v>0.9</v>
+      </c>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="16">
+        <v>255</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="16">
+        <v>3</v>
+      </c>
+      <c r="K20" s="16">
+        <v>0</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0</v>
+      </c>
+      <c r="O20" s="17"/>
+      <c r="P20" s="26">
+        <v>45717</v>
+      </c>
+      <c r="Q20" s="26">
+        <v>45737</v>
+      </c>
+      <c r="S20" s="34" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="21" t="s">
+    <row r="21" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C21" s="22">
         <v>0.9</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="17">
-        <v>255</v>
-      </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="19">
-        <v>3</v>
-      </c>
-      <c r="K20" s="19">
-        <v>0</v>
-      </c>
-      <c r="M20" s="19">
-        <v>0</v>
-      </c>
-      <c r="O20" s="25"/>
-      <c r="P20" s="13">
+      <c r="E21" s="32"/>
+      <c r="H21" s="16">
+        <v>6</v>
+      </c>
+      <c r="K21" s="16">
+        <v>0</v>
+      </c>
+      <c r="M21" s="16">
+        <v>0</v>
+      </c>
+      <c r="O21" s="17"/>
+      <c r="P21" s="26">
         <v>45717</v>
       </c>
-      <c r="Q20" s="13">
+      <c r="Q21" s="26">
         <v>45737</v>
       </c>
-      <c r="S20" s="26" t="s">
+      <c r="S21" s="34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="19" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="10">
-        <v>0.9</v>
-      </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="22"/>
-      <c r="H21" s="19">
-        <v>3</v>
-      </c>
-      <c r="K21" s="19">
-        <v>0</v>
-      </c>
-      <c r="M21" s="19">
-        <v>0</v>
-      </c>
-      <c r="O21" s="25"/>
-      <c r="P21" s="13">
-        <v>45717</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>45737</v>
-      </c>
-      <c r="S21" s="26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:19" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="33" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="34" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="35" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="36" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="37" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="38" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="39" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="40" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="41" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="42" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="43" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="44" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="45" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="46" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="47" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="48" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="49" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="50" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="51" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="52" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="53" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="54" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="55" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="56" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="57" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="58" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="59" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="60" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="61" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="62" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="63" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="64" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="65" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="66" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="67" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="68" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="69" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="70" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="71" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="72" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="73" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="74" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="75" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="76" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="77" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="78" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="79" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="80" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="81" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="82" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="83" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="84" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="85" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="86" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="87" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="88" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="89" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="90" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="91" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="92" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="93" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="94" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="95" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="96" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="97" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="98" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="99" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="100" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="101" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="102" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="103" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="104" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="105" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="106" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="107" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="108" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="109" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="110" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="111" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="112" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="113" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="114" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="115" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="116" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="117" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="118" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="119" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="120" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="121" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="122" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="123" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="124" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="125" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="126" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="127" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="128" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="129" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="130" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="131" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="132" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="133" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="134" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="135" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="136" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="137" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="138" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="139" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="140" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="141" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="142" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="143" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="144" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="145" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="146" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="147" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="148" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="149" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="150" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="151" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="152" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="153" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="154" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="155" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="156" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="157" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="158" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="159" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="160" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="161" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="162" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="163" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="164" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="165" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="166" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="167" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="168" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="169" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="170" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="171" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="172" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="173" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="174" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="175" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="176" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="177" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="178" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="179" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="180" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="181" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="182" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="183" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="184" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="185" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="186" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="187" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="188" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="33" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="34" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="35" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="36" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="37" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="38" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="39" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="40" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="41" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="42" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="43" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="44" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="45" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="46" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="47" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="48" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="49" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="50" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="51" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="52" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="53" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="54" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="55" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="56" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="57" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="58" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="59" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="60" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="61" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="62" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="63" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="64" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="65" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="66" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="67" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="68" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="69" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="70" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="71" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="72" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="73" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="74" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="75" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="76" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="77" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="78" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="79" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="80" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="81" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="82" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="83" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="84" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="85" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="86" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="87" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="88" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="89" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="90" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="91" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="92" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="93" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="94" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="95" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="96" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="97" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="98" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="99" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="100" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="101" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="102" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="103" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="104" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="105" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="106" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="107" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="108" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="109" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="110" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="111" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="112" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="113" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="114" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="115" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="116" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="117" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="118" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="119" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="120" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="121" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="122" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="123" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="124" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="125" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="126" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="127" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="128" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="129" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="130" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="131" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="132" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="133" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="134" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="135" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="136" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="137" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="138" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="139" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="140" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="141" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="142" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="143" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="144" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="145" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="146" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="147" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="148" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="149" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="150" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="151" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="152" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="153" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="154" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="155" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="156" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="157" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="158" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="159" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="160" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="161" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="162" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="163" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="164" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="165" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="166" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="167" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="168" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="169" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="170" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="171" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="172" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="173" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="174" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="175" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="176" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="177" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="178" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="179" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="180" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="181" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="182" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="183" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="184" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="185" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="186" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="187" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="188" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
@@ -2860,18 +2881,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3027,9 +3048,15 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="4"/>
+      <c r="A19" s="3">
+        <v>46209</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="4">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
@@ -3086,6 +3113,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -3338,29 +3387,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3377,23 +3423,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{4D5E45EE-EAC0-4096-82D3-C82E547233F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3276A669-893A-4488-8791-EDE67B210EDF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3855FAE-453D-49B5-A4C9-C937F825A970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="75">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -220,9 +220,6 @@
     <t>Optional sheet — one row = one team member's site visit hours in one month. Powers the team-wide Monthly Site Visit Overview chart on the Dashboard (not tied to a specific project).</t>
   </si>
   <si>
-    <t>Month</t>
-  </si>
-  <si>
     <t>Inspector Name</t>
   </si>
   <si>
@@ -254,6 +251,21 @@
   </si>
   <si>
     <t>07/24/2026 เริ่มเข้าไซต์ (Draft)</t>
+  </si>
+  <si>
+    <t>Project Type</t>
+  </si>
+  <si>
+    <t>External</t>
+  </si>
+  <si>
+    <t>Visit Date</t>
+  </si>
+  <si>
+    <t>Master Schedule PDF</t>
+  </si>
+  <si>
+    <t>https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQB_OM8tpcqzSYSvJ6iVtRP4AfoT3xxyU-FbYl9w1ZSicrI?e=Z2SvXD</t>
   </si>
 </sst>
 </file>
@@ -265,7 +277,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +354,14 @@
       <name val="Cordia New"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -409,11 +429,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -440,16 +461,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -510,8 +521,22 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -912,28 +937,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -962,7 +987,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="35" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -980,13 +1005,13 @@
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="33">
         <v>46213</v>
       </c>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
@@ -1002,11 +1027,11 @@
       <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="35" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1024,13 +1049,13 @@
       <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="33" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
@@ -1046,11 +1071,11 @@
       <c r="F8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="13"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="35" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1068,13 +1093,13 @@
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="33">
         <v>46218</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
@@ -1090,11 +1115,11 @@
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="13"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="35" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1112,13 +1137,13 @@
       <c r="F11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="33">
         <v>46171</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1134,11 +1159,11 @@
       <c r="F12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="13"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1156,13 +1181,13 @@
       <c r="F13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="33" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1178,11 +1203,11 @@
       <c r="F14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="13"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="35" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1200,13 +1225,13 @@
       <c r="F15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="33">
         <v>46199</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
@@ -1222,11 +1247,11 @@
       <c r="F16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="13"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="35" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1244,13 +1269,13 @@
       <c r="F17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="33">
         <v>46305</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
@@ -1266,11 +1291,11 @@
       <c r="F18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="13"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="35" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1288,13 +1313,13 @@
       <c r="F19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="33">
         <v>46336</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="5" t="s">
         <v>13</v>
       </c>
@@ -1310,11 +1335,11 @@
       <c r="F20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="13"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="35" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1332,12 +1357,12 @@
       <c r="F21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="33">
         <v>46336</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="5" t="s">
         <v>13</v>
       </c>
@@ -1353,10 +1378,10 @@
       <c r="F22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="13"/>
+      <c r="G22" s="34"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="35" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1374,12 +1399,12 @@
       <c r="F23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="33">
         <v>46218</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="34"/>
       <c r="B24" s="5" t="s">
         <v>13</v>
       </c>
@@ -1395,10 +1420,10 @@
       <c r="F24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="13"/>
+      <c r="G24" s="34"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="35" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1416,12 +1441,12 @@
       <c r="F25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="33">
         <v>46188</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="5" t="s">
         <v>13</v>
       </c>
@@ -1437,10 +1462,10 @@
       <c r="F26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="13"/>
+      <c r="G26" s="34"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="35" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1458,12 +1483,12 @@
       <c r="F27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="33">
         <v>46321</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="5" t="s">
         <v>13</v>
       </c>
@@ -1479,10 +1504,10 @@
       <c r="F28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="13"/>
+      <c r="G28" s="34"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="35" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1500,12 +1525,12 @@
       <c r="F29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="33">
         <v>46139</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="5" t="s">
         <v>13</v>
       </c>
@@ -1521,10 +1546,10 @@
       <c r="F30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="13"/>
+      <c r="G30" s="34"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="35" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1542,12 +1567,12 @@
       <c r="F31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="33">
         <v>46133</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
+      <c r="A32" s="34"/>
       <c r="B32" s="5" t="s">
         <v>13</v>
       </c>
@@ -1563,10 +1588,10 @@
       <c r="F32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="13"/>
+      <c r="G32" s="34"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="35" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1584,12 +1609,12 @@
       <c r="F33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="33">
         <v>46295</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="5" t="s">
         <v>13</v>
       </c>
@@ -1605,10 +1630,10 @@
       <c r="F34" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="13"/>
+      <c r="G34" s="34"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="35" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1626,12 +1651,12 @@
       <c r="F35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="33">
         <v>45737</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="5" t="s">
         <v>13</v>
       </c>
@@ -1647,10 +1672,10 @@
       <c r="F36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="13"/>
+      <c r="G36" s="34"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="35" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1668,12 +1693,12 @@
       <c r="F37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="33">
         <v>45737</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
+      <c r="A38" s="34"/>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
@@ -1689,7 +1714,7 @@
       <c r="F38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="13"/>
+      <c r="G38" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -1741,73 +1766,78 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S188"/>
+  <dimension ref="A1:U188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="28" customWidth="1"/>
+    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="4" max="6" width="16" customWidth="1"/>
+    <col min="7" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="28" customWidth="1"/>
+    <col min="21" max="21" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-    </row>
-    <row r="4" spans="1:19" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+    </row>
+    <row r="4" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1815,898 +1845,974 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="21" t="s">
+      <c r="U4" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="16">
         <v>0.9</v>
       </c>
-      <c r="D5" s="23">
+      <c r="E5" s="17">
         <v>326786.36</v>
       </c>
-      <c r="E5" s="23">
-        <f>O5</f>
+      <c r="F5" s="17">
+        <f>P5</f>
         <v>130000</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23">
-        <f>D5*0.8</f>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17">
+        <f>E5*0.8</f>
         <v>261429.08799999999</v>
       </c>
-      <c r="H5" s="24">
+      <c r="I5" s="18">
         <v>12</v>
       </c>
-      <c r="I5" s="24"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="23">
+      <c r="J5" s="18"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="17">
         <v>5198</v>
       </c>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23">
-        <v>0</v>
-      </c>
-      <c r="N5" s="21" t="s">
+      <c r="M5" s="17"/>
+      <c r="N5" s="17">
+        <v>0</v>
+      </c>
+      <c r="O5" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="25">
+      <c r="P5" s="19">
         <v>130000</v>
       </c>
-      <c r="P5" s="26">
+      <c r="Q5" s="20">
         <f>'[1]Master Schedule'!C5</f>
         <v>46084</v>
       </c>
-      <c r="Q5" s="26">
+      <c r="R5" s="20">
         <v>46106</v>
       </c>
-      <c r="R5" s="21"/>
-      <c r="S5" s="33" t="s">
+      <c r="S5" s="15"/>
+      <c r="T5" s="27" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="21" t="s">
+      <c r="U5" s="27"/>
+    </row>
+    <row r="6" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="22">
-        <v>0</v>
-      </c>
-      <c r="D6" s="23">
+      <c r="C6" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="16">
+        <v>0</v>
+      </c>
+      <c r="E6" s="17">
         <v>409599.64</v>
       </c>
-      <c r="E6" s="23">
-        <f>O6*0.3</f>
+      <c r="F6" s="17">
+        <f>P6*0.3</f>
         <v>41833.799999999996</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23">
-        <f t="shared" ref="G6:G14" si="0">D6*0.4</f>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17">
+        <f t="shared" ref="H6:H14" si="0">E6*0.4</f>
         <v>163839.85600000003</v>
       </c>
-      <c r="H6" s="24">
-        <v>0</v>
-      </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="23">
+      <c r="I6" s="18">
+        <v>0</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="17">
         <v>6972.5</v>
       </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23">
-        <v>0</v>
-      </c>
-      <c r="N6" s="21" t="s">
+      <c r="M6" s="17"/>
+      <c r="N6" s="17">
+        <v>0</v>
+      </c>
+      <c r="O6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="O6" s="25">
+      <c r="P6" s="19">
         <v>139446</v>
       </c>
-      <c r="P6" s="26">
+      <c r="Q6" s="20">
         <f>'[1]Master Schedule'!C6</f>
         <v>46189</v>
       </c>
-      <c r="Q6" s="26">
+      <c r="R6" s="20">
         <v>46264</v>
       </c>
-      <c r="R6" s="21"/>
-      <c r="S6" s="33" t="s">
+      <c r="S6" s="15"/>
+      <c r="T6" s="27" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="21" t="s">
+      <c r="U6" s="27"/>
+    </row>
+    <row r="7" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="16">
         <v>0.9</v>
       </c>
-      <c r="D7" s="23">
+      <c r="E7" s="17">
         <v>576317.9</v>
       </c>
-      <c r="E7" s="23">
-        <f t="shared" ref="E7:E18" si="1">O7</f>
+      <c r="F7" s="17">
+        <f t="shared" ref="F7:F18" si="1">P7</f>
         <v>280000</v>
       </c>
-      <c r="F7" s="23">
+      <c r="G7" s="17">
         <v>603</v>
       </c>
-      <c r="G7" s="23">
-        <f>D7*0.9</f>
+      <c r="H7" s="17">
+        <f>E7*0.9</f>
         <v>518686.11000000004</v>
       </c>
-      <c r="H7" s="24">
+      <c r="I7" s="18">
         <v>20</v>
       </c>
-      <c r="I7" s="24"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="23">
+      <c r="J7" s="18"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="17">
         <v>12045</v>
       </c>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23">
-        <v>0</v>
-      </c>
-      <c r="N7" s="21" t="s">
+      <c r="M7" s="17"/>
+      <c r="N7" s="17">
+        <v>0</v>
+      </c>
+      <c r="O7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="25">
+      <c r="P7" s="19">
         <v>280000</v>
       </c>
-      <c r="P7" s="26">
+      <c r="Q7" s="20">
         <f>'[1]Master Schedule'!C7</f>
         <v>46219</v>
       </c>
-      <c r="Q7" s="26">
+      <c r="R7" s="20">
         <v>46102</v>
       </c>
-      <c r="R7" s="21"/>
-      <c r="S7" s="33" t="s">
+      <c r="S7" s="15"/>
+      <c r="T7" s="27" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="21" t="s">
+      <c r="U7" s="27"/>
+    </row>
+    <row r="8" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="16">
         <v>1</v>
       </c>
-      <c r="D8" s="23">
+      <c r="E8" s="17">
         <v>322961.08</v>
       </c>
-      <c r="E8" s="23">
+      <c r="F8" s="17">
         <f t="shared" si="1"/>
         <v>89000</v>
       </c>
-      <c r="F8" s="23">
+      <c r="G8" s="17">
         <v>715</v>
       </c>
-      <c r="G8" s="23">
-        <f>D8*1</f>
+      <c r="H8" s="17">
+        <f>E8*1</f>
         <v>322961.08</v>
       </c>
-      <c r="H8" s="24">
+      <c r="I8" s="18">
         <v>7</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="23">
+      <c r="J8" s="18"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="17">
         <v>24166</v>
       </c>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23">
+      <c r="M8" s="17"/>
+      <c r="N8" s="17">
         <v>1444</v>
       </c>
-      <c r="N8" s="21" t="s">
+      <c r="O8" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="O8" s="25">
+      <c r="P8" s="19">
         <v>89000</v>
       </c>
-      <c r="P8" s="26">
+      <c r="Q8" s="20">
         <f>'[1]Master Schedule'!C8</f>
         <v>46244</v>
       </c>
-      <c r="Q8" s="26">
+      <c r="R8" s="20">
         <v>46171</v>
       </c>
-      <c r="R8" s="21"/>
-      <c r="S8" s="33"/>
-    </row>
-    <row r="9" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="21" t="s">
+      <c r="S8" s="15"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+    </row>
+    <row r="9" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="22">
-        <v>0</v>
-      </c>
-      <c r="D9" s="23">
+      <c r="C9" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="16">
+        <v>0</v>
+      </c>
+      <c r="E9" s="17">
         <v>630619.19999999995</v>
       </c>
-      <c r="E9" s="23" t="str">
+      <c r="F9" s="17" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23">
-        <f>D9*0.4</f>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17">
+        <f>E9*0.4</f>
         <v>252247.67999999999</v>
       </c>
-      <c r="H9" s="24">
-        <v>0</v>
-      </c>
-      <c r="I9" s="24"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23">
-        <v>0</v>
-      </c>
-      <c r="N9" s="21"/>
-      <c r="O9" s="25" t="s">
+      <c r="I9" s="18">
+        <v>0</v>
+      </c>
+      <c r="J9" s="18"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17">
+        <v>0</v>
+      </c>
+      <c r="O9" s="15"/>
+      <c r="P9" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="P9" s="26">
+      <c r="Q9" s="20">
         <v>46388</v>
       </c>
-      <c r="Q9" s="26">
+      <c r="R9" s="20">
         <v>46447</v>
       </c>
-      <c r="R9" s="21"/>
-      <c r="S9" s="33"/>
-    </row>
-    <row r="10" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="16" t="s">
+      <c r="S9" s="15"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+    </row>
+    <row r="10" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="16">
         <v>1</v>
       </c>
-      <c r="D10" s="23">
+      <c r="E10" s="17">
         <v>338450.2</v>
       </c>
-      <c r="E10" s="23">
-        <f>O10*0.8</f>
+      <c r="F10" s="17">
+        <f>P10*0.8</f>
         <v>110400</v>
       </c>
-      <c r="F10" s="23">
+      <c r="G10" s="17">
         <v>370</v>
       </c>
-      <c r="G10" s="23">
-        <f>D10*1</f>
+      <c r="H10" s="17">
+        <f>E10*1</f>
         <v>338450.2</v>
       </c>
-      <c r="H10" s="24">
+      <c r="I10" s="18">
         <v>12</v>
       </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="23">
+      <c r="J10" s="18"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="17">
         <v>5783</v>
       </c>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23">
+      <c r="M10" s="17"/>
+      <c r="N10" s="17">
         <v>787</v>
       </c>
-      <c r="N10" s="21" t="s">
+      <c r="O10" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="25">
+      <c r="P10" s="19">
         <v>138000</v>
       </c>
-      <c r="P10" s="26">
+      <c r="Q10" s="20">
         <f>'[1]Master Schedule'!C10</f>
         <v>46168</v>
       </c>
-      <c r="Q10" s="26">
+      <c r="R10" s="20">
         <v>46199</v>
       </c>
-      <c r="R10" s="21"/>
-      <c r="S10" s="34"/>
-    </row>
-    <row r="11" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="16" t="s">
+      <c r="S10" s="15"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="27"/>
+    </row>
+    <row r="11" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="16">
         <v>0.7</v>
       </c>
-      <c r="D11" s="23">
+      <c r="E11" s="17">
         <v>1156111.18</v>
       </c>
-      <c r="E11" s="23">
-        <f>O11*0.3</f>
+      <c r="F11" s="17">
+        <f>P11*0.3</f>
         <v>84000</v>
       </c>
-      <c r="F11" s="23">
+      <c r="G11" s="17">
         <v>840</v>
       </c>
-      <c r="G11" s="23">
+      <c r="H11" s="17">
         <f t="shared" si="0"/>
         <v>462444.47200000001</v>
       </c>
-      <c r="H11" s="24">
+      <c r="I11" s="18">
         <v>10</v>
       </c>
-      <c r="I11" s="24"/>
-      <c r="K11" s="23">
+      <c r="J11" s="18"/>
+      <c r="L11" s="17">
         <v>26094</v>
       </c>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23">
+      <c r="M11" s="17"/>
+      <c r="N11" s="17">
         <v>46175</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="O11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="O11" s="25">
+      <c r="P11" s="19">
         <v>280000</v>
       </c>
-      <c r="P11" s="26">
+      <c r="Q11" s="20">
         <f>'[1]Master Schedule'!C11</f>
         <v>46184</v>
       </c>
-      <c r="Q11" s="26">
+      <c r="R11" s="20">
         <v>46305</v>
       </c>
-      <c r="R11" s="21"/>
-      <c r="S11" s="34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="16" t="s">
+      <c r="S11" s="15"/>
+      <c r="T11" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="U11" s="27"/>
+    </row>
+    <row r="12" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="22">
-        <v>0</v>
-      </c>
-      <c r="D12" s="23">
+      <c r="C12" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17">
         <v>594114</v>
       </c>
-      <c r="E12" s="23">
-        <f>O12*0</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23">
+      <c r="F12" s="17">
+        <f>P12*0</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17">
         <f t="shared" si="0"/>
         <v>237645.6</v>
       </c>
-      <c r="H12" s="24">
-        <v>0</v>
-      </c>
-      <c r="I12" s="24"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="23">
+      <c r="I12" s="18">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="17">
         <v>20261</v>
       </c>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23">
+      <c r="M12" s="17"/>
+      <c r="N12" s="17">
         <v>20018</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="O12" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="O12" s="25">
+      <c r="P12" s="19">
         <v>233247.9</v>
       </c>
-      <c r="P12" s="26">
+      <c r="Q12" s="20">
         <f>'[1]Master Schedule'!C12</f>
         <v>46200</v>
       </c>
-      <c r="Q12" s="26">
+      <c r="R12" s="20">
         <v>46336</v>
       </c>
-      <c r="R12" s="21"/>
-      <c r="S12" s="34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="16" t="s">
+      <c r="S12" s="15"/>
+      <c r="T12" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="U12" s="27"/>
+    </row>
+    <row r="13" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="22">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
+      <c r="C13" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="16">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
         <v>327102.8</v>
       </c>
-      <c r="E13" s="23">
-        <f>O13*0.3</f>
+      <c r="F13" s="17">
+        <f>P13*0.3</f>
         <v>36000</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23">
+      <c r="G13" s="17"/>
+      <c r="H13" s="17">
         <f t="shared" si="0"/>
         <v>130841.12</v>
       </c>
-      <c r="H13" s="27">
+      <c r="I13" s="21">
         <v>3</v>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="23">
+      <c r="K13" s="15"/>
+      <c r="L13" s="17">
         <v>14327</v>
       </c>
-      <c r="M13" s="16">
+      <c r="N13" s="10">
         <v>4164</v>
       </c>
-      <c r="N13" s="21" t="s">
+      <c r="O13" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="O13" s="17">
+      <c r="P13" s="11">
         <v>120000</v>
       </c>
-      <c r="P13" s="26">
+      <c r="Q13" s="20">
         <f>'[1]Master Schedule'!C13</f>
         <v>46392</v>
       </c>
-      <c r="Q13" s="18">
+      <c r="R13" s="12">
         <v>46336</v>
       </c>
-      <c r="S13" s="33" t="s">
+      <c r="T13" s="27" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="16" t="s">
+      <c r="U13" s="27"/>
+    </row>
+    <row r="14" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="22">
         <v>0.6</v>
       </c>
-      <c r="D14" s="23">
+      <c r="E14" s="17">
         <v>1707089</v>
       </c>
-      <c r="E14" s="23">
-        <f>O14*0.3</f>
+      <c r="F14" s="17">
+        <f>P14*0.3</f>
         <v>197003.709</v>
       </c>
-      <c r="F14" s="23">
+      <c r="G14" s="17">
         <v>215</v>
       </c>
-      <c r="G14" s="23">
+      <c r="H14" s="17">
         <f t="shared" si="0"/>
         <v>682835.60000000009</v>
       </c>
-      <c r="H14" s="27">
+      <c r="I14" s="21">
         <v>10</v>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="23">
+      <c r="K14" s="15"/>
+      <c r="L14" s="17">
         <v>54190</v>
       </c>
-      <c r="M14" s="16">
+      <c r="N14" s="10">
         <v>20695.969999999972</v>
       </c>
-      <c r="N14" s="16" t="s">
+      <c r="O14" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="O14" s="17">
+      <c r="P14" s="11">
         <v>656679.03</v>
       </c>
-      <c r="P14" s="26">
+      <c r="Q14" s="20">
         <f>'[1]Master Schedule'!C14</f>
         <v>46042</v>
       </c>
-      <c r="Q14" s="18">
+      <c r="R14" s="12">
         <v>46218</v>
       </c>
-      <c r="S14" s="34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="16" t="s">
+      <c r="T14" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="U14" s="36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="16">
         <v>1</v>
       </c>
-      <c r="D15" s="23">
+      <c r="E15" s="17">
         <v>80000</v>
       </c>
-      <c r="E15" s="23">
-        <f>O15</f>
+      <c r="F15" s="17">
+        <f>P15</f>
         <v>40000</v>
       </c>
-      <c r="F15" s="23">
+      <c r="G15" s="17">
         <v>489</v>
       </c>
-      <c r="G15" s="23">
-        <f>D15*1</f>
+      <c r="H15" s="17">
+        <f>E15*1</f>
         <v>80000</v>
       </c>
-      <c r="H15" s="27">
+      <c r="I15" s="21">
         <v>4</v>
       </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="23">
-        <v>0</v>
-      </c>
-      <c r="M15" s="16">
-        <v>0</v>
-      </c>
-      <c r="N15" s="16" t="s">
+      <c r="K15" s="15"/>
+      <c r="L15" s="17">
+        <v>0</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="O15" s="17">
+      <c r="P15" s="11">
         <v>40000</v>
       </c>
-      <c r="P15" s="26">
+      <c r="Q15" s="20">
         <f>'[1]Master Schedule'!C15</f>
         <v>46168</v>
       </c>
-      <c r="Q15" s="18">
+      <c r="R15" s="12">
         <v>46188</v>
       </c>
-      <c r="S15" s="35"/>
-    </row>
-    <row r="16" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="16" t="s">
+      <c r="T15" s="29"/>
+      <c r="U15" s="27"/>
+    </row>
+    <row r="16" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="22">
-        <v>0</v>
-      </c>
-      <c r="D16" s="23">
+      <c r="C16" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="16">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
         <v>1199960.02</v>
       </c>
-      <c r="E16" s="23">
-        <f>O16*0</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23">
-        <f>D16*0.4</f>
+      <c r="F16" s="17">
+        <f>P16*0</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17">
+        <f>E16*0.4</f>
         <v>479984.00800000003</v>
       </c>
-      <c r="H16" s="27">
-        <v>0</v>
-      </c>
-      <c r="K16" s="23">
+      <c r="I16" s="21">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
         <v>27535</v>
       </c>
-      <c r="M16" s="16">
+      <c r="N16" s="10">
         <v>34414</v>
       </c>
-      <c r="N16" s="16" t="s">
+      <c r="O16" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="O16" s="17">
+      <c r="P16" s="11">
         <v>430000</v>
       </c>
-      <c r="P16" s="26">
+      <c r="Q16" s="20">
         <f>'[1]Master Schedule'!C16</f>
         <v>46198</v>
       </c>
-      <c r="Q16" s="18">
+      <c r="R16" s="12">
         <v>46321</v>
       </c>
-      <c r="S16" s="33" t="s">
+      <c r="T16" s="27" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="16" t="s">
+      <c r="U16" s="27"/>
+    </row>
+    <row r="17" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="16">
         <v>1</v>
       </c>
-      <c r="D17" s="23">
+      <c r="E17" s="17">
         <v>600000</v>
       </c>
-      <c r="E17" s="23">
-        <f>O17</f>
+      <c r="F17" s="17">
+        <f>P17</f>
         <v>234861</v>
       </c>
-      <c r="F17" s="23">
+      <c r="G17" s="17">
         <v>735</v>
       </c>
-      <c r="G17" s="23">
-        <f>D17*1</f>
+      <c r="H17" s="17">
+        <f>E17*1</f>
         <v>600000</v>
       </c>
-      <c r="H17" s="29">
+      <c r="I17" s="23">
         <v>10</v>
       </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="23">
+      <c r="K17" s="15"/>
+      <c r="L17" s="17">
         <v>10000</v>
       </c>
-      <c r="M17" s="16">
-        <v>0</v>
-      </c>
-      <c r="N17" s="16" t="s">
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="O17" s="17">
+      <c r="P17" s="11">
         <v>234861</v>
       </c>
-      <c r="P17" s="26">
+      <c r="Q17" s="20">
         <f>'[1]Master Schedule'!C17</f>
         <v>46188</v>
       </c>
-      <c r="Q17" s="18">
+      <c r="R17" s="12">
         <v>46139</v>
       </c>
-      <c r="S17" s="35"/>
-    </row>
-    <row r="18" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="16" t="s">
+      <c r="T17" s="29"/>
+      <c r="U17" s="27"/>
+    </row>
+    <row r="18" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="16">
         <v>1</v>
       </c>
-      <c r="D18" s="23">
+      <c r="E18" s="17">
         <v>317648</v>
       </c>
-      <c r="E18" s="23">
+      <c r="F18" s="17">
         <f t="shared" si="1"/>
         <v>119980</v>
       </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23">
-        <f>D18*1</f>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17">
+        <f>E18*1</f>
         <v>317648</v>
       </c>
-      <c r="H18" s="29">
+      <c r="I18" s="23">
         <v>10</v>
       </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="23">
+      <c r="K18" s="15"/>
+      <c r="L18" s="17">
         <v>8760</v>
       </c>
-      <c r="M18" s="16">
-        <v>0</v>
-      </c>
-      <c r="N18" s="21" t="s">
+      <c r="N18" s="10">
+        <v>0</v>
+      </c>
+      <c r="O18" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="O18" s="17">
+      <c r="P18" s="11">
         <v>119980</v>
       </c>
-      <c r="P18" s="26">
+      <c r="Q18" s="20">
         <f>'[1]Master Schedule'!C18</f>
         <v>46200</v>
       </c>
-      <c r="Q18" s="18">
+      <c r="R18" s="12">
         <v>46133</v>
       </c>
-      <c r="S18" s="35"/>
-    </row>
-    <row r="19" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="16" t="s">
+      <c r="T18" s="29"/>
+      <c r="U18" s="27"/>
+    </row>
+    <row r="19" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="22">
-        <v>0</v>
-      </c>
-      <c r="D19" s="23">
+      <c r="C19" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="16">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17">
         <v>832813</v>
       </c>
-      <c r="E19" s="23">
-        <f>O19*0.3</f>
+      <c r="F19" s="17">
+        <f>P19*0.3</f>
         <v>84000</v>
       </c>
-      <c r="F19" s="23">
+      <c r="G19" s="17">
         <v>630</v>
       </c>
-      <c r="G19" s="23">
+      <c r="H19" s="17">
         <f>455555</f>
         <v>455555</v>
       </c>
-      <c r="H19" s="29">
+      <c r="I19" s="23">
         <v>3</v>
       </c>
-      <c r="J19" s="21"/>
-      <c r="K19" s="23">
+      <c r="K19" s="15"/>
+      <c r="L19" s="17">
         <v>35070</v>
       </c>
-      <c r="M19" s="16">
+      <c r="N19" s="10">
         <v>7702</v>
       </c>
-      <c r="N19" s="21" t="s">
+      <c r="O19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="O19" s="17">
+      <c r="P19" s="11">
         <v>280000</v>
       </c>
-      <c r="P19" s="26">
+      <c r="Q19" s="20">
         <f>'Master Schedule'!C33</f>
         <v>46091</v>
       </c>
-      <c r="Q19" s="18">
+      <c r="R19" s="12">
         <v>46295</v>
       </c>
-      <c r="S19" s="34" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="16" t="s">
+      <c r="T19" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="U19" s="27"/>
+    </row>
+    <row r="20" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="16">
         <v>0.9</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="16">
+      <c r="E20" s="25"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="10">
         <v>255</v>
       </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="16">
+      <c r="H20" s="13"/>
+      <c r="I20" s="10">
         <v>3</v>
       </c>
-      <c r="K20" s="16">
-        <v>0</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17"/>
-      <c r="P20" s="26">
+      <c r="L20" s="10">
+        <v>0</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0</v>
+      </c>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="20">
         <v>45717</v>
       </c>
-      <c r="Q20" s="26">
+      <c r="R20" s="20">
         <v>45737</v>
       </c>
-      <c r="S20" s="34" t="s">
+      <c r="T20" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="U20" s="27"/>
+    </row>
+    <row r="21" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="F21" s="26"/>
+      <c r="I21" s="10">
+        <v>6</v>
+      </c>
+      <c r="L21" s="10">
+        <v>0</v>
+      </c>
+      <c r="N21" s="10">
+        <v>0</v>
+      </c>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="20">
+        <v>45717</v>
+      </c>
+      <c r="R21" s="20">
+        <v>45737</v>
+      </c>
+      <c r="T21" s="28" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" s="16" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="22">
-        <v>0.9</v>
-      </c>
-      <c r="E21" s="32"/>
-      <c r="H21" s="16">
-        <v>6</v>
-      </c>
-      <c r="K21" s="16">
-        <v>0</v>
-      </c>
-      <c r="M21" s="16">
-        <v>0</v>
-      </c>
-      <c r="O21" s="17"/>
-      <c r="P21" s="26">
-        <v>45717</v>
-      </c>
-      <c r="Q21" s="26">
-        <v>45737</v>
-      </c>
-      <c r="S21" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:19" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="33" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="34" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="35" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="36" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="37" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="38" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="39" s="20" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+      <c r="U21" s="27"/>
+    </row>
+    <row r="22" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="33" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="34" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="35" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="36" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="37" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="38" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="39" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
     <row r="40" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
     <row r="41" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
     <row r="42" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
@@ -2858,255 +2964,297 @@
     <row r="188" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="B5:B39" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C200" xr:uid="{362D2387-52AE-4045-809E-2C75EB9CCBFB}">
+      <formula1>"Internal,External"</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="U14" r:id="rId1" xr:uid="{D16A580D-0F23-4F6F-8F5B-CB904485C44F}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B2" s="32"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+    </row>
+    <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="8"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="6"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="6"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>46185</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>46189</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>46183</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>46185</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="8">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="8">
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>46190</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="8">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>46190</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="8">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>46192</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="8">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>46197</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="8">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>46198</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>46202</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>46205</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>46206</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>46209</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>46216</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="3"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="3"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="4"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="3"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="3"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="4"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3855FAE-453D-49B5-A4C9-C937F825A970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7CDBA4-7A0D-4755-B1E6-DDB997BA83E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
     <sheet name="Summary Report" sheetId="2" r:id="rId2"/>
     <sheet name="Site Visit Log" sheetId="3" r:id="rId3"/>
+    <sheet name="Internal Work" sheetId="4" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="88">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -266,6 +267,45 @@
   </si>
   <si>
     <t>https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQB_OM8tpcqzSYSvJ6iVtRP4AfoT3xxyU-FbYl9w1ZSicrI?e=Z2SvXD</t>
+  </si>
+  <si>
+    <t>Actual Start Date</t>
+  </si>
+  <si>
+    <t>Actual End Date</t>
+  </si>
+  <si>
+    <t>Actual Delivery Date</t>
+  </si>
+  <si>
+    <t>BD Data Received Date</t>
+  </si>
+  <si>
+    <t>INTERNAL WORK</t>
+  </si>
+  <si>
+    <t>Optional sheet — one row = one internal (non-project) work item or initiative.</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>ปรับปรุงระบบ CRM</t>
+  </si>
+  <si>
+    <t>อัปเดตฟอร์มบันทึกข้อมูลลูกค้าให้รองรับโครงการ Internal</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>จัดอบรมทีมช่าง</t>
+  </si>
+  <si>
+    <t>อบรมมาตรฐานความปลอดภัยหน้างานประจำไตรมาส</t>
   </si>
 </sst>
 </file>
@@ -434,7 +474,7 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -521,19 +561,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -924,43 +965,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="5" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="18.77734375" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-    </row>
-    <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+    </row>
+    <row r="4" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -974,20 +1023,29 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -999,19 +1057,22 @@
       <c r="D5" s="6">
         <v>46127</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="33">
+      <c r="I5" s="36">
         <v>46213</v>
       </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="34"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
@@ -1021,17 +1082,20 @@
       <c r="D6" s="6">
         <v>46189</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="34"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="I6" s="35"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="34" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1043,19 +1107,22 @@
       <c r="D7" s="6">
         <v>46233</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7">
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="I7" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="35"/>
       <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
@@ -1065,17 +1132,20 @@
       <c r="D8" s="6">
         <v>46247</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7">
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+      <c r="I8" s="35"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1087,19 +1157,22 @@
       <c r="D9" s="6">
         <v>46096</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="33">
+      <c r="I9" s="36">
         <v>46218</v>
       </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="35"/>
       <c r="B10" s="5" t="s">
         <v>13</v>
       </c>
@@ -1109,17 +1182,20 @@
       <c r="D10" s="6">
         <v>46213</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
+      <c r="I10" s="35"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="34" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1131,19 +1207,22 @@
       <c r="D11" s="6">
         <v>46191</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7">
         <v>1</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="33">
+      <c r="I11" s="36">
         <v>46171</v>
       </c>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="35"/>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1153,17 +1232,20 @@
       <c r="D12" s="6">
         <v>46202</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
+      <c r="I12" s="35"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1175,19 +1257,22 @@
       <c r="D13" s="6">
         <v>46402</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7">
         <v>0</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="I13" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="34"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="35"/>
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1197,17 +1282,20 @@
       <c r="D14" s="6">
         <v>46042</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7">
         <v>0</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="35" t="s">
+      <c r="I14" s="35"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="34" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1219,19 +1307,22 @@
       <c r="D15" s="6">
         <v>46188</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7">
         <v>1</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="33">
+      <c r="I15" s="36">
         <v>46199</v>
       </c>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="34"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="35"/>
       <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
@@ -1241,17 +1332,20 @@
       <c r="D16" s="6">
         <v>46199</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7">
         <v>1</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="35" t="s">
+      <c r="I16" s="35"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="34" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1263,19 +1357,22 @@
       <c r="D17" s="6">
         <v>46198</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7">
         <v>0.8</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="33">
+      <c r="I17" s="36">
         <v>46305</v>
       </c>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="34"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="35"/>
       <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
@@ -1285,17 +1382,20 @@
       <c r="D18" s="6">
         <v>46298</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7">
         <v>0.4</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="35" t="s">
+      <c r="I18" s="35"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="34" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1307,19 +1407,22 @@
       <c r="D19" s="6">
         <v>46290</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7">
         <v>0</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="33">
+      <c r="I19" s="36">
         <v>46336</v>
       </c>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="34"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="35"/>
       <c r="B20" s="5" t="s">
         <v>13</v>
       </c>
@@ -1329,17 +1432,20 @@
       <c r="D20" s="6">
         <v>46329</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7">
         <v>0</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="35" t="s">
+      <c r="I20" s="35"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1351,18 +1457,21 @@
       <c r="D21" s="6">
         <v>46249</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="7">
         <v>0</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="33">
+      <c r="I21" s="36">
         <v>46336</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="34"/>
+      <c r="J21" s="36"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="35"/>
       <c r="B22" s="5" t="s">
         <v>13</v>
       </c>
@@ -1372,16 +1481,19 @@
       <c r="D22" s="6">
         <v>46329</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="7">
         <v>0</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="34"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="35" t="s">
+      <c r="I22" s="35"/>
+      <c r="J22" s="36"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="34" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1393,18 +1505,21 @@
       <c r="D23" s="6">
         <v>46206</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="7">
         <v>0.7</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="33">
+      <c r="I23" s="36">
         <v>46218</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="34"/>
+      <c r="J23" s="36"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="35"/>
       <c r="B24" s="5" t="s">
         <v>13</v>
       </c>
@@ -1414,16 +1529,19 @@
       <c r="D24" s="6">
         <v>46211</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="7">
         <v>0</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="34"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="35" t="s">
+      <c r="I24" s="35"/>
+      <c r="J24" s="36"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="34" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1435,18 +1553,21 @@
       <c r="D25" s="6">
         <v>46188</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="7">
         <v>1</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="33">
+      <c r="I25" s="36">
         <v>46188</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="34"/>
+      <c r="J25" s="36"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="35"/>
       <c r="B26" s="5" t="s">
         <v>13</v>
       </c>
@@ -1456,16 +1577,19 @@
       <c r="D26" s="6">
         <v>46188</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="7">
         <v>1</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="34"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="35" t="s">
+      <c r="I26" s="35"/>
+      <c r="J26" s="36"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="34" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1477,18 +1601,21 @@
       <c r="D27" s="6">
         <v>46247</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="7">
         <v>0</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="33">
+      <c r="I27" s="36">
         <v>46321</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="34"/>
+      <c r="J27" s="36"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="35"/>
       <c r="B28" s="5" t="s">
         <v>13</v>
       </c>
@@ -1498,16 +1625,19 @@
       <c r="D28" s="6">
         <v>46316</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="7">
         <v>0</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="34"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="35" t="s">
+      <c r="I28" s="35"/>
+      <c r="J28" s="36"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="34" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1519,18 +1649,21 @@
       <c r="D29" s="6">
         <v>46100</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="7">
         <v>1</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="33">
+      <c r="I29" s="36">
         <v>46139</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="34"/>
+      <c r="J29" s="36"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="35"/>
       <c r="B30" s="5" t="s">
         <v>13</v>
       </c>
@@ -1540,16 +1673,19 @@
       <c r="D30" s="6">
         <v>46124</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="7">
         <v>1</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="34"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="35" t="s">
+      <c r="I30" s="35"/>
+      <c r="J30" s="36"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="34" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1561,18 +1697,21 @@
       <c r="D31" s="6">
         <v>46094</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="7">
         <v>1</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="33">
+      <c r="I31" s="36">
         <v>46133</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="34"/>
+      <c r="J31" s="36"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="35"/>
       <c r="B32" s="5" t="s">
         <v>13</v>
       </c>
@@ -1582,16 +1721,19 @@
       <c r="D32" s="6">
         <v>46094</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="7">
         <v>1</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="H32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="34"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="35" t="s">
+      <c r="I32" s="35"/>
+      <c r="J32" s="36"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="34" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1603,18 +1745,21 @@
       <c r="D33" s="6">
         <v>46094</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="7">
         <v>0</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="33">
+      <c r="I33" s="36">
         <v>46295</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="34"/>
+      <c r="J33" s="36"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="35"/>
       <c r="B34" s="5" t="s">
         <v>13</v>
       </c>
@@ -1624,16 +1769,19 @@
       <c r="D34" s="6">
         <v>46094</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="7">
         <v>0</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="H34" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="34"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="35" t="s">
+      <c r="I34" s="35"/>
+      <c r="J34" s="36"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="34" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1645,18 +1793,21 @@
       <c r="D35" s="6">
         <v>45729</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="7">
         <v>1</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="H35" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="33">
+      <c r="I35" s="36">
         <v>45737</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="34"/>
+      <c r="J35" s="36"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="35"/>
       <c r="B36" s="5" t="s">
         <v>13</v>
       </c>
@@ -1666,16 +1817,19 @@
       <c r="D36" s="6">
         <v>45732</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="7">
         <v>0.9</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="H36" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="34"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="35" t="s">
+      <c r="I36" s="35"/>
+      <c r="J36" s="36"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="34" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1687,18 +1841,21 @@
       <c r="D37" s="6">
         <v>45729</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="7">
         <v>1</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="H37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="33">
+      <c r="I37" s="36">
         <v>45737</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="34"/>
+      <c r="J37" s="36"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="35"/>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
@@ -1708,55 +1865,75 @@
       <c r="D38" s="6">
         <v>45732</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="7">
         <v>0.9</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G38" s="34"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="53">
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
     <mergeCell ref="A37:A38"/>
-    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="I37:I38"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="I23:I24"/>
     <mergeCell ref="A31:A32"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="I31:I32"/>
     <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="I25:I26"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="I27:I28"/>
     <mergeCell ref="A29:A30"/>
-    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="I33:I34"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="I21:I22"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="F5:F48" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1766,7 +1943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U188"/>
+  <dimension ref="A1:V188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
@@ -1784,60 +1961,63 @@
     <col min="17" max="18" width="13" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="28" customWidth="1"/>
-    <col min="21" max="21" width="34.77734375" customWidth="1"/>
+    <col min="21" max="21" width="99.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-    </row>
-    <row r="4" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+    </row>
+    <row r="4" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1901,8 +2081,11 @@
       <c r="U4" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V4" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
@@ -1957,8 +2140,9 @@
         <v>50</v>
       </c>
       <c r="U5" s="27"/>
-    </row>
-    <row r="6" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V5" s="20"/>
+    </row>
+    <row r="6" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="15" t="s">
         <v>14</v>
       </c>
@@ -2013,8 +2197,9 @@
         <v>51</v>
       </c>
       <c r="U6" s="27"/>
-    </row>
-    <row r="7" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V6" s="20"/>
+    </row>
+    <row r="7" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="15" t="s">
         <v>17</v>
       </c>
@@ -2071,8 +2256,9 @@
         <v>52</v>
       </c>
       <c r="U7" s="27"/>
-    </row>
-    <row r="8" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V7" s="20"/>
+    </row>
+    <row r="8" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
@@ -2127,8 +2313,11 @@
       <c r="S8" s="15"/>
       <c r="T8" s="27"/>
       <c r="U8" s="27"/>
-    </row>
-    <row r="9" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V8" s="20">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="15" t="s">
         <v>19</v>
       </c>
@@ -2176,8 +2365,9 @@
       <c r="S9" s="15"/>
       <c r="T9" s="27"/>
       <c r="U9" s="27"/>
-    </row>
-    <row r="10" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V9" s="20"/>
+    </row>
+    <row r="10" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10" t="s">
         <v>20</v>
       </c>
@@ -2232,8 +2422,11 @@
       <c r="S10" s="15"/>
       <c r="T10" s="28"/>
       <c r="U10" s="27"/>
-    </row>
-    <row r="11" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V10" s="20">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -2289,8 +2482,11 @@
         <v>64</v>
       </c>
       <c r="U11" s="27"/>
-    </row>
-    <row r="12" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V11" s="20">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="10" t="s">
         <v>23</v>
       </c>
@@ -2345,8 +2541,11 @@
         <v>66</v>
       </c>
       <c r="U12" s="27"/>
-    </row>
-    <row r="13" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V12" s="20">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
@@ -2398,8 +2597,11 @@
         <v>51</v>
       </c>
       <c r="U13" s="27"/>
-    </row>
-    <row r="14" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V13" s="20">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
@@ -2452,11 +2654,14 @@
       <c r="T14" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="U14" s="36" t="s">
+      <c r="U14" s="30" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V14" s="20">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="10" t="s">
         <v>26</v>
       </c>
@@ -2508,8 +2713,11 @@
       </c>
       <c r="T15" s="29"/>
       <c r="U15" s="27"/>
-    </row>
-    <row r="16" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V15" s="20">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="10" t="s">
         <v>27</v>
       </c>
@@ -2560,8 +2768,11 @@
         <v>51</v>
       </c>
       <c r="U16" s="27"/>
-    </row>
-    <row r="17" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V16" s="20">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="10" t="s">
         <v>28</v>
       </c>
@@ -2613,8 +2824,11 @@
       </c>
       <c r="T17" s="29"/>
       <c r="U17" s="27"/>
-    </row>
-    <row r="18" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V17" s="20">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="10" t="s">
         <v>29</v>
       </c>
@@ -2664,8 +2878,9 @@
       </c>
       <c r="T18" s="29"/>
       <c r="U18" s="27"/>
-    </row>
-    <row r="19" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V18" s="20"/>
+    </row>
+    <row r="19" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="10" t="s">
         <v>30</v>
       </c>
@@ -2719,8 +2934,9 @@
         <v>69</v>
       </c>
       <c r="U19" s="27"/>
-    </row>
-    <row r="20" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V19" s="20"/>
+    </row>
+    <row r="20" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="10" t="s">
         <v>31</v>
       </c>
@@ -2759,8 +2975,9 @@
         <v>67</v>
       </c>
       <c r="U20" s="27"/>
-    </row>
-    <row r="21" spans="1:21" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V20" s="20"/>
+    </row>
+    <row r="21" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="10" t="s">
         <v>32</v>
       </c>
@@ -2794,180 +3011,518 @@
         <v>68</v>
       </c>
       <c r="U21" s="27"/>
-    </row>
-    <row r="22" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:21" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="33" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="34" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="35" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="36" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="37" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="38" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="39" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="40" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="41" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="42" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="43" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="44" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="45" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="46" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="47" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="48" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="49" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="50" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="51" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="52" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="53" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="54" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="55" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="56" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="57" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="58" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="59" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="60" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="61" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="62" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="63" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="64" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="65" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="66" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="67" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="68" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="69" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="70" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="71" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="72" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="73" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="74" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="75" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="76" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="77" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="78" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="79" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="80" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="81" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="82" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="83" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="84" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="85" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="86" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="87" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="88" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="89" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="90" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="91" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="92" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="93" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="94" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="95" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="96" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="97" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="98" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="99" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="100" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="101" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="102" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="103" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="104" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="105" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="106" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="107" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="108" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="109" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="110" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="111" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="112" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="113" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="114" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="115" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="116" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="117" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="118" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="119" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="120" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="121" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="122" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="123" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="124" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="125" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="126" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="127" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="128" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="129" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="130" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="131" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="132" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="133" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="134" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="135" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="136" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="137" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="138" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="139" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="140" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="141" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="142" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="143" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="144" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="145" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="146" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="147" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="148" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="149" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="150" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="151" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="152" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="153" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="154" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="155" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="156" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="157" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="158" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="159" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="160" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="161" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="162" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="163" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="164" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="165" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="166" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="167" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="168" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="169" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="170" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="171" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="172" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="173" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="174" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="175" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="176" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="177" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="178" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="179" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="180" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="181" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="182" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="183" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="184" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="185" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="186" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="187" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="188" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+      <c r="V21" s="20"/>
+    </row>
+    <row r="22" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="G22" s="14">
+        <v>2444</v>
+      </c>
+      <c r="V22" s="20"/>
+    </row>
+    <row r="23" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V23" s="20"/>
+    </row>
+    <row r="24" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V24" s="20"/>
+    </row>
+    <row r="25" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V25" s="20"/>
+    </row>
+    <row r="26" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V26" s="20"/>
+    </row>
+    <row r="27" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V27" s="20"/>
+    </row>
+    <row r="28" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V28" s="20"/>
+    </row>
+    <row r="29" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V29" s="20"/>
+    </row>
+    <row r="30" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V30" s="20"/>
+    </row>
+    <row r="31" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V31" s="20"/>
+    </row>
+    <row r="32" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V32" s="20"/>
+    </row>
+    <row r="33" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V33" s="20"/>
+    </row>
+    <row r="34" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V34" s="20"/>
+    </row>
+    <row r="35" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V35" s="20"/>
+    </row>
+    <row r="36" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V36" s="20"/>
+    </row>
+    <row r="37" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V37" s="20"/>
+    </row>
+    <row r="38" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V38" s="20"/>
+    </row>
+    <row r="39" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V39" s="20"/>
+    </row>
+    <row r="40" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V40" s="20"/>
+    </row>
+    <row r="41" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V41" s="20"/>
+    </row>
+    <row r="42" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V42" s="20"/>
+    </row>
+    <row r="43" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V43" s="20"/>
+    </row>
+    <row r="44" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V44" s="20"/>
+    </row>
+    <row r="45" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V45" s="20"/>
+    </row>
+    <row r="46" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V46" s="20"/>
+    </row>
+    <row r="47" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V47" s="20"/>
+    </row>
+    <row r="48" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V48" s="20"/>
+    </row>
+    <row r="49" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V49" s="20"/>
+    </row>
+    <row r="50" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V50" s="20"/>
+    </row>
+    <row r="51" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V51" s="20"/>
+    </row>
+    <row r="52" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V52" s="20"/>
+    </row>
+    <row r="53" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V53" s="20"/>
+    </row>
+    <row r="54" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V54" s="20"/>
+    </row>
+    <row r="55" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V55" s="20"/>
+    </row>
+    <row r="56" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V56" s="20"/>
+    </row>
+    <row r="57" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V57" s="20"/>
+    </row>
+    <row r="58" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V58" s="20"/>
+    </row>
+    <row r="59" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V59" s="20"/>
+    </row>
+    <row r="60" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V60" s="20"/>
+    </row>
+    <row r="61" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V61" s="20"/>
+    </row>
+    <row r="62" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V62" s="20"/>
+    </row>
+    <row r="63" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V63" s="20"/>
+    </row>
+    <row r="64" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V64" s="20"/>
+    </row>
+    <row r="65" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V65" s="20"/>
+    </row>
+    <row r="66" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V66" s="20"/>
+    </row>
+    <row r="67" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V67" s="20"/>
+    </row>
+    <row r="68" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V68" s="20"/>
+    </row>
+    <row r="69" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V69" s="20"/>
+    </row>
+    <row r="70" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V70" s="20"/>
+    </row>
+    <row r="71" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V71" s="20"/>
+    </row>
+    <row r="72" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V72" s="20"/>
+    </row>
+    <row r="73" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V73" s="20"/>
+    </row>
+    <row r="74" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V74" s="20"/>
+    </row>
+    <row r="75" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V75" s="20"/>
+    </row>
+    <row r="76" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V76" s="20"/>
+    </row>
+    <row r="77" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V77" s="20"/>
+    </row>
+    <row r="78" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V78" s="20"/>
+    </row>
+    <row r="79" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V79" s="20"/>
+    </row>
+    <row r="80" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V80" s="20"/>
+    </row>
+    <row r="81" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V81" s="20"/>
+    </row>
+    <row r="82" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V82" s="20"/>
+    </row>
+    <row r="83" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V83" s="20"/>
+    </row>
+    <row r="84" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V84" s="20"/>
+    </row>
+    <row r="85" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V85" s="20"/>
+    </row>
+    <row r="86" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V86" s="20"/>
+    </row>
+    <row r="87" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V87" s="20"/>
+    </row>
+    <row r="88" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V88" s="20"/>
+    </row>
+    <row r="89" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V89" s="20"/>
+    </row>
+    <row r="90" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V90" s="20"/>
+    </row>
+    <row r="91" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V91" s="20"/>
+    </row>
+    <row r="92" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V92" s="20"/>
+    </row>
+    <row r="93" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V93" s="20"/>
+    </row>
+    <row r="94" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V94" s="20"/>
+    </row>
+    <row r="95" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V95" s="20"/>
+    </row>
+    <row r="96" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V96" s="20"/>
+    </row>
+    <row r="97" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V97" s="20"/>
+    </row>
+    <row r="98" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V98" s="20"/>
+    </row>
+    <row r="99" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V99" s="20"/>
+    </row>
+    <row r="100" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V100" s="20"/>
+    </row>
+    <row r="101" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V101" s="20"/>
+    </row>
+    <row r="102" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V102" s="20"/>
+    </row>
+    <row r="103" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V103" s="20"/>
+    </row>
+    <row r="104" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V104" s="20"/>
+    </row>
+    <row r="105" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V105" s="20"/>
+    </row>
+    <row r="106" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V106" s="20"/>
+    </row>
+    <row r="107" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V107" s="20"/>
+    </row>
+    <row r="108" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V108" s="20"/>
+    </row>
+    <row r="109" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V109" s="20"/>
+    </row>
+    <row r="110" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V110" s="20"/>
+    </row>
+    <row r="111" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V111" s="20"/>
+    </row>
+    <row r="112" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V112" s="20"/>
+    </row>
+    <row r="113" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V113" s="20"/>
+    </row>
+    <row r="114" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V114" s="20"/>
+    </row>
+    <row r="115" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V115" s="20"/>
+    </row>
+    <row r="116" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V116" s="20"/>
+    </row>
+    <row r="117" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V117" s="20"/>
+    </row>
+    <row r="118" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V118" s="20"/>
+    </row>
+    <row r="119" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V119" s="20"/>
+    </row>
+    <row r="120" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V120" s="20"/>
+    </row>
+    <row r="121" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V121" s="20"/>
+    </row>
+    <row r="122" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V122" s="20"/>
+    </row>
+    <row r="123" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V123" s="20"/>
+    </row>
+    <row r="124" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V124" s="20"/>
+    </row>
+    <row r="125" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V125" s="20"/>
+    </row>
+    <row r="126" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V126" s="20"/>
+    </row>
+    <row r="127" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V127" s="20"/>
+    </row>
+    <row r="128" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V128" s="20"/>
+    </row>
+    <row r="129" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V129" s="20"/>
+    </row>
+    <row r="130" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V130" s="20"/>
+    </row>
+    <row r="131" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V131" s="20"/>
+    </row>
+    <row r="132" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V132" s="20"/>
+    </row>
+    <row r="133" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V133" s="20"/>
+    </row>
+    <row r="134" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V134" s="20"/>
+    </row>
+    <row r="135" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V135" s="20"/>
+    </row>
+    <row r="136" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V136" s="20"/>
+    </row>
+    <row r="137" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V137" s="20"/>
+    </row>
+    <row r="138" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V138" s="20"/>
+    </row>
+    <row r="139" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V139" s="20"/>
+    </row>
+    <row r="140" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V140" s="20"/>
+    </row>
+    <row r="141" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V141" s="20"/>
+    </row>
+    <row r="142" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V142" s="20"/>
+    </row>
+    <row r="143" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V143" s="20"/>
+    </row>
+    <row r="144" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V144" s="20"/>
+    </row>
+    <row r="145" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V145" s="20"/>
+    </row>
+    <row r="146" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V146" s="20"/>
+    </row>
+    <row r="147" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V147" s="20"/>
+    </row>
+    <row r="148" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V148" s="20"/>
+    </row>
+    <row r="149" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V149" s="20"/>
+    </row>
+    <row r="150" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V150" s="20"/>
+    </row>
+    <row r="151" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V151" s="20"/>
+    </row>
+    <row r="152" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V152" s="20"/>
+    </row>
+    <row r="153" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V153" s="20"/>
+    </row>
+    <row r="154" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V154" s="20"/>
+    </row>
+    <row r="155" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V155" s="20"/>
+    </row>
+    <row r="156" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V156" s="20"/>
+    </row>
+    <row r="157" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V157" s="20"/>
+    </row>
+    <row r="158" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V158" s="20"/>
+    </row>
+    <row r="159" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V159" s="20"/>
+    </row>
+    <row r="160" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V160" s="20"/>
+    </row>
+    <row r="161" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V161" s="20"/>
+    </row>
+    <row r="162" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V162" s="20"/>
+    </row>
+    <row r="163" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V163" s="20"/>
+    </row>
+    <row r="164" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V164" s="20"/>
+    </row>
+    <row r="165" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V165" s="20"/>
+    </row>
+    <row r="166" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V166" s="20"/>
+    </row>
+    <row r="167" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V167" s="20"/>
+    </row>
+    <row r="168" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V168" s="20"/>
+    </row>
+    <row r="169" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V169" s="20"/>
+    </row>
+    <row r="170" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V170" s="20"/>
+    </row>
+    <row r="171" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V171" s="20"/>
+    </row>
+    <row r="172" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V172" s="20"/>
+    </row>
+    <row r="173" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V173" s="20"/>
+    </row>
+    <row r="174" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V174" s="20"/>
+    </row>
+    <row r="175" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V175" s="20"/>
+    </row>
+    <row r="176" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V176" s="20"/>
+    </row>
+    <row r="177" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V177" s="20"/>
+    </row>
+    <row r="178" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V178" s="20"/>
+    </row>
+    <row r="179" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V179" s="20"/>
+    </row>
+    <row r="180" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V180" s="20"/>
+    </row>
+    <row r="181" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V181" s="20"/>
+    </row>
+    <row r="182" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V182" s="20"/>
+    </row>
+    <row r="183" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V183" s="20"/>
+    </row>
+    <row r="184" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V184" s="20"/>
+    </row>
+    <row r="185" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V185" s="20"/>
+    </row>
+    <row r="186" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V186" s="20"/>
+    </row>
+    <row r="187" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V187" s="20"/>
+    </row>
+    <row r="188" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V188" s="20"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" sqref="B5:B39" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -2994,20 +3549,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
     </row>
     <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3260,29 +3815,921 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CACF7FE-A4AF-4302-B8F5-800998C4C21C}">
+  <dimension ref="A1:E200"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="45.77734375" customWidth="1"/>
+    <col min="3" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="6">
+        <v>46174</v>
+      </c>
+      <c r="D5" s="6">
+        <v>46218</v>
+      </c>
+      <c r="E5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="6">
+        <v>46152</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46154</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C56" s="31"/>
+      <c r="D56" s="31"/>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C62" s="31"/>
+      <c r="D62" s="31"/>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C68" s="31"/>
+      <c r="D68" s="31"/>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C75" s="31"/>
+      <c r="D75" s="31"/>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C76" s="31"/>
+      <c r="D76" s="31"/>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C77" s="31"/>
+      <c r="D77" s="31"/>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C80" s="31"/>
+      <c r="D80" s="31"/>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+    </row>
+    <row r="82" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C82" s="31"/>
+      <c r="D82" s="31"/>
+    </row>
+    <row r="83" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C83" s="31"/>
+      <c r="D83" s="31"/>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C84" s="31"/>
+      <c r="D84" s="31"/>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C85" s="31"/>
+      <c r="D85" s="31"/>
+    </row>
+    <row r="86" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C86" s="31"/>
+      <c r="D86" s="31"/>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C88" s="31"/>
+      <c r="D88" s="31"/>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C89" s="31"/>
+      <c r="D89" s="31"/>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C90" s="31"/>
+      <c r="D90" s="31"/>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C91" s="31"/>
+      <c r="D91" s="31"/>
+    </row>
+    <row r="92" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C92" s="31"/>
+      <c r="D92" s="31"/>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C93" s="31"/>
+      <c r="D93" s="31"/>
+    </row>
+    <row r="94" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C94" s="31"/>
+      <c r="D94" s="31"/>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C95" s="31"/>
+      <c r="D95" s="31"/>
+    </row>
+    <row r="96" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C96" s="31"/>
+      <c r="D96" s="31"/>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C97" s="31"/>
+      <c r="D97" s="31"/>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C98" s="31"/>
+      <c r="D98" s="31"/>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C99" s="31"/>
+      <c r="D99" s="31"/>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C100" s="31"/>
+      <c r="D100" s="31"/>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C101" s="31"/>
+      <c r="D101" s="31"/>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C102" s="31"/>
+      <c r="D102" s="31"/>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C103" s="31"/>
+      <c r="D103" s="31"/>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C104" s="31"/>
+      <c r="D104" s="31"/>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C105" s="31"/>
+      <c r="D105" s="31"/>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C106" s="31"/>
+      <c r="D106" s="31"/>
+    </row>
+    <row r="107" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C107" s="31"/>
+      <c r="D107" s="31"/>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C108" s="31"/>
+      <c r="D108" s="31"/>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C109" s="31"/>
+      <c r="D109" s="31"/>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C110" s="31"/>
+      <c r="D110" s="31"/>
+    </row>
+    <row r="111" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C111" s="31"/>
+      <c r="D111" s="31"/>
+    </row>
+    <row r="112" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C112" s="31"/>
+      <c r="D112" s="31"/>
+    </row>
+    <row r="113" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C113" s="31"/>
+      <c r="D113" s="31"/>
+    </row>
+    <row r="114" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C114" s="31"/>
+      <c r="D114" s="31"/>
+    </row>
+    <row r="115" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C115" s="31"/>
+      <c r="D115" s="31"/>
+    </row>
+    <row r="116" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C116" s="31"/>
+      <c r="D116" s="31"/>
+    </row>
+    <row r="117" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C117" s="31"/>
+      <c r="D117" s="31"/>
+    </row>
+    <row r="118" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C118" s="31"/>
+      <c r="D118" s="31"/>
+    </row>
+    <row r="119" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C119" s="31"/>
+      <c r="D119" s="31"/>
+    </row>
+    <row r="120" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C120" s="31"/>
+      <c r="D120" s="31"/>
+    </row>
+    <row r="121" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C121" s="31"/>
+      <c r="D121" s="31"/>
+    </row>
+    <row r="122" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C122" s="31"/>
+      <c r="D122" s="31"/>
+    </row>
+    <row r="123" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C123" s="31"/>
+      <c r="D123" s="31"/>
+    </row>
+    <row r="124" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C124" s="31"/>
+      <c r="D124" s="31"/>
+    </row>
+    <row r="125" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C125" s="31"/>
+      <c r="D125" s="31"/>
+    </row>
+    <row r="126" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C126" s="31"/>
+      <c r="D126" s="31"/>
+    </row>
+    <row r="127" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C127" s="31"/>
+      <c r="D127" s="31"/>
+    </row>
+    <row r="128" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C128" s="31"/>
+      <c r="D128" s="31"/>
+    </row>
+    <row r="129" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C129" s="31"/>
+      <c r="D129" s="31"/>
+    </row>
+    <row r="130" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C130" s="31"/>
+      <c r="D130" s="31"/>
+    </row>
+    <row r="131" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C131" s="31"/>
+      <c r="D131" s="31"/>
+    </row>
+    <row r="132" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C132" s="31"/>
+      <c r="D132" s="31"/>
+    </row>
+    <row r="133" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C133" s="31"/>
+      <c r="D133" s="31"/>
+    </row>
+    <row r="134" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C134" s="31"/>
+      <c r="D134" s="31"/>
+    </row>
+    <row r="135" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C135" s="31"/>
+      <c r="D135" s="31"/>
+    </row>
+    <row r="136" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C136" s="31"/>
+      <c r="D136" s="31"/>
+    </row>
+    <row r="137" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C137" s="31"/>
+      <c r="D137" s="31"/>
+    </row>
+    <row r="138" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C138" s="31"/>
+      <c r="D138" s="31"/>
+    </row>
+    <row r="139" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C139" s="31"/>
+      <c r="D139" s="31"/>
+    </row>
+    <row r="140" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C140" s="31"/>
+      <c r="D140" s="31"/>
+    </row>
+    <row r="141" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C141" s="31"/>
+      <c r="D141" s="31"/>
+    </row>
+    <row r="142" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C142" s="31"/>
+      <c r="D142" s="31"/>
+    </row>
+    <row r="143" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C143" s="31"/>
+      <c r="D143" s="31"/>
+    </row>
+    <row r="144" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C144" s="31"/>
+      <c r="D144" s="31"/>
+    </row>
+    <row r="145" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C145" s="31"/>
+      <c r="D145" s="31"/>
+    </row>
+    <row r="146" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C146" s="31"/>
+      <c r="D146" s="31"/>
+    </row>
+    <row r="147" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C147" s="31"/>
+      <c r="D147" s="31"/>
+    </row>
+    <row r="148" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C148" s="31"/>
+      <c r="D148" s="31"/>
+    </row>
+    <row r="149" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C149" s="31"/>
+      <c r="D149" s="31"/>
+    </row>
+    <row r="150" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C150" s="31"/>
+      <c r="D150" s="31"/>
+    </row>
+    <row r="151" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C151" s="31"/>
+      <c r="D151" s="31"/>
+    </row>
+    <row r="152" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C152" s="31"/>
+      <c r="D152" s="31"/>
+    </row>
+    <row r="153" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C153" s="31"/>
+      <c r="D153" s="31"/>
+    </row>
+    <row r="154" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C154" s="31"/>
+      <c r="D154" s="31"/>
+    </row>
+    <row r="155" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C155" s="31"/>
+      <c r="D155" s="31"/>
+    </row>
+    <row r="156" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C156" s="31"/>
+      <c r="D156" s="31"/>
+    </row>
+    <row r="157" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C157" s="31"/>
+      <c r="D157" s="31"/>
+    </row>
+    <row r="158" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C158" s="31"/>
+      <c r="D158" s="31"/>
+    </row>
+    <row r="159" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C159" s="31"/>
+      <c r="D159" s="31"/>
+    </row>
+    <row r="160" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C160" s="31"/>
+      <c r="D160" s="31"/>
+    </row>
+    <row r="161" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C161" s="31"/>
+      <c r="D161" s="31"/>
+    </row>
+    <row r="162" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C162" s="31"/>
+      <c r="D162" s="31"/>
+    </row>
+    <row r="163" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C163" s="31"/>
+      <c r="D163" s="31"/>
+    </row>
+    <row r="164" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C164" s="31"/>
+      <c r="D164" s="31"/>
+    </row>
+    <row r="165" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C165" s="31"/>
+      <c r="D165" s="31"/>
+    </row>
+    <row r="166" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C166" s="31"/>
+      <c r="D166" s="31"/>
+    </row>
+    <row r="167" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C167" s="31"/>
+      <c r="D167" s="31"/>
+    </row>
+    <row r="168" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C168" s="31"/>
+      <c r="D168" s="31"/>
+    </row>
+    <row r="169" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C169" s="31"/>
+      <c r="D169" s="31"/>
+    </row>
+    <row r="170" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C170" s="31"/>
+      <c r="D170" s="31"/>
+    </row>
+    <row r="171" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C171" s="31"/>
+      <c r="D171" s="31"/>
+    </row>
+    <row r="172" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C172" s="31"/>
+      <c r="D172" s="31"/>
+    </row>
+    <row r="173" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C173" s="31"/>
+      <c r="D173" s="31"/>
+    </row>
+    <row r="174" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C174" s="31"/>
+      <c r="D174" s="31"/>
+    </row>
+    <row r="175" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C175" s="31"/>
+      <c r="D175" s="31"/>
+    </row>
+    <row r="176" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C176" s="31"/>
+      <c r="D176" s="31"/>
+    </row>
+    <row r="177" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C177" s="31"/>
+      <c r="D177" s="31"/>
+    </row>
+    <row r="178" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C178" s="31"/>
+      <c r="D178" s="31"/>
+    </row>
+    <row r="179" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C179" s="31"/>
+      <c r="D179" s="31"/>
+    </row>
+    <row r="180" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C180" s="31"/>
+      <c r="D180" s="31"/>
+    </row>
+    <row r="181" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C181" s="31"/>
+      <c r="D181" s="31"/>
+    </row>
+    <row r="182" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C182" s="31"/>
+      <c r="D182" s="31"/>
+    </row>
+    <row r="183" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C183" s="31"/>
+      <c r="D183" s="31"/>
+    </row>
+    <row r="184" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C184" s="31"/>
+      <c r="D184" s="31"/>
+    </row>
+    <row r="185" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C185" s="31"/>
+      <c r="D185" s="31"/>
+    </row>
+    <row r="186" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C186" s="31"/>
+      <c r="D186" s="31"/>
+    </row>
+    <row r="187" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C187" s="31"/>
+      <c r="D187" s="31"/>
+    </row>
+    <row r="188" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C188" s="31"/>
+      <c r="D188" s="31"/>
+    </row>
+    <row r="189" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C189" s="31"/>
+      <c r="D189" s="31"/>
+    </row>
+    <row r="190" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C190" s="31"/>
+      <c r="D190" s="31"/>
+    </row>
+    <row r="191" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C191" s="31"/>
+      <c r="D191" s="31"/>
+    </row>
+    <row r="192" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C192" s="31"/>
+      <c r="D192" s="31"/>
+    </row>
+    <row r="193" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C193" s="31"/>
+      <c r="D193" s="31"/>
+    </row>
+    <row r="194" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C194" s="31"/>
+      <c r="D194" s="31"/>
+    </row>
+    <row r="195" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C195" s="31"/>
+      <c r="D195" s="31"/>
+    </row>
+    <row r="196" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C196" s="31"/>
+      <c r="D196" s="31"/>
+    </row>
+    <row r="197" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C197" s="31"/>
+      <c r="D197" s="31"/>
+    </row>
+    <row r="198" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C198" s="31"/>
+      <c r="D198" s="31"/>
+    </row>
+    <row r="199" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C199" s="31"/>
+      <c r="D199" s="31"/>
+    </row>
+    <row r="200" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C200" s="31"/>
+      <c r="D200" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E200" xr:uid="{0ABCEF69-CFAC-437F-9DF5-474C398D3B95}">
+      <formula1>"In Progress,Completed,Planning,On Hold"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -3535,26 +4982,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3571,4 +5021,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7CDBA4-7A0D-4755-B1E6-DDB997BA83E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9B41E0-B82C-4704-B1AD-A5C9B3A83964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="97">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -306,6 +306,33 @@
   </si>
   <si>
     <t>อบรมมาตรฐานความปลอดภัยหน้างานประจำไตรมาส</t>
+  </si>
+  <si>
+    <t>https://corallife806.sharepoint.com/:x:/s/CoralLife2/IQAgdsPc2zNkQ5C41kKVppzcAUn7FZ408wMYJu9xdLOXGAk?e=Y6xkaQ</t>
+  </si>
+  <si>
+    <t>https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQD85m2EY5inQ6fSr-DozZluAQlFM028ytXMvyGjL_sTCAA?e=b5Wm0X</t>
+  </si>
+  <si>
+    <t>แผนงาน.pdf</t>
+  </si>
+  <si>
+    <t>Master Schedule_R1.pdf</t>
+  </si>
+  <si>
+    <t>แผนงาน R2.pdf</t>
+  </si>
+  <si>
+    <t>https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQApiS38eEhNRKjVNVlpbA9jAaIPpzh_L5MpG-uJ9pPUXhI?e=Unknsk</t>
+  </si>
+  <si>
+    <t>https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQDFiWBSbZRCQLrA6vXOjE_4AXR2LclL9wuGBQobu8VGhpE?e=lzbSti</t>
+  </si>
+  <si>
+    <t>อื่นๆ (ไม่ผูกกับโปรเจค) - Cash Advance</t>
+  </si>
+  <si>
+    <t>รวมยอด Cash Advance ที่ไม่มีชื่อโปรเจคใน database - กรอกยอดในคอลัมน์ Petty Cash (THB)</t>
   </si>
 </sst>
 </file>
@@ -403,7 +430,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,8 +447,20 @@
         <fgColor rgb="FFE9E4D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -468,13 +507,140 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D4C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D4C6"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D4C6"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D4C6"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D4C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D4C6"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D4C6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D4C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D4C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D4C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D4C6"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -565,16 +731,94 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -980,36 +1224,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-    </row>
-    <row r="4" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+    </row>
+    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1045,7 +1289,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="65" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1065,833 +1309,860 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="57">
         <v>46213</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="35"/>
-      <c r="B6" s="5" t="s">
+      <c r="J5" s="57"/>
+      <c r="K5" s="49"/>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="60"/>
+      <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="38">
         <v>46189</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="38">
         <v>46189</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="7">
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="39">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="5"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="41">
         <v>46219</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="41">
         <v>46233</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="7">
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="42">
         <v>0</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="I7" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
-      <c r="B8" s="5" t="s">
+      <c r="J7" s="55"/>
+      <c r="K7" s="51"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="60"/>
+      <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="38">
         <v>46244</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="38">
         <v>46247</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="7">
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="39">
         <v>0</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="35"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="5"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="41">
         <v>46082</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="41">
         <v>46096</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="7">
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="42">
         <v>1</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="55">
         <v>46218</v>
       </c>
-      <c r="J9" s="36"/>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
-      <c r="B10" s="5" t="s">
+      <c r="J9" s="55"/>
+      <c r="K9" s="51"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="60"/>
+      <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="38">
         <v>46168</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="38">
         <v>46213</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7">
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="39">
         <v>1</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="35"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="5"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="44">
         <v>46184</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="44">
         <v>46191</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="7">
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="45">
         <v>1</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="55">
         <v>46171</v>
       </c>
-      <c r="J11" s="36"/>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="35"/>
-      <c r="B12" s="5" t="s">
+      <c r="J11" s="55"/>
+      <c r="K11" s="51"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="60"/>
+      <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="47">
         <v>46200</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="47">
         <v>46202</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7">
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48">
         <v>1</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="35"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="5"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="41">
         <v>46392</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="41">
         <v>46402</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7">
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42">
         <v>0</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="36" t="s">
+      <c r="I13" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
-      <c r="B14" s="5" t="s">
+      <c r="J13" s="55"/>
+      <c r="K13" s="51"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="60"/>
+      <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="38">
         <v>46042</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="38">
         <v>46042</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="7">
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39">
         <v>0</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="35"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="5"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="44">
         <v>46168</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="44">
         <v>46188</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="7">
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="45">
         <v>1</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="55">
         <v>46199</v>
       </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="35"/>
-      <c r="B16" s="5" t="s">
+      <c r="J15" s="55"/>
+      <c r="K15" s="51"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="60"/>
+      <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="47">
         <v>46198</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="47">
         <v>46199</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="7">
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="48">
         <v>1</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="35"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="5"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="35">
         <v>46188</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="35">
         <v>46198</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7">
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="36">
         <v>0.8</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="58">
         <v>46305</v>
       </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="35"/>
-      <c r="B18" s="5" t="s">
+      <c r="J17" s="58"/>
+      <c r="K17" s="52"/>
+    </row>
+    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="60"/>
+      <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="38">
         <v>46296</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="38">
         <v>46298</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="7">
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39">
         <v>0.4</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="35"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="5"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="35">
         <v>46275</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="35">
         <v>46290</v>
       </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="7">
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="36">
         <v>0</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="36">
+      <c r="I19" s="58">
         <v>46336</v>
       </c>
-      <c r="J19" s="36"/>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="35"/>
-      <c r="B20" s="5" t="s">
+      <c r="J19" s="58"/>
+      <c r="K19" s="52"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="60"/>
+      <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="38">
         <v>46327</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="38">
         <v>46329</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="7">
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="39">
         <v>0</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="35"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="5"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="41">
         <v>46240</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="41">
         <v>46249</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="7">
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42">
         <v>0</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="55">
         <v>46336</v>
       </c>
-      <c r="J21" s="36"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="35"/>
-      <c r="B22" s="5" t="s">
+      <c r="J21" s="55"/>
+      <c r="K21" s="53"/>
+    </row>
+    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="60"/>
+      <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="38">
         <v>46327</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="38">
         <v>46329</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="7">
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="39">
         <v>0</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="35"/>
-      <c r="J22" s="36"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="41">
         <v>46190</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="41">
         <v>46206</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="7">
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42">
         <v>0.7</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="55">
         <v>46218</v>
       </c>
-      <c r="J23" s="36"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="35"/>
-      <c r="B24" s="5" t="s">
+      <c r="J23" s="55"/>
+      <c r="K23" s="53"/>
+    </row>
+    <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="60"/>
+      <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="38">
         <v>46209</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="38">
         <v>46211</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="7">
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="39">
         <v>0</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="35"/>
-      <c r="J24" s="36"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="44">
         <v>46185</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="44">
         <v>46188</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="7">
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="45">
         <v>1</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="55">
         <v>46188</v>
       </c>
-      <c r="J25" s="36"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="35"/>
-      <c r="B26" s="5" t="s">
+      <c r="J25" s="55"/>
+      <c r="K25" s="53"/>
+    </row>
+    <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="60"/>
+      <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="47">
         <v>46185</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="47">
         <v>46188</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="7">
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48">
         <v>1</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="35"/>
-      <c r="J26" s="36"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="41">
         <v>46234</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="41">
         <v>46247</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7">
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42">
         <v>0</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="36">
+      <c r="I27" s="55">
         <v>46321</v>
       </c>
-      <c r="J27" s="36"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="35"/>
-      <c r="B28" s="5" t="s">
+      <c r="J27" s="55"/>
+      <c r="K27" s="53"/>
+    </row>
+    <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="60"/>
+      <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="38">
         <v>46314</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="38">
         <v>46316</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7">
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="39">
         <v>0</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="35"/>
-      <c r="J28" s="36"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="44">
         <v>46091</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="44">
         <v>46100</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7">
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="45">
         <v>1</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="36">
+      <c r="I29" s="55">
         <v>46139</v>
       </c>
-      <c r="J29" s="36"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="35"/>
-      <c r="B30" s="5" t="s">
+      <c r="J29" s="55"/>
+      <c r="K29" s="53"/>
+    </row>
+    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="60"/>
+      <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="47">
         <v>46120</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="47">
         <v>46124</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7">
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="48">
         <v>1</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="35"/>
-      <c r="J30" s="36"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="34" t="s">
+      <c r="A31" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="44">
         <v>46091</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="44">
         <v>46094</v>
       </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7">
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="45">
         <v>1</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="55">
         <v>46133</v>
       </c>
-      <c r="J31" s="36"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="35"/>
-      <c r="B32" s="5" t="s">
+      <c r="J31" s="55"/>
+      <c r="K31" s="53"/>
+    </row>
+    <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="60"/>
+      <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="47">
         <v>46091</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="47">
         <v>46094</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7">
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48">
         <v>1</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="35"/>
-      <c r="J32" s="36"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="I32" s="60"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="54"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="41">
         <v>46091</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="41">
         <v>46094</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="7">
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42">
         <v>0</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="55">
         <v>46295</v>
       </c>
-      <c r="J33" s="36"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="35"/>
-      <c r="B34" s="5" t="s">
+      <c r="J33" s="55"/>
+      <c r="K33" s="53"/>
+    </row>
+    <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="60"/>
+      <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="38">
         <v>46091</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="38">
         <v>46094</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="7">
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="39">
         <v>0</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="35"/>
-      <c r="J34" s="36"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="34" t="s">
+      <c r="I34" s="60"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="54"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="41">
         <v>45723</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="41">
         <v>45729</v>
       </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="7">
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="42">
         <v>1</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="55">
         <v>45737</v>
       </c>
-      <c r="J35" s="36"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="35"/>
-      <c r="B36" s="5" t="s">
+      <c r="J35" s="55"/>
+      <c r="K35" s="53"/>
+    </row>
+    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="60"/>
+      <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="38">
         <v>45729</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="38">
         <v>45732</v>
       </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="7">
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="39">
         <v>0.9</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="35"/>
-      <c r="J36" s="36"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="I36" s="60"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="54"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="41">
         <v>45723</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="41">
         <v>45729</v>
       </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="7">
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="42">
         <v>1</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="36">
+      <c r="I37" s="55">
         <v>45737</v>
       </c>
-      <c r="J37" s="36"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="35"/>
-      <c r="B38" s="5" t="s">
+      <c r="J37" s="55"/>
+      <c r="K37" s="53"/>
+    </row>
+    <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="60"/>
+      <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="38">
         <v>45729</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="38">
         <v>45732</v>
       </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="7">
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="39">
         <v>0.9</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="35"/>
-      <c r="J38" s="36"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -1908,29 +2179,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1943,7 +2205,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V188"/>
+  <dimension ref="A1:V189"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
@@ -1960,62 +2222,62 @@
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="18" width="13" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="28" customWidth="1"/>
+    <col min="20" max="20" width="42.5546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="99.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
     </row>
     <row r="4" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2139,7 +2401,9 @@
       <c r="T5" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="U5" s="27"/>
+      <c r="U5" s="30" t="s">
+        <v>88</v>
+      </c>
       <c r="V5" s="20"/>
     </row>
     <row r="6" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2255,7 +2519,9 @@
       <c r="T7" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="U7" s="27"/>
+      <c r="U7" s="30" t="s">
+        <v>89</v>
+      </c>
       <c r="V7" s="20"/>
     </row>
     <row r="8" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2312,7 +2578,9 @@
       </c>
       <c r="S8" s="15"/>
       <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
+      <c r="U8" s="32" t="s">
+        <v>90</v>
+      </c>
       <c r="V8" s="20">
         <v>46134</v>
       </c>
@@ -2421,7 +2689,9 @@
       </c>
       <c r="S10" s="15"/>
       <c r="T10" s="28"/>
-      <c r="U10" s="27"/>
+      <c r="U10" s="32" t="s">
+        <v>90</v>
+      </c>
       <c r="V10" s="20">
         <v>46141</v>
       </c>
@@ -2481,7 +2751,9 @@
       <c r="T11" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="U11" s="27"/>
+      <c r="U11" s="32" t="s">
+        <v>91</v>
+      </c>
       <c r="V11" s="20">
         <v>46147</v>
       </c>
@@ -2565,7 +2837,6 @@
         <f>P13*0.3</f>
         <v>36000</v>
       </c>
-      <c r="G13" s="17"/>
       <c r="H13" s="17">
         <f t="shared" si="0"/>
         <v>130841.12</v>
@@ -2596,7 +2867,9 @@
       <c r="T13" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="U13" s="27"/>
+      <c r="U13" s="32" t="s">
+        <v>92</v>
+      </c>
       <c r="V13" s="20">
         <v>46147</v>
       </c>
@@ -2767,7 +3040,9 @@
       <c r="T16" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="27"/>
+      <c r="U16" s="30" t="s">
+        <v>93</v>
+      </c>
       <c r="V16" s="20">
         <v>46182</v>
       </c>
@@ -2933,8 +3208,12 @@
       <c r="T19" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="U19" s="27"/>
-      <c r="V19" s="20"/>
+      <c r="U19" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="V19" s="20">
+        <v>46203</v>
+      </c>
     </row>
     <row r="20" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="10" t="s">
@@ -3010,12 +3289,28 @@
       <c r="T21" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="U21" s="27"/>
       <c r="V21" s="20"/>
     </row>
-    <row r="22" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="G22" s="14">
+    <row r="22" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="10">
         <v>2444</v>
+      </c>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="T22" s="28" t="s">
+        <v>96</v>
       </c>
       <c r="V22" s="20"/>
     </row>
@@ -3070,7 +3365,7 @@
     <row r="39" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="V39" s="20"/>
     </row>
-    <row r="40" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="V40" s="20"/>
     </row>
     <row r="41" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -3516,6 +3811,9 @@
     </row>
     <row r="188" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="V188" s="20"/>
+    </row>
+    <row r="189" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="V189" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3523,15 +3821,23 @@
     <mergeCell ref="A2:V2"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B5:B39" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C200" xr:uid="{362D2387-52AE-4045-809E-2C75EB9CCBFB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C201" xr:uid="{362D2387-52AE-4045-809E-2C75EB9CCBFB}">
       <formula1>"Internal,External"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="U14" r:id="rId1" xr:uid="{D16A580D-0F23-4F6F-8F5B-CB904485C44F}"/>
+    <hyperlink ref="U5" r:id="rId2" xr:uid="{F2A67D83-7EE6-4F43-A7CF-9A7A41DDE6BE}"/>
+    <hyperlink ref="U7" r:id="rId3" xr:uid="{0976AF2F-EFAD-4D62-A5D9-EA0400669608}"/>
+    <hyperlink ref="U8" r:id="rId4" display="https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQC_1O9ATjPsQomIvw1ojRYNAaU5LIg7fkK9VUpOyGFWeRU?e=lM49aH" xr:uid="{1FB45799-2375-45C8-B4B2-95EDCB78A986}"/>
+    <hyperlink ref="U10" r:id="rId5" display="https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQDPRH31b2MuQrHsnyp3t2p9AUx2BIPH7d5CaCZiEXf91Ts?e=epteGe" xr:uid="{34875C2B-60EA-4950-BA38-A9B5F38806DD}"/>
+    <hyperlink ref="U11" r:id="rId6" display="https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQBzSAX63zsdTaCxQyovwEpUAdqoBcvGSGMOniM5cwxdJJo?e=0608OK" xr:uid="{6E29E81C-1257-45E3-ADA8-3D8AF9C8F473}"/>
+    <hyperlink ref="U13" r:id="rId7" display="https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQBSB6_w6g72TLKUHWGlGBMFARs9IGLaqRfLn5C5zWJMU04?e=8SAokd" xr:uid="{60CE460F-1314-44B6-832C-5ABF13522EB6}"/>
+    <hyperlink ref="U16" r:id="rId8" xr:uid="{02895EAD-8F6D-4728-91D1-12231471B411}"/>
+    <hyperlink ref="U19" r:id="rId9" xr:uid="{64B77621-4464-4729-B1C8-C74F3BC4DC5C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3549,20 +3855,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
     </row>
     <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3827,22 +4133,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4730,6 +5036,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -4982,29 +5310,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5021,23 +5346,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9B41E0-B82C-4704-B1AD-A5C9B3A83964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AF645F-0057-4C33-A8EF-75B405A444C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7860" yWindow="3360" windowWidth="13128" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="98">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>รวมยอด Cash Advance ที่ไม่มีชื่อโปรเจคใน database - กรอกยอดในคอลัมน์ Petty Cash (THB)</t>
+  </si>
+  <si>
+    <t>Non-Project</t>
   </si>
 </sst>
 </file>
@@ -794,6 +797,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -813,9 +818,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1224,34 +1227,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1309,14 +1312,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="57">
+      <c r="I5" s="59">
         <v>46213</v>
       </c>
-      <c r="J5" s="57"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="60"/>
+      <c r="A6" s="62"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1334,12 +1337,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="60"/>
-      <c r="J6" s="56"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="58"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="61" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1359,14 +1362,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="55" t="s">
+      <c r="I7" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="55"/>
+      <c r="J7" s="57"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="60"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1384,12 +1387,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="60"/>
-      <c r="J8" s="56"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="58"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="61" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1409,14 +1412,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="55">
+      <c r="I9" s="57">
         <v>46218</v>
       </c>
-      <c r="J9" s="55"/>
+      <c r="J9" s="57"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="60"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1434,12 +1437,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="60"/>
-      <c r="J10" s="56"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="58"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1459,14 +1462,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="55">
+      <c r="I11" s="57">
         <v>46171</v>
       </c>
-      <c r="J11" s="55"/>
+      <c r="J11" s="57"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="60"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1484,12 +1487,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="60"/>
-      <c r="J12" s="56"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="58"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="61" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1509,14 +1512,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="55" t="s">
+      <c r="I13" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="55"/>
+      <c r="J13" s="57"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="60"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1534,12 +1537,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="60"/>
-      <c r="J14" s="56"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="58"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="61" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1559,14 +1562,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="55">
+      <c r="I15" s="57">
         <v>46199</v>
       </c>
-      <c r="J15" s="55"/>
+      <c r="J15" s="57"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="60"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1584,12 +1587,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="60"/>
-      <c r="J16" s="56"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="58"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="63" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1609,14 +1612,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="58">
+      <c r="I17" s="60">
         <v>46305</v>
       </c>
-      <c r="J17" s="58"/>
+      <c r="J17" s="60"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="60"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1634,12 +1637,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="60"/>
-      <c r="J18" s="56"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="58"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="63" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1659,14 +1662,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="58">
+      <c r="I19" s="60">
         <v>46336</v>
       </c>
-      <c r="J19" s="58"/>
+      <c r="J19" s="60"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="60"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1684,12 +1687,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="60"/>
-      <c r="J20" s="56"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="58"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="61" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1709,14 +1712,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="55">
+      <c r="I21" s="57">
         <v>46336</v>
       </c>
-      <c r="J21" s="55"/>
+      <c r="J21" s="57"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="60"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1734,12 +1737,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="56"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="58"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="61" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1759,14 +1762,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="55">
+      <c r="I23" s="57">
         <v>46218</v>
       </c>
-      <c r="J23" s="55"/>
+      <c r="J23" s="57"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="60"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1784,12 +1787,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="60"/>
-      <c r="J24" s="56"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="58"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="61" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1809,14 +1812,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="55">
+      <c r="I25" s="57">
         <v>46188</v>
       </c>
-      <c r="J25" s="55"/>
+      <c r="J25" s="57"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="60"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1834,12 +1837,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="60"/>
-      <c r="J26" s="56"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="58"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="61" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1859,14 +1862,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="55">
+      <c r="I27" s="57">
         <v>46321</v>
       </c>
-      <c r="J27" s="55"/>
+      <c r="J27" s="57"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="60"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -1884,12 +1887,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="60"/>
-      <c r="J28" s="56"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="58"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="59" t="s">
+      <c r="A29" s="61" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -1909,14 +1912,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="55">
+      <c r="I29" s="57">
         <v>46139</v>
       </c>
-      <c r="J29" s="55"/>
+      <c r="J29" s="57"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="60"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -1934,12 +1937,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="60"/>
-      <c r="J30" s="56"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="58"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="61" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -1959,14 +1962,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="55">
+      <c r="I31" s="57">
         <v>46133</v>
       </c>
-      <c r="J31" s="55"/>
+      <c r="J31" s="57"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="60"/>
+      <c r="A32" s="62"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -1984,12 +1987,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="60"/>
-      <c r="J32" s="56"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="58"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="59" t="s">
+      <c r="A33" s="61" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2009,14 +2012,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="55">
+      <c r="I33" s="57">
         <v>46295</v>
       </c>
-      <c r="J33" s="55"/>
+      <c r="J33" s="57"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="60"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2034,12 +2037,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="60"/>
-      <c r="J34" s="56"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="58"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="59" t="s">
+      <c r="A35" s="61" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2059,14 +2062,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="55">
+      <c r="I35" s="57">
         <v>45737</v>
       </c>
-      <c r="J35" s="55"/>
+      <c r="J35" s="57"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="60"/>
+      <c r="A36" s="62"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2084,12 +2087,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="60"/>
-      <c r="J36" s="56"/>
+      <c r="I36" s="62"/>
+      <c r="J36" s="58"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="59" t="s">
+      <c r="A37" s="61" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2109,14 +2112,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="55">
+      <c r="I37" s="57">
         <v>45737</v>
       </c>
-      <c r="J37" s="55"/>
+      <c r="J37" s="57"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="60"/>
+      <c r="A38" s="62"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2134,8 +2137,8 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="60"/>
-      <c r="J38" s="56"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="58"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
@@ -2228,56 +2231,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="64"/>
-      <c r="S2" s="64"/>
-      <c r="T2" s="64"/>
-      <c r="U2" s="64"/>
-      <c r="V2" s="64"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
     </row>
     <row r="4" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3299,7 +3302,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="D22" s="16"/>
       <c r="F22" s="26"/>
@@ -3820,12 +3823,15 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C201" xr:uid="{362D2387-52AE-4045-809E-2C75EB9CCBFB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C201" xr:uid="{362D2387-52AE-4045-809E-2C75EB9CCBFB}">
       <formula1>"Internal,External"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C200" xr:uid="{CD75D35E-1DBF-46B7-ADB8-F3026CC204AA}">
+      <formula1>"Internal,External,Non-Project"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -3855,20 +3861,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
     </row>
     <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4133,22 +4139,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AF645F-0057-4C33-A8EF-75B405A444C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A97328D-2598-4308-A86F-7614633E70DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7860" yWindow="3360" windowWidth="13128" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -799,28 +799,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1230,31 +1230,31 @@
       <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1292,7 +1292,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="63" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1312,14 +1312,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="64">
         <v>46213</v>
       </c>
-      <c r="J5" s="59"/>
+      <c r="J5" s="64"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="62"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1337,12 +1337,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="65"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="57" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1362,14 +1362,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="57"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="62"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1387,12 +1387,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="62"/>
-      <c r="J8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="65"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="57" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1412,14 +1412,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="59">
         <v>46218</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="62"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1437,12 +1437,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="65"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="57" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1462,14 +1462,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="57">
+      <c r="I11" s="59">
         <v>46171</v>
       </c>
-      <c r="J11" s="57"/>
+      <c r="J11" s="59"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="62"/>
+      <c r="A12" s="58"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1487,12 +1487,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="62"/>
-      <c r="J12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="65"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="57" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1512,14 +1512,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="57"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="62"/>
+      <c r="A14" s="58"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1537,12 +1537,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="62"/>
-      <c r="J14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="65"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="57" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1562,14 +1562,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="57">
+      <c r="I15" s="59">
         <v>46199</v>
       </c>
-      <c r="J15" s="57"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="62"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1587,12 +1587,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="65"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="62" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1612,14 +1612,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="60">
+      <c r="I17" s="61">
         <v>46305</v>
       </c>
-      <c r="J17" s="60"/>
+      <c r="J17" s="61"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="62"/>
+      <c r="A18" s="58"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1637,12 +1637,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="62"/>
-      <c r="J18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="65"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="62" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1662,14 +1662,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="60">
+      <c r="I19" s="61">
         <v>46336</v>
       </c>
-      <c r="J19" s="60"/>
+      <c r="J19" s="61"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="62"/>
+      <c r="A20" s="58"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1687,12 +1687,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="62"/>
-      <c r="J20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="65"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="57" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1712,14 +1712,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="57">
+      <c r="I21" s="59">
         <v>46336</v>
       </c>
-      <c r="J21" s="57"/>
+      <c r="J21" s="59"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="62"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1737,12 +1737,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="62"/>
-      <c r="J22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="65"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="57" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1762,14 +1762,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="57">
+      <c r="I23" s="59">
         <v>46218</v>
       </c>
-      <c r="J23" s="57"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="62"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1787,12 +1787,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="62"/>
-      <c r="J24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="65"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="57" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1812,14 +1812,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="57">
+      <c r="I25" s="59">
         <v>46188</v>
       </c>
-      <c r="J25" s="57"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="62"/>
+      <c r="A26" s="58"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1837,12 +1837,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="62"/>
-      <c r="J26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="65"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="61" t="s">
+      <c r="A27" s="57" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1862,14 +1862,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="57">
+      <c r="I27" s="59">
         <v>46321</v>
       </c>
-      <c r="J27" s="57"/>
+      <c r="J27" s="59"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="62"/>
+      <c r="A28" s="58"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -1887,12 +1887,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="62"/>
-      <c r="J28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="65"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="61" t="s">
+      <c r="A29" s="57" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -1912,14 +1912,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="57">
+      <c r="I29" s="59">
         <v>46139</v>
       </c>
-      <c r="J29" s="57"/>
+      <c r="J29" s="59"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="62"/>
+      <c r="A30" s="58"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -1937,12 +1937,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="62"/>
-      <c r="J30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="65"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="57" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -1962,14 +1962,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="57">
+      <c r="I31" s="59">
         <v>46133</v>
       </c>
-      <c r="J31" s="57"/>
+      <c r="J31" s="59"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="62"/>
+      <c r="A32" s="58"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -1987,12 +1987,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="62"/>
-      <c r="J32" s="58"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="65"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="61" t="s">
+      <c r="A33" s="57" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2012,14 +2012,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="57">
+      <c r="I33" s="59">
         <v>46295</v>
       </c>
-      <c r="J33" s="57"/>
+      <c r="J33" s="59"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="62"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2037,12 +2037,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="62"/>
-      <c r="J34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="65"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="61" t="s">
+      <c r="A35" s="57" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2062,14 +2062,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="57">
+      <c r="I35" s="59">
         <v>45737</v>
       </c>
-      <c r="J35" s="57"/>
+      <c r="J35" s="59"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="62"/>
+      <c r="A36" s="58"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2087,12 +2087,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="62"/>
-      <c r="J36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="65"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="61" t="s">
+      <c r="A37" s="57" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2112,14 +2112,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="57">
+      <c r="I37" s="59">
         <v>45737</v>
       </c>
-      <c r="J37" s="57"/>
+      <c r="J37" s="59"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="62"/>
+      <c r="A38" s="58"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2137,12 +2137,49 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="62"/>
-      <c r="J38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="65"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2159,43 +2196,6 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3307,7 +3307,7 @@
       <c r="D22" s="16"/>
       <c r="F22" s="26"/>
       <c r="G22" s="10">
-        <v>2444</v>
+        <v>2484</v>
       </c>
       <c r="P22" s="11"/>
       <c r="Q22" s="20"/>
@@ -3865,16 +3865,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="55"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="56"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
     </row>
     <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -5042,6 +5042,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5052,15 +5061,6 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5317,20 +5317,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A97328D-2598-4308-A86F-7614633E70DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E2FED6-E042-4D74-A932-E65662F29DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -799,28 +799,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1230,31 +1230,31 @@
       <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1292,7 +1292,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="65" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1312,14 +1312,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="64">
+      <c r="I5" s="59">
         <v>46213</v>
       </c>
-      <c r="J5" s="64"/>
+      <c r="J5" s="59"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="58"/>
+      <c r="A6" s="62"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1337,12 +1337,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="58"/>
-      <c r="J6" s="65"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="58"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="61" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1362,14 +1362,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="59"/>
+      <c r="J7" s="57"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="58"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1387,12 +1387,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="58"/>
-      <c r="J8" s="65"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="58"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="61" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1412,14 +1412,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="57">
         <v>46218</v>
       </c>
-      <c r="J9" s="59"/>
+      <c r="J9" s="57"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="58"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1437,12 +1437,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="58"/>
-      <c r="J10" s="65"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="58"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="61" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1462,14 +1462,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="57">
         <v>46171</v>
       </c>
-      <c r="J11" s="59"/>
+      <c r="J11" s="57"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="58"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1487,12 +1487,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="58"/>
-      <c r="J12" s="65"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="58"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="61" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1512,14 +1512,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="59" t="s">
+      <c r="I13" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="59"/>
+      <c r="J13" s="57"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="58"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1537,12 +1537,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="58"/>
-      <c r="J14" s="65"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="58"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="61" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1562,14 +1562,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="59">
+      <c r="I15" s="57">
         <v>46199</v>
       </c>
-      <c r="J15" s="59"/>
+      <c r="J15" s="57"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="58"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1587,12 +1587,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="58"/>
-      <c r="J16" s="65"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="58"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="63" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1612,14 +1612,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="61">
+      <c r="I17" s="60">
         <v>46305</v>
       </c>
-      <c r="J17" s="61"/>
+      <c r="J17" s="60"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="58"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1637,12 +1637,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="58"/>
-      <c r="J18" s="65"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="58"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="63" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1662,14 +1662,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="60">
         <v>46336</v>
       </c>
-      <c r="J19" s="61"/>
+      <c r="J19" s="60"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="58"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1687,12 +1687,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="58"/>
-      <c r="J20" s="65"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="58"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="61" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1712,14 +1712,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="57">
         <v>46336</v>
       </c>
-      <c r="J21" s="59"/>
+      <c r="J21" s="57"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="58"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1737,12 +1737,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="58"/>
-      <c r="J22" s="65"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="58"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="61" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1762,14 +1762,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="59">
+      <c r="I23" s="57">
         <v>46218</v>
       </c>
-      <c r="J23" s="59"/>
+      <c r="J23" s="57"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="58"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1787,12 +1787,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="58"/>
-      <c r="J24" s="65"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="58"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="61" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1812,14 +1812,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="59">
+      <c r="I25" s="57">
         <v>46188</v>
       </c>
-      <c r="J25" s="59"/>
+      <c r="J25" s="57"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="58"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1837,12 +1837,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="58"/>
-      <c r="J26" s="65"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="58"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="61" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1862,14 +1862,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="59">
+      <c r="I27" s="57">
         <v>46321</v>
       </c>
-      <c r="J27" s="59"/>
+      <c r="J27" s="57"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="58"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -1887,12 +1887,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="58"/>
-      <c r="J28" s="65"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="58"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="61" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -1912,14 +1912,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="59">
+      <c r="I29" s="57">
         <v>46139</v>
       </c>
-      <c r="J29" s="59"/>
+      <c r="J29" s="57"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="58"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -1937,12 +1937,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="58"/>
-      <c r="J30" s="65"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="58"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="61" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -1962,14 +1962,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="59">
+      <c r="I31" s="57">
         <v>46133</v>
       </c>
-      <c r="J31" s="59"/>
+      <c r="J31" s="57"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="58"/>
+      <c r="A32" s="62"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -1987,12 +1987,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="58"/>
-      <c r="J32" s="65"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="58"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="57" t="s">
+      <c r="A33" s="61" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2012,14 +2012,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="59">
+      <c r="I33" s="57">
         <v>46295</v>
       </c>
-      <c r="J33" s="59"/>
+      <c r="J33" s="57"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="58"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2037,12 +2037,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="58"/>
-      <c r="J34" s="65"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="58"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="57" t="s">
+      <c r="A35" s="61" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2062,14 +2062,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="57">
         <v>45737</v>
       </c>
-      <c r="J35" s="59"/>
+      <c r="J35" s="57"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="58"/>
+      <c r="A36" s="62"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2087,12 +2087,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="58"/>
-      <c r="J36" s="65"/>
+      <c r="I36" s="62"/>
+      <c r="J36" s="58"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="57" t="s">
+      <c r="A37" s="61" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2112,14 +2112,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="59">
+      <c r="I37" s="57">
         <v>45737</v>
       </c>
-      <c r="J37" s="59"/>
+      <c r="J37" s="57"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="58"/>
+      <c r="A38" s="62"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2137,26 +2137,35 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="58"/>
-      <c r="J38" s="65"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="58"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2173,29 +2182,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3309,6 +3309,9 @@
       <c r="G22" s="10">
         <v>2484</v>
       </c>
+      <c r="M22" s="10">
+        <v>10000</v>
+      </c>
       <c r="P22" s="11"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20"/>
@@ -3823,7 +3826,7 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -3865,16 +3868,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="55"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="56"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
     </row>
     <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -5042,15 +5045,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5061,6 +5055,15 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5317,20 +5320,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E2FED6-E042-4D74-A932-E65662F29DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73012E8E-3D09-4DC9-B564-16A6C8AD7BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="100">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -251,9 +251,6 @@
     <t>โครงการล่าช้า/ติดกริลวันที่ 17/07/2026 กำหนดส่งงานได้ กันยา-ตุลา</t>
   </si>
   <si>
-    <t>07/24/2026 เริ่มเข้าไซต์ (Draft)</t>
-  </si>
-  <si>
     <t>Project Type</t>
   </si>
   <si>
@@ -336,6 +333,15 @@
   </si>
   <si>
     <t>Non-Project</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>คุณทวีชัย สมุทรปราการ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/31/2026 เริ่มเข้าไซต์ </t>
   </si>
 </sst>
 </file>
@@ -347,7 +353,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,8 +438,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,6 +473,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16243A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -643,7 +663,7 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -797,6 +817,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1227,34 +1248,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1270,10 +1291,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>6</v>
@@ -1285,14 +1306,14 @@
         <v>8</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="66" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1312,14 +1333,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="59">
+      <c r="I5" s="60">
         <v>46213</v>
       </c>
-      <c r="J5" s="59"/>
+      <c r="J5" s="60"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="62"/>
+      <c r="A6" s="63"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1337,12 +1358,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="58"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1362,14 +1383,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="57"/>
+      <c r="J7" s="58"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="62"/>
+      <c r="A8" s="63"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1387,12 +1408,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="62"/>
-      <c r="J8" s="58"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="59"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="62" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1412,14 +1433,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="58">
         <v>46218</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="62"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1437,12 +1458,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="58"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="59"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="62" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1462,14 +1483,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="57">
+      <c r="I11" s="58">
         <v>46171</v>
       </c>
-      <c r="J11" s="57"/>
+      <c r="J11" s="58"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="62"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1487,12 +1508,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="62"/>
-      <c r="J12" s="58"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="62" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1512,14 +1533,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="57"/>
+      <c r="J13" s="58"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="62"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1537,12 +1558,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="62"/>
-      <c r="J14" s="58"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="59"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="62" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1562,14 +1583,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="57">
+      <c r="I15" s="58">
         <v>46199</v>
       </c>
-      <c r="J15" s="57"/>
+      <c r="J15" s="58"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="62"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1587,12 +1608,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="58"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="59"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="64" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1612,14 +1633,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="60">
+      <c r="I17" s="61">
         <v>46305</v>
       </c>
-      <c r="J17" s="60"/>
+      <c r="J17" s="61"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="62"/>
+      <c r="A18" s="63"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1637,12 +1658,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="62"/>
-      <c r="J18" s="58"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="59"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="64" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1662,14 +1683,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="60">
+      <c r="I19" s="61">
         <v>46336</v>
       </c>
-      <c r="J19" s="60"/>
+      <c r="J19" s="61"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="62"/>
+      <c r="A20" s="63"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1687,12 +1708,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="62"/>
-      <c r="J20" s="58"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="59"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="62" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1712,14 +1733,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="57">
+      <c r="I21" s="58">
         <v>46336</v>
       </c>
-      <c r="J21" s="57"/>
+      <c r="J21" s="58"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="62"/>
+      <c r="A22" s="63"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1737,12 +1758,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="62"/>
-      <c r="J22" s="58"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="59"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="62" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1762,14 +1783,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="57">
+      <c r="I23" s="58">
         <v>46218</v>
       </c>
-      <c r="J23" s="57"/>
+      <c r="J23" s="58"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="62"/>
+      <c r="A24" s="63"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1787,12 +1808,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="62"/>
-      <c r="J24" s="58"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="59"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="62" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1812,14 +1833,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="57">
+      <c r="I25" s="58">
         <v>46188</v>
       </c>
-      <c r="J25" s="57"/>
+      <c r="J25" s="58"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="62"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1837,12 +1858,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="62"/>
-      <c r="J26" s="58"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="59"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="61" t="s">
+      <c r="A27" s="62" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1862,14 +1883,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="57">
+      <c r="I27" s="58">
         <v>46321</v>
       </c>
-      <c r="J27" s="57"/>
+      <c r="J27" s="58"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="62"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -1887,12 +1908,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="62"/>
-      <c r="J28" s="58"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="59"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="61" t="s">
+      <c r="A29" s="62" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -1912,14 +1933,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="57">
+      <c r="I29" s="58">
         <v>46139</v>
       </c>
-      <c r="J29" s="57"/>
+      <c r="J29" s="58"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="62"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -1937,12 +1958,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="62"/>
-      <c r="J30" s="58"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="59"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="62" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -1962,14 +1983,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="57">
+      <c r="I31" s="58">
         <v>46133</v>
       </c>
-      <c r="J31" s="57"/>
+      <c r="J31" s="58"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="62"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -1987,12 +2008,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="62"/>
-      <c r="J32" s="58"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="59"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="61" t="s">
+      <c r="A33" s="62" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2012,14 +2033,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="57">
+      <c r="I33" s="58">
         <v>46295</v>
       </c>
-      <c r="J33" s="57"/>
+      <c r="J33" s="58"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="62"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2037,12 +2058,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="62"/>
-      <c r="J34" s="58"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="59"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="61" t="s">
+      <c r="A35" s="62" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2062,14 +2083,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="57">
+      <c r="I35" s="58">
         <v>45737</v>
       </c>
-      <c r="J35" s="57"/>
+      <c r="J35" s="58"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="62"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2087,12 +2108,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="62"/>
-      <c r="J36" s="58"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="59"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="61" t="s">
+      <c r="A37" s="62" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2112,14 +2133,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="57">
+      <c r="I37" s="58">
         <v>45737</v>
       </c>
-      <c r="J37" s="57"/>
+      <c r="J37" s="58"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="62"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2137,8 +2158,8 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="62"/>
-      <c r="J38" s="58"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="59"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
@@ -2231,56 +2252,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
     </row>
     <row r="4" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2290,7 +2311,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>35</v>
@@ -2344,10 +2365,10 @@
         <v>9</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
@@ -2358,7 +2379,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" s="16">
         <v>0.9</v>
@@ -2405,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="U5" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V5" s="20"/>
     </row>
@@ -2417,7 +2438,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="16">
         <v>0</v>
@@ -2474,7 +2495,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="16">
         <v>0.9</v>
@@ -2523,7 +2544,7 @@
         <v>52</v>
       </c>
       <c r="U7" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="V7" s="20"/>
     </row>
@@ -2535,7 +2556,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" s="16">
         <v>1</v>
@@ -2582,7 +2603,7 @@
       <c r="S8" s="15"/>
       <c r="T8" s="27"/>
       <c r="U8" s="32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V8" s="20">
         <v>46134</v>
@@ -2596,7 +2617,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" s="16">
         <v>0</v>
@@ -2646,7 +2667,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" s="16">
         <v>1</v>
@@ -2693,7 +2714,7 @@
       <c r="S10" s="15"/>
       <c r="T10" s="28"/>
       <c r="U10" s="32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V10" s="20">
         <v>46141</v>
@@ -2707,7 +2728,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" s="16">
         <v>0.7</v>
@@ -2755,7 +2776,7 @@
         <v>64</v>
       </c>
       <c r="U11" s="32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V11" s="20">
         <v>46147</v>
@@ -2769,7 +2790,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" s="16">
         <v>0</v>
@@ -2828,7 +2849,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" s="16">
         <v>0</v>
@@ -2871,7 +2892,7 @@
         <v>51</v>
       </c>
       <c r="U13" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="V13" s="20">
         <v>46147</v>
@@ -2885,7 +2906,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" s="22">
         <v>0.6</v>
@@ -2931,7 +2952,7 @@
         <v>65</v>
       </c>
       <c r="U14" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V14" s="20">
         <v>46169</v>
@@ -2945,7 +2966,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
@@ -3001,7 +3022,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" s="16">
         <v>0</v>
@@ -3044,7 +3065,7 @@
         <v>51</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V16" s="20">
         <v>46182</v>
@@ -3058,7 +3079,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" s="16">
         <v>1</v>
@@ -3114,7 +3135,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
@@ -3166,7 +3187,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D19" s="16">
         <v>0</v>
@@ -3209,10 +3230,10 @@
         <v>46295</v>
       </c>
       <c r="T19" s="28" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="U19" s="33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V19" s="20">
         <v>46203</v>
@@ -3226,7 +3247,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D20" s="16">
         <v>0.9</v>
@@ -3267,7 +3288,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21" s="16">
         <v>0.9</v>
@@ -3296,13 +3317,13 @@
     </row>
     <row r="22" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D22" s="16"/>
       <c r="F22" s="26"/>
@@ -3316,12 +3337,50 @@
       <c r="Q22" s="20"/>
       <c r="R22" s="20"/>
       <c r="T22" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="V22" s="20"/>
     </row>
-    <row r="23" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="V23" s="20"/>
+    <row r="23" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="16">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17">
+        <v>460000</v>
+      </c>
+      <c r="F23" s="17">
+        <v>0</v>
+      </c>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17">
+        <f>E23*0.5</f>
+        <v>230000</v>
+      </c>
+      <c r="I23" s="23"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="17"/>
+      <c r="O23" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P23" s="11">
+        <v>215000</v>
+      </c>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="12"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="20">
+        <v>46209</v>
+      </c>
     </row>
     <row r="24" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="V24" s="20"/>
@@ -3854,7 +3913,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3863,25 +3922,25 @@
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+    <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-    </row>
-    <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="57"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
@@ -3892,20 +3951,23 @@
       <c r="D4" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="5"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="5"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>46185</v>
       </c>
@@ -3917,7 +3979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>46189</v>
       </c>
@@ -3929,7 +3991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>46183</v>
       </c>
@@ -3941,7 +4003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>46185</v>
       </c>
@@ -3953,7 +4015,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>46190</v>
       </c>
@@ -3965,7 +4027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>46190</v>
       </c>
@@ -3977,7 +4039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>46192</v>
       </c>
@@ -3989,7 +4051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>46197</v>
       </c>
@@ -4001,7 +4063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>46198</v>
       </c>
@@ -4013,7 +4075,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>46202</v>
       </c>
@@ -4142,29 +4204,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -4178,10 +4240,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="C5" s="6">
         <v>46174</v>
@@ -4190,15 +4252,15 @@
         <v>46218</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="C6" s="6">
         <v>46152</v>
@@ -5045,28 +5107,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5319,26 +5359,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5355,4 +5398,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73012E8E-3D09-4DC9-B564-16A6C8AD7BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ABA983-CF47-43C6-B364-35D559028165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="102">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -290,21 +290,9 @@
     <t>Details</t>
   </si>
   <si>
-    <t>ปรับปรุงระบบ CRM</t>
-  </si>
-  <si>
-    <t>อัปเดตฟอร์มบันทึกข้อมูลลูกค้าให้รองรับโครงการ Internal</t>
-  </si>
-  <si>
     <t>In Progress</t>
   </si>
   <si>
-    <t>จัดอบรมทีมช่าง</t>
-  </si>
-  <si>
-    <t>อบรมมาตรฐานความปลอดภัยหน้างานประจำไตรมาส</t>
-  </si>
-  <si>
     <t>https://corallife806.sharepoint.com/:x:/s/CoralLife2/IQAgdsPc2zNkQ5C41kKVppzcAUn7FZ408wMYJu9xdLOXGAk?e=Y6xkaQ</t>
   </si>
   <si>
@@ -342,6 +330,24 @@
   </si>
   <si>
     <t xml:space="preserve">07/31/2026 เริ่มเข้าไซต์ </t>
+  </si>
+  <si>
+    <t>ERV - Project Management</t>
+  </si>
+  <si>
+    <t>Dashboard สำหรับ Management</t>
+  </si>
+  <si>
+    <t>สัญญาผู้รับเหมา &amp; Note ของ QT ลูกค้า</t>
+  </si>
+  <si>
+    <t>รอนัดวัน ผู้รับเหมาเข้ามาประชุม</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find contractor </t>
+  </si>
+  <si>
+    <t>หาผู้รับเหมาเพิ่มเติม เจ้าเล็กๆ อีก 2 เจ้า</t>
   </si>
 </sst>
 </file>
@@ -441,7 +447,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -817,32 +823,32 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1248,34 +1254,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1313,7 +1319,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="63" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1333,14 +1339,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="60">
+      <c r="I5" s="64">
         <v>46213</v>
       </c>
-      <c r="J5" s="60"/>
+      <c r="J5" s="64"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="63"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1358,12 +1364,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="59"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="65"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="57" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1383,14 +1389,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="58" t="s">
+      <c r="I7" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="58"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1408,12 +1414,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="63"/>
-      <c r="J8" s="59"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="65"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="57" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1433,14 +1439,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="58">
+      <c r="I9" s="59">
         <v>46218</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="63"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1458,12 +1464,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="63"/>
-      <c r="J10" s="59"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="65"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="57" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1483,14 +1489,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="58">
+      <c r="I11" s="59">
         <v>46171</v>
       </c>
-      <c r="J11" s="58"/>
+      <c r="J11" s="59"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="63"/>
+      <c r="A12" s="58"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1508,12 +1514,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="63"/>
-      <c r="J12" s="59"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="65"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="57" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1533,14 +1539,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="58" t="s">
+      <c r="I13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="58"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="63"/>
+      <c r="A14" s="58"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1558,12 +1564,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="63"/>
-      <c r="J14" s="59"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="65"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="57" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1583,14 +1589,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15" s="59">
         <v>46199</v>
       </c>
-      <c r="J15" s="58"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="63"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1608,12 +1614,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="63"/>
-      <c r="J16" s="59"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="65"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="62" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1640,7 +1646,7 @@
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="63"/>
+      <c r="A18" s="58"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1658,12 +1664,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="63"/>
-      <c r="J18" s="59"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="65"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="62" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1690,7 +1696,7 @@
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="63"/>
+      <c r="A20" s="58"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1708,12 +1714,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="63"/>
-      <c r="J20" s="59"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="65"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="57" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1733,14 +1739,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="58">
+      <c r="I21" s="59">
         <v>46336</v>
       </c>
-      <c r="J21" s="58"/>
+      <c r="J21" s="59"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="63"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1758,12 +1764,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="63"/>
-      <c r="J22" s="59"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="65"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="57" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1783,14 +1789,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="58">
+      <c r="I23" s="59">
         <v>46218</v>
       </c>
-      <c r="J23" s="58"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="63"/>
+      <c r="A24" s="58"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1808,12 +1814,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="63"/>
-      <c r="J24" s="59"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="65"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="62" t="s">
+      <c r="A25" s="57" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1833,14 +1839,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="58">
+      <c r="I25" s="59">
         <v>46188</v>
       </c>
-      <c r="J25" s="58"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="63"/>
+      <c r="A26" s="58"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1858,12 +1864,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="63"/>
-      <c r="J26" s="59"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="65"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="57" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1883,14 +1889,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="58">
+      <c r="I27" s="59">
         <v>46321</v>
       </c>
-      <c r="J27" s="58"/>
+      <c r="J27" s="59"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="63"/>
+      <c r="A28" s="58"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -1908,12 +1914,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="63"/>
-      <c r="J28" s="59"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="65"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="57" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -1933,14 +1939,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="58">
+      <c r="I29" s="59">
         <v>46139</v>
       </c>
-      <c r="J29" s="58"/>
+      <c r="J29" s="59"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="63"/>
+      <c r="A30" s="58"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -1958,12 +1964,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="63"/>
-      <c r="J30" s="59"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="65"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="57" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -1983,14 +1989,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="58">
+      <c r="I31" s="59">
         <v>46133</v>
       </c>
-      <c r="J31" s="58"/>
+      <c r="J31" s="59"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="63"/>
+      <c r="A32" s="58"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2008,12 +2014,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="63"/>
-      <c r="J32" s="59"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="65"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="62" t="s">
+      <c r="A33" s="57" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2033,14 +2039,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="58">
+      <c r="I33" s="59">
         <v>46295</v>
       </c>
-      <c r="J33" s="58"/>
+      <c r="J33" s="59"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="63"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2058,12 +2064,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="63"/>
-      <c r="J34" s="59"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="65"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="62" t="s">
+      <c r="A35" s="57" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2083,14 +2089,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="58">
+      <c r="I35" s="59">
         <v>45737</v>
       </c>
-      <c r="J35" s="58"/>
+      <c r="J35" s="59"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="63"/>
+      <c r="A36" s="58"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2108,12 +2114,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="63"/>
-      <c r="J36" s="59"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="65"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="62" t="s">
+      <c r="A37" s="57" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2133,14 +2139,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="58">
+      <c r="I37" s="59">
         <v>45737</v>
       </c>
-      <c r="J37" s="58"/>
+      <c r="J37" s="59"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="63"/>
+      <c r="A38" s="58"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2158,12 +2164,49 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="63"/>
-      <c r="J38" s="59"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="65"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2180,43 +2223,6 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2232,7 +2238,7 @@
   <dimension ref="A1:V189"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="6" width="16" customWidth="1"/>
     <col min="7" max="8" width="15" customWidth="1"/>
@@ -2246,62 +2252,62 @@
     <col min="16" max="16" width="18" customWidth="1"/>
     <col min="17" max="18" width="13" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="61" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="99.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
     </row>
     <row r="4" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2426,7 +2432,7 @@
         <v>50</v>
       </c>
       <c r="U5" s="30" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="V5" s="20"/>
     </row>
@@ -2544,7 +2550,7 @@
         <v>52</v>
       </c>
       <c r="U7" s="30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="V7" s="20"/>
     </row>
@@ -2603,7 +2609,7 @@
       <c r="S8" s="15"/>
       <c r="T8" s="27"/>
       <c r="U8" s="32" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V8" s="20">
         <v>46134</v>
@@ -2714,7 +2720,7 @@
       <c r="S10" s="15"/>
       <c r="T10" s="28"/>
       <c r="U10" s="32" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V10" s="20">
         <v>46141</v>
@@ -2776,7 +2782,7 @@
         <v>64</v>
       </c>
       <c r="U11" s="32" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="V11" s="20">
         <v>46147</v>
@@ -2892,7 +2898,7 @@
         <v>51</v>
       </c>
       <c r="U13" s="32" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="V13" s="20">
         <v>46147</v>
@@ -3065,7 +3071,7 @@
         <v>51</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="V16" s="20">
         <v>46182</v>
@@ -3230,10 +3236,10 @@
         <v>46295</v>
       </c>
       <c r="T19" s="28" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="U19" s="33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V19" s="20">
         <v>46203</v>
@@ -3317,13 +3323,13 @@
     </row>
     <row r="22" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D22" s="16"/>
       <c r="F22" s="26"/>
@@ -3337,13 +3343,13 @@
       <c r="Q22" s="20"/>
       <c r="R22" s="20"/>
       <c r="T22" s="28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="V22" s="20"/>
     </row>
     <row r="23" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>22</v>
@@ -3923,20 +3929,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3951,8 +3957,8 @@
       <c r="D4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="55" t="s">
-        <v>97</v>
+      <c r="E4" s="66" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -4197,29 +4203,29 @@
   <dimension ref="A1:E200"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="2" max="2" width="45.77734375" customWidth="1"/>
-    <col min="3" max="4" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4239,44 +4245,55 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="6">
+        <v>46204</v>
+      </c>
+      <c r="D5" s="6">
+        <v>46224</v>
+      </c>
+      <c r="E5" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="6">
-        <v>46174</v>
-      </c>
-      <c r="D5" s="6">
-        <v>46218</v>
-      </c>
-      <c r="E5" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>86</v>
+      <c r="A6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C6" s="6">
-        <v>46152</v>
+        <v>46204</v>
       </c>
       <c r="D6" s="6">
-        <v>46154</v>
+        <v>46224</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="A7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="6">
+        <v>46204</v>
+      </c>
+      <c r="D7" s="6">
+        <v>46224</v>
+      </c>
+      <c r="E7" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -5097,7 +5114,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E200" xr:uid="{0ABCEF69-CFAC-437F-9DF5-474C398D3B95}">
       <formula1>"In Progress,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -5107,6 +5124,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5359,19 +5389,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5382,6 +5399,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5400,17 +5428,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ABA983-CF47-43C6-B364-35D559028165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE7CD41-88BB-4BAB-85B4-D981A68DFE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="103">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>หาผู้รับเหมาเพิ่มเติม เจ้าเล็กๆ อีก 2 เจ้า</t>
+  </si>
+  <si>
+    <t>รองานโครงสร้าง ปลายเดือน 7/26 สามารถเข้าดูหน้างานได้</t>
   </si>
 </sst>
 </file>
@@ -823,32 +826,32 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1254,34 +1257,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1319,7 +1322,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="66" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1339,14 +1342,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="64">
+      <c r="I5" s="60">
         <v>46213</v>
       </c>
-      <c r="J5" s="64"/>
+      <c r="J5" s="60"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="58"/>
+      <c r="A6" s="63"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1364,12 +1367,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="58"/>
-      <c r="J6" s="65"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="59"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1389,14 +1392,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="59"/>
+      <c r="J7" s="58"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="58"/>
+      <c r="A8" s="63"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1414,12 +1417,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="58"/>
-      <c r="J8" s="65"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="59"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="62" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1439,14 +1442,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="58">
         <v>46218</v>
       </c>
-      <c r="J9" s="59"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="58"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1464,12 +1467,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="58"/>
-      <c r="J10" s="65"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="59"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="62" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1489,14 +1492,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="58">
         <v>46171</v>
       </c>
-      <c r="J11" s="59"/>
+      <c r="J11" s="58"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="58"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1514,12 +1517,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="58"/>
-      <c r="J12" s="65"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="62" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1539,14 +1542,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="59" t="s">
+      <c r="I13" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="59"/>
+      <c r="J13" s="58"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="58"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1564,12 +1567,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="58"/>
-      <c r="J14" s="65"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="59"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="62" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1589,14 +1592,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="59">
+      <c r="I15" s="58">
         <v>46199</v>
       </c>
-      <c r="J15" s="59"/>
+      <c r="J15" s="58"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="58"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1614,12 +1617,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="58"/>
-      <c r="J16" s="65"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="59"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="64" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1646,7 +1649,7 @@
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="58"/>
+      <c r="A18" s="63"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1664,12 +1667,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="58"/>
-      <c r="J18" s="65"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="59"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="64" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1696,7 +1699,7 @@
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="58"/>
+      <c r="A20" s="63"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1714,12 +1717,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="58"/>
-      <c r="J20" s="65"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="59"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="62" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1739,14 +1742,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="58">
         <v>46336</v>
       </c>
-      <c r="J21" s="59"/>
+      <c r="J21" s="58"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="58"/>
+      <c r="A22" s="63"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1764,12 +1767,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="58"/>
-      <c r="J22" s="65"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="59"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="62" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1789,14 +1792,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="59">
+      <c r="I23" s="58">
         <v>46218</v>
       </c>
-      <c r="J23" s="59"/>
+      <c r="J23" s="58"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="58"/>
+      <c r="A24" s="63"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1814,12 +1817,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="58"/>
-      <c r="J24" s="65"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="59"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="62" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1839,14 +1842,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="59">
+      <c r="I25" s="58">
         <v>46188</v>
       </c>
-      <c r="J25" s="59"/>
+      <c r="J25" s="58"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="58"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1864,12 +1867,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="58"/>
-      <c r="J26" s="65"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="59"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="62" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1889,14 +1892,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="59">
+      <c r="I27" s="58">
         <v>46321</v>
       </c>
-      <c r="J27" s="59"/>
+      <c r="J27" s="58"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="58"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -1914,12 +1917,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="58"/>
-      <c r="J28" s="65"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="59"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="62" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -1939,14 +1942,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="59">
+      <c r="I29" s="58">
         <v>46139</v>
       </c>
-      <c r="J29" s="59"/>
+      <c r="J29" s="58"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="58"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -1964,12 +1967,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="58"/>
-      <c r="J30" s="65"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="59"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="62" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -1989,14 +1992,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="59">
+      <c r="I31" s="58">
         <v>46133</v>
       </c>
-      <c r="J31" s="59"/>
+      <c r="J31" s="58"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="58"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2014,12 +2017,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="58"/>
-      <c r="J32" s="65"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="59"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="57" t="s">
+      <c r="A33" s="62" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2039,14 +2042,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="59">
+      <c r="I33" s="58">
         <v>46295</v>
       </c>
-      <c r="J33" s="59"/>
+      <c r="J33" s="58"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="58"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2064,12 +2067,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="58"/>
-      <c r="J34" s="65"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="59"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="57" t="s">
+      <c r="A35" s="62" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2089,14 +2092,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="58">
         <v>45737</v>
       </c>
-      <c r="J35" s="59"/>
+      <c r="J35" s="58"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="58"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2114,12 +2117,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="58"/>
-      <c r="J36" s="65"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="59"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="57" t="s">
+      <c r="A37" s="62" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2139,14 +2142,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="59">
+      <c r="I37" s="58">
         <v>45737</v>
       </c>
-      <c r="J37" s="59"/>
+      <c r="J37" s="58"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="58"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2164,26 +2167,35 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="58"/>
-      <c r="J38" s="65"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="59"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2200,29 +2212,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2258,56 +2261,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
     </row>
     <row r="4" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2488,7 +2491,7 @@
       </c>
       <c r="S6" s="15"/>
       <c r="T6" s="27" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="U6" s="27"/>
       <c r="V6" s="20"/>
@@ -3929,20 +3932,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3957,7 +3960,7 @@
       <c r="D4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="55" t="s">
         <v>93</v>
       </c>
     </row>
@@ -4210,22 +4213,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -5124,19 +5127,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5389,6 +5379,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5399,17 +5402,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5428,6 +5420,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE7CD41-88BB-4BAB-85B4-D981A68DFE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C364ABD8-3C3C-4826-9BA3-EE46484E356E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="106">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -351,6 +351,15 @@
   </si>
   <si>
     <t>รองานโครงสร้าง ปลายเดือน 7/26 สามารถเข้าดูหน้างานได้</t>
+  </si>
+  <si>
+    <t>The Grand Pinkao</t>
+  </si>
+  <si>
+    <t>บริษัท NAME 7 AIR</t>
+  </si>
+  <si>
+    <t>รอสรุปแผนงานหลังจากสำรวจหน้างาน</t>
   </si>
 </sst>
 </file>
@@ -672,7 +681,7 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -851,6 +860,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2924,15 +2936,15 @@
         <v>1707089</v>
       </c>
       <c r="F14" s="17">
-        <f>P14*0.3</f>
-        <v>197003.709</v>
+        <f>P14*0.8</f>
+        <v>525343.22400000005</v>
       </c>
       <c r="G14" s="17">
         <v>215</v>
       </c>
       <c r="H14" s="17">
-        <f t="shared" si="0"/>
-        <v>682835.60000000009</v>
+        <f>E14*0.8</f>
+        <v>1365671.2000000002</v>
       </c>
       <c r="I14" s="21">
         <v>10</v>
@@ -3391,8 +3403,55 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
-      <c r="V24" s="20"/>
+    <row r="24" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="16">
+        <v>0</v>
+      </c>
+      <c r="E24" s="17">
+        <v>203880</v>
+      </c>
+      <c r="F24" s="17">
+        <v>0</v>
+      </c>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17">
+        <f>E24*0.4</f>
+        <v>81552</v>
+      </c>
+      <c r="I24" s="23"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="17">
+        <f>36480/2</f>
+        <v>18240</v>
+      </c>
+      <c r="N24" s="67">
+        <f>82500-P24</f>
+        <v>17500</v>
+      </c>
+      <c r="O24" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="P24" s="11">
+        <v>65000</v>
+      </c>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="12"/>
+      <c r="T24" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="U24" s="33"/>
+      <c r="V24" s="20">
+        <v>46213</v>
+      </c>
     </row>
     <row r="25" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
       <c r="V25" s="20"/>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C364ABD8-3C3C-4826-9BA3-EE46484E356E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CB2A7A-2962-4EAB-A878-3182C00F76EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="130">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -360,18 +360,91 @@
   </si>
   <si>
     <t>รอสรุปแผนงานหลังจากสำรวจหน้างาน</t>
+  </si>
+  <si>
+    <t>Phanasorn</t>
+  </si>
+  <si>
+    <t>ตรวจสอบหน้างานก่อนติดตั้ง</t>
+  </si>
+  <si>
+    <t>Prawet Resident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P'Gummy </t>
+  </si>
+  <si>
+    <t>K'Issara House</t>
+  </si>
+  <si>
+    <t>S'rin House</t>
+  </si>
+  <si>
+    <t>28-คุณเต้ย หมู่บ้านรัตนาวดี</t>
+  </si>
+  <si>
+    <t>D'Land</t>
+  </si>
+  <si>
+    <t>K'Pong House</t>
+  </si>
+  <si>
+    <t>K'Sarut House</t>
+  </si>
+  <si>
+    <t>ตรวจสอบงานติดตั้ง 2nd Fix</t>
+  </si>
+  <si>
+    <t>เปิดฝ้า,ติดตั้งหน้างาน</t>
+  </si>
+  <si>
+    <t>ส่งมอบงาน</t>
+  </si>
+  <si>
+    <t>ตรวจสอบเปิดฝ้าหน้างานก่อนติดตั้ง</t>
+  </si>
+  <si>
+    <t>ติดตามหน้างาน Firt fix</t>
+  </si>
+  <si>
+    <t>สำรวจหน้างาน</t>
+  </si>
+  <si>
+    <t>ส่งเอกสารวางบิล</t>
+  </si>
+  <si>
+    <t>ติดตามหน้างาน Firt fix ก่อนปิดฝ้า</t>
+  </si>
+  <si>
+    <t>ติดตามหน้างาน</t>
+  </si>
+  <si>
+    <t>K'Bamrung House</t>
+  </si>
+  <si>
+    <t>ส่งมอบงาน Firt fix</t>
+  </si>
+  <si>
+    <t>ส่งมอบงาน งวดสุดท้าย</t>
+  </si>
+  <si>
+    <t>Site Meeting</t>
+  </si>
+  <si>
+    <t>กันตพัฒน์ มากมูล</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,6 +535,14 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="222"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -676,10 +757,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -836,36 +918,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Comma 2 2 3 2" xfId="3" xr:uid="{10CA6883-C0B4-442D-A7D0-FF27A9ED468E}"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -1255,7 +1338,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1268,37 +1351,37 @@
     <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:11" ht="17.399999999999999">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-    </row>
-    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+    </row>
+    <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1333,8 +1416,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="66" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="65" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1354,14 +1437,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="60">
+      <c r="I5" s="66">
         <v>46213</v>
       </c>
-      <c r="J5" s="60"/>
+      <c r="J5" s="66"/>
       <c r="K5" s="49"/>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="63"/>
+    <row r="6" spans="1:11" ht="15" thickBot="1">
+      <c r="A6" s="61"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1379,12 +1462,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="59"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="67"/>
       <c r="K6" s="50"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="62" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" s="60" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1404,14 +1487,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="58" t="s">
+      <c r="I7" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="58"/>
+      <c r="J7" s="62"/>
       <c r="K7" s="51"/>
     </row>
-    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63"/>
+    <row r="8" spans="1:11" ht="15" thickBot="1">
+      <c r="A8" s="61"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1429,12 +1512,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="63"/>
-      <c r="J8" s="59"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="67"/>
       <c r="K8" s="50"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="62" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="60" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1454,14 +1537,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="58">
+      <c r="I9" s="62">
         <v>46218</v>
       </c>
-      <c r="J9" s="58"/>
+      <c r="J9" s="62"/>
       <c r="K9" s="51"/>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="63"/>
+    <row r="10" spans="1:11" ht="15" thickBot="1">
+      <c r="A10" s="61"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1479,12 +1562,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="63"/>
-      <c r="J10" s="59"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="67"/>
       <c r="K10" s="50"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="62" t="s">
+    <row r="11" spans="1:11">
+      <c r="A11" s="60" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1504,14 +1587,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="58">
+      <c r="I11" s="62">
         <v>46171</v>
       </c>
-      <c r="J11" s="58"/>
+      <c r="J11" s="62"/>
       <c r="K11" s="51"/>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="63"/>
+    <row r="12" spans="1:11" ht="15" thickBot="1">
+      <c r="A12" s="61"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1529,12 +1612,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="63"/>
-      <c r="J12" s="59"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="67"/>
       <c r="K12" s="50"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="62" t="s">
+    <row r="13" spans="1:11">
+      <c r="A13" s="60" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1554,14 +1637,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="58" t="s">
+      <c r="I13" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="58"/>
+      <c r="J13" s="62"/>
       <c r="K13" s="51"/>
     </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="63"/>
+    <row r="14" spans="1:11" ht="15" thickBot="1">
+      <c r="A14" s="61"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1579,12 +1662,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="63"/>
-      <c r="J14" s="59"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="67"/>
       <c r="K14" s="50"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="62" t="s">
+    <row r="15" spans="1:11">
+      <c r="A15" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1604,14 +1687,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15" s="62">
         <v>46199</v>
       </c>
-      <c r="J15" s="58"/>
+      <c r="J15" s="62"/>
       <c r="K15" s="51"/>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="63"/>
+    <row r="16" spans="1:11" ht="15" thickBot="1">
+      <c r="A16" s="61"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1629,11 +1712,11 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="63"/>
-      <c r="J16" s="59"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="67"/>
       <c r="K16" s="50"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17" s="64" t="s">
         <v>21</v>
       </c>
@@ -1654,14 +1737,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="61">
+      <c r="I17" s="63">
         <v>46305</v>
       </c>
-      <c r="J17" s="61"/>
+      <c r="J17" s="63"/>
       <c r="K17" s="52"/>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="63"/>
+    <row r="18" spans="1:11" ht="15" thickBot="1">
+      <c r="A18" s="61"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1679,11 +1762,11 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="63"/>
-      <c r="J18" s="59"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="67"/>
       <c r="K18" s="50"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19" s="64" t="s">
         <v>23</v>
       </c>
@@ -1704,14 +1787,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="63">
         <v>46336</v>
       </c>
-      <c r="J19" s="61"/>
+      <c r="J19" s="63"/>
       <c r="K19" s="52"/>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="63"/>
+    <row r="20" spans="1:11" ht="15" thickBot="1">
+      <c r="A20" s="61"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1729,12 +1812,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="63"/>
-      <c r="J20" s="59"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="67"/>
       <c r="K20" s="50"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="62" t="s">
+    <row r="21" spans="1:11">
+      <c r="A21" s="60" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1754,14 +1837,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="58">
+      <c r="I21" s="62">
         <v>46336</v>
       </c>
-      <c r="J21" s="58"/>
+      <c r="J21" s="62"/>
       <c r="K21" s="53"/>
     </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="63"/>
+    <row r="22" spans="1:11" ht="15" thickBot="1">
+      <c r="A22" s="61"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1779,12 +1862,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="63"/>
-      <c r="J22" s="59"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="67"/>
       <c r="K22" s="54"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="62" t="s">
+    <row r="23" spans="1:11">
+      <c r="A23" s="60" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1804,14 +1887,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="58">
+      <c r="I23" s="62">
         <v>46218</v>
       </c>
-      <c r="J23" s="58"/>
+      <c r="J23" s="62"/>
       <c r="K23" s="53"/>
     </row>
-    <row r="24" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="63"/>
+    <row r="24" spans="1:11" ht="15" thickBot="1">
+      <c r="A24" s="61"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1829,12 +1912,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="63"/>
-      <c r="J24" s="59"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="67"/>
       <c r="K24" s="54"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="62" t="s">
+    <row r="25" spans="1:11">
+      <c r="A25" s="60" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1854,14 +1937,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="58">
+      <c r="I25" s="62">
         <v>46188</v>
       </c>
-      <c r="J25" s="58"/>
+      <c r="J25" s="62"/>
       <c r="K25" s="53"/>
     </row>
-    <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="63"/>
+    <row r="26" spans="1:11" ht="15" thickBot="1">
+      <c r="A26" s="61"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1879,12 +1962,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="63"/>
-      <c r="J26" s="59"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="67"/>
       <c r="K26" s="54"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="62" t="s">
+    <row r="27" spans="1:11">
+      <c r="A27" s="60" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1904,14 +1987,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="58">
+      <c r="I27" s="62">
         <v>46321</v>
       </c>
-      <c r="J27" s="58"/>
+      <c r="J27" s="62"/>
       <c r="K27" s="53"/>
     </row>
-    <row r="28" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="63"/>
+    <row r="28" spans="1:11" ht="15" thickBot="1">
+      <c r="A28" s="61"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -1929,12 +2012,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="63"/>
-      <c r="J28" s="59"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="67"/>
       <c r="K28" s="54"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="62" t="s">
+    <row r="29" spans="1:11">
+      <c r="A29" s="60" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -1954,14 +2037,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="58">
+      <c r="I29" s="62">
         <v>46139</v>
       </c>
-      <c r="J29" s="58"/>
+      <c r="J29" s="62"/>
       <c r="K29" s="53"/>
     </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="63"/>
+    <row r="30" spans="1:11" ht="15" thickBot="1">
+      <c r="A30" s="61"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -1979,12 +2062,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="63"/>
-      <c r="J30" s="59"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="67"/>
       <c r="K30" s="54"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="62" t="s">
+    <row r="31" spans="1:11">
+      <c r="A31" s="60" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2004,14 +2087,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="58">
+      <c r="I31" s="62">
         <v>46133</v>
       </c>
-      <c r="J31" s="58"/>
+      <c r="J31" s="62"/>
       <c r="K31" s="53"/>
     </row>
-    <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="63"/>
+    <row r="32" spans="1:11" ht="15" thickBot="1">
+      <c r="A32" s="61"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2029,12 +2112,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="63"/>
-      <c r="J32" s="59"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="67"/>
       <c r="K32" s="54"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="62" t="s">
+    <row r="33" spans="1:11">
+      <c r="A33" s="60" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2054,14 +2137,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="58">
+      <c r="I33" s="62">
         <v>46295</v>
       </c>
-      <c r="J33" s="58"/>
+      <c r="J33" s="62"/>
       <c r="K33" s="53"/>
     </row>
-    <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="63"/>
+    <row r="34" spans="1:11" ht="15" thickBot="1">
+      <c r="A34" s="61"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2079,12 +2162,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="63"/>
-      <c r="J34" s="59"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="67"/>
       <c r="K34" s="54"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="62" t="s">
+    <row r="35" spans="1:11">
+      <c r="A35" s="60" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2104,14 +2187,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="58">
+      <c r="I35" s="62">
         <v>45737</v>
       </c>
-      <c r="J35" s="58"/>
+      <c r="J35" s="62"/>
       <c r="K35" s="53"/>
     </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="63"/>
+    <row r="36" spans="1:11" ht="15" thickBot="1">
+      <c r="A36" s="61"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2129,12 +2212,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="63"/>
-      <c r="J36" s="59"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="67"/>
       <c r="K36" s="54"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="62" t="s">
+    <row r="37" spans="1:11">
+      <c r="A37" s="60" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2154,14 +2237,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="58">
+      <c r="I37" s="62">
         <v>45737</v>
       </c>
-      <c r="J37" s="58"/>
+      <c r="J37" s="62"/>
       <c r="K37" s="53"/>
     </row>
-    <row r="38" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="63"/>
+    <row r="38" spans="1:11" ht="15" thickBot="1">
+      <c r="A38" s="61"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2179,12 +2262,49 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="63"/>
-      <c r="J38" s="59"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="67"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2201,43 +2321,6 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2251,7 +2334,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V189"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -2272,59 +2355,59 @@
     <col min="22" max="22" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:22" ht="17.399999999999999">
+      <c r="A1" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-    </row>
-    <row r="4" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+    </row>
+    <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2392,7 +2475,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
@@ -2451,7 +2534,7 @@
       </c>
       <c r="V5" s="20"/>
     </row>
-    <row r="6" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A6" s="15" t="s">
         <v>14</v>
       </c>
@@ -2473,7 +2556,7 @@
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17">
-        <f t="shared" ref="H6:H14" si="0">E6*0.4</f>
+        <f t="shared" ref="H6:H13" si="0">E6*0.4</f>
         <v>163839.85600000003</v>
       </c>
       <c r="I6" s="18">
@@ -2508,7 +2591,7 @@
       <c r="U6" s="27"/>
       <c r="V6" s="20"/>
     </row>
-    <row r="7" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A7" s="15" t="s">
         <v>17</v>
       </c>
@@ -2569,7 +2652,7 @@
       </c>
       <c r="V7" s="20"/>
     </row>
-    <row r="8" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A8" s="15" t="s">
         <v>18</v>
       </c>
@@ -2630,7 +2713,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A9" s="15" t="s">
         <v>19</v>
       </c>
@@ -2680,7 +2763,7 @@
       <c r="U9" s="27"/>
       <c r="V9" s="20"/>
     </row>
-    <row r="10" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A10" s="10" t="s">
         <v>20</v>
       </c>
@@ -2741,7 +2824,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -2803,7 +2886,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A12" s="10" t="s">
         <v>23</v>
       </c>
@@ -2862,7 +2945,7 @@
         <v>46331</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
@@ -2919,7 +3002,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
@@ -2979,7 +3062,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A15" s="10" t="s">
         <v>26</v>
       </c>
@@ -3035,7 +3118,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A16" s="10" t="s">
         <v>27</v>
       </c>
@@ -3092,7 +3175,7 @@
         <v>46182</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A17" s="10" t="s">
         <v>28</v>
       </c>
@@ -3148,7 +3231,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="18" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A18" s="10" t="s">
         <v>29</v>
       </c>
@@ -3200,7 +3283,7 @@
       <c r="U18" s="27"/>
       <c r="V18" s="20"/>
     </row>
-    <row r="19" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A19" s="10" t="s">
         <v>30</v>
       </c>
@@ -3260,7 +3343,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A20" s="10" t="s">
         <v>31</v>
       </c>
@@ -3301,7 +3384,7 @@
       <c r="U20" s="27"/>
       <c r="V20" s="20"/>
     </row>
-    <row r="21" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A21" s="10" t="s">
         <v>32</v>
       </c>
@@ -3336,7 +3419,7 @@
       </c>
       <c r="V21" s="20"/>
     </row>
-    <row r="22" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A22" s="10" t="s">
         <v>90</v>
       </c>
@@ -3362,7 +3445,7 @@
       </c>
       <c r="V22" s="20"/>
     </row>
-    <row r="23" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A23" s="10" t="s">
         <v>94</v>
       </c>
@@ -3403,7 +3486,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="10" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A24" s="10" t="s">
         <v>103</v>
       </c>
@@ -3433,7 +3516,7 @@
         <f>36480/2</f>
         <v>18240</v>
       </c>
-      <c r="N24" s="67">
+      <c r="N24" s="56">
         <f>82500-P24</f>
         <v>17500</v>
       </c>
@@ -3453,499 +3536,499 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V25" s="20"/>
     </row>
-    <row r="26" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V26" s="20"/>
     </row>
-    <row r="27" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V27" s="20"/>
     </row>
-    <row r="28" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V28" s="20"/>
     </row>
-    <row r="29" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V29" s="20"/>
     </row>
-    <row r="30" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V30" s="20"/>
     </row>
-    <row r="31" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V31" s="20"/>
     </row>
-    <row r="32" spans="1:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V32" s="20"/>
     </row>
-    <row r="33" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V33" s="20"/>
     </row>
-    <row r="34" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V34" s="20"/>
     </row>
-    <row r="35" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V35" s="20"/>
     </row>
-    <row r="36" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V36" s="20"/>
     </row>
-    <row r="37" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V37" s="20"/>
     </row>
-    <row r="38" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V38" s="20"/>
     </row>
-    <row r="39" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V39" s="20"/>
     </row>
-    <row r="40" spans="22:22" s="14" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
       <c r="V40" s="20"/>
     </row>
-    <row r="41" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V41" s="20"/>
     </row>
-    <row r="42" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V42" s="20"/>
     </row>
-    <row r="43" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V43" s="20"/>
     </row>
-    <row r="44" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V44" s="20"/>
     </row>
-    <row r="45" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V45" s="20"/>
     </row>
-    <row r="46" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V46" s="20"/>
     </row>
-    <row r="47" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V47" s="20"/>
     </row>
-    <row r="48" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V48" s="20"/>
     </row>
-    <row r="49" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V49" s="20"/>
     </row>
-    <row r="50" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V50" s="20"/>
     </row>
-    <row r="51" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V51" s="20"/>
     </row>
-    <row r="52" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V52" s="20"/>
     </row>
-    <row r="53" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V53" s="20"/>
     </row>
-    <row r="54" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V54" s="20"/>
     </row>
-    <row r="55" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V55" s="20"/>
     </row>
-    <row r="56" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V56" s="20"/>
     </row>
-    <row r="57" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V57" s="20"/>
     </row>
-    <row r="58" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V58" s="20"/>
     </row>
-    <row r="59" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V59" s="20"/>
     </row>
-    <row r="60" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V60" s="20"/>
     </row>
-    <row r="61" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V61" s="20"/>
     </row>
-    <row r="62" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V62" s="20"/>
     </row>
-    <row r="63" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V63" s="20"/>
     </row>
-    <row r="64" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V64" s="20"/>
     </row>
-    <row r="65" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V65" s="20"/>
     </row>
-    <row r="66" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V66" s="20"/>
     </row>
-    <row r="67" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V67" s="20"/>
     </row>
-    <row r="68" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V68" s="20"/>
     </row>
-    <row r="69" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V69" s="20"/>
     </row>
-    <row r="70" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V70" s="20"/>
     </row>
-    <row r="71" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V71" s="20"/>
     </row>
-    <row r="72" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V72" s="20"/>
     </row>
-    <row r="73" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V73" s="20"/>
     </row>
-    <row r="74" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V74" s="20"/>
     </row>
-    <row r="75" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V75" s="20"/>
     </row>
-    <row r="76" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V76" s="20"/>
     </row>
-    <row r="77" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V77" s="20"/>
     </row>
-    <row r="78" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V78" s="20"/>
     </row>
-    <row r="79" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V79" s="20"/>
     </row>
-    <row r="80" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V80" s="20"/>
     </row>
-    <row r="81" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V81" s="20"/>
     </row>
-    <row r="82" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V82" s="20"/>
     </row>
-    <row r="83" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V83" s="20"/>
     </row>
-    <row r="84" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V84" s="20"/>
     </row>
-    <row r="85" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V85" s="20"/>
     </row>
-    <row r="86" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V86" s="20"/>
     </row>
-    <row r="87" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V87" s="20"/>
     </row>
-    <row r="88" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V88" s="20"/>
     </row>
-    <row r="89" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V89" s="20"/>
     </row>
-    <row r="90" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V90" s="20"/>
     </row>
-    <row r="91" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V91" s="20"/>
     </row>
-    <row r="92" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V92" s="20"/>
     </row>
-    <row r="93" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V93" s="20"/>
     </row>
-    <row r="94" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V94" s="20"/>
     </row>
-    <row r="95" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V95" s="20"/>
     </row>
-    <row r="96" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V96" s="20"/>
     </row>
-    <row r="97" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V97" s="20"/>
     </row>
-    <row r="98" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V98" s="20"/>
     </row>
-    <row r="99" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V99" s="20"/>
     </row>
-    <row r="100" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V100" s="20"/>
     </row>
-    <row r="101" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V101" s="20"/>
     </row>
-    <row r="102" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V102" s="20"/>
     </row>
-    <row r="103" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V103" s="20"/>
     </row>
-    <row r="104" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V104" s="20"/>
     </row>
-    <row r="105" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V105" s="20"/>
     </row>
-    <row r="106" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V106" s="20"/>
     </row>
-    <row r="107" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V107" s="20"/>
     </row>
-    <row r="108" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V108" s="20"/>
     </row>
-    <row r="109" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V109" s="20"/>
     </row>
-    <row r="110" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V110" s="20"/>
     </row>
-    <row r="111" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V111" s="20"/>
     </row>
-    <row r="112" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V112" s="20"/>
     </row>
-    <row r="113" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V113" s="20"/>
     </row>
-    <row r="114" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V114" s="20"/>
     </row>
-    <row r="115" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V115" s="20"/>
     </row>
-    <row r="116" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V116" s="20"/>
     </row>
-    <row r="117" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V117" s="20"/>
     </row>
-    <row r="118" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V118" s="20"/>
     </row>
-    <row r="119" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V119" s="20"/>
     </row>
-    <row r="120" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V120" s="20"/>
     </row>
-    <row r="121" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V121" s="20"/>
     </row>
-    <row r="122" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V122" s="20"/>
     </row>
-    <row r="123" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V123" s="20"/>
     </row>
-    <row r="124" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V124" s="20"/>
     </row>
-    <row r="125" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V125" s="20"/>
     </row>
-    <row r="126" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V126" s="20"/>
     </row>
-    <row r="127" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V127" s="20"/>
     </row>
-    <row r="128" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V128" s="20"/>
     </row>
-    <row r="129" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V129" s="20"/>
     </row>
-    <row r="130" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V130" s="20"/>
     </row>
-    <row r="131" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V131" s="20"/>
     </row>
-    <row r="132" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V132" s="20"/>
     </row>
-    <row r="133" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V133" s="20"/>
     </row>
-    <row r="134" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V134" s="20"/>
     </row>
-    <row r="135" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V135" s="20"/>
     </row>
-    <row r="136" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V136" s="20"/>
     </row>
-    <row r="137" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V137" s="20"/>
     </row>
-    <row r="138" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V138" s="20"/>
     </row>
-    <row r="139" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V139" s="20"/>
     </row>
-    <row r="140" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V140" s="20"/>
     </row>
-    <row r="141" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V141" s="20"/>
     </row>
-    <row r="142" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V142" s="20"/>
     </row>
-    <row r="143" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V143" s="20"/>
     </row>
-    <row r="144" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V144" s="20"/>
     </row>
-    <row r="145" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V145" s="20"/>
     </row>
-    <row r="146" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V146" s="20"/>
     </row>
-    <row r="147" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V147" s="20"/>
     </row>
-    <row r="148" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V148" s="20"/>
     </row>
-    <row r="149" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V149" s="20"/>
     </row>
-    <row r="150" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V150" s="20"/>
     </row>
-    <row r="151" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V151" s="20"/>
     </row>
-    <row r="152" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V152" s="20"/>
     </row>
-    <row r="153" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V153" s="20"/>
     </row>
-    <row r="154" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V154" s="20"/>
     </row>
-    <row r="155" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V155" s="20"/>
     </row>
-    <row r="156" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V156" s="20"/>
     </row>
-    <row r="157" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V157" s="20"/>
     </row>
-    <row r="158" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V158" s="20"/>
     </row>
-    <row r="159" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V159" s="20"/>
     </row>
-    <row r="160" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V160" s="20"/>
     </row>
-    <row r="161" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V161" s="20"/>
     </row>
-    <row r="162" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V162" s="20"/>
     </row>
-    <row r="163" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V163" s="20"/>
     </row>
-    <row r="164" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V164" s="20"/>
     </row>
-    <row r="165" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V165" s="20"/>
     </row>
-    <row r="166" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V166" s="20"/>
     </row>
-    <row r="167" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V167" s="20"/>
     </row>
-    <row r="168" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V168" s="20"/>
     </row>
-    <row r="169" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V169" s="20"/>
     </row>
-    <row r="170" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V170" s="20"/>
     </row>
-    <row r="171" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V171" s="20"/>
     </row>
-    <row r="172" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V172" s="20"/>
     </row>
-    <row r="173" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V173" s="20"/>
     </row>
-    <row r="174" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V174" s="20"/>
     </row>
-    <row r="175" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V175" s="20"/>
     </row>
-    <row r="176" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V176" s="20"/>
     </row>
-    <row r="177" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V177" s="20"/>
     </row>
-    <row r="178" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V178" s="20"/>
     </row>
-    <row r="179" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V179" s="20"/>
     </row>
-    <row r="180" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V180" s="20"/>
     </row>
-    <row r="181" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V181" s="20"/>
     </row>
-    <row r="182" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V182" s="20"/>
     </row>
-    <row r="183" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V183" s="20"/>
     </row>
-    <row r="184" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V184" s="20"/>
     </row>
-    <row r="185" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V185" s="20"/>
     </row>
-    <row r="186" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V186" s="20"/>
     </row>
-    <row r="187" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V187" s="20"/>
     </row>
-    <row r="188" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V188" s="20"/>
     </row>
-    <row r="189" spans="22:22" s="9" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="V189" s="20"/>
     </row>
   </sheetData>
@@ -3982,31 +4065,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="26.77734375" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:5" ht="17.399999999999999">
+      <c r="A1" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="59"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,229 +4107,343 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="5"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="5"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="6">
         <v>46185</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="C7" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="6">
         <v>46189</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="C8" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D8" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="6">
         <v>46183</v>
       </c>
-      <c r="B9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="C9" s="5" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="6">
         <v>46185</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="C10" s="5" t="s">
         <v>63</v>
       </c>
       <c r="D10" s="8">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="6">
         <v>46190</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="C11" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="6">
         <v>46190</v>
       </c>
-      <c r="B12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="C12" s="5" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="6">
         <v>46192</v>
       </c>
-      <c r="B13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="C13" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D13" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="6">
         <v>46197</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="C14" s="5" t="s">
         <v>63</v>
       </c>
       <c r="D14" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="3">
         <v>46198</v>
       </c>
-      <c r="B15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="C15" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="3">
         <v>46202</v>
       </c>
-      <c r="B16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="C16" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="3">
         <v>46205</v>
       </c>
-      <c r="B17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>114</v>
+      </c>
       <c r="C17" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="3">
         <v>46206</v>
       </c>
-      <c r="B18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>115</v>
+      </c>
       <c r="C18" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D18" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="3">
         <v>46216</v>
       </c>
-      <c r="B19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="C19" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D19" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="3">
         <v>46218</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="C20" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="4">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="4">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="4">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="2"/>
       <c r="D26" s="4"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="2"/>
@@ -4263,7 +4461,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CACF7FE-A4AF-4302-B8F5-800998C4C21C}">
   <dimension ref="A1:E200"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.88671875" bestFit="1" customWidth="1"/>
@@ -4271,25 +4469,25 @@
     <col min="5" max="5" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:5" ht="17.399999999999999">
+      <c r="A1" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>80</v>
       </c>
@@ -4306,7 +4504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>96</v>
       </c>
@@ -4323,7 +4521,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>98</v>
       </c>
@@ -4340,7 +4538,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>100</v>
       </c>
@@ -4357,817 +4555,817 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="6"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="6"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="6"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="6"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="6"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="6"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="6"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="3"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="3"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="3"/>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="3"/>
       <c r="B20" s="5"/>
       <c r="C20" s="6"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:4">
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:4">
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:4">
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:4">
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:4">
       <c r="C37" s="31"/>
       <c r="D37" s="31"/>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:4">
       <c r="C38" s="31"/>
       <c r="D38" s="31"/>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:4">
       <c r="C39" s="31"/>
       <c r="D39" s="31"/>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:4">
       <c r="C40" s="31"/>
       <c r="D40" s="31"/>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:4">
       <c r="C41" s="31"/>
       <c r="D41" s="31"/>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:4">
       <c r="C42" s="31"/>
       <c r="D42" s="31"/>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:4">
       <c r="C43" s="31"/>
       <c r="D43" s="31"/>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:4">
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:4">
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:4">
       <c r="C46" s="31"/>
       <c r="D46" s="31"/>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:4">
       <c r="C47" s="31"/>
       <c r="D47" s="31"/>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:4">
       <c r="C48" s="31"/>
       <c r="D48" s="31"/>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:4">
       <c r="C49" s="31"/>
       <c r="D49" s="31"/>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:4">
       <c r="C50" s="31"/>
       <c r="D50" s="31"/>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:4">
       <c r="C51" s="31"/>
       <c r="D51" s="31"/>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:4">
       <c r="C52" s="31"/>
       <c r="D52" s="31"/>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:4">
       <c r="C53" s="31"/>
       <c r="D53" s="31"/>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:4">
       <c r="C54" s="31"/>
       <c r="D54" s="31"/>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:4">
       <c r="C55" s="31"/>
       <c r="D55" s="31"/>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:4">
       <c r="C56" s="31"/>
       <c r="D56" s="31"/>
     </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:4">
       <c r="C57" s="31"/>
       <c r="D57" s="31"/>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:4">
       <c r="C58" s="31"/>
       <c r="D58" s="31"/>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:4">
       <c r="C59" s="31"/>
       <c r="D59" s="31"/>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:4">
       <c r="C60" s="31"/>
       <c r="D60" s="31"/>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:4">
       <c r="C61" s="31"/>
       <c r="D61" s="31"/>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:4">
       <c r="C62" s="31"/>
       <c r="D62" s="31"/>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:4">
       <c r="C63" s="31"/>
       <c r="D63" s="31"/>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:4">
       <c r="C64" s="31"/>
       <c r="D64" s="31"/>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:4">
       <c r="C65" s="31"/>
       <c r="D65" s="31"/>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:4">
       <c r="C66" s="31"/>
       <c r="D66" s="31"/>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:4">
       <c r="C67" s="31"/>
       <c r="D67" s="31"/>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:4">
       <c r="C68" s="31"/>
       <c r="D68" s="31"/>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:4">
       <c r="C69" s="31"/>
       <c r="D69" s="31"/>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:4">
       <c r="C70" s="31"/>
       <c r="D70" s="31"/>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:4">
       <c r="C71" s="31"/>
       <c r="D71" s="31"/>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:4">
       <c r="C72" s="31"/>
       <c r="D72" s="31"/>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:4">
       <c r="C73" s="31"/>
       <c r="D73" s="31"/>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:4">
       <c r="C74" s="31"/>
       <c r="D74" s="31"/>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:4">
       <c r="C75" s="31"/>
       <c r="D75" s="31"/>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:4">
       <c r="C76" s="31"/>
       <c r="D76" s="31"/>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:4">
       <c r="C77" s="31"/>
       <c r="D77" s="31"/>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:4">
       <c r="C78" s="31"/>
       <c r="D78" s="31"/>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:4">
       <c r="C79" s="31"/>
       <c r="D79" s="31"/>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:4">
       <c r="C80" s="31"/>
       <c r="D80" s="31"/>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:4">
       <c r="C81" s="31"/>
       <c r="D81" s="31"/>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:4">
       <c r="C82" s="31"/>
       <c r="D82" s="31"/>
     </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:4">
       <c r="C83" s="31"/>
       <c r="D83" s="31"/>
     </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:4">
       <c r="C84" s="31"/>
       <c r="D84" s="31"/>
     </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:4">
       <c r="C85" s="31"/>
       <c r="D85" s="31"/>
     </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:4">
       <c r="C86" s="31"/>
       <c r="D86" s="31"/>
     </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:4">
       <c r="C87" s="31"/>
       <c r="D87" s="31"/>
     </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:4">
       <c r="C88" s="31"/>
       <c r="D88" s="31"/>
     </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:4">
       <c r="C89" s="31"/>
       <c r="D89" s="31"/>
     </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:4">
       <c r="C90" s="31"/>
       <c r="D90" s="31"/>
     </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:4">
       <c r="C91" s="31"/>
       <c r="D91" s="31"/>
     </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:4">
       <c r="C92" s="31"/>
       <c r="D92" s="31"/>
     </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:4">
       <c r="C93" s="31"/>
       <c r="D93" s="31"/>
     </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:4">
       <c r="C94" s="31"/>
       <c r="D94" s="31"/>
     </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:4">
       <c r="C95" s="31"/>
       <c r="D95" s="31"/>
     </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:4">
       <c r="C96" s="31"/>
       <c r="D96" s="31"/>
     </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:4">
       <c r="C97" s="31"/>
       <c r="D97" s="31"/>
     </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:4">
       <c r="C98" s="31"/>
       <c r="D98" s="31"/>
     </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:4">
       <c r="C99" s="31"/>
       <c r="D99" s="31"/>
     </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:4">
       <c r="C100" s="31"/>
       <c r="D100" s="31"/>
     </row>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:4">
       <c r="C101" s="31"/>
       <c r="D101" s="31"/>
     </row>
-    <row r="102" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:4">
       <c r="C102" s="31"/>
       <c r="D102" s="31"/>
     </row>
-    <row r="103" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:4">
       <c r="C103" s="31"/>
       <c r="D103" s="31"/>
     </row>
-    <row r="104" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:4">
       <c r="C104" s="31"/>
       <c r="D104" s="31"/>
     </row>
-    <row r="105" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:4">
       <c r="C105" s="31"/>
       <c r="D105" s="31"/>
     </row>
-    <row r="106" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:4">
       <c r="C106" s="31"/>
       <c r="D106" s="31"/>
     </row>
-    <row r="107" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:4">
       <c r="C107" s="31"/>
       <c r="D107" s="31"/>
     </row>
-    <row r="108" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:4">
       <c r="C108" s="31"/>
       <c r="D108" s="31"/>
     </row>
-    <row r="109" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:4">
       <c r="C109" s="31"/>
       <c r="D109" s="31"/>
     </row>
-    <row r="110" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:4">
       <c r="C110" s="31"/>
       <c r="D110" s="31"/>
     </row>
-    <row r="111" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:4">
       <c r="C111" s="31"/>
       <c r="D111" s="31"/>
     </row>
-    <row r="112" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:4">
       <c r="C112" s="31"/>
       <c r="D112" s="31"/>
     </row>
-    <row r="113" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:4">
       <c r="C113" s="31"/>
       <c r="D113" s="31"/>
     </row>
-    <row r="114" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:4">
       <c r="C114" s="31"/>
       <c r="D114" s="31"/>
     </row>
-    <row r="115" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:4">
       <c r="C115" s="31"/>
       <c r="D115" s="31"/>
     </row>
-    <row r="116" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:4">
       <c r="C116" s="31"/>
       <c r="D116" s="31"/>
     </row>
-    <row r="117" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:4">
       <c r="C117" s="31"/>
       <c r="D117" s="31"/>
     </row>
-    <row r="118" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:4">
       <c r="C118" s="31"/>
       <c r="D118" s="31"/>
     </row>
-    <row r="119" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:4">
       <c r="C119" s="31"/>
       <c r="D119" s="31"/>
     </row>
-    <row r="120" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:4">
       <c r="C120" s="31"/>
       <c r="D120" s="31"/>
     </row>
-    <row r="121" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:4">
       <c r="C121" s="31"/>
       <c r="D121" s="31"/>
     </row>
-    <row r="122" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:4">
       <c r="C122" s="31"/>
       <c r="D122" s="31"/>
     </row>
-    <row r="123" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:4">
       <c r="C123" s="31"/>
       <c r="D123" s="31"/>
     </row>
-    <row r="124" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:4">
       <c r="C124" s="31"/>
       <c r="D124" s="31"/>
     </row>
-    <row r="125" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:4">
       <c r="C125" s="31"/>
       <c r="D125" s="31"/>
     </row>
-    <row r="126" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:4">
       <c r="C126" s="31"/>
       <c r="D126" s="31"/>
     </row>
-    <row r="127" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:4">
       <c r="C127" s="31"/>
       <c r="D127" s="31"/>
     </row>
-    <row r="128" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:4">
       <c r="C128" s="31"/>
       <c r="D128" s="31"/>
     </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:4">
       <c r="C129" s="31"/>
       <c r="D129" s="31"/>
     </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:4">
       <c r="C130" s="31"/>
       <c r="D130" s="31"/>
     </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:4">
       <c r="C131" s="31"/>
       <c r="D131" s="31"/>
     </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:4">
       <c r="C132" s="31"/>
       <c r="D132" s="31"/>
     </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:4">
       <c r="C133" s="31"/>
       <c r="D133" s="31"/>
     </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:4">
       <c r="C134" s="31"/>
       <c r="D134" s="31"/>
     </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:4">
       <c r="C135" s="31"/>
       <c r="D135" s="31"/>
     </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:4">
       <c r="C136" s="31"/>
       <c r="D136" s="31"/>
     </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:4">
       <c r="C137" s="31"/>
       <c r="D137" s="31"/>
     </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:4">
       <c r="C138" s="31"/>
       <c r="D138" s="31"/>
     </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:4">
       <c r="C139" s="31"/>
       <c r="D139" s="31"/>
     </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:4">
       <c r="C140" s="31"/>
       <c r="D140" s="31"/>
     </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:4">
       <c r="C141" s="31"/>
       <c r="D141" s="31"/>
     </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:4">
       <c r="C142" s="31"/>
       <c r="D142" s="31"/>
     </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:4">
       <c r="C143" s="31"/>
       <c r="D143" s="31"/>
     </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:4">
       <c r="C144" s="31"/>
       <c r="D144" s="31"/>
     </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:4">
       <c r="C145" s="31"/>
       <c r="D145" s="31"/>
     </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:4">
       <c r="C146" s="31"/>
       <c r="D146" s="31"/>
     </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:4">
       <c r="C147" s="31"/>
       <c r="D147" s="31"/>
     </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:4">
       <c r="C148" s="31"/>
       <c r="D148" s="31"/>
     </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:4">
       <c r="C149" s="31"/>
       <c r="D149" s="31"/>
     </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:4">
       <c r="C150" s="31"/>
       <c r="D150" s="31"/>
     </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:4">
       <c r="C151" s="31"/>
       <c r="D151" s="31"/>
     </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:4">
       <c r="C152" s="31"/>
       <c r="D152" s="31"/>
     </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:4">
       <c r="C153" s="31"/>
       <c r="D153" s="31"/>
     </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:4">
       <c r="C154" s="31"/>
       <c r="D154" s="31"/>
     </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:4">
       <c r="C155" s="31"/>
       <c r="D155" s="31"/>
     </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:4">
       <c r="C156" s="31"/>
       <c r="D156" s="31"/>
     </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:4">
       <c r="C157" s="31"/>
       <c r="D157" s="31"/>
     </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:4">
       <c r="C158" s="31"/>
       <c r="D158" s="31"/>
     </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:4">
       <c r="C159" s="31"/>
       <c r="D159" s="31"/>
     </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:4">
       <c r="C160" s="31"/>
       <c r="D160" s="31"/>
     </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:4">
       <c r="C161" s="31"/>
       <c r="D161" s="31"/>
     </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:4">
       <c r="C162" s="31"/>
       <c r="D162" s="31"/>
     </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:4">
       <c r="C163" s="31"/>
       <c r="D163" s="31"/>
     </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:4">
       <c r="C164" s="31"/>
       <c r="D164" s="31"/>
     </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:4">
       <c r="C165" s="31"/>
       <c r="D165" s="31"/>
     </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:4">
       <c r="C166" s="31"/>
       <c r="D166" s="31"/>
     </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:4">
       <c r="C167" s="31"/>
       <c r="D167" s="31"/>
     </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:4">
       <c r="C168" s="31"/>
       <c r="D168" s="31"/>
     </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:4">
       <c r="C169" s="31"/>
       <c r="D169" s="31"/>
     </row>
-    <row r="170" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:4">
       <c r="C170" s="31"/>
       <c r="D170" s="31"/>
     </row>
-    <row r="171" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:4">
       <c r="C171" s="31"/>
       <c r="D171" s="31"/>
     </row>
-    <row r="172" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:4">
       <c r="C172" s="31"/>
       <c r="D172" s="31"/>
     </row>
-    <row r="173" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:4">
       <c r="C173" s="31"/>
       <c r="D173" s="31"/>
     </row>
-    <row r="174" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:4">
       <c r="C174" s="31"/>
       <c r="D174" s="31"/>
     </row>
-    <row r="175" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:4">
       <c r="C175" s="31"/>
       <c r="D175" s="31"/>
     </row>
-    <row r="176" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:4">
       <c r="C176" s="31"/>
       <c r="D176" s="31"/>
     </row>
-    <row r="177" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:4">
       <c r="C177" s="31"/>
       <c r="D177" s="31"/>
     </row>
-    <row r="178" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:4">
       <c r="C178" s="31"/>
       <c r="D178" s="31"/>
     </row>
-    <row r="179" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:4">
       <c r="C179" s="31"/>
       <c r="D179" s="31"/>
     </row>
-    <row r="180" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:4">
       <c r="C180" s="31"/>
       <c r="D180" s="31"/>
     </row>
-    <row r="181" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:4">
       <c r="C181" s="31"/>
       <c r="D181" s="31"/>
     </row>
-    <row r="182" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:4">
       <c r="C182" s="31"/>
       <c r="D182" s="31"/>
     </row>
-    <row r="183" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:4">
       <c r="C183" s="31"/>
       <c r="D183" s="31"/>
     </row>
-    <row r="184" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:4">
       <c r="C184" s="31"/>
       <c r="D184" s="31"/>
     </row>
-    <row r="185" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:4">
       <c r="C185" s="31"/>
       <c r="D185" s="31"/>
     </row>
-    <row r="186" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="3:4">
       <c r="C186" s="31"/>
       <c r="D186" s="31"/>
     </row>
-    <row r="187" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="3:4">
       <c r="C187" s="31"/>
       <c r="D187" s="31"/>
     </row>
-    <row r="188" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:4">
       <c r="C188" s="31"/>
       <c r="D188" s="31"/>
     </row>
-    <row r="189" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:4">
       <c r="C189" s="31"/>
       <c r="D189" s="31"/>
     </row>
-    <row r="190" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:4">
       <c r="C190" s="31"/>
       <c r="D190" s="31"/>
     </row>
-    <row r="191" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:4">
       <c r="C191" s="31"/>
       <c r="D191" s="31"/>
     </row>
-    <row r="192" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="3:4">
       <c r="C192" s="31"/>
       <c r="D192" s="31"/>
     </row>
-    <row r="193" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:4">
       <c r="C193" s="31"/>
       <c r="D193" s="31"/>
     </row>
-    <row r="194" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:4">
       <c r="C194" s="31"/>
       <c r="D194" s="31"/>
     </row>
-    <row r="195" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:4">
       <c r="C195" s="31"/>
       <c r="D195" s="31"/>
     </row>
-    <row r="196" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:4">
       <c r="C196" s="31"/>
       <c r="D196" s="31"/>
     </row>
-    <row r="197" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:4">
       <c r="C197" s="31"/>
       <c r="D197" s="31"/>
     </row>
-    <row r="198" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:4">
       <c r="C198" s="31"/>
       <c r="D198" s="31"/>
     </row>
-    <row r="199" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:4">
       <c r="C199" s="31"/>
       <c r="D199" s="31"/>
     </row>
-    <row r="200" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:4">
       <c r="C200" s="31"/>
       <c r="D200" s="31"/>
     </row>
@@ -5186,6 +5384,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5438,29 +5658,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5477,23 +5694,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CB2A7A-2962-4EAB-A878-3182C00F76EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A235242E-F928-4DDE-980A-F6C95284F22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4334,7 +4334,7 @@
         <v>61</v>
       </c>
       <c r="D19" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" t="s">
         <v>126</v>
@@ -4351,7 +4351,7 @@
         <v>61</v>
       </c>
       <c r="D20" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
         <v>127</v>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A235242E-F928-4DDE-980A-F6C95284F22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4235C340-25A1-4BE3-93C5-01123C692F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -924,27 +924,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="67" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1437,14 +1437,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="62">
         <v>46213</v>
       </c>
-      <c r="J5" s="66"/>
+      <c r="J5" s="62"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="61"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1462,12 +1462,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="67"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="61"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="64" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1487,14 +1487,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="62" t="s">
+      <c r="I7" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="62"/>
+      <c r="J7" s="60"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="61"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1512,12 +1512,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="61"/>
-      <c r="J8" s="67"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="61"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="64" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1537,14 +1537,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="60">
         <v>46218</v>
       </c>
-      <c r="J9" s="62"/>
+      <c r="J9" s="60"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="61"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1562,12 +1562,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="61"/>
-      <c r="J10" s="67"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="61"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1587,14 +1587,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="60">
         <v>46171</v>
       </c>
-      <c r="J11" s="62"/>
+      <c r="J11" s="60"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="61"/>
+      <c r="A12" s="65"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1612,12 +1612,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="61"/>
-      <c r="J12" s="67"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="61"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="64" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1637,14 +1637,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="62" t="s">
+      <c r="I13" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="62"/>
+      <c r="J13" s="60"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="61"/>
+      <c r="A14" s="65"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1662,12 +1662,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="61"/>
-      <c r="J14" s="67"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="61"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="64" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1687,14 +1687,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="62">
+      <c r="I15" s="60">
         <v>46199</v>
       </c>
-      <c r="J15" s="62"/>
+      <c r="J15" s="60"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="61"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1712,12 +1712,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="61"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="61"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="66" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1744,7 +1744,7 @@
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="61"/>
+      <c r="A18" s="65"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1762,12 +1762,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="61"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="61"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="66" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1794,7 +1794,7 @@
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="61"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1812,12 +1812,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="61"/>
-      <c r="J20" s="67"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="61"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="64" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1837,14 +1837,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="62">
+      <c r="I21" s="60">
         <v>46336</v>
       </c>
-      <c r="J21" s="62"/>
+      <c r="J21" s="60"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="61"/>
+      <c r="A22" s="65"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1862,12 +1862,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="61"/>
-      <c r="J22" s="67"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="61"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="64" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1887,14 +1887,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="62">
+      <c r="I23" s="60">
         <v>46218</v>
       </c>
-      <c r="J23" s="62"/>
+      <c r="J23" s="60"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="61"/>
+      <c r="A24" s="65"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1912,12 +1912,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="61"/>
-      <c r="J24" s="67"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="61"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="64" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1937,14 +1937,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="62">
+      <c r="I25" s="60">
         <v>46188</v>
       </c>
-      <c r="J25" s="62"/>
+      <c r="J25" s="60"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="61"/>
+      <c r="A26" s="65"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1962,12 +1962,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="61"/>
-      <c r="J26" s="67"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="61"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="64" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1987,14 +1987,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="62">
+      <c r="I27" s="60">
         <v>46321</v>
       </c>
-      <c r="J27" s="62"/>
+      <c r="J27" s="60"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="61"/>
+      <c r="A28" s="65"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2012,12 +2012,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="61"/>
-      <c r="J28" s="67"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="61"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="60" t="s">
+      <c r="A29" s="64" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2037,14 +2037,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="62">
+      <c r="I29" s="60">
         <v>46139</v>
       </c>
-      <c r="J29" s="62"/>
+      <c r="J29" s="60"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="61"/>
+      <c r="A30" s="65"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2062,12 +2062,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="61"/>
-      <c r="J30" s="67"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="61"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="64" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2087,14 +2087,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="62">
+      <c r="I31" s="60">
         <v>46133</v>
       </c>
-      <c r="J31" s="62"/>
+      <c r="J31" s="60"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="61"/>
+      <c r="A32" s="65"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2112,12 +2112,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="61"/>
-      <c r="J32" s="67"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="61"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="64" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2137,14 +2137,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="62">
+      <c r="I33" s="60">
         <v>46295</v>
       </c>
-      <c r="J33" s="62"/>
+      <c r="J33" s="60"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="61"/>
+      <c r="A34" s="65"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2162,12 +2162,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="61"/>
-      <c r="J34" s="67"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="61"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="60" t="s">
+      <c r="A35" s="64" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2187,14 +2187,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="62">
+      <c r="I35" s="60">
         <v>45737</v>
       </c>
-      <c r="J35" s="62"/>
+      <c r="J35" s="60"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="61"/>
+      <c r="A36" s="65"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2212,12 +2212,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="61"/>
-      <c r="J36" s="67"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="61"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="60" t="s">
+      <c r="A37" s="64" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2237,14 +2237,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="62">
+      <c r="I37" s="60">
         <v>45737</v>
       </c>
-      <c r="J37" s="62"/>
+      <c r="J37" s="60"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="61"/>
+      <c r="A38" s="65"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2262,26 +2262,35 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="61"/>
-      <c r="J38" s="67"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="61"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2298,29 +2307,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -4385,7 +4385,7 @@
         <v>61</v>
       </c>
       <c r="D22" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
         <v>126</v>
@@ -5384,15 +5384,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5403,6 +5394,15 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5659,20 +5659,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4235C340-25A1-4BE3-93C5-01123C692F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89825AA-5E33-4460-8FBE-7FC2C745075D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="130">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -389,9 +389,6 @@
     <t>K'Pong House</t>
   </si>
   <si>
-    <t>K'Sarut House</t>
-  </si>
-  <si>
     <t>ตรวจสอบงานติดตั้ง 2nd Fix</t>
   </si>
   <si>
@@ -416,22 +413,25 @@
     <t>ติดตามหน้างาน Firt fix ก่อนปิดฝ้า</t>
   </si>
   <si>
-    <t>ติดตามหน้างาน</t>
-  </si>
-  <si>
     <t>K'Bamrung House</t>
   </si>
   <si>
     <t>ส่งมอบงาน Firt fix</t>
   </si>
   <si>
-    <t>ส่งมอบงาน งวดสุดท้าย</t>
-  </si>
-  <si>
-    <t>Site Meeting</t>
-  </si>
-  <si>
     <t>กันตพัฒน์ มากมูล</t>
+  </si>
+  <si>
+    <t>วริษฐ์ ยุวชติพันธุ์</t>
+  </si>
+  <si>
+    <t>HouseX</t>
+  </si>
+  <si>
+    <t>ประชุม,เก็บงานติดตั้งกริล</t>
+  </si>
+  <si>
+    <t>Site Meenting</t>
   </si>
 </sst>
 </file>
@@ -924,27 +924,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="65" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1437,14 +1437,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="66">
         <v>46213</v>
       </c>
-      <c r="J5" s="62"/>
+      <c r="J5" s="66"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="65"/>
+      <c r="A6" s="61"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1462,12 +1462,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="65"/>
-      <c r="J6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="67"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="60" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1487,14 +1487,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="60" t="s">
+      <c r="I7" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="60"/>
+      <c r="J7" s="62"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="65"/>
+      <c r="A8" s="61"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1512,12 +1512,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="65"/>
-      <c r="J8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="67"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="60" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1537,14 +1537,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="62">
         <v>46218</v>
       </c>
-      <c r="J9" s="60"/>
+      <c r="J9" s="62"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="65"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1562,12 +1562,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="65"/>
-      <c r="J10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="67"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="60" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1587,14 +1587,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="60">
+      <c r="I11" s="62">
         <v>46171</v>
       </c>
-      <c r="J11" s="60"/>
+      <c r="J11" s="62"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="65"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1612,12 +1612,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="65"/>
-      <c r="J12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="67"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="60" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1637,14 +1637,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="60" t="s">
+      <c r="I13" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="60"/>
+      <c r="J13" s="62"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="65"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1662,12 +1662,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="65"/>
-      <c r="J14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="67"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1687,14 +1687,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="60">
+      <c r="I15" s="62">
         <v>46199</v>
       </c>
-      <c r="J15" s="60"/>
+      <c r="J15" s="62"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="65"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1712,12 +1712,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="65"/>
-      <c r="J16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="67"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="64" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1744,7 +1744,7 @@
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="65"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1762,12 +1762,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="65"/>
-      <c r="J18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="67"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="64" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1794,7 +1794,7 @@
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="65"/>
+      <c r="A20" s="61"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1812,12 +1812,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="65"/>
-      <c r="J20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="67"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="60" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1837,14 +1837,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="60">
+      <c r="I21" s="62">
         <v>46336</v>
       </c>
-      <c r="J21" s="60"/>
+      <c r="J21" s="62"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="65"/>
+      <c r="A22" s="61"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1862,12 +1862,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="65"/>
-      <c r="J22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="67"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="60" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="40" t="s">
@@ -1887,14 +1887,14 @@
       <c r="H23" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="60">
+      <c r="I23" s="62">
         <v>46218</v>
       </c>
-      <c r="J23" s="60"/>
+      <c r="J23" s="62"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="65"/>
+      <c r="A24" s="61"/>
       <c r="B24" s="37" t="s">
         <v>13</v>
       </c>
@@ -1912,12 +1912,12 @@
       <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="65"/>
-      <c r="J24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="67"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="60" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1937,14 +1937,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="60">
+      <c r="I25" s="62">
         <v>46188</v>
       </c>
-      <c r="J25" s="60"/>
+      <c r="J25" s="62"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="65"/>
+      <c r="A26" s="61"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1962,12 +1962,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="65"/>
-      <c r="J26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="67"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="64" t="s">
+      <c r="A27" s="60" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1987,14 +1987,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="60">
+      <c r="I27" s="62">
         <v>46321</v>
       </c>
-      <c r="J27" s="60"/>
+      <c r="J27" s="62"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="65"/>
+      <c r="A28" s="61"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2012,12 +2012,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="65"/>
-      <c r="J28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="67"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="64" t="s">
+      <c r="A29" s="60" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2037,14 +2037,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="60">
+      <c r="I29" s="62">
         <v>46139</v>
       </c>
-      <c r="J29" s="60"/>
+      <c r="J29" s="62"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="65"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2062,12 +2062,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="65"/>
-      <c r="J30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="67"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="64" t="s">
+      <c r="A31" s="60" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2087,14 +2087,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="60">
+      <c r="I31" s="62">
         <v>46133</v>
       </c>
-      <c r="J31" s="60"/>
+      <c r="J31" s="62"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="65"/>
+      <c r="A32" s="61"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2112,12 +2112,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="65"/>
-      <c r="J32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="67"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="64" t="s">
+      <c r="A33" s="60" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2137,14 +2137,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="60">
+      <c r="I33" s="62">
         <v>46295</v>
       </c>
-      <c r="J33" s="60"/>
+      <c r="J33" s="62"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="65"/>
+      <c r="A34" s="61"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2162,12 +2162,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="65"/>
-      <c r="J34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="67"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="64" t="s">
+      <c r="A35" s="60" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2187,14 +2187,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="60">
+      <c r="I35" s="62">
         <v>45737</v>
       </c>
-      <c r="J35" s="60"/>
+      <c r="J35" s="62"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="65"/>
+      <c r="A36" s="61"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2212,12 +2212,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="65"/>
-      <c r="J36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="67"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="64" t="s">
+      <c r="A37" s="60" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2237,14 +2237,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="60">
+      <c r="I37" s="62">
         <v>45737</v>
       </c>
-      <c r="J37" s="60"/>
+      <c r="J37" s="62"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="65"/>
+      <c r="A38" s="61"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2262,12 +2262,49 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="65"/>
-      <c r="J38" s="61"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="67"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2284,43 +2321,6 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -4071,7 +4071,7 @@
     <col min="2" max="2" width="26.77734375" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
@@ -4150,7 +4150,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4184,7 +4184,7 @@
         <v>2.5</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4201,7 +4201,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4218,7 +4218,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4235,7 +4235,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4252,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4269,7 +4269,7 @@
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4286,7 +4286,7 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4294,7 +4294,7 @@
         <v>46205</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>61</v>
@@ -4303,15 +4303,15 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>61</v>
@@ -4320,41 +4320,41 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3">
-        <v>46216</v>
+        <v>46211</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="4">
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="D20" s="4">
-        <v>3</v>
+        <v>2.6999999999999993</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4362,16 +4362,16 @@
         <v>46216</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>63</v>
+        <v>106</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="D21" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4379,16 +4379,16 @@
         <v>46218</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4396,16 +4396,16 @@
         <v>46218</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>129</v>
+        <v>111</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="D23" s="4">
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -4415,21 +4415,32 @@
       <c r="B24" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>63</v>
+      <c r="C24" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="D24" s="4">
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="4"/>
+      <c r="A25" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3"/>
@@ -5384,28 +5395,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5658,26 +5647,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5694,4 +5686,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89825AA-5E33-4460-8FBE-7FC2C745075D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB89A13-8B60-478F-BAD3-06683222C7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -1882,7 +1882,7 @@
       <c r="E23" s="41"/>
       <c r="F23" s="41"/>
       <c r="G23" s="42">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H23" s="40" t="s">
         <v>22</v>
@@ -1907,7 +1907,7 @@
       <c r="E24" s="38"/>
       <c r="F24" s="38"/>
       <c r="G24" s="39">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H24" s="37" t="s">
         <v>22</v>
@@ -3013,7 +3013,7 @@
         <v>70</v>
       </c>
       <c r="D14" s="22">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" s="17">
         <v>1707089</v>
@@ -5395,6 +5395,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5647,29 +5669,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5686,23 +5705,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB89A13-8B60-478F-BAD3-06683222C7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FAE77B-CAFF-4E48-B1AA-92AECADB3EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,21 +236,12 @@
     <t>วริษฐ์ ยุวโชติพันธุ์</t>
   </si>
   <si>
-    <t>รอลูกค้าคอนเฟิมวันส่งงาน Frist fix</t>
-  </si>
-  <si>
-    <t>ส่งงาน Frist fix 07/13/2026</t>
-  </si>
-  <si>
     <t>1 กันยา เริ่มเข้าไซต์</t>
   </si>
   <si>
     <t>โครงการล่าช้า เดือน 9 ส่งมอบงาน</t>
   </si>
   <si>
-    <t>โครงการล่าช้า/ติดกริลวันที่ 17/07/2026 กำหนดส่งงานได้ กันยา-ตุลา</t>
-  </si>
-  <si>
     <t>Project Type</t>
   </si>
   <si>
@@ -356,9 +347,6 @@
     <t>The Grand Pinkao</t>
   </si>
   <si>
-    <t>บริษัท NAME 7 AIR</t>
-  </si>
-  <si>
     <t>รอสรุปแผนงานหลังจากสำรวจหน้างาน</t>
   </si>
   <si>
@@ -432,6 +420,18 @@
   </si>
   <si>
     <t>Site Meenting</t>
+  </si>
+  <si>
+    <t>รอลูกค้าแจ้งการแก้ไขเรื่องไฟฟ้าไม่สามารถ ออนไฟได้ งวดสุดท้าย</t>
+  </si>
+  <si>
+    <t>โครงการล่าช้า/ติดกริลวันที่ 24-27 /07 Pretest 30/07/2026 ส่งงานงวดสุดท้าย เดือนตุลา</t>
+  </si>
+  <si>
+    <t>ส่งงาน Frist Fix เสร็จแล้ว รอเดือนตุลาเข้าดำเนินงาน Second Fix</t>
+  </si>
+  <si>
+    <t>รองานโครงสร้าง เข้าได้ ปลายเดือน 8</t>
   </si>
 </sst>
 </file>
@@ -922,29 +922,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1355,31 +1355,31 @@
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1395,10 +1395,10 @@
         <v>5</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>6</v>
@@ -1410,14 +1410,14 @@
         <v>8</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="67" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1437,14 +1437,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="61">
         <v>46213</v>
       </c>
-      <c r="J5" s="66"/>
+      <c r="J5" s="61"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="61"/>
+      <c r="A6" s="64"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1462,12 +1462,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="67"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="60"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="63" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1487,14 +1487,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="62" t="s">
+      <c r="I7" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="62"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="61"/>
+      <c r="A8" s="64"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1512,12 +1512,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="61"/>
-      <c r="J8" s="67"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="60"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="63" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1537,14 +1537,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="59">
         <v>46218</v>
       </c>
-      <c r="J9" s="62"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="61"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1562,12 +1562,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="61"/>
-      <c r="J10" s="67"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="60"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="63" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1587,14 +1587,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="59">
         <v>46171</v>
       </c>
-      <c r="J11" s="62"/>
+      <c r="J11" s="59"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="61"/>
+      <c r="A12" s="64"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1612,12 +1612,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="61"/>
-      <c r="J12" s="67"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="60"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="63" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1637,14 +1637,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="62" t="s">
+      <c r="I13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="62"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="61"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1662,12 +1662,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="61"/>
-      <c r="J14" s="67"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="60"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="63" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1687,14 +1687,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="62">
+      <c r="I15" s="59">
         <v>46199</v>
       </c>
-      <c r="J15" s="62"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="61"/>
+      <c r="A16" s="64"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1712,12 +1712,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="61"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="60"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="65" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1737,14 +1737,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="62">
         <v>46305</v>
       </c>
-      <c r="J17" s="63"/>
+      <c r="J17" s="62"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="61"/>
+      <c r="A18" s="64"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1762,12 +1762,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="61"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="60"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="65" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1787,14 +1787,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="63">
+      <c r="I19" s="62">
         <v>46336</v>
       </c>
-      <c r="J19" s="63"/>
+      <c r="J19" s="62"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="61"/>
+      <c r="A20" s="64"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1812,12 +1812,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="61"/>
-      <c r="J20" s="67"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="60"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="63" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1837,14 +1837,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="62">
+      <c r="I21" s="59">
         <v>46336</v>
       </c>
-      <c r="J21" s="62"/>
+      <c r="J21" s="59"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="61"/>
+      <c r="A22" s="64"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1862,62 +1862,62 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="61"/>
-      <c r="J22" s="67"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="60"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="41">
+      <c r="C23" s="44">
         <v>46190</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="44">
         <v>46206</v>
       </c>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="42">
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="45">
         <v>1</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="H23" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="62">
-        <v>46218</v>
-      </c>
-      <c r="J23" s="62"/>
+      <c r="I23" s="59">
+        <v>46220</v>
+      </c>
+      <c r="J23" s="59"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="61"/>
-      <c r="B24" s="37" t="s">
+      <c r="A24" s="64"/>
+      <c r="B24" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="38">
-        <v>46209</v>
-      </c>
-      <c r="D24" s="38">
-        <v>46211</v>
-      </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="39">
-        <v>0.2</v>
-      </c>
-      <c r="H24" s="37" t="s">
+      <c r="C24" s="47">
+        <v>46216</v>
+      </c>
+      <c r="D24" s="47">
+        <v>46220</v>
+      </c>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="48">
+        <v>1</v>
+      </c>
+      <c r="H24" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="61"/>
-      <c r="J24" s="67"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="60"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="63" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1937,14 +1937,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="62">
+      <c r="I25" s="59">
         <v>46188</v>
       </c>
-      <c r="J25" s="62"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="61"/>
+      <c r="A26" s="64"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1962,12 +1962,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="61"/>
-      <c r="J26" s="67"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="60"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="63" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1987,14 +1987,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="62">
+      <c r="I27" s="59">
         <v>46321</v>
       </c>
-      <c r="J27" s="62"/>
+      <c r="J27" s="59"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="61"/>
+      <c r="A28" s="64"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2012,12 +2012,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="61"/>
-      <c r="J28" s="67"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="60"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="60" t="s">
+      <c r="A29" s="63" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2037,14 +2037,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="62">
+      <c r="I29" s="59">
         <v>46139</v>
       </c>
-      <c r="J29" s="62"/>
+      <c r="J29" s="59"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="61"/>
+      <c r="A30" s="64"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2062,12 +2062,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="61"/>
-      <c r="J30" s="67"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="60"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="63" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2087,14 +2087,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="62">
+      <c r="I31" s="59">
         <v>46133</v>
       </c>
-      <c r="J31" s="62"/>
+      <c r="J31" s="59"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="61"/>
+      <c r="A32" s="64"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2112,12 +2112,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="61"/>
-      <c r="J32" s="67"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="60"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="63" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2137,14 +2137,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="62">
+      <c r="I33" s="59">
         <v>46295</v>
       </c>
-      <c r="J33" s="62"/>
+      <c r="J33" s="59"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="61"/>
+      <c r="A34" s="64"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2162,12 +2162,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="61"/>
-      <c r="J34" s="67"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="60"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="60" t="s">
+      <c r="A35" s="63" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2187,14 +2187,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="62">
+      <c r="I35" s="59">
         <v>45737</v>
       </c>
-      <c r="J35" s="62"/>
+      <c r="J35" s="59"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="61"/>
+      <c r="A36" s="64"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2212,12 +2212,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="61"/>
-      <c r="J36" s="67"/>
+      <c r="I36" s="64"/>
+      <c r="J36" s="60"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="60" t="s">
+      <c r="A37" s="63" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2237,14 +2237,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="62">
+      <c r="I37" s="59">
         <v>45737</v>
       </c>
-      <c r="J37" s="62"/>
+      <c r="J37" s="59"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="61"/>
+      <c r="A38" s="64"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2262,26 +2262,35 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="61"/>
-      <c r="J38" s="67"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="60"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2298,29 +2307,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2382,30 +2382,30 @@
       <c r="V1" s="57"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -2415,7 +2415,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>35</v>
@@ -2469,10 +2469,10 @@
         <v>9</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
@@ -2483,7 +2483,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D5" s="16">
         <v>0.9</v>
@@ -2497,8 +2497,8 @@
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="17">
-        <f>E5*0.8</f>
-        <v>261429.08799999999</v>
+        <f>E5*0.9</f>
+        <v>294107.72399999999</v>
       </c>
       <c r="I5" s="18">
         <v>12</v>
@@ -2530,7 +2530,7 @@
         <v>50</v>
       </c>
       <c r="U5" s="30" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="V5" s="20"/>
     </row>
@@ -2542,7 +2542,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D6" s="16">
         <v>0</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="S6" s="15"/>
       <c r="T6" s="27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="U6" s="27"/>
       <c r="V6" s="20"/>
@@ -2596,13 +2596,13 @@
         <v>17</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D7" s="16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E7" s="17">
         <v>576317.9</v>
@@ -2615,8 +2615,8 @@
         <v>603</v>
       </c>
       <c r="H7" s="17">
-        <f>E7*0.9</f>
-        <v>518686.11000000004</v>
+        <f>E7*1</f>
+        <v>576317.9</v>
       </c>
       <c r="I7" s="18">
         <v>20</v>
@@ -2648,7 +2648,7 @@
         <v>52</v>
       </c>
       <c r="U7" s="30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="V7" s="20"/>
     </row>
@@ -2660,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" s="16">
         <v>1</v>
@@ -2707,7 +2707,7 @@
       <c r="S8" s="15"/>
       <c r="T8" s="27"/>
       <c r="U8" s="32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="V8" s="20">
         <v>46134</v>
@@ -2721,7 +2721,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" s="16">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D10" s="16">
         <v>1</v>
@@ -2818,7 +2818,7 @@
       <c r="S10" s="15"/>
       <c r="T10" s="28"/>
       <c r="U10" s="32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="V10" s="20">
         <v>46141</v>
@@ -2832,7 +2832,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D11" s="16">
         <v>0.7</v>
@@ -2841,15 +2841,15 @@
         <v>1156111.18</v>
       </c>
       <c r="F11" s="17">
-        <f>P11*0.3</f>
-        <v>84000</v>
+        <f>P11*0.5</f>
+        <v>140000</v>
       </c>
       <c r="G11" s="17">
         <v>840</v>
       </c>
       <c r="H11" s="17">
-        <f t="shared" si="0"/>
-        <v>462444.47200000001</v>
+        <f>E11*0.7</f>
+        <v>809277.82599999988</v>
       </c>
       <c r="I11" s="18">
         <v>10</v>
@@ -2877,10 +2877,10 @@
       </c>
       <c r="S11" s="15"/>
       <c r="T11" s="28" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="U11" s="32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="V11" s="20">
         <v>46147</v>
@@ -2894,7 +2894,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" s="16">
         <v>0</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="S12" s="15"/>
       <c r="T12" s="28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="U12" s="27"/>
       <c r="V12" s="20">
@@ -2953,7 +2953,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D13" s="16">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>46336</v>
       </c>
       <c r="T13" s="27" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="U13" s="32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="V13" s="20">
         <v>46147</v>
@@ -3010,10 +3010,10 @@
         <v>22</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D14" s="22">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E14" s="17">
         <v>1707089</v>
@@ -3050,13 +3050,13 @@
         <v>46042</v>
       </c>
       <c r="R14" s="12">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="T14" s="28" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="U14" s="30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="V14" s="20">
         <v>46169</v>
@@ -3070,7 +3070,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
@@ -3126,7 +3126,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" s="16">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         <v>51</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="V16" s="20">
         <v>46182</v>
@@ -3183,7 +3183,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D17" s="16">
         <v>1</v>
@@ -3239,7 +3239,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D19" s="16">
         <v>0</v>
@@ -3334,10 +3334,10 @@
         <v>46295</v>
       </c>
       <c r="T19" s="28" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="U19" s="33" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="V19" s="20">
         <v>46203</v>
@@ -3351,7 +3351,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D20" s="16">
         <v>0.9</v>
@@ -3379,7 +3379,7 @@
         <v>45737</v>
       </c>
       <c r="T20" s="28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="U20" s="27"/>
       <c r="V20" s="20"/>
@@ -3392,7 +3392,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D21" s="16">
         <v>0.9</v>
@@ -3415,19 +3415,19 @@
         <v>45737</v>
       </c>
       <c r="T21" s="28" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="V21" s="20"/>
     </row>
     <row r="22" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A22" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D22" s="16"/>
       <c r="F22" s="26"/>
@@ -3441,19 +3441,19 @@
       <c r="Q22" s="20"/>
       <c r="R22" s="20"/>
       <c r="T22" s="28" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="V22" s="20"/>
     </row>
     <row r="23" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A23" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D23" s="16">
         <v>0</v>
@@ -3488,13 +3488,13 @@
     </row>
     <row r="24" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
       <c r="A24" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D24" s="16">
         <v>0</v>
@@ -3505,31 +3505,39 @@
       <c r="F24" s="17">
         <v>0</v>
       </c>
-      <c r="G24" s="17"/>
+      <c r="G24" s="17">
+        <f>400+140</f>
+        <v>540</v>
+      </c>
       <c r="H24" s="17">
         <f>E24*0.4</f>
         <v>81552</v>
       </c>
-      <c r="I24" s="23"/>
+      <c r="I24" s="23">
+        <v>6</v>
+      </c>
       <c r="K24" s="15"/>
       <c r="L24" s="17">
         <f>36480/2</f>
         <v>18240</v>
       </c>
       <c r="N24" s="56">
-        <f>82500-P24</f>
-        <v>17500</v>
+        <v>497</v>
       </c>
       <c r="O24" s="10" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="P24" s="11">
-        <v>65000</v>
-      </c>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="12"/>
+        <v>58000</v>
+      </c>
+      <c r="Q24" s="20">
+        <v>46225</v>
+      </c>
+      <c r="R24" s="12">
+        <v>46227</v>
+      </c>
       <c r="T24" s="28" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="U24" s="33"/>
       <c r="V24" s="20">
@@ -4079,20 +4087,20 @@
         <v>57</v>
       </c>
       <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
@@ -4104,7 +4112,7 @@
         <v>60</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4124,7 +4132,7 @@
         <v>46185</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>61</v>
@@ -4133,7 +4141,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4141,7 +4149,7 @@
         <v>46189</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>61</v>
@@ -4150,7 +4158,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4158,7 +4166,7 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>62</v>
@@ -4167,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4175,7 +4183,7 @@
         <v>46185</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>63</v>
@@ -4184,7 +4192,7 @@
         <v>2.5</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4192,7 +4200,7 @@
         <v>46190</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>61</v>
@@ -4201,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4209,7 +4217,7 @@
         <v>46190</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>63</v>
@@ -4218,7 +4226,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4226,7 +4234,7 @@
         <v>46192</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>61</v>
@@ -4235,7 +4243,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4243,7 +4251,7 @@
         <v>46197</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>63</v>
@@ -4252,7 +4260,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4260,7 +4268,7 @@
         <v>46198</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>61</v>
@@ -4269,7 +4277,7 @@
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4277,7 +4285,7 @@
         <v>46202</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>61</v>
@@ -4286,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4294,7 +4302,7 @@
         <v>46205</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>61</v>
@@ -4303,7 +4311,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4311,7 +4319,7 @@
         <v>46209</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>61</v>
@@ -4320,7 +4328,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4328,7 +4336,7 @@
         <v>46211</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>62</v>
@@ -4337,7 +4345,7 @@
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4345,16 +4353,16 @@
         <v>46216</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D20" s="4">
         <v>2.6999999999999993</v>
       </c>
       <c r="E20" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4362,7 +4370,7 @@
         <v>46216</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>61</v>
@@ -4371,7 +4379,7 @@
         <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4379,7 +4387,7 @@
         <v>46218</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>61</v>
@@ -4388,7 +4396,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4396,7 +4404,7 @@
         <v>46218</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>61</v>
@@ -4405,7 +4413,7 @@
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -4413,16 +4421,16 @@
         <v>46218</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D24" s="4">
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -4430,16 +4438,16 @@
         <v>46218</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D25" s="4">
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -4482,7 +4490,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
       <c r="A1" s="57" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4490,20 +4498,20 @@
       <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="59" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
+      <c r="A2" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -4517,10 +4525,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C5" s="6">
         <v>46204</v>
@@ -4529,15 +4537,15 @@
         <v>46224</v>
       </c>
       <c r="E5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C6" s="6">
         <v>46204</v>
@@ -4546,15 +4554,15 @@
         <v>46224</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" s="6">
         <v>46204</v>
@@ -4563,11 +4571,11 @@
         <v>46224</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="6"/>
+      <c r="A8" s="3"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -5395,15 +5403,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5414,6 +5413,15 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5670,20 +5678,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FAE77B-CAFF-4E48-B1AA-92AECADB3EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CE05AD-A82A-48BF-B807-F10904D9BD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -923,28 +923,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1355,31 +1355,31 @@
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="65" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1437,14 +1437,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="61">
+      <c r="I5" s="66">
         <v>46213</v>
       </c>
-      <c r="J5" s="61"/>
+      <c r="J5" s="66"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="64"/>
+      <c r="A6" s="60"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1462,12 +1462,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="67"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="59" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1487,14 +1487,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="59"/>
+      <c r="J7" s="61"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="64"/>
+      <c r="A8" s="60"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1512,12 +1512,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="64"/>
-      <c r="J8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="67"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="59" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1537,14 +1537,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="61">
         <v>46218</v>
       </c>
-      <c r="J9" s="59"/>
+      <c r="J9" s="61"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="64"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1562,12 +1562,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="64"/>
-      <c r="J10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="67"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="59" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1587,14 +1587,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="61">
         <v>46171</v>
       </c>
-      <c r="J11" s="59"/>
+      <c r="J11" s="61"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="64"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1612,12 +1612,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="64"/>
-      <c r="J12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="67"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="59" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1637,14 +1637,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="59" t="s">
+      <c r="I13" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="59"/>
+      <c r="J13" s="61"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="64"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1662,12 +1662,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="64"/>
-      <c r="J14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="67"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1687,14 +1687,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="59">
+      <c r="I15" s="61">
         <v>46199</v>
       </c>
-      <c r="J15" s="59"/>
+      <c r="J15" s="61"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="64"/>
+      <c r="A16" s="60"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1712,12 +1712,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="67"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="64" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1737,14 +1737,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="62">
+      <c r="I17" s="63">
         <v>46305</v>
       </c>
-      <c r="J17" s="62"/>
+      <c r="J17" s="63"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="64"/>
+      <c r="A18" s="60"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1762,12 +1762,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="67"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="64" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1787,14 +1787,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="62">
+      <c r="I19" s="63">
         <v>46336</v>
       </c>
-      <c r="J19" s="62"/>
+      <c r="J19" s="63"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="64"/>
+      <c r="A20" s="60"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1812,12 +1812,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="64"/>
-      <c r="J20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="67"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="59" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1837,14 +1837,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="61">
         <v>46336</v>
       </c>
-      <c r="J21" s="59"/>
+      <c r="J21" s="61"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="64"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1862,12 +1862,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="64"/>
-      <c r="J22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="67"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="63" t="s">
+      <c r="A23" s="59" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="43" t="s">
@@ -1887,14 +1887,14 @@
       <c r="H23" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="59">
+      <c r="I23" s="61">
         <v>46220</v>
       </c>
-      <c r="J23" s="59"/>
+      <c r="J23" s="61"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="64"/>
+      <c r="A24" s="60"/>
       <c r="B24" s="46" t="s">
         <v>13</v>
       </c>
@@ -1912,12 +1912,12 @@
       <c r="H24" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="64"/>
-      <c r="J24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="67"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="59" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1937,14 +1937,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="59">
+      <c r="I25" s="61">
         <v>46188</v>
       </c>
-      <c r="J25" s="59"/>
+      <c r="J25" s="61"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="64"/>
+      <c r="A26" s="60"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1962,12 +1962,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="64"/>
-      <c r="J26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="67"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="63" t="s">
+      <c r="A27" s="59" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1987,14 +1987,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="59">
+      <c r="I27" s="61">
         <v>46321</v>
       </c>
-      <c r="J27" s="59"/>
+      <c r="J27" s="61"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="64"/>
+      <c r="A28" s="60"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2012,12 +2012,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="64"/>
-      <c r="J28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="67"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="63" t="s">
+      <c r="A29" s="59" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2037,14 +2037,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="59">
+      <c r="I29" s="61">
         <v>46139</v>
       </c>
-      <c r="J29" s="59"/>
+      <c r="J29" s="61"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="64"/>
+      <c r="A30" s="60"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2062,12 +2062,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="64"/>
-      <c r="J30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="67"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="59" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2087,14 +2087,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="59">
+      <c r="I31" s="61">
         <v>46133</v>
       </c>
-      <c r="J31" s="59"/>
+      <c r="J31" s="61"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="64"/>
+      <c r="A32" s="60"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2112,12 +2112,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="64"/>
-      <c r="J32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="67"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="59" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2137,14 +2137,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="59">
+      <c r="I33" s="61">
         <v>46295</v>
       </c>
-      <c r="J33" s="59"/>
+      <c r="J33" s="61"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="64"/>
+      <c r="A34" s="60"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2162,12 +2162,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="64"/>
-      <c r="J34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="67"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="59" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2187,14 +2187,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="61">
         <v>45737</v>
       </c>
-      <c r="J35" s="59"/>
+      <c r="J35" s="61"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="64"/>
+      <c r="A36" s="60"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2212,12 +2212,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="64"/>
-      <c r="J36" s="60"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="67"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="63" t="s">
+      <c r="A37" s="59" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2237,14 +2237,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="59">
+      <c r="I37" s="61">
         <v>45737</v>
       </c>
-      <c r="J37" s="59"/>
+      <c r="J37" s="61"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="64"/>
+      <c r="A38" s="60"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2262,12 +2262,49 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="64"/>
-      <c r="J38" s="60"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="67"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2284,43 +2321,6 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3450,7 +3450,7 @@
         <v>91</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>67</v>
@@ -4087,16 +4087,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="57"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="58" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="58"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5416,15 +5416,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5677,6 +5668,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
@@ -5689,14 +5689,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5713,4 +5705,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CE05AD-A82A-48BF-B807-F10904D9BD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A76920B-F05A-4B55-A076-41831A8D29FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -923,28 +923,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1355,31 +1355,31 @@
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="67" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1437,14 +1437,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="61">
         <v>46213</v>
       </c>
-      <c r="J5" s="66"/>
+      <c r="J5" s="61"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="60"/>
+      <c r="A6" s="64"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1462,12 +1462,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="60"/>
-      <c r="J6" s="67"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="60"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="63" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1487,14 +1487,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="61"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="60"/>
+      <c r="A8" s="64"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1512,12 +1512,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="60"/>
-      <c r="J8" s="67"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="60"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="63" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1537,14 +1537,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="61">
+      <c r="I9" s="59">
         <v>46218</v>
       </c>
-      <c r="J9" s="61"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="60"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1562,12 +1562,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="60"/>
-      <c r="J10" s="67"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="60"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="63" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1587,14 +1587,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="61">
+      <c r="I11" s="59">
         <v>46171</v>
       </c>
-      <c r="J11" s="61"/>
+      <c r="J11" s="59"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="60"/>
+      <c r="A12" s="64"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1612,12 +1612,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="60"/>
-      <c r="J12" s="67"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="60"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="63" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1637,14 +1637,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="61" t="s">
+      <c r="I13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="60"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1662,12 +1662,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="60"/>
-      <c r="J14" s="67"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="60"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="63" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1687,14 +1687,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="59">
         <v>46199</v>
       </c>
-      <c r="J15" s="61"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="60"/>
+      <c r="A16" s="64"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1712,12 +1712,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="60"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="60"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="65" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1737,14 +1737,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="62">
         <v>46305</v>
       </c>
-      <c r="J17" s="63"/>
+      <c r="J17" s="62"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="60"/>
+      <c r="A18" s="64"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1762,12 +1762,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="60"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="60"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="65" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1787,14 +1787,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="63">
+      <c r="I19" s="62">
         <v>46336</v>
       </c>
-      <c r="J19" s="63"/>
+      <c r="J19" s="62"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="60"/>
+      <c r="A20" s="64"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1812,12 +1812,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="60"/>
-      <c r="J20" s="67"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="60"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="63" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1837,14 +1837,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="61">
+      <c r="I21" s="59">
         <v>46336</v>
       </c>
-      <c r="J21" s="61"/>
+      <c r="J21" s="59"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="60"/>
+      <c r="A22" s="64"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1862,12 +1862,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="67"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="60"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="63" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="43" t="s">
@@ -1887,14 +1887,14 @@
       <c r="H23" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="61">
+      <c r="I23" s="59">
         <v>46220</v>
       </c>
-      <c r="J23" s="61"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="60"/>
+      <c r="A24" s="64"/>
       <c r="B24" s="46" t="s">
         <v>13</v>
       </c>
@@ -1912,12 +1912,12 @@
       <c r="H24" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="60"/>
-      <c r="J24" s="67"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="60"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="63" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1937,14 +1937,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="61">
+      <c r="I25" s="59">
         <v>46188</v>
       </c>
-      <c r="J25" s="61"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="60"/>
+      <c r="A26" s="64"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1962,12 +1962,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="60"/>
-      <c r="J26" s="67"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="60"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="63" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1987,14 +1987,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="61">
+      <c r="I27" s="59">
         <v>46321</v>
       </c>
-      <c r="J27" s="61"/>
+      <c r="J27" s="59"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="60"/>
+      <c r="A28" s="64"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2012,12 +2012,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="60"/>
-      <c r="J28" s="67"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="60"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="59" t="s">
+      <c r="A29" s="63" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2037,14 +2037,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="61">
+      <c r="I29" s="59">
         <v>46139</v>
       </c>
-      <c r="J29" s="61"/>
+      <c r="J29" s="59"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="60"/>
+      <c r="A30" s="64"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2062,12 +2062,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="60"/>
-      <c r="J30" s="67"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="60"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="63" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2087,14 +2087,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="61">
+      <c r="I31" s="59">
         <v>46133</v>
       </c>
-      <c r="J31" s="61"/>
+      <c r="J31" s="59"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="60"/>
+      <c r="A32" s="64"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2112,12 +2112,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="60"/>
-      <c r="J32" s="67"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="60"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="59" t="s">
+      <c r="A33" s="63" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2137,14 +2137,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="61">
+      <c r="I33" s="59">
         <v>46295</v>
       </c>
-      <c r="J33" s="61"/>
+      <c r="J33" s="59"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="60"/>
+      <c r="A34" s="64"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2162,12 +2162,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="60"/>
-      <c r="J34" s="67"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="60"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="59" t="s">
+      <c r="A35" s="63" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2187,14 +2187,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="61">
+      <c r="I35" s="59">
         <v>45737</v>
       </c>
-      <c r="J35" s="61"/>
+      <c r="J35" s="59"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="60"/>
+      <c r="A36" s="64"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2212,12 +2212,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="60"/>
-      <c r="J36" s="67"/>
+      <c r="I36" s="64"/>
+      <c r="J36" s="60"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="59" t="s">
+      <c r="A37" s="63" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2237,14 +2237,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="61">
+      <c r="I37" s="59">
         <v>45737</v>
       </c>
-      <c r="J37" s="61"/>
+      <c r="J37" s="59"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="60"/>
+      <c r="A38" s="64"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2262,26 +2262,35 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="60"/>
-      <c r="J38" s="67"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="60"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2298,29 +2307,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3013,7 +3013,7 @@
         <v>67</v>
       </c>
       <c r="D14" s="22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E14" s="17">
         <v>1707089</v>
@@ -4087,16 +4087,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="57"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="58" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="58"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5403,19 +5403,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5668,6 +5655,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5678,17 +5678,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5707,6 +5696,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A76920B-F05A-4B55-A076-41831A8D29FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A37062-5A93-4A6E-972C-45BB4D2D5887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="131">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -347,9 +347,6 @@
     <t>The Grand Pinkao</t>
   </si>
   <si>
-    <t>รอสรุปแผนงานหลังจากสำรวจหน้างาน</t>
-  </si>
-  <si>
     <t>Phanasorn</t>
   </si>
   <si>
@@ -432,6 +429,12 @@
   </si>
   <si>
     <t>รองานโครงสร้าง เข้าได้ ปลายเดือน 8</t>
+  </si>
+  <si>
+    <t>https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQB85P7JtoSZT6532Il6VakbAcqfI6xy5EwPf0pgbRJpT3Y?e=Qwe5V0</t>
+  </si>
+  <si>
+    <t>ส่งงาน 100% วันที่ 07/24/2026</t>
   </si>
 </sst>
 </file>
@@ -923,28 +926,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1355,31 +1358,31 @@
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1417,7 +1420,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="65" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1437,14 +1440,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="61">
+      <c r="I5" s="66">
         <v>46213</v>
       </c>
-      <c r="J5" s="61"/>
+      <c r="J5" s="66"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="64"/>
+      <c r="A6" s="60"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1462,12 +1465,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="67"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="59" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1487,14 +1490,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="59"/>
+      <c r="J7" s="61"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="64"/>
+      <c r="A8" s="60"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1512,12 +1515,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="64"/>
-      <c r="J8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="67"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="59" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1537,14 +1540,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="61">
         <v>46218</v>
       </c>
-      <c r="J9" s="59"/>
+      <c r="J9" s="61"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="64"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1562,12 +1565,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="64"/>
-      <c r="J10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="67"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="59" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1587,14 +1590,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="61">
         <v>46171</v>
       </c>
-      <c r="J11" s="59"/>
+      <c r="J11" s="61"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="64"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1612,12 +1615,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="64"/>
-      <c r="J12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="67"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="59" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1637,14 +1640,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="59" t="s">
+      <c r="I13" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="59"/>
+      <c r="J13" s="61"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="64"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1662,12 +1665,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="64"/>
-      <c r="J14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="67"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1687,14 +1690,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="59">
+      <c r="I15" s="61">
         <v>46199</v>
       </c>
-      <c r="J15" s="59"/>
+      <c r="J15" s="61"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="64"/>
+      <c r="A16" s="60"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1712,12 +1715,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="67"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="64" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1737,14 +1740,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="62">
+      <c r="I17" s="63">
         <v>46305</v>
       </c>
-      <c r="J17" s="62"/>
+      <c r="J17" s="63"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="64"/>
+      <c r="A18" s="60"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1762,12 +1765,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="67"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="64" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1787,14 +1790,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="62">
+      <c r="I19" s="63">
         <v>46336</v>
       </c>
-      <c r="J19" s="62"/>
+      <c r="J19" s="63"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="64"/>
+      <c r="A20" s="60"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1812,12 +1815,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="64"/>
-      <c r="J20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="67"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="59" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1837,14 +1840,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="61">
         <v>46336</v>
       </c>
-      <c r="J21" s="59"/>
+      <c r="J21" s="61"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="64"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1862,12 +1865,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="64"/>
-      <c r="J22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="67"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="63" t="s">
+      <c r="A23" s="59" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="43" t="s">
@@ -1887,14 +1890,14 @@
       <c r="H23" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="59">
+      <c r="I23" s="61">
         <v>46220</v>
       </c>
-      <c r="J23" s="59"/>
+      <c r="J23" s="61"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="64"/>
+      <c r="A24" s="60"/>
       <c r="B24" s="46" t="s">
         <v>13</v>
       </c>
@@ -1912,12 +1915,12 @@
       <c r="H24" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="64"/>
-      <c r="J24" s="60"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="67"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="59" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1937,14 +1940,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="59">
+      <c r="I25" s="61">
         <v>46188</v>
       </c>
-      <c r="J25" s="59"/>
+      <c r="J25" s="61"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="64"/>
+      <c r="A26" s="60"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1962,12 +1965,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="64"/>
-      <c r="J26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="67"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="63" t="s">
+      <c r="A27" s="59" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1987,14 +1990,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="59">
+      <c r="I27" s="61">
         <v>46321</v>
       </c>
-      <c r="J27" s="59"/>
+      <c r="J27" s="61"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="64"/>
+      <c r="A28" s="60"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2012,12 +2015,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="64"/>
-      <c r="J28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="67"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="63" t="s">
+      <c r="A29" s="59" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2037,14 +2040,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="59">
+      <c r="I29" s="61">
         <v>46139</v>
       </c>
-      <c r="J29" s="59"/>
+      <c r="J29" s="61"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="64"/>
+      <c r="A30" s="60"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2062,12 +2065,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="64"/>
-      <c r="J30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="67"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="59" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2087,14 +2090,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="59">
+      <c r="I31" s="61">
         <v>46133</v>
       </c>
-      <c r="J31" s="59"/>
+      <c r="J31" s="61"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="64"/>
+      <c r="A32" s="60"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2112,12 +2115,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="64"/>
-      <c r="J32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="67"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="59" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2137,14 +2140,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="59">
+      <c r="I33" s="61">
         <v>46295</v>
       </c>
-      <c r="J33" s="59"/>
+      <c r="J33" s="61"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="64"/>
+      <c r="A34" s="60"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2162,12 +2165,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="64"/>
-      <c r="J34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="67"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="59" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2187,14 +2190,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="61">
         <v>45737</v>
       </c>
-      <c r="J35" s="59"/>
+      <c r="J35" s="61"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="64"/>
+      <c r="A36" s="60"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2212,12 +2215,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="64"/>
-      <c r="J36" s="60"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="67"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="63" t="s">
+      <c r="A37" s="59" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2237,14 +2240,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="59">
+      <c r="I37" s="61">
         <v>45737</v>
       </c>
-      <c r="J37" s="59"/>
+      <c r="J37" s="61"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="64"/>
+      <c r="A38" s="60"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2262,12 +2265,49 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="64"/>
-      <c r="J38" s="60"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="67"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2284,43 +2324,6 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2877,7 +2880,7 @@
       </c>
       <c r="S11" s="15"/>
       <c r="T11" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U11" s="32" t="s">
         <v>83</v>
@@ -2993,7 +2996,7 @@
         <v>46336</v>
       </c>
       <c r="T13" s="27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U13" s="32" t="s">
         <v>84</v>
@@ -3053,7 +3056,7 @@
         <v>46220</v>
       </c>
       <c r="T14" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U14" s="30" t="s">
         <v>70</v>
@@ -3415,7 +3418,7 @@
         <v>45737</v>
       </c>
       <c r="T21" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="V21" s="20"/>
     </row>
@@ -3537,9 +3540,11 @@
         <v>46227</v>
       </c>
       <c r="T24" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="U24" s="33"/>
+        <v>130</v>
+      </c>
+      <c r="U24" s="33" t="s">
+        <v>129</v>
+      </c>
       <c r="V24" s="20">
         <v>46213</v>
       </c>
@@ -4065,6 +4070,7 @@
     <hyperlink ref="U13" r:id="rId7" display="https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQBSB6_w6g72TLKUHWGlGBMFARs9IGLaqRfLn5C5zWJMU04?e=8SAokd" xr:uid="{60CE460F-1314-44B6-832C-5ABF13522EB6}"/>
     <hyperlink ref="U16" r:id="rId8" xr:uid="{02895EAD-8F6D-4728-91D1-12231471B411}"/>
     <hyperlink ref="U19" r:id="rId9" xr:uid="{64B77621-4464-4729-B1C8-C74F3BC4DC5C}"/>
+    <hyperlink ref="U24" r:id="rId10" xr:uid="{DFFF659B-3A50-4FD0-AA9F-289AE4EB0963}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4087,16 +4093,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="57"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="58" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="58"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4132,7 +4138,7 @@
         <v>46185</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>61</v>
@@ -4141,7 +4147,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4149,7 +4155,7 @@
         <v>46189</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>61</v>
@@ -4158,7 +4164,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4166,7 +4172,7 @@
         <v>46183</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>62</v>
@@ -4175,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4183,7 +4189,7 @@
         <v>46185</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>63</v>
@@ -4192,7 +4198,7 @@
         <v>2.5</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4200,7 +4206,7 @@
         <v>46190</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>61</v>
@@ -4209,7 +4215,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4217,7 +4223,7 @@
         <v>46190</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>63</v>
@@ -4226,7 +4232,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4234,7 +4240,7 @@
         <v>46192</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>61</v>
@@ -4243,7 +4249,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4251,7 +4257,7 @@
         <v>46197</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>63</v>
@@ -4260,7 +4266,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4268,7 +4274,7 @@
         <v>46198</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>61</v>
@@ -4277,7 +4283,7 @@
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4285,7 +4291,7 @@
         <v>46202</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>61</v>
@@ -4294,7 +4300,7 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4302,7 +4308,7 @@
         <v>46205</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>61</v>
@@ -4311,7 +4317,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4319,7 +4325,7 @@
         <v>46209</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>61</v>
@@ -4328,7 +4334,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4336,7 +4342,7 @@
         <v>46211</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>62</v>
@@ -4345,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4353,16 +4359,16 @@
         <v>46216</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D20" s="4">
         <v>2.6999999999999993</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4370,7 +4376,7 @@
         <v>46216</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>61</v>
@@ -4379,7 +4385,7 @@
         <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4387,7 +4393,7 @@
         <v>46218</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>61</v>
@@ -4396,7 +4402,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4404,7 +4410,7 @@
         <v>46218</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>61</v>
@@ -4413,7 +4419,7 @@
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -4424,13 +4430,13 @@
         <v>100</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D24" s="4">
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -4441,13 +4447,13 @@
         <v>100</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" s="4">
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5403,6 +5409,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5655,19 +5674,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5678,6 +5684,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5696,17 +5713,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A37062-5A93-4A6E-972C-45BB4D2D5887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FC008C-45B0-4002-96F0-2DCEC69E496B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,28 +926,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1358,31 +1358,31 @@
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1420,7 +1420,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="67" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1440,14 +1440,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="61">
         <v>46213</v>
       </c>
-      <c r="J5" s="66"/>
+      <c r="J5" s="61"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="60"/>
+      <c r="A6" s="64"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1465,12 +1465,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="60"/>
-      <c r="J6" s="67"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="60"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="63" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1490,14 +1490,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="61"/>
+      <c r="J7" s="59"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="60"/>
+      <c r="A8" s="64"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1515,12 +1515,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="60"/>
-      <c r="J8" s="67"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="60"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="63" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1540,14 +1540,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="61">
+      <c r="I9" s="59">
         <v>46218</v>
       </c>
-      <c r="J9" s="61"/>
+      <c r="J9" s="59"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="60"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1565,12 +1565,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="60"/>
-      <c r="J10" s="67"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="60"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="63" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1590,14 +1590,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="61">
+      <c r="I11" s="59">
         <v>46171</v>
       </c>
-      <c r="J11" s="61"/>
+      <c r="J11" s="59"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="60"/>
+      <c r="A12" s="64"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1615,12 +1615,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="60"/>
-      <c r="J12" s="67"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="60"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="63" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1640,14 +1640,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="61" t="s">
+      <c r="I13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="59"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="60"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1665,12 +1665,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="60"/>
-      <c r="J14" s="67"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="60"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="63" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1690,14 +1690,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="59">
         <v>46199</v>
       </c>
-      <c r="J15" s="61"/>
+      <c r="J15" s="59"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="60"/>
+      <c r="A16" s="64"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1715,12 +1715,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="60"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="60"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="65" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1740,14 +1740,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="63">
+      <c r="I17" s="62">
         <v>46305</v>
       </c>
-      <c r="J17" s="63"/>
+      <c r="J17" s="62"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="60"/>
+      <c r="A18" s="64"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1765,12 +1765,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="60"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="60"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="65" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1790,14 +1790,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="63">
+      <c r="I19" s="62">
         <v>46336</v>
       </c>
-      <c r="J19" s="63"/>
+      <c r="J19" s="62"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="60"/>
+      <c r="A20" s="64"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1815,12 +1815,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="60"/>
-      <c r="J20" s="67"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="60"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="63" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1840,14 +1840,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="61">
+      <c r="I21" s="59">
         <v>46336</v>
       </c>
-      <c r="J21" s="61"/>
+      <c r="J21" s="59"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="60"/>
+      <c r="A22" s="64"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1865,12 +1865,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="67"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="60"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="63" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="43" t="s">
@@ -1890,14 +1890,14 @@
       <c r="H23" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="61">
+      <c r="I23" s="59">
         <v>46220</v>
       </c>
-      <c r="J23" s="61"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="60"/>
+      <c r="A24" s="64"/>
       <c r="B24" s="46" t="s">
         <v>13</v>
       </c>
@@ -1915,12 +1915,12 @@
       <c r="H24" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="60"/>
-      <c r="J24" s="67"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="60"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="63" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1940,14 +1940,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="61">
+      <c r="I25" s="59">
         <v>46188</v>
       </c>
-      <c r="J25" s="61"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="60"/>
+      <c r="A26" s="64"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1965,12 +1965,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="60"/>
-      <c r="J26" s="67"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="60"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="63" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -1990,14 +1990,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="61">
+      <c r="I27" s="59">
         <v>46321</v>
       </c>
-      <c r="J27" s="61"/>
+      <c r="J27" s="59"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="60"/>
+      <c r="A28" s="64"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2015,12 +2015,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="60"/>
-      <c r="J28" s="67"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="60"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="59" t="s">
+      <c r="A29" s="63" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2040,14 +2040,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="61">
+      <c r="I29" s="59">
         <v>46139</v>
       </c>
-      <c r="J29" s="61"/>
+      <c r="J29" s="59"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="60"/>
+      <c r="A30" s="64"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2065,12 +2065,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="60"/>
-      <c r="J30" s="67"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="60"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="63" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2090,14 +2090,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="61">
+      <c r="I31" s="59">
         <v>46133</v>
       </c>
-      <c r="J31" s="61"/>
+      <c r="J31" s="59"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="60"/>
+      <c r="A32" s="64"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2115,12 +2115,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="60"/>
-      <c r="J32" s="67"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="60"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="59" t="s">
+      <c r="A33" s="63" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2140,14 +2140,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="61">
+      <c r="I33" s="59">
         <v>46295</v>
       </c>
-      <c r="J33" s="61"/>
+      <c r="J33" s="59"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="60"/>
+      <c r="A34" s="64"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2165,12 +2165,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="60"/>
-      <c r="J34" s="67"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="60"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="59" t="s">
+      <c r="A35" s="63" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2190,14 +2190,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="61">
+      <c r="I35" s="59">
         <v>45737</v>
       </c>
-      <c r="J35" s="61"/>
+      <c r="J35" s="59"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="60"/>
+      <c r="A36" s="64"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2215,12 +2215,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="60"/>
-      <c r="J36" s="67"/>
+      <c r="I36" s="64"/>
+      <c r="J36" s="60"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="59" t="s">
+      <c r="A37" s="63" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2240,14 +2240,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="61">
+      <c r="I37" s="59">
         <v>45737</v>
       </c>
-      <c r="J37" s="61"/>
+      <c r="J37" s="59"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="60"/>
+      <c r="A38" s="64"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2265,26 +2265,35 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="60"/>
-      <c r="J38" s="67"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="60"/>
       <c r="K38" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2301,29 +2310,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -4093,16 +4093,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="57"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="58" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="58"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5409,19 +5409,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5674,6 +5661,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5684,17 +5684,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5713,6 +5702,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\Desktop\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FC008C-45B0-4002-96F0-2DCEC69E496B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{A99066B1-997E-44F2-9F7D-DC0E9654FB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C6943DA-79D2-448E-9995-3F7348B8A102}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="132">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -435,6 +435,9 @@
   </si>
   <si>
     <t>ส่งงาน 100% วันที่ 07/24/2026</t>
+  </si>
+  <si>
+    <t>บ้านคุณทวีชัย สมุทปราการ</t>
   </si>
 </sst>
 </file>
@@ -766,7 +769,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -948,6 +951,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1340,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
@@ -2269,8 +2290,88 @@
       <c r="J38" s="60"/>
       <c r="K38" s="54"/>
     </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="59"/>
+      <c r="K39" s="53"/>
+    </row>
+    <row r="40" spans="1:11" ht="15" thickBot="1">
+      <c r="A40" s="64"/>
+      <c r="B40" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="54"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="69">
+        <v>46225</v>
+      </c>
+      <c r="D41" s="69">
+        <v>46227</v>
+      </c>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="70">
+        <v>0</v>
+      </c>
+      <c r="H41" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="59">
+        <v>46227</v>
+      </c>
+      <c r="J41" s="59"/>
+      <c r="K41" s="53"/>
+    </row>
+    <row r="42" spans="1:11" ht="15" thickBot="1">
+      <c r="A42" s="64"/>
+      <c r="B42" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="54"/>
+    </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="59">
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -4049,7 +4150,7 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{A99066B1-997E-44F2-9F7D-DC0E9654FB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C6943DA-79D2-448E-9995-3F7348B8A102}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{A99066B1-997E-44F2-9F7D-DC0E9654FB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC8067FE-3EFF-493D-9D70-ACAA281592D9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="132">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -769,7 +769,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -927,6 +927,15 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -951,24 +960,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1376,34 +1367,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1441,7 +1432,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="70" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1461,14 +1452,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="61">
+      <c r="I5" s="64">
         <v>46213</v>
       </c>
-      <c r="J5" s="61"/>
+      <c r="J5" s="64"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="64"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1486,12 +1477,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="60"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="63"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="63" t="s">
+      <c r="A7" s="66" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1511,14 +1502,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="59"/>
+      <c r="J7" s="62"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="64"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1536,12 +1527,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="64"/>
-      <c r="J8" s="60"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="63"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="66" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1561,14 +1552,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="62">
         <v>46218</v>
       </c>
-      <c r="J9" s="59"/>
+      <c r="J9" s="62"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="64"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1586,12 +1577,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="64"/>
-      <c r="J10" s="60"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="63"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="66" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1611,14 +1602,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="59">
+      <c r="I11" s="62">
         <v>46171</v>
       </c>
-      <c r="J11" s="59"/>
+      <c r="J11" s="62"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="64"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1636,12 +1627,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="64"/>
-      <c r="J12" s="60"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="63"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="66" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1661,14 +1652,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="59" t="s">
+      <c r="I13" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="59"/>
+      <c r="J13" s="62"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="64"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1686,12 +1677,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="64"/>
-      <c r="J14" s="60"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="63"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="66" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1711,14 +1702,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="59">
+      <c r="I15" s="62">
         <v>46199</v>
       </c>
-      <c r="J15" s="59"/>
+      <c r="J15" s="62"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="64"/>
+      <c r="A16" s="67"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1736,12 +1727,12 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="60"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="63"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="68" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -1761,14 +1752,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="62">
+      <c r="I17" s="65">
         <v>46305</v>
       </c>
-      <c r="J17" s="62"/>
+      <c r="J17" s="65"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="64"/>
+      <c r="A18" s="67"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1786,12 +1777,12 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="60"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="63"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="68" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="34" t="s">
@@ -1811,14 +1802,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="62">
+      <c r="I19" s="65">
         <v>46336</v>
       </c>
-      <c r="J19" s="62"/>
+      <c r="J19" s="65"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="64"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1836,12 +1827,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="64"/>
-      <c r="J20" s="60"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="63"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="66" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1861,14 +1852,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="62">
         <v>46336</v>
       </c>
-      <c r="J21" s="59"/>
+      <c r="J21" s="62"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="64"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1886,12 +1877,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="64"/>
-      <c r="J22" s="60"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="63"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="63" t="s">
+      <c r="A23" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="43" t="s">
@@ -1911,14 +1902,14 @@
       <c r="H23" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="59">
+      <c r="I23" s="62">
         <v>46220</v>
       </c>
-      <c r="J23" s="59"/>
+      <c r="J23" s="62"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="64"/>
+      <c r="A24" s="67"/>
       <c r="B24" s="46" t="s">
         <v>13</v>
       </c>
@@ -1936,12 +1927,12 @@
       <c r="H24" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="64"/>
-      <c r="J24" s="60"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="63"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="66" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1961,14 +1952,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="59">
+      <c r="I25" s="62">
         <v>46188</v>
       </c>
-      <c r="J25" s="59"/>
+      <c r="J25" s="62"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="64"/>
+      <c r="A26" s="67"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1986,12 +1977,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="64"/>
-      <c r="J26" s="60"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="63"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="63" t="s">
+      <c r="A27" s="66" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -2011,14 +2002,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="59">
+      <c r="I27" s="62">
         <v>46321</v>
       </c>
-      <c r="J27" s="59"/>
+      <c r="J27" s="62"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="64"/>
+      <c r="A28" s="67"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2036,12 +2027,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="64"/>
-      <c r="J28" s="60"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="63"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="63" t="s">
+      <c r="A29" s="66" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2061,14 +2052,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="59">
+      <c r="I29" s="62">
         <v>46139</v>
       </c>
-      <c r="J29" s="59"/>
+      <c r="J29" s="62"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="64"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2086,12 +2077,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="64"/>
-      <c r="J30" s="60"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="63"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="66" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2111,14 +2102,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="59">
+      <c r="I31" s="62">
         <v>46133</v>
       </c>
-      <c r="J31" s="59"/>
+      <c r="J31" s="62"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="64"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2136,12 +2127,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="64"/>
-      <c r="J32" s="60"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="63"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="66" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2161,14 +2152,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="59">
+      <c r="I33" s="62">
         <v>46295</v>
       </c>
-      <c r="J33" s="59"/>
+      <c r="J33" s="62"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="64"/>
+      <c r="A34" s="67"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2186,12 +2177,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="64"/>
-      <c r="J34" s="60"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="63"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="66" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2211,14 +2202,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="62">
         <v>45737</v>
       </c>
-      <c r="J35" s="59"/>
+      <c r="J35" s="62"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="64"/>
+      <c r="A36" s="67"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2236,12 +2227,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="64"/>
-      <c r="J36" s="60"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="63"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="63" t="s">
+      <c r="A37" s="66" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2261,14 +2252,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="59">
+      <c r="I37" s="62">
         <v>45737</v>
       </c>
-      <c r="J37" s="59"/>
+      <c r="J37" s="62"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="64"/>
+      <c r="A38" s="67"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2286,82 +2277,90 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="64"/>
-      <c r="J38" s="60"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="63"/>
       <c r="K38" s="54"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="63" t="s">
+      <c r="A39" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="B39" s="68" t="s">
+      <c r="B39" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="59"/>
-      <c r="J39" s="59"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="42">
+        <v>0</v>
+      </c>
+      <c r="H39" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="62"/>
+      <c r="J39" s="62"/>
       <c r="K39" s="53"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="64"/>
-      <c r="B40" s="71" t="s">
+      <c r="A40" s="67"/>
+      <c r="B40" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="60"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="59">
+        <v>0</v>
+      </c>
+      <c r="H40" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="67"/>
+      <c r="J40" s="63"/>
       <c r="K40" s="54"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="63" t="s">
+      <c r="A41" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="68" t="s">
+      <c r="B41" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="69">
+      <c r="C41" s="41">
         <v>46225</v>
       </c>
-      <c r="D41" s="69">
+      <c r="D41" s="41">
         <v>46227</v>
       </c>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="70">
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="42">
         <v>0</v>
       </c>
-      <c r="H41" s="68" t="s">
+      <c r="H41" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="59">
+      <c r="I41" s="62">
         <v>46227</v>
       </c>
-      <c r="J41" s="59"/>
+      <c r="J41" s="62"/>
       <c r="K41" s="53"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="64"/>
-      <c r="B42" s="71" t="s">
+      <c r="A42" s="67"/>
+      <c r="B42" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="72"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="60"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="63"/>
       <c r="K42" s="54"/>
     </row>
   </sheetData>
@@ -2460,56 +2459,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
-      <c r="U1" s="57"/>
-      <c r="V1" s="57"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -3575,7 +3574,9 @@
       </c>
       <c r="I23" s="23"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="17"/>
+      <c r="L23" s="17">
+        <v>15000</v>
+      </c>
       <c r="O23" s="10" t="s">
         <v>54</v>
       </c>
@@ -3622,8 +3623,7 @@
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="17">
-        <f>36480/2</f>
-        <v>18240</v>
+        <v>13500</v>
       </c>
       <c r="N24" s="56">
         <v>497</v>
@@ -4150,7 +4150,7 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -4190,20 +4190,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4596,22 +4596,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5510,6 +5510,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5762,7 +5771,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5775,16 +5784,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5803,7 +5811,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5812,12 +5820,4 @@
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{A99066B1-997E-44F2-9F7D-DC0E9654FB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC8067FE-3EFF-493D-9D70-ACAA281592D9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BD7622-B184-4FD8-9186-EA2DC3959814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -938,28 +938,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1370,31 +1370,31 @@
       <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1432,7 +1432,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="69" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1452,14 +1452,14 @@
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="64">
+      <c r="I5" s="70">
         <v>46213</v>
       </c>
-      <c r="J5" s="64"/>
+      <c r="J5" s="70"/>
       <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="67"/>
+      <c r="A6" s="63"/>
       <c r="B6" s="37" t="s">
         <v>13</v>
       </c>
@@ -1477,12 +1477,12 @@
       <c r="H6" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="67"/>
-      <c r="J6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="65"/>
       <c r="K6" s="50"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="40" t="s">
@@ -1502,14 +1502,14 @@
       <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="62" t="s">
+      <c r="I7" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="62"/>
+      <c r="J7" s="64"/>
       <c r="K7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="67"/>
+      <c r="A8" s="63"/>
       <c r="B8" s="37" t="s">
         <v>13</v>
       </c>
@@ -1527,12 +1527,12 @@
       <c r="H8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="67"/>
-      <c r="J8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="65"/>
       <c r="K8" s="50"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="62" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -1552,14 +1552,14 @@
       <c r="H9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="64">
         <v>46218</v>
       </c>
-      <c r="J9" s="62"/>
+      <c r="J9" s="64"/>
       <c r="K9" s="51"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="67"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="37" t="s">
         <v>13</v>
       </c>
@@ -1577,12 +1577,12 @@
       <c r="H10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="67"/>
-      <c r="J10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="65"/>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="62" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -1602,14 +1602,14 @@
       <c r="H11" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="64">
         <v>46171</v>
       </c>
-      <c r="J11" s="62"/>
+      <c r="J11" s="64"/>
       <c r="K11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="67"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="46" t="s">
         <v>13</v>
       </c>
@@ -1627,12 +1627,12 @@
       <c r="H12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="67"/>
-      <c r="J12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="65"/>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="62" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -1652,14 +1652,14 @@
       <c r="H13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="62" t="s">
+      <c r="I13" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="62"/>
+      <c r="J13" s="64"/>
       <c r="K13" s="51"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="67"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="37" t="s">
         <v>13</v>
       </c>
@@ -1677,12 +1677,12 @@
       <c r="H14" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="67"/>
-      <c r="J14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="65"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="62" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -1702,14 +1702,14 @@
       <c r="H15" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="62">
+      <c r="I15" s="64">
         <v>46199</v>
       </c>
-      <c r="J15" s="62"/>
+      <c r="J15" s="64"/>
       <c r="K15" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="67"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="46" t="s">
         <v>13</v>
       </c>
@@ -1727,8 +1727,8 @@
       <c r="H16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="67"/>
-      <c r="J16" s="63"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="65"/>
       <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11">
@@ -1752,14 +1752,14 @@
       <c r="H17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="65">
+      <c r="I17" s="67">
         <v>46305</v>
       </c>
-      <c r="J17" s="65"/>
+      <c r="J17" s="67"/>
       <c r="K17" s="52"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="67"/>
+      <c r="A18" s="63"/>
       <c r="B18" s="37" t="s">
         <v>13</v>
       </c>
@@ -1777,8 +1777,8 @@
       <c r="H18" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="67"/>
-      <c r="J18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="65"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11">
@@ -1802,14 +1802,14 @@
       <c r="H19" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="65">
+      <c r="I19" s="67">
         <v>46336</v>
       </c>
-      <c r="J19" s="65"/>
+      <c r="J19" s="67"/>
       <c r="K19" s="52"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="67"/>
+      <c r="A20" s="63"/>
       <c r="B20" s="37" t="s">
         <v>13</v>
       </c>
@@ -1827,12 +1827,12 @@
       <c r="H20" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="67"/>
-      <c r="J20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="65"/>
       <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="62" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -1852,14 +1852,14 @@
       <c r="H21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="62">
+      <c r="I21" s="64">
         <v>46336</v>
       </c>
-      <c r="J21" s="62"/>
+      <c r="J21" s="64"/>
       <c r="K21" s="53"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="67"/>
+      <c r="A22" s="63"/>
       <c r="B22" s="37" t="s">
         <v>13</v>
       </c>
@@ -1877,12 +1877,12 @@
       <c r="H22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="67"/>
-      <c r="J22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="65"/>
       <c r="K22" s="54"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="62" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="43" t="s">
@@ -1902,14 +1902,14 @@
       <c r="H23" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="62">
+      <c r="I23" s="64">
         <v>46220</v>
       </c>
-      <c r="J23" s="62"/>
+      <c r="J23" s="64"/>
       <c r="K23" s="53"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="67"/>
+      <c r="A24" s="63"/>
       <c r="B24" s="46" t="s">
         <v>13</v>
       </c>
@@ -1927,12 +1927,12 @@
       <c r="H24" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="67"/>
-      <c r="J24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="65"/>
       <c r="K24" s="54"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="62" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -1952,14 +1952,14 @@
       <c r="H25" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="62">
+      <c r="I25" s="64">
         <v>46188</v>
       </c>
-      <c r="J25" s="62"/>
+      <c r="J25" s="64"/>
       <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="67"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="46" t="s">
         <v>13</v>
       </c>
@@ -1977,12 +1977,12 @@
       <c r="H26" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="67"/>
-      <c r="J26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="65"/>
       <c r="K26" s="54"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="62" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="40" t="s">
@@ -2002,14 +2002,14 @@
       <c r="H27" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="62">
+      <c r="I27" s="64">
         <v>46321</v>
       </c>
-      <c r="J27" s="62"/>
+      <c r="J27" s="64"/>
       <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="67"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="37" t="s">
         <v>13</v>
       </c>
@@ -2027,12 +2027,12 @@
       <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="67"/>
-      <c r="J28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="65"/>
       <c r="K28" s="54"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="66" t="s">
+      <c r="A29" s="62" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="43" t="s">
@@ -2052,14 +2052,14 @@
       <c r="H29" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="62">
+      <c r="I29" s="64">
         <v>46139</v>
       </c>
-      <c r="J29" s="62"/>
+      <c r="J29" s="64"/>
       <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="67"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="46" t="s">
         <v>13</v>
       </c>
@@ -2077,12 +2077,12 @@
       <c r="H30" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="67"/>
-      <c r="J30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="65"/>
       <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="62" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="43" t="s">
@@ -2102,14 +2102,14 @@
       <c r="H31" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="62">
+      <c r="I31" s="64">
         <v>46133</v>
       </c>
-      <c r="J31" s="62"/>
+      <c r="J31" s="64"/>
       <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="67"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="46" t="s">
         <v>13</v>
       </c>
@@ -2127,12 +2127,12 @@
       <c r="H32" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="67"/>
-      <c r="J32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="65"/>
       <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="62" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="40" t="s">
@@ -2152,14 +2152,14 @@
       <c r="H33" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="62">
+      <c r="I33" s="64">
         <v>46295</v>
       </c>
-      <c r="J33" s="62"/>
+      <c r="J33" s="64"/>
       <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="67"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="37" t="s">
         <v>13</v>
       </c>
@@ -2177,12 +2177,12 @@
       <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="67"/>
-      <c r="J34" s="63"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="65"/>
       <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="62" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -2202,14 +2202,14 @@
       <c r="H35" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="62">
+      <c r="I35" s="64">
         <v>45737</v>
       </c>
-      <c r="J35" s="62"/>
+      <c r="J35" s="64"/>
       <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="67"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="37" t="s">
         <v>13</v>
       </c>
@@ -2227,12 +2227,12 @@
       <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="67"/>
-      <c r="J36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="65"/>
       <c r="K36" s="54"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="66" t="s">
+      <c r="A37" s="62" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2252,14 +2252,14 @@
       <c r="H37" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="62">
+      <c r="I37" s="64">
         <v>45737</v>
       </c>
-      <c r="J37" s="62"/>
+      <c r="J37" s="64"/>
       <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="67"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="37" t="s">
         <v>13</v>
       </c>
@@ -2277,12 +2277,12 @@
       <c r="H38" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="67"/>
-      <c r="J38" s="63"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="65"/>
       <c r="K38" s="54"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="62" t="s">
         <v>131</v>
       </c>
       <c r="B39" s="40" t="s">
@@ -2298,12 +2298,12 @@
       <c r="H39" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
+      <c r="I39" s="64"/>
+      <c r="J39" s="64"/>
       <c r="K39" s="53"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="67"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="57" t="s">
         <v>13</v>
       </c>
@@ -2317,12 +2317,12 @@
       <c r="H40" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="67"/>
-      <c r="J40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="65"/>
       <c r="K40" s="54"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="62" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="40" t="s">
@@ -2342,14 +2342,14 @@
       <c r="H41" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="62">
+      <c r="I41" s="64">
         <v>46227</v>
       </c>
-      <c r="J41" s="62"/>
+      <c r="J41" s="64"/>
       <c r="K41" s="53"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="67"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="57" t="s">
         <v>13</v>
       </c>
@@ -2359,18 +2359,49 @@
       <c r="F42" s="58"/>
       <c r="G42" s="59"/>
       <c r="H42" s="57"/>
-      <c r="I42" s="67"/>
-      <c r="J42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="65"/>
       <c r="K42" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2387,43 +2418,12 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2444,8 +2444,8 @@
     <col min="4" max="6" width="16" customWidth="1"/>
     <col min="7" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="10" max="10" width="13" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="16" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
@@ -2883,8 +2883,8 @@
         <v>338450.2</v>
       </c>
       <c r="F10" s="17">
-        <f>P10*0.8</f>
-        <v>110400</v>
+        <f>P10*1</f>
+        <v>138000</v>
       </c>
       <c r="G10" s="17">
         <v>370</v>
@@ -2944,8 +2944,8 @@
         <v>1156111.18</v>
       </c>
       <c r="F11" s="17">
-        <f>P11*0.5</f>
-        <v>140000</v>
+        <f>P11*0.8</f>
+        <v>224000</v>
       </c>
       <c r="G11" s="17">
         <v>840</v>
@@ -4194,16 +4194,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="60"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="61" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="61"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5510,15 +5510,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5771,6 +5762,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5785,14 +5785,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5811,6 +5803,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BD7622-B184-4FD8-9186-EA2DC3959814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAC909E-603B-4776-A9D2-B09EBA2A8D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3553,7 +3553,7 @@
         <v>91</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>67</v>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAC909E-603B-4776-A9D2-B09EBA2A8D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="134">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -438,6 +438,12 @@
   </si>
   <si>
     <t>บ้านคุณทวีชัย สมุทปราการ</t>
+  </si>
+  <si>
+    <t>ราคา Minimum ของผู้รับเหมา</t>
+  </si>
+  <si>
+    <t>ทำราคาขั้นต่ำ ในกรณีงานเล็กเป็นงานเหมา</t>
   </si>
 </sst>
 </file>
@@ -769,7 +775,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -787,9 +793,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -960,6 +963,15 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1027,16 +1039,6 @@
         <row r="12">
           <cell r="C12">
             <v>46200</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="C13">
-            <v>46392</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="C14">
-            <v>46042</v>
           </cell>
         </row>
         <row r="15">
@@ -1367,34 +1369,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1432,936 +1434,936 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="71">
         <v>46084</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="71">
         <v>46127</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7">
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="72">
         <v>1</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="70">
+      <c r="I5" s="69">
         <v>46213</v>
       </c>
-      <c r="J5" s="70"/>
-      <c r="K5" s="49"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="48"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="63"/>
-      <c r="B6" s="37" t="s">
+      <c r="A6" s="62"/>
+      <c r="B6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="46">
         <v>46189</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="46">
         <v>46189</v>
       </c>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="39">
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="47">
         <v>1</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="63"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="50"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="49"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="40">
         <v>46219</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="40">
         <v>46233</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="42">
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41">
         <v>0</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="64"/>
-      <c r="K7" s="51"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="37" t="s">
+      <c r="A8" s="62"/>
+      <c r="B8" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="37">
         <v>46244</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="37">
         <v>46247</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="39">
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="38">
         <v>0</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="63"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="50"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="40">
         <v>46082</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="40">
         <v>46096</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="42">
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41">
         <v>1</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="64">
+      <c r="I9" s="63">
         <v>46218</v>
       </c>
-      <c r="J9" s="64"/>
-      <c r="K9" s="51"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="37" t="s">
+      <c r="A10" s="62"/>
+      <c r="B10" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="37">
         <v>46168</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="37">
         <v>46213</v>
       </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="39">
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="38">
         <v>1</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="63"/>
-      <c r="J10" s="65"/>
-      <c r="K10" s="50"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="49"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="43">
         <v>46184</v>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="43">
         <v>46191</v>
       </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="45">
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44">
         <v>1</v>
       </c>
-      <c r="H11" s="43" t="s">
+      <c r="H11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="64">
+      <c r="I11" s="63">
         <v>46171</v>
       </c>
-      <c r="J11" s="64"/>
-      <c r="K11" s="51"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="46" t="s">
+      <c r="A12" s="62"/>
+      <c r="B12" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="46">
         <v>46200</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="46">
         <v>46202</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="48">
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47">
         <v>1</v>
       </c>
-      <c r="H12" s="46" t="s">
+      <c r="H12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="63"/>
-      <c r="J12" s="65"/>
-      <c r="K12" s="50"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="49"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="40">
         <v>46392</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="40">
         <v>46402</v>
       </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="42">
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41">
         <v>0</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="64"/>
-      <c r="K13" s="51"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="63"/>
-      <c r="B14" s="37" t="s">
+      <c r="A14" s="62"/>
+      <c r="B14" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="37">
         <v>46042</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="37">
         <v>46042</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="39">
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="38">
         <v>0</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="63"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="50"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="49"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="43">
         <v>46168</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="43">
         <v>46188</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="45">
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44">
         <v>1</v>
       </c>
-      <c r="H15" s="43" t="s">
+      <c r="H15" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="64">
+      <c r="I15" s="63">
         <v>46199</v>
       </c>
-      <c r="J15" s="64"/>
-      <c r="K15" s="51"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="63"/>
-      <c r="B16" s="46" t="s">
+      <c r="A16" s="62"/>
+      <c r="B16" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="46">
         <v>46198</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="46">
         <v>46199</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="48">
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="47">
         <v>1</v>
       </c>
-      <c r="H16" s="46" t="s">
+      <c r="H16" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="63"/>
-      <c r="J16" s="65"/>
-      <c r="K16" s="50"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="49"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="34">
         <v>46188</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="34">
         <v>46198</v>
       </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36">
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="35">
         <v>0.8</v>
       </c>
-      <c r="H17" s="34" t="s">
+      <c r="H17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="67">
+      <c r="I17" s="66">
         <v>46305</v>
       </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="52"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="51"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="63"/>
-      <c r="B18" s="37" t="s">
+      <c r="A18" s="62"/>
+      <c r="B18" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="37">
         <v>46296</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="37">
         <v>46298</v>
       </c>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39">
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="38">
         <v>0.4</v>
       </c>
-      <c r="H18" s="37" t="s">
+      <c r="H18" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="63"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="50"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="49"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="34">
         <v>46275</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="34">
         <v>46290</v>
       </c>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="36">
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="35">
         <v>0</v>
       </c>
-      <c r="H19" s="34" t="s">
+      <c r="H19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="67">
+      <c r="I19" s="66">
         <v>46336</v>
       </c>
-      <c r="J19" s="67"/>
-      <c r="K19" s="52"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="63"/>
-      <c r="B20" s="37" t="s">
+      <c r="A20" s="62"/>
+      <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="37">
         <v>46327</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="37">
         <v>46329</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39">
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38">
         <v>0</v>
       </c>
-      <c r="H20" s="37" t="s">
+      <c r="H20" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="63"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="50"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="49"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="40">
         <v>46240</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="40">
         <v>46249</v>
       </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="42">
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41">
         <v>0</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="64">
+      <c r="I21" s="63">
         <v>46336</v>
       </c>
-      <c r="J21" s="64"/>
-      <c r="K21" s="53"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="52"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="63"/>
-      <c r="B22" s="37" t="s">
+      <c r="A22" s="62"/>
+      <c r="B22" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="37">
         <v>46327</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="37">
         <v>46329</v>
       </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39">
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38">
         <v>0</v>
       </c>
-      <c r="H22" s="37" t="s">
+      <c r="H22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="63"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="54"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="53"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="43">
         <v>46190</v>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="43">
         <v>46206</v>
       </c>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="45">
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="44">
         <v>1</v>
       </c>
-      <c r="H23" s="43" t="s">
+      <c r="H23" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="64">
+      <c r="I23" s="63">
+        <v>46237</v>
+      </c>
+      <c r="J23" s="63"/>
+      <c r="K23" s="52"/>
+    </row>
+    <row r="24" spans="1:11" ht="15" thickBot="1">
+      <c r="A24" s="62"/>
+      <c r="B24" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="46">
+        <v>46216</v>
+      </c>
+      <c r="D24" s="46">
         <v>46220</v>
       </c>
-      <c r="J23" s="64"/>
-      <c r="K23" s="53"/>
-    </row>
-    <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="63"/>
-      <c r="B24" s="46" t="s">
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="47">
+        <v>1</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="62"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="53"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="43">
+        <v>46185</v>
+      </c>
+      <c r="D25" s="43">
+        <v>46188</v>
+      </c>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="44">
+        <v>1</v>
+      </c>
+      <c r="H25" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="63">
+        <v>46188</v>
+      </c>
+      <c r="J25" s="63"/>
+      <c r="K25" s="52"/>
+    </row>
+    <row r="26" spans="1:11" ht="15" thickBot="1">
+      <c r="A26" s="62"/>
+      <c r="B26" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="47">
-        <v>46216</v>
-      </c>
-      <c r="D24" s="47">
-        <v>46220</v>
-      </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="48">
+      <c r="C26" s="46">
+        <v>46185</v>
+      </c>
+      <c r="D26" s="46">
+        <v>46188</v>
+      </c>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="47">
         <v>1</v>
       </c>
-      <c r="H24" s="46" t="s">
+      <c r="H26" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="62"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="53"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="40">
+        <v>46234</v>
+      </c>
+      <c r="D27" s="40">
+        <v>46247</v>
+      </c>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="41">
+        <v>0</v>
+      </c>
+      <c r="H27" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="63"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="54"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="43" t="s">
+      <c r="I27" s="63">
+        <v>46321</v>
+      </c>
+      <c r="J27" s="63"/>
+      <c r="K27" s="52"/>
+    </row>
+    <row r="28" spans="1:11" ht="15" thickBot="1">
+      <c r="A28" s="62"/>
+      <c r="B28" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="37">
+        <v>46314</v>
+      </c>
+      <c r="D28" s="37">
+        <v>46316</v>
+      </c>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="38">
+        <v>0</v>
+      </c>
+      <c r="H28" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="62"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="53"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="44">
-        <v>46185</v>
-      </c>
-      <c r="D25" s="44">
-        <v>46188</v>
-      </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="45">
+      <c r="C29" s="43">
+        <v>46091</v>
+      </c>
+      <c r="D29" s="43">
+        <v>46100</v>
+      </c>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="44">
         <v>1</v>
       </c>
-      <c r="H25" s="43" t="s">
+      <c r="H29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="64">
-        <v>46188</v>
-      </c>
-      <c r="J25" s="64"/>
-      <c r="K25" s="53"/>
-    </row>
-    <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="63"/>
-      <c r="B26" s="46" t="s">
+      <c r="I29" s="63">
+        <v>46139</v>
+      </c>
+      <c r="J29" s="63"/>
+      <c r="K29" s="52"/>
+    </row>
+    <row r="30" spans="1:11" ht="15" thickBot="1">
+      <c r="A30" s="62"/>
+      <c r="B30" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="47">
-        <v>46185</v>
-      </c>
-      <c r="D26" s="47">
-        <v>46188</v>
-      </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="48">
+      <c r="C30" s="46">
+        <v>46120</v>
+      </c>
+      <c r="D30" s="46">
+        <v>46124</v>
+      </c>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="47">
         <v>1</v>
       </c>
-      <c r="H26" s="46" t="s">
+      <c r="H30" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="63"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="54"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="40" t="s">
+      <c r="I30" s="62"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="53"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="41">
-        <v>46234</v>
-      </c>
-      <c r="D27" s="41">
-        <v>46247</v>
-      </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="42">
+      <c r="C31" s="43">
+        <v>46091</v>
+      </c>
+      <c r="D31" s="43">
+        <v>46094</v>
+      </c>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="44">
+        <v>1</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="63">
+        <v>46133</v>
+      </c>
+      <c r="J31" s="63"/>
+      <c r="K31" s="52"/>
+    </row>
+    <row r="32" spans="1:11" ht="15" thickBot="1">
+      <c r="A32" s="62"/>
+      <c r="B32" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="46">
+        <v>46091</v>
+      </c>
+      <c r="D32" s="46">
+        <v>46094</v>
+      </c>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="47">
+        <v>1</v>
+      </c>
+      <c r="H32" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" s="62"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="53"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="40">
+        <v>46091</v>
+      </c>
+      <c r="D33" s="40">
+        <v>46094</v>
+      </c>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41">
         <v>0</v>
       </c>
-      <c r="H27" s="40" t="s">
+      <c r="H33" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="64">
-        <v>46321</v>
-      </c>
-      <c r="J27" s="64"/>
-      <c r="K27" s="53"/>
-    </row>
-    <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="63"/>
-      <c r="B28" s="37" t="s">
+      <c r="I33" s="63">
+        <v>46295</v>
+      </c>
+      <c r="J33" s="63"/>
+      <c r="K33" s="52"/>
+    </row>
+    <row r="34" spans="1:11" ht="15" thickBot="1">
+      <c r="A34" s="62"/>
+      <c r="B34" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="38">
-        <v>46314</v>
-      </c>
-      <c r="D28" s="38">
-        <v>46316</v>
-      </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="39">
+      <c r="C34" s="37">
+        <v>46091</v>
+      </c>
+      <c r="D34" s="37">
+        <v>46094</v>
+      </c>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="38">
         <v>0</v>
       </c>
-      <c r="H28" s="37" t="s">
+      <c r="H34" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="63"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="54"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="43" t="s">
+      <c r="I34" s="62"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="53"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="44">
-        <v>46091</v>
-      </c>
-      <c r="D29" s="44">
-        <v>46100</v>
-      </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="45">
+      <c r="C35" s="40">
+        <v>45723</v>
+      </c>
+      <c r="D35" s="40">
+        <v>45729</v>
+      </c>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="41">
         <v>1</v>
       </c>
-      <c r="H29" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" s="64">
-        <v>46139</v>
-      </c>
-      <c r="J29" s="64"/>
-      <c r="K29" s="53"/>
-    </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="63"/>
-      <c r="B30" s="46" t="s">
+      <c r="H35" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="63">
+        <v>45884</v>
+      </c>
+      <c r="J35" s="63"/>
+      <c r="K35" s="52"/>
+    </row>
+    <row r="36" spans="1:11" ht="15" thickBot="1">
+      <c r="A36" s="62"/>
+      <c r="B36" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="47">
-        <v>46120</v>
-      </c>
-      <c r="D30" s="47">
-        <v>46124</v>
-      </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="48">
+      <c r="C36" s="37">
+        <v>45729</v>
+      </c>
+      <c r="D36" s="37">
+        <v>45732</v>
+      </c>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="38">
+        <v>0.9</v>
+      </c>
+      <c r="H36" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="62"/>
+      <c r="J36" s="64"/>
+      <c r="K36" s="53"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="40">
+        <v>45723</v>
+      </c>
+      <c r="D37" s="40">
+        <v>45729</v>
+      </c>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="41">
         <v>1</v>
       </c>
-      <c r="H30" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="63"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="54"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="43" t="s">
+      <c r="H37" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="63">
+        <v>45915</v>
+      </c>
+      <c r="J37" s="63"/>
+      <c r="K37" s="52"/>
+    </row>
+    <row r="38" spans="1:11" ht="15" thickBot="1">
+      <c r="A38" s="62"/>
+      <c r="B38" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="37">
+        <v>45729</v>
+      </c>
+      <c r="D38" s="37">
+        <v>45732</v>
+      </c>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="38">
+        <v>0.9</v>
+      </c>
+      <c r="H38" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="62"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="53"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="44">
-        <v>46091</v>
-      </c>
-      <c r="D31" s="44">
-        <v>46094</v>
-      </c>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="45">
-        <v>1</v>
-      </c>
-      <c r="H31" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="64">
-        <v>46133</v>
-      </c>
-      <c r="J31" s="64"/>
-      <c r="K31" s="53"/>
-    </row>
-    <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="63"/>
-      <c r="B32" s="46" t="s">
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="41">
+        <v>0</v>
+      </c>
+      <c r="H39" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="52"/>
+    </row>
+    <row r="40" spans="1:11" ht="15" thickBot="1">
+      <c r="A40" s="62"/>
+      <c r="B40" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="47">
-        <v>46091</v>
-      </c>
-      <c r="D32" s="47">
-        <v>46094</v>
-      </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="48">
-        <v>1</v>
-      </c>
-      <c r="H32" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="I32" s="63"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="54"/>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="40" t="s">
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="58">
+        <v>0</v>
+      </c>
+      <c r="H40" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="62"/>
+      <c r="J40" s="64"/>
+      <c r="K40" s="53"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="61" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="41">
-        <v>46091</v>
-      </c>
-      <c r="D33" s="41">
-        <v>46094</v>
-      </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="42">
-        <v>0</v>
-      </c>
-      <c r="H33" s="40" t="s">
+      <c r="C41" s="40">
+        <v>46226</v>
+      </c>
+      <c r="D41" s="40">
+        <v>46228</v>
+      </c>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="41">
+        <v>0.35</v>
+      </c>
+      <c r="H41" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="64">
-        <v>46295</v>
-      </c>
-      <c r="J33" s="64"/>
-      <c r="K33" s="53"/>
-    </row>
-    <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="37" t="s">
+      <c r="I41" s="63">
+        <v>46230</v>
+      </c>
+      <c r="J41" s="63"/>
+      <c r="K41" s="52"/>
+    </row>
+    <row r="42" spans="1:11" ht="15" thickBot="1">
+      <c r="A42" s="62"/>
+      <c r="B42" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="38">
-        <v>46091</v>
-      </c>
-      <c r="D34" s="38">
-        <v>46094</v>
-      </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="39">
-        <v>0</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="63"/>
-      <c r="J34" s="65"/>
-      <c r="K34" s="54"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="41">
-        <v>45723</v>
-      </c>
-      <c r="D35" s="41">
-        <v>45729</v>
-      </c>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="42">
-        <v>1</v>
-      </c>
-      <c r="H35" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="64">
-        <v>45737</v>
-      </c>
-      <c r="J35" s="64"/>
-      <c r="K35" s="53"/>
-    </row>
-    <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="63"/>
-      <c r="B36" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="38">
-        <v>45729</v>
-      </c>
-      <c r="D36" s="38">
-        <v>45732</v>
-      </c>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="39">
-        <v>0.9</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="63"/>
-      <c r="J36" s="65"/>
-      <c r="K36" s="54"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="41">
-        <v>45723</v>
-      </c>
-      <c r="D37" s="41">
-        <v>45729</v>
-      </c>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="42">
-        <v>1</v>
-      </c>
-      <c r="H37" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" s="64">
-        <v>45737</v>
-      </c>
-      <c r="J37" s="64"/>
-      <c r="K37" s="53"/>
-    </row>
-    <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="63"/>
-      <c r="B38" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="38">
-        <v>45729</v>
-      </c>
-      <c r="D38" s="38">
-        <v>45732</v>
-      </c>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="39">
-        <v>0.9</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="63"/>
-      <c r="J38" s="65"/>
-      <c r="K38" s="54"/>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="B39" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="42">
-        <v>0</v>
-      </c>
-      <c r="H39" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="53"/>
-    </row>
-    <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="63"/>
-      <c r="B40" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="59">
-        <v>0</v>
-      </c>
-      <c r="H40" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="63"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="54"/>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="B41" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="41">
-        <v>46225</v>
-      </c>
-      <c r="D41" s="41">
-        <v>46227</v>
-      </c>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="42">
-        <v>0</v>
-      </c>
-      <c r="H41" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="64">
-        <v>46227</v>
-      </c>
-      <c r="J41" s="64"/>
-      <c r="K41" s="53"/>
-    </row>
-    <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="63"/>
-      <c r="B42" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="63"/>
-      <c r="J42" s="65"/>
-      <c r="K42" s="54"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="62"/>
+      <c r="J42" s="64"/>
+      <c r="K42" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="59">
@@ -2425,7 +2427,7 @@
     <mergeCell ref="I41:I42"/>
     <mergeCell ref="J41:J42"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -2459,56 +2461,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -2578,1579 +2580,1577 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>0.9</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <v>326786.36</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="16">
         <f>P5</f>
         <v>130000</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17">
+      <c r="G5" s="16"/>
+      <c r="H5" s="16">
         <f>E5*0.9</f>
         <v>294107.72399999999</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="17">
         <v>12</v>
       </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="17">
+      <c r="J5" s="17"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="16">
         <v>5198</v>
       </c>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17">
+      <c r="M5" s="16"/>
+      <c r="N5" s="16">
         <v>0</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="18">
         <v>130000</v>
       </c>
-      <c r="Q5" s="20">
+      <c r="Q5" s="19">
         <f>'[1]Master Schedule'!C5</f>
         <v>46084</v>
       </c>
-      <c r="R5" s="20">
+      <c r="R5" s="19">
         <v>46106</v>
       </c>
-      <c r="S5" s="15"/>
-      <c r="T5" s="27" t="s">
+      <c r="S5" s="14"/>
+      <c r="T5" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="U5" s="30" t="s">
+      <c r="U5" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="V5" s="20"/>
-    </row>
-    <row r="6" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A6" s="15" t="s">
+      <c r="V5" s="19"/>
+    </row>
+    <row r="6" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>0</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="16">
         <v>409599.64</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="16">
         <f>P6*0.3</f>
         <v>41833.799999999996</v>
       </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17">
+      <c r="G6" s="16"/>
+      <c r="H6" s="16">
         <f t="shared" ref="H6:H13" si="0">E6*0.4</f>
         <v>163839.85600000003</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="17">
         <v>0</v>
       </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="17">
+      <c r="J6" s="17"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="16">
         <v>6972.5</v>
       </c>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17">
+      <c r="M6" s="16"/>
+      <c r="N6" s="16">
         <v>0</v>
       </c>
-      <c r="O6" s="15" t="s">
+      <c r="O6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="18">
         <v>139446</v>
       </c>
-      <c r="Q6" s="20">
+      <c r="Q6" s="19">
         <f>'[1]Master Schedule'!C6</f>
         <v>46189</v>
       </c>
-      <c r="R6" s="20">
+      <c r="R6" s="19">
         <v>46264</v>
       </c>
-      <c r="S6" s="15"/>
-      <c r="T6" s="27" t="s">
+      <c r="S6" s="14"/>
+      <c r="T6" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="U6" s="27"/>
-      <c r="V6" s="20"/>
-    </row>
-    <row r="7" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A7" s="15" t="s">
+      <c r="U6" s="26"/>
+      <c r="V6" s="19"/>
+    </row>
+    <row r="7" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>1</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>576317.9</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <f t="shared" ref="F7:F18" si="1">P7</f>
         <v>280000</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>603</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <f>E7*1</f>
         <v>576317.9</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="17">
         <v>20</v>
       </c>
-      <c r="J7" s="18"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="17">
+      <c r="J7" s="17"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="16">
         <v>12045</v>
       </c>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17">
+      <c r="M7" s="16"/>
+      <c r="N7" s="16">
         <v>0</v>
       </c>
-      <c r="O7" s="15" t="s">
+      <c r="O7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="18">
         <v>280000</v>
       </c>
-      <c r="Q7" s="20">
+      <c r="Q7" s="19">
         <f>'[1]Master Schedule'!C7</f>
         <v>46219</v>
       </c>
-      <c r="R7" s="20">
+      <c r="R7" s="19">
         <v>46102</v>
       </c>
-      <c r="S7" s="15"/>
-      <c r="T7" s="27" t="s">
+      <c r="S7" s="14"/>
+      <c r="T7" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="U7" s="30" t="s">
+      <c r="U7" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="V7" s="20"/>
-    </row>
-    <row r="8" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A8" s="15" t="s">
+      <c r="V7" s="19"/>
+    </row>
+    <row r="8" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A8" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>1</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="16">
         <v>322961.08</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="16">
         <f t="shared" si="1"/>
         <v>89000</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="16">
         <v>715</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="16">
         <f>E8*1</f>
         <v>322961.08</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="17">
         <v>7</v>
       </c>
-      <c r="J8" s="18"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="17">
+      <c r="J8" s="17"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="16">
         <v>24166</v>
       </c>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17">
+      <c r="M8" s="16"/>
+      <c r="N8" s="16">
         <v>1444</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="O8" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="18">
         <v>89000</v>
       </c>
-      <c r="Q8" s="20">
+      <c r="Q8" s="19">
         <f>'[1]Master Schedule'!C8</f>
         <v>46244</v>
       </c>
-      <c r="R8" s="20">
+      <c r="R8" s="19">
         <v>46171</v>
       </c>
-      <c r="S8" s="15"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="32" t="s">
+      <c r="S8" s="14"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="V8" s="20">
+      <c r="V8" s="19">
         <v>46134</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>630619.19999999995</v>
       </c>
-      <c r="F9" s="17" t="str">
+      <c r="F9" s="16" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17">
+      <c r="G9" s="16"/>
+      <c r="H9" s="16">
         <f>E9*0.4</f>
         <v>252247.67999999999</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="17">
         <v>0</v>
       </c>
-      <c r="J9" s="18"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17">
+      <c r="J9" s="17"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16">
         <v>0</v>
       </c>
-      <c r="O9" s="15"/>
-      <c r="P9" s="19" t="s">
+      <c r="O9" s="14"/>
+      <c r="P9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="20">
+      <c r="Q9" s="19">
         <v>46388</v>
       </c>
-      <c r="R9" s="20">
+      <c r="R9" s="19">
         <v>46447</v>
       </c>
-      <c r="S9" s="15"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="20"/>
-    </row>
-    <row r="10" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A10" s="10" t="s">
+      <c r="S9" s="14"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="19"/>
+    </row>
+    <row r="10" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <v>1</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <v>338450.2</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <f>P10*1</f>
         <v>138000</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="16">
         <v>370</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="16">
         <f>E10*1</f>
         <v>338450.2</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="17">
         <v>12</v>
       </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="17">
+      <c r="J10" s="17"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="16">
         <v>5783</v>
       </c>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17">
+      <c r="M10" s="16"/>
+      <c r="N10" s="16">
         <v>787</v>
       </c>
-      <c r="O10" s="15" t="s">
+      <c r="O10" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="18">
         <v>138000</v>
       </c>
-      <c r="Q10" s="20">
+      <c r="Q10" s="19">
         <f>'[1]Master Schedule'!C10</f>
         <v>46168</v>
       </c>
-      <c r="R10" s="20">
+      <c r="R10" s="19">
         <v>46199</v>
       </c>
-      <c r="S10" s="15"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="32" t="s">
+      <c r="S10" s="14"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="V10" s="20">
+      <c r="V10" s="19">
         <v>46141</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>0.7</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>1156111.18</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="16">
         <f>P11*0.8</f>
         <v>224000</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <v>840</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="16">
         <f>E11*0.7</f>
         <v>809277.82599999988</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="17">
         <v>10</v>
       </c>
-      <c r="J11" s="18"/>
-      <c r="L11" s="17">
+      <c r="J11" s="17"/>
+      <c r="L11" s="16">
         <v>26094</v>
       </c>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17">
+      <c r="M11" s="16"/>
+      <c r="N11" s="16">
         <v>46175</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="18">
         <v>280000</v>
       </c>
-      <c r="Q11" s="20">
+      <c r="Q11" s="19">
         <f>'[1]Master Schedule'!C11</f>
         <v>46184</v>
       </c>
-      <c r="R11" s="20">
+      <c r="R11" s="19">
         <v>46305</v>
       </c>
-      <c r="S11" s="15"/>
-      <c r="T11" s="28" t="s">
+      <c r="S11" s="14"/>
+      <c r="T11" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="U11" s="32" t="s">
+      <c r="U11" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="V11" s="20">
+      <c r="V11" s="19">
         <v>46147</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>0</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="16">
         <v>594114</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="16">
         <f>P12*0</f>
         <v>0</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17">
+      <c r="G12" s="16"/>
+      <c r="H12" s="16">
         <f t="shared" si="0"/>
         <v>237645.6</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="17">
         <v>0</v>
       </c>
-      <c r="J12" s="18"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="17">
+      <c r="J12" s="17"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="16">
         <v>20261</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17">
+      <c r="M12" s="16"/>
+      <c r="N12" s="16">
         <v>20018</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="P12" s="19">
+      <c r="P12" s="18">
         <v>233247.9</v>
       </c>
-      <c r="Q12" s="20">
+      <c r="Q12" s="19">
         <f>'[1]Master Schedule'!C12</f>
         <v>46200</v>
       </c>
-      <c r="R12" s="20">
+      <c r="R12" s="19">
         <v>46336</v>
       </c>
-      <c r="S12" s="15"/>
-      <c r="T12" s="28" t="s">
+      <c r="S12" s="14"/>
+      <c r="T12" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="U12" s="27"/>
-      <c r="V12" s="20">
+      <c r="U12" s="26"/>
+      <c r="V12" s="19">
         <v>46331</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <v>0</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="16">
         <v>327102.8</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="16">
         <f>P13*0.3</f>
         <v>36000</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="16">
         <f t="shared" si="0"/>
         <v>130841.12</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="20">
         <v>3</v>
       </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="17">
+      <c r="K13" s="14"/>
+      <c r="L13" s="16">
         <v>14327</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="9">
         <v>4164</v>
       </c>
-      <c r="O13" s="15" t="s">
+      <c r="O13" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="10">
         <v>120000</v>
       </c>
-      <c r="Q13" s="20">
-        <f>'[1]Master Schedule'!C13</f>
-        <v>46392</v>
-      </c>
-      <c r="R13" s="12">
+      <c r="Q13" s="19">
+        <v>46235</v>
+      </c>
+      <c r="R13" s="11">
         <v>46336</v>
       </c>
-      <c r="T13" s="27" t="s">
+      <c r="T13" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="U13" s="32" t="s">
+      <c r="U13" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="V13" s="20">
+      <c r="V13" s="19">
         <v>46147</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A14" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>0.9</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <v>1707089</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="16">
         <f>P14*0.8</f>
         <v>525343.22400000005</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="16">
         <v>215</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="16">
         <f>E14*0.8</f>
         <v>1365671.2000000002</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="20">
         <v>10</v>
       </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="17">
+      <c r="K14" s="14"/>
+      <c r="L14" s="16">
         <v>54190</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <v>20695.969999999972</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="10">
         <v>656679.03</v>
       </c>
-      <c r="Q14" s="20">
-        <f>'[1]Master Schedule'!C14</f>
-        <v>46042</v>
-      </c>
-      <c r="R14" s="12">
-        <v>46220</v>
-      </c>
-      <c r="T14" s="28" t="s">
+      <c r="Q14" s="19">
+        <v>46229</v>
+      </c>
+      <c r="R14" s="11">
+        <v>46237</v>
+      </c>
+      <c r="T14" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="U14" s="30" t="s">
+      <c r="U14" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="V14" s="20">
+      <c r="V14" s="19">
         <v>46169</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="16">
         <v>80000</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="16">
         <f>P15</f>
         <v>40000</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="16">
         <v>489</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="16">
         <f>E15*1</f>
         <v>80000</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="20">
         <v>4</v>
       </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="17">
+      <c r="K15" s="14"/>
+      <c r="L15" s="16">
         <v>0</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="9">
         <v>0</v>
       </c>
-      <c r="O15" s="10" t="s">
+      <c r="O15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P15" s="11">
+      <c r="P15" s="10">
         <v>40000</v>
       </c>
-      <c r="Q15" s="20">
+      <c r="Q15" s="19">
         <f>'[1]Master Schedule'!C15</f>
         <v>46168</v>
       </c>
-      <c r="R15" s="12">
+      <c r="R15" s="11">
         <v>46188</v>
       </c>
-      <c r="T15" s="29"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="20">
+      <c r="T15" s="28"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="19">
         <v>46169</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A16" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>0</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>1199960.02</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="16">
         <f>P16*0</f>
         <v>0</v>
       </c>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17">
+      <c r="G16" s="16"/>
+      <c r="H16" s="16">
         <f>E16*0.4</f>
         <v>479984.00800000003</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="20">
         <v>0</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="16">
         <v>27535</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="9">
         <v>34414</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O16" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="11">
+      <c r="P16" s="10">
         <v>430000</v>
       </c>
-      <c r="Q16" s="20">
+      <c r="Q16" s="19">
         <f>'[1]Master Schedule'!C16</f>
         <v>46198</v>
       </c>
-      <c r="R16" s="12">
+      <c r="R16" s="11">
         <v>46321</v>
       </c>
-      <c r="T16" s="27" t="s">
+      <c r="T16" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="30" t="s">
+      <c r="U16" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="V16" s="20">
+      <c r="V16" s="19">
         <v>46182</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="15">
         <v>1</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="16">
         <v>600000</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="16">
         <f>P17</f>
         <v>234861</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="16">
         <v>735</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="16">
         <f>E17*1</f>
         <v>600000</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <v>10</v>
       </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="17">
+      <c r="K17" s="14"/>
+      <c r="L17" s="16">
         <v>10000</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="9">
         <v>0</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P17" s="11">
+      <c r="P17" s="10">
         <v>234861</v>
       </c>
-      <c r="Q17" s="20">
+      <c r="Q17" s="19">
         <f>'[1]Master Schedule'!C17</f>
         <v>46188</v>
       </c>
-      <c r="R17" s="12">
+      <c r="R17" s="11">
         <v>46139</v>
       </c>
-      <c r="T17" s="29"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="20">
+      <c r="T17" s="28"/>
+      <c r="U17" s="26"/>
+      <c r="V17" s="19">
         <v>46079</v>
       </c>
     </row>
-    <row r="18" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A18" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>1</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="16">
         <v>317648</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="16">
         <f t="shared" si="1"/>
         <v>119980</v>
       </c>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17">
+      <c r="G18" s="16"/>
+      <c r="H18" s="16">
         <f>E18*1</f>
         <v>317648</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <v>10</v>
       </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="17">
+      <c r="K18" s="14"/>
+      <c r="L18" s="16">
         <v>8760</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="9">
         <v>0</v>
       </c>
-      <c r="O18" s="15" t="s">
+      <c r="O18" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="10">
         <v>119980</v>
       </c>
-      <c r="Q18" s="20">
+      <c r="Q18" s="19">
         <f>'[1]Master Schedule'!C18</f>
         <v>46200</v>
       </c>
-      <c r="R18" s="12">
+      <c r="R18" s="11">
         <v>46133</v>
       </c>
-      <c r="T18" s="29"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="20"/>
-    </row>
-    <row r="19" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A19" s="10" t="s">
+      <c r="T18" s="28"/>
+      <c r="U18" s="26"/>
+      <c r="V18" s="19"/>
+    </row>
+    <row r="19" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A19" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>0</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>832813</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="16">
         <f>P19*0.3</f>
         <v>84000</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="16">
         <v>630</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="16">
         <f>455555</f>
         <v>455555</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="22">
         <v>3</v>
       </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="17">
+      <c r="K19" s="14"/>
+      <c r="L19" s="16">
         <v>35070</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="9">
         <v>7702</v>
       </c>
-      <c r="O19" s="15" t="s">
+      <c r="O19" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="10">
         <v>280000</v>
       </c>
-      <c r="Q19" s="20">
+      <c r="Q19" s="19">
         <f>'Master Schedule'!C33</f>
         <v>46091</v>
       </c>
-      <c r="R19" s="12">
+      <c r="R19" s="11">
         <v>46295</v>
       </c>
-      <c r="T19" s="28" t="s">
+      <c r="T19" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="U19" s="33" t="s">
+      <c r="U19" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="V19" s="20">
+      <c r="V19" s="19">
         <v>46203</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A20" s="10" t="s">
+    <row r="20" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A20" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>0.9</v>
       </c>
-      <c r="E20" s="25"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="10">
+      <c r="E20" s="24"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="9">
         <v>255</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="10">
+      <c r="H20" s="12"/>
+      <c r="I20" s="9">
         <v>3</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>0</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="9">
         <v>0</v>
       </c>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="20">
+      <c r="P20" s="10"/>
+      <c r="Q20" s="19">
         <v>45717</v>
       </c>
-      <c r="R20" s="20">
+      <c r="R20" s="19">
         <v>45737</v>
       </c>
-      <c r="T20" s="28" t="s">
+      <c r="T20" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="U20" s="27"/>
-      <c r="V20" s="20"/>
-    </row>
-    <row r="21" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A21" s="10" t="s">
+      <c r="U20" s="26"/>
+      <c r="V20" s="19"/>
+    </row>
+    <row r="21" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A21" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="15">
         <v>0.9</v>
       </c>
-      <c r="F21" s="26"/>
-      <c r="I21" s="10">
+      <c r="F21" s="25"/>
+      <c r="I21" s="9">
         <v>6</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <v>0</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="9">
         <v>0</v>
       </c>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="20">
+      <c r="P21" s="10"/>
+      <c r="Q21" s="19">
         <v>45717</v>
       </c>
-      <c r="R21" s="20">
+      <c r="R21" s="19">
         <v>45737</v>
       </c>
-      <c r="T21" s="28" t="s">
+      <c r="T21" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="V21" s="20"/>
-    </row>
-    <row r="22" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A22" s="10" t="s">
+      <c r="V21" s="19"/>
+    </row>
+    <row r="22" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A22" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="10">
+      <c r="D22" s="15"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="9">
         <v>2484</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="9">
         <v>10000</v>
       </c>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="T22" s="28" t="s">
+      <c r="P22" s="10"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="T22" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="V22" s="20"/>
-    </row>
-    <row r="23" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A23" s="10" t="s">
+      <c r="V22" s="19"/>
+    </row>
+    <row r="23" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A23" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="15">
         <v>0</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>460000</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="16">
         <v>0</v>
       </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17">
+      <c r="G23" s="16"/>
+      <c r="H23" s="16">
         <f>E23*0.5</f>
         <v>230000</v>
       </c>
-      <c r="I23" s="23"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="17">
+      <c r="I23" s="22"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="16">
         <v>15000</v>
       </c>
-      <c r="O23" s="10" t="s">
+      <c r="O23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P23" s="11">
+      <c r="P23" s="10">
         <v>215000</v>
       </c>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="12"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="33"/>
-      <c r="V23" s="20">
+      <c r="Q23" s="19"/>
+      <c r="R23" s="11"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="19">
         <v>46209</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="10" customFormat="1" ht="18.600000000000001">
-      <c r="A24" s="10" t="s">
+    <row r="24" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A24" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
         <v>0</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>203880</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="16">
         <v>0</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="16">
         <f>400+140</f>
         <v>540</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="16">
         <f>E24*0.4</f>
         <v>81552</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="22">
         <v>6</v>
       </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="17">
+      <c r="K24" s="14"/>
+      <c r="L24" s="16">
         <v>13500</v>
       </c>
-      <c r="N24" s="56">
+      <c r="N24" s="55">
         <v>497</v>
       </c>
-      <c r="O24" s="10" t="s">
+      <c r="O24" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P24" s="11">
+      <c r="P24" s="10">
         <v>58000</v>
       </c>
-      <c r="Q24" s="20">
+      <c r="Q24" s="19">
         <v>46225</v>
       </c>
-      <c r="R24" s="12">
+      <c r="R24" s="11">
         <v>46227</v>
       </c>
-      <c r="T24" s="28" t="s">
+      <c r="T24" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="U24" s="33" t="s">
+      <c r="U24" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="V24" s="20">
+      <c r="V24" s="19">
         <v>46213</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V25" s="20"/>
-    </row>
-    <row r="26" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V26" s="20"/>
-    </row>
-    <row r="27" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V27" s="20"/>
-    </row>
-    <row r="28" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V28" s="20"/>
-    </row>
-    <row r="29" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V29" s="20"/>
-    </row>
-    <row r="30" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V30" s="20"/>
-    </row>
-    <row r="31" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V31" s="20"/>
-    </row>
-    <row r="32" spans="1:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V32" s="20"/>
-    </row>
-    <row r="33" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V33" s="20"/>
-    </row>
-    <row r="34" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V34" s="20"/>
-    </row>
-    <row r="35" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V35" s="20"/>
-    </row>
-    <row r="36" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V36" s="20"/>
-    </row>
-    <row r="37" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V37" s="20"/>
-    </row>
-    <row r="38" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V38" s="20"/>
-    </row>
-    <row r="39" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V39" s="20"/>
-    </row>
-    <row r="40" spans="22:22" s="14" customFormat="1" ht="18.600000000000001">
-      <c r="V40" s="20"/>
-    </row>
-    <row r="41" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V41" s="20"/>
-    </row>
-    <row r="42" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V42" s="20"/>
-    </row>
-    <row r="43" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V43" s="20"/>
-    </row>
-    <row r="44" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V44" s="20"/>
-    </row>
-    <row r="45" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V45" s="20"/>
-    </row>
-    <row r="46" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V46" s="20"/>
-    </row>
-    <row r="47" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V47" s="20"/>
-    </row>
-    <row r="48" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V48" s="20"/>
-    </row>
-    <row r="49" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V49" s="20"/>
-    </row>
-    <row r="50" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V50" s="20"/>
-    </row>
-    <row r="51" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V51" s="20"/>
-    </row>
-    <row r="52" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V52" s="20"/>
-    </row>
-    <row r="53" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V53" s="20"/>
-    </row>
-    <row r="54" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V54" s="20"/>
-    </row>
-    <row r="55" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V55" s="20"/>
-    </row>
-    <row r="56" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V56" s="20"/>
-    </row>
-    <row r="57" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V57" s="20"/>
-    </row>
-    <row r="58" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V58" s="20"/>
-    </row>
-    <row r="59" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V59" s="20"/>
-    </row>
-    <row r="60" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V60" s="20"/>
-    </row>
-    <row r="61" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V61" s="20"/>
-    </row>
-    <row r="62" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V62" s="20"/>
-    </row>
-    <row r="63" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V63" s="20"/>
-    </row>
-    <row r="64" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V64" s="20"/>
-    </row>
-    <row r="65" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V65" s="20"/>
-    </row>
-    <row r="66" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V66" s="20"/>
-    </row>
-    <row r="67" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V67" s="20"/>
-    </row>
-    <row r="68" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V68" s="20"/>
-    </row>
-    <row r="69" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V69" s="20"/>
-    </row>
-    <row r="70" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V70" s="20"/>
-    </row>
-    <row r="71" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V71" s="20"/>
-    </row>
-    <row r="72" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V72" s="20"/>
-    </row>
-    <row r="73" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V73" s="20"/>
-    </row>
-    <row r="74" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V74" s="20"/>
-    </row>
-    <row r="75" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V75" s="20"/>
-    </row>
-    <row r="76" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V76" s="20"/>
-    </row>
-    <row r="77" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V77" s="20"/>
-    </row>
-    <row r="78" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V78" s="20"/>
-    </row>
-    <row r="79" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V79" s="20"/>
-    </row>
-    <row r="80" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V80" s="20"/>
-    </row>
-    <row r="81" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V81" s="20"/>
-    </row>
-    <row r="82" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V82" s="20"/>
-    </row>
-    <row r="83" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V83" s="20"/>
-    </row>
-    <row r="84" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V84" s="20"/>
-    </row>
-    <row r="85" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V85" s="20"/>
-    </row>
-    <row r="86" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V86" s="20"/>
-    </row>
-    <row r="87" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V87" s="20"/>
-    </row>
-    <row r="88" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V88" s="20"/>
-    </row>
-    <row r="89" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V89" s="20"/>
-    </row>
-    <row r="90" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V90" s="20"/>
-    </row>
-    <row r="91" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V91" s="20"/>
-    </row>
-    <row r="92" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V92" s="20"/>
-    </row>
-    <row r="93" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V93" s="20"/>
-    </row>
-    <row r="94" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V94" s="20"/>
-    </row>
-    <row r="95" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V95" s="20"/>
-    </row>
-    <row r="96" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V96" s="20"/>
-    </row>
-    <row r="97" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V97" s="20"/>
-    </row>
-    <row r="98" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V98" s="20"/>
-    </row>
-    <row r="99" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V99" s="20"/>
-    </row>
-    <row r="100" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V100" s="20"/>
-    </row>
-    <row r="101" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V101" s="20"/>
-    </row>
-    <row r="102" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V102" s="20"/>
-    </row>
-    <row r="103" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V103" s="20"/>
-    </row>
-    <row r="104" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V104" s="20"/>
-    </row>
-    <row r="105" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V105" s="20"/>
-    </row>
-    <row r="106" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V106" s="20"/>
-    </row>
-    <row r="107" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V107" s="20"/>
-    </row>
-    <row r="108" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V108" s="20"/>
-    </row>
-    <row r="109" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V109" s="20"/>
-    </row>
-    <row r="110" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V110" s="20"/>
-    </row>
-    <row r="111" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V111" s="20"/>
-    </row>
-    <row r="112" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V112" s="20"/>
-    </row>
-    <row r="113" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V113" s="20"/>
-    </row>
-    <row r="114" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V114" s="20"/>
-    </row>
-    <row r="115" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V115" s="20"/>
-    </row>
-    <row r="116" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V116" s="20"/>
-    </row>
-    <row r="117" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V117" s="20"/>
-    </row>
-    <row r="118" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V118" s="20"/>
-    </row>
-    <row r="119" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V119" s="20"/>
-    </row>
-    <row r="120" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V120" s="20"/>
-    </row>
-    <row r="121" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V121" s="20"/>
-    </row>
-    <row r="122" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V122" s="20"/>
-    </row>
-    <row r="123" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V123" s="20"/>
-    </row>
-    <row r="124" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V124" s="20"/>
-    </row>
-    <row r="125" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V125" s="20"/>
-    </row>
-    <row r="126" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V126" s="20"/>
-    </row>
-    <row r="127" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V127" s="20"/>
-    </row>
-    <row r="128" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V128" s="20"/>
-    </row>
-    <row r="129" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V129" s="20"/>
-    </row>
-    <row r="130" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V130" s="20"/>
-    </row>
-    <row r="131" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V131" s="20"/>
-    </row>
-    <row r="132" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V132" s="20"/>
-    </row>
-    <row r="133" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V133" s="20"/>
-    </row>
-    <row r="134" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V134" s="20"/>
-    </row>
-    <row r="135" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V135" s="20"/>
-    </row>
-    <row r="136" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V136" s="20"/>
-    </row>
-    <row r="137" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V137" s="20"/>
-    </row>
-    <row r="138" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V138" s="20"/>
-    </row>
-    <row r="139" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V139" s="20"/>
-    </row>
-    <row r="140" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V140" s="20"/>
-    </row>
-    <row r="141" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V141" s="20"/>
-    </row>
-    <row r="142" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V142" s="20"/>
-    </row>
-    <row r="143" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V143" s="20"/>
-    </row>
-    <row r="144" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V144" s="20"/>
-    </row>
-    <row r="145" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V145" s="20"/>
-    </row>
-    <row r="146" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V146" s="20"/>
-    </row>
-    <row r="147" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V147" s="20"/>
-    </row>
-    <row r="148" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V148" s="20"/>
-    </row>
-    <row r="149" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V149" s="20"/>
-    </row>
-    <row r="150" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V150" s="20"/>
-    </row>
-    <row r="151" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V151" s="20"/>
-    </row>
-    <row r="152" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V152" s="20"/>
-    </row>
-    <row r="153" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V153" s="20"/>
-    </row>
-    <row r="154" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V154" s="20"/>
-    </row>
-    <row r="155" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V155" s="20"/>
-    </row>
-    <row r="156" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V156" s="20"/>
-    </row>
-    <row r="157" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V157" s="20"/>
-    </row>
-    <row r="158" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V158" s="20"/>
-    </row>
-    <row r="159" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V159" s="20"/>
-    </row>
-    <row r="160" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V160" s="20"/>
-    </row>
-    <row r="161" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V161" s="20"/>
-    </row>
-    <row r="162" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V162" s="20"/>
-    </row>
-    <row r="163" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V163" s="20"/>
-    </row>
-    <row r="164" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V164" s="20"/>
-    </row>
-    <row r="165" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V165" s="20"/>
-    </row>
-    <row r="166" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V166" s="20"/>
-    </row>
-    <row r="167" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V167" s="20"/>
-    </row>
-    <row r="168" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V168" s="20"/>
-    </row>
-    <row r="169" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V169" s="20"/>
-    </row>
-    <row r="170" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V170" s="20"/>
-    </row>
-    <row r="171" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V171" s="20"/>
-    </row>
-    <row r="172" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V172" s="20"/>
-    </row>
-    <row r="173" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V173" s="20"/>
-    </row>
-    <row r="174" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V174" s="20"/>
-    </row>
-    <row r="175" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V175" s="20"/>
-    </row>
-    <row r="176" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V176" s="20"/>
-    </row>
-    <row r="177" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V177" s="20"/>
-    </row>
-    <row r="178" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V178" s="20"/>
-    </row>
-    <row r="179" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V179" s="20"/>
-    </row>
-    <row r="180" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V180" s="20"/>
-    </row>
-    <row r="181" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V181" s="20"/>
-    </row>
-    <row r="182" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V182" s="20"/>
-    </row>
-    <row r="183" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V183" s="20"/>
-    </row>
-    <row r="184" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V184" s="20"/>
-    </row>
-    <row r="185" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V185" s="20"/>
-    </row>
-    <row r="186" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V186" s="20"/>
-    </row>
-    <row r="187" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V187" s="20"/>
-    </row>
-    <row r="188" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V188" s="20"/>
-    </row>
-    <row r="189" spans="22:22" s="9" customFormat="1" ht="18.600000000000001">
-      <c r="V189" s="20"/>
+    <row r="25" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V25" s="19"/>
+    </row>
+    <row r="26" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V26" s="19"/>
+    </row>
+    <row r="27" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V27" s="19"/>
+    </row>
+    <row r="28" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V28" s="19"/>
+    </row>
+    <row r="29" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V29" s="19"/>
+    </row>
+    <row r="30" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V30" s="19"/>
+    </row>
+    <row r="31" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V31" s="19"/>
+    </row>
+    <row r="32" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V32" s="19"/>
+    </row>
+    <row r="33" spans="22:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V33" s="19"/>
+    </row>
+    <row r="34" spans="22:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V34" s="19"/>
+    </row>
+    <row r="35" spans="22:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V35" s="19"/>
+    </row>
+    <row r="36" spans="22:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V36" s="19"/>
+    </row>
+    <row r="37" spans="22:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V37" s="19"/>
+    </row>
+    <row r="38" spans="22:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V38" s="19"/>
+    </row>
+    <row r="39" spans="22:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V39" s="19"/>
+    </row>
+    <row r="40" spans="22:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="V40" s="19"/>
+    </row>
+    <row r="41" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V41" s="19"/>
+    </row>
+    <row r="42" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V42" s="19"/>
+    </row>
+    <row r="43" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V43" s="19"/>
+    </row>
+    <row r="44" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V44" s="19"/>
+    </row>
+    <row r="45" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V45" s="19"/>
+    </row>
+    <row r="46" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V46" s="19"/>
+    </row>
+    <row r="47" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V47" s="19"/>
+    </row>
+    <row r="48" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V48" s="19"/>
+    </row>
+    <row r="49" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V49" s="19"/>
+    </row>
+    <row r="50" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V50" s="19"/>
+    </row>
+    <row r="51" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V51" s="19"/>
+    </row>
+    <row r="52" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V52" s="19"/>
+    </row>
+    <row r="53" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V53" s="19"/>
+    </row>
+    <row r="54" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V54" s="19"/>
+    </row>
+    <row r="55" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V55" s="19"/>
+    </row>
+    <row r="56" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V56" s="19"/>
+    </row>
+    <row r="57" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V57" s="19"/>
+    </row>
+    <row r="58" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V58" s="19"/>
+    </row>
+    <row r="59" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V59" s="19"/>
+    </row>
+    <row r="60" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V60" s="19"/>
+    </row>
+    <row r="61" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V61" s="19"/>
+    </row>
+    <row r="62" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V62" s="19"/>
+    </row>
+    <row r="63" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V63" s="19"/>
+    </row>
+    <row r="64" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V64" s="19"/>
+    </row>
+    <row r="65" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V65" s="19"/>
+    </row>
+    <row r="66" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V66" s="19"/>
+    </row>
+    <row r="67" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V67" s="19"/>
+    </row>
+    <row r="68" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V68" s="19"/>
+    </row>
+    <row r="69" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V69" s="19"/>
+    </row>
+    <row r="70" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V70" s="19"/>
+    </row>
+    <row r="71" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V71" s="19"/>
+    </row>
+    <row r="72" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V72" s="19"/>
+    </row>
+    <row r="73" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V73" s="19"/>
+    </row>
+    <row r="74" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V74" s="19"/>
+    </row>
+    <row r="75" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V75" s="19"/>
+    </row>
+    <row r="76" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V76" s="19"/>
+    </row>
+    <row r="77" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V77" s="19"/>
+    </row>
+    <row r="78" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V78" s="19"/>
+    </row>
+    <row r="79" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V79" s="19"/>
+    </row>
+    <row r="80" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V80" s="19"/>
+    </row>
+    <row r="81" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V81" s="19"/>
+    </row>
+    <row r="82" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V82" s="19"/>
+    </row>
+    <row r="83" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V83" s="19"/>
+    </row>
+    <row r="84" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V84" s="19"/>
+    </row>
+    <row r="85" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V85" s="19"/>
+    </row>
+    <row r="86" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V86" s="19"/>
+    </row>
+    <row r="87" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V87" s="19"/>
+    </row>
+    <row r="88" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V88" s="19"/>
+    </row>
+    <row r="89" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V89" s="19"/>
+    </row>
+    <row r="90" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V90" s="19"/>
+    </row>
+    <row r="91" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V91" s="19"/>
+    </row>
+    <row r="92" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V92" s="19"/>
+    </row>
+    <row r="93" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V93" s="19"/>
+    </row>
+    <row r="94" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V94" s="19"/>
+    </row>
+    <row r="95" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V95" s="19"/>
+    </row>
+    <row r="96" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V96" s="19"/>
+    </row>
+    <row r="97" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V97" s="19"/>
+    </row>
+    <row r="98" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V98" s="19"/>
+    </row>
+    <row r="99" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V99" s="19"/>
+    </row>
+    <row r="100" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V100" s="19"/>
+    </row>
+    <row r="101" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V101" s="19"/>
+    </row>
+    <row r="102" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V102" s="19"/>
+    </row>
+    <row r="103" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V103" s="19"/>
+    </row>
+    <row r="104" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V104" s="19"/>
+    </row>
+    <row r="105" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V105" s="19"/>
+    </row>
+    <row r="106" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V106" s="19"/>
+    </row>
+    <row r="107" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V107" s="19"/>
+    </row>
+    <row r="108" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V108" s="19"/>
+    </row>
+    <row r="109" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V109" s="19"/>
+    </row>
+    <row r="110" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V110" s="19"/>
+    </row>
+    <row r="111" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V111" s="19"/>
+    </row>
+    <row r="112" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V112" s="19"/>
+    </row>
+    <row r="113" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V113" s="19"/>
+    </row>
+    <row r="114" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V114" s="19"/>
+    </row>
+    <row r="115" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V115" s="19"/>
+    </row>
+    <row r="116" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V116" s="19"/>
+    </row>
+    <row r="117" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V117" s="19"/>
+    </row>
+    <row r="118" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V118" s="19"/>
+    </row>
+    <row r="119" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V119" s="19"/>
+    </row>
+    <row r="120" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V120" s="19"/>
+    </row>
+    <row r="121" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V121" s="19"/>
+    </row>
+    <row r="122" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V122" s="19"/>
+    </row>
+    <row r="123" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V123" s="19"/>
+    </row>
+    <row r="124" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V124" s="19"/>
+    </row>
+    <row r="125" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V125" s="19"/>
+    </row>
+    <row r="126" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V126" s="19"/>
+    </row>
+    <row r="127" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V127" s="19"/>
+    </row>
+    <row r="128" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V128" s="19"/>
+    </row>
+    <row r="129" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V129" s="19"/>
+    </row>
+    <row r="130" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V130" s="19"/>
+    </row>
+    <row r="131" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V131" s="19"/>
+    </row>
+    <row r="132" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V132" s="19"/>
+    </row>
+    <row r="133" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V133" s="19"/>
+    </row>
+    <row r="134" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V134" s="19"/>
+    </row>
+    <row r="135" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V135" s="19"/>
+    </row>
+    <row r="136" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V136" s="19"/>
+    </row>
+    <row r="137" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V137" s="19"/>
+    </row>
+    <row r="138" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V138" s="19"/>
+    </row>
+    <row r="139" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V139" s="19"/>
+    </row>
+    <row r="140" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V140" s="19"/>
+    </row>
+    <row r="141" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V141" s="19"/>
+    </row>
+    <row r="142" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V142" s="19"/>
+    </row>
+    <row r="143" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V143" s="19"/>
+    </row>
+    <row r="144" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V144" s="19"/>
+    </row>
+    <row r="145" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V145" s="19"/>
+    </row>
+    <row r="146" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V146" s="19"/>
+    </row>
+    <row r="147" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V147" s="19"/>
+    </row>
+    <row r="148" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V148" s="19"/>
+    </row>
+    <row r="149" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V149" s="19"/>
+    </row>
+    <row r="150" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V150" s="19"/>
+    </row>
+    <row r="151" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V151" s="19"/>
+    </row>
+    <row r="152" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V152" s="19"/>
+    </row>
+    <row r="153" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V153" s="19"/>
+    </row>
+    <row r="154" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V154" s="19"/>
+    </row>
+    <row r="155" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V155" s="19"/>
+    </row>
+    <row r="156" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V156" s="19"/>
+    </row>
+    <row r="157" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V157" s="19"/>
+    </row>
+    <row r="158" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V158" s="19"/>
+    </row>
+    <row r="159" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V159" s="19"/>
+    </row>
+    <row r="160" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V160" s="19"/>
+    </row>
+    <row r="161" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V161" s="19"/>
+    </row>
+    <row r="162" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V162" s="19"/>
+    </row>
+    <row r="163" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V163" s="19"/>
+    </row>
+    <row r="164" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V164" s="19"/>
+    </row>
+    <row r="165" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V165" s="19"/>
+    </row>
+    <row r="166" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V166" s="19"/>
+    </row>
+    <row r="167" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V167" s="19"/>
+    </row>
+    <row r="168" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V168" s="19"/>
+    </row>
+    <row r="169" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V169" s="19"/>
+    </row>
+    <row r="170" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V170" s="19"/>
+    </row>
+    <row r="171" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V171" s="19"/>
+    </row>
+    <row r="172" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V172" s="19"/>
+    </row>
+    <row r="173" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V173" s="19"/>
+    </row>
+    <row r="174" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V174" s="19"/>
+    </row>
+    <row r="175" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V175" s="19"/>
+    </row>
+    <row r="176" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V176" s="19"/>
+    </row>
+    <row r="177" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V177" s="19"/>
+    </row>
+    <row r="178" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V178" s="19"/>
+    </row>
+    <row r="179" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V179" s="19"/>
+    </row>
+    <row r="180" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V180" s="19"/>
+    </row>
+    <row r="181" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V181" s="19"/>
+    </row>
+    <row r="182" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V182" s="19"/>
+    </row>
+    <row r="183" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V183" s="19"/>
+    </row>
+    <row r="184" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V184" s="19"/>
+    </row>
+    <row r="185" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V185" s="19"/>
+    </row>
+    <row r="186" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V186" s="19"/>
+    </row>
+    <row r="187" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V187" s="19"/>
+    </row>
+    <row r="188" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V188" s="19"/>
+    </row>
+    <row r="189" spans="22:22" s="8" customFormat="1" ht="18.600000000000001">
+      <c r="V189" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -4190,20 +4190,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4218,7 +4218,7 @@
       <c r="D4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="54" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4226,13 +4226,13 @@
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="8"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="8"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6">
@@ -4244,7 +4244,7 @@
       <c r="C7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
@@ -4261,7 +4261,7 @@
       <c r="C8" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>4</v>
       </c>
       <c r="E8" t="s">
@@ -4278,7 +4278,7 @@
       <c r="C9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>3</v>
       </c>
       <c r="E9" t="s">
@@ -4295,7 +4295,7 @@
       <c r="C10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>2.5</v>
       </c>
       <c r="E10" t="s">
@@ -4312,7 +4312,7 @@
       <c r="C11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>3</v>
       </c>
       <c r="E11" t="s">
@@ -4329,7 +4329,7 @@
       <c r="C12" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>3</v>
       </c>
       <c r="E12" t="s">
@@ -4346,7 +4346,7 @@
       <c r="C13" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>3</v>
       </c>
       <c r="E13" t="s">
@@ -4363,7 +4363,7 @@
       <c r="C14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>3</v>
       </c>
       <c r="E14" t="s">
@@ -4596,22 +4596,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4682,10 +4682,21 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="3"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="A8" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="6">
+        <v>46226</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46249</v>
+      </c>
+      <c r="E8" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="6"/>
@@ -4808,699 +4819,699 @@
       <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
     </row>
     <row r="33" spans="3:4">
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
     </row>
     <row r="34" spans="3:4">
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
     </row>
     <row r="35" spans="3:4">
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
     </row>
     <row r="36" spans="3:4">
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
     </row>
     <row r="37" spans="3:4">
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
     </row>
     <row r="38" spans="3:4">
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
     </row>
     <row r="39" spans="3:4">
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
     </row>
     <row r="40" spans="3:4">
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
     </row>
     <row r="42" spans="3:4">
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
     </row>
     <row r="43" spans="3:4">
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
     </row>
     <row r="44" spans="3:4">
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
     </row>
     <row r="45" spans="3:4">
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
     </row>
     <row r="46" spans="3:4">
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
     </row>
     <row r="47" spans="3:4">
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
     </row>
     <row r="48" spans="3:4">
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
     </row>
     <row r="49" spans="3:4">
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
     </row>
     <row r="50" spans="3:4">
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
     </row>
     <row r="51" spans="3:4">
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
     </row>
     <row r="52" spans="3:4">
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
     </row>
     <row r="53" spans="3:4">
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
     </row>
     <row r="54" spans="3:4">
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
     </row>
     <row r="55" spans="3:4">
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
     </row>
     <row r="56" spans="3:4">
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
     </row>
     <row r="57" spans="3:4">
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
     </row>
     <row r="58" spans="3:4">
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
     </row>
     <row r="59" spans="3:4">
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
     </row>
     <row r="60" spans="3:4">
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
     </row>
     <row r="61" spans="3:4">
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
     </row>
     <row r="62" spans="3:4">
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
     </row>
     <row r="63" spans="3:4">
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
     </row>
     <row r="64" spans="3:4">
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
     </row>
     <row r="65" spans="3:4">
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
     </row>
     <row r="66" spans="3:4">
-      <c r="C66" s="31"/>
-      <c r="D66" s="31"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
     </row>
     <row r="67" spans="3:4">
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
     </row>
     <row r="68" spans="3:4">
-      <c r="C68" s="31"/>
-      <c r="D68" s="31"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
     </row>
     <row r="69" spans="3:4">
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
     </row>
     <row r="70" spans="3:4">
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
     </row>
     <row r="71" spans="3:4">
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
     </row>
     <row r="72" spans="3:4">
-      <c r="C72" s="31"/>
-      <c r="D72" s="31"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
     </row>
     <row r="73" spans="3:4">
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
+      <c r="C73" s="30"/>
+      <c r="D73" s="30"/>
     </row>
     <row r="74" spans="3:4">
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
     </row>
     <row r="75" spans="3:4">
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
     </row>
     <row r="76" spans="3:4">
-      <c r="C76" s="31"/>
-      <c r="D76" s="31"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
     </row>
     <row r="77" spans="3:4">
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="30"/>
     </row>
     <row r="78" spans="3:4">
-      <c r="C78" s="31"/>
-      <c r="D78" s="31"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
     </row>
     <row r="79" spans="3:4">
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
     </row>
     <row r="80" spans="3:4">
-      <c r="C80" s="31"/>
-      <c r="D80" s="31"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
     </row>
     <row r="81" spans="3:4">
-      <c r="C81" s="31"/>
-      <c r="D81" s="31"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
     </row>
     <row r="82" spans="3:4">
-      <c r="C82" s="31"/>
-      <c r="D82" s="31"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
     </row>
     <row r="83" spans="3:4">
-      <c r="C83" s="31"/>
-      <c r="D83" s="31"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
     </row>
     <row r="84" spans="3:4">
-      <c r="C84" s="31"/>
-      <c r="D84" s="31"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
     </row>
     <row r="85" spans="3:4">
-      <c r="C85" s="31"/>
-      <c r="D85" s="31"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
     </row>
     <row r="86" spans="3:4">
-      <c r="C86" s="31"/>
-      <c r="D86" s="31"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
     </row>
     <row r="87" spans="3:4">
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
     </row>
     <row r="88" spans="3:4">
-      <c r="C88" s="31"/>
-      <c r="D88" s="31"/>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
     </row>
     <row r="89" spans="3:4">
-      <c r="C89" s="31"/>
-      <c r="D89" s="31"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
     </row>
     <row r="90" spans="3:4">
-      <c r="C90" s="31"/>
-      <c r="D90" s="31"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
     </row>
     <row r="91" spans="3:4">
-      <c r="C91" s="31"/>
-      <c r="D91" s="31"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
     </row>
     <row r="92" spans="3:4">
-      <c r="C92" s="31"/>
-      <c r="D92" s="31"/>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
     </row>
     <row r="93" spans="3:4">
-      <c r="C93" s="31"/>
-      <c r="D93" s="31"/>
+      <c r="C93" s="30"/>
+      <c r="D93" s="30"/>
     </row>
     <row r="94" spans="3:4">
-      <c r="C94" s="31"/>
-      <c r="D94" s="31"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
     </row>
     <row r="95" spans="3:4">
-      <c r="C95" s="31"/>
-      <c r="D95" s="31"/>
+      <c r="C95" s="30"/>
+      <c r="D95" s="30"/>
     </row>
     <row r="96" spans="3:4">
-      <c r="C96" s="31"/>
-      <c r="D96" s="31"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
     </row>
     <row r="97" spans="3:4">
-      <c r="C97" s="31"/>
-      <c r="D97" s="31"/>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
     </row>
     <row r="98" spans="3:4">
-      <c r="C98" s="31"/>
-      <c r="D98" s="31"/>
+      <c r="C98" s="30"/>
+      <c r="D98" s="30"/>
     </row>
     <row r="99" spans="3:4">
-      <c r="C99" s="31"/>
-      <c r="D99" s="31"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
     </row>
     <row r="100" spans="3:4">
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
     </row>
     <row r="101" spans="3:4">
-      <c r="C101" s="31"/>
-      <c r="D101" s="31"/>
+      <c r="C101" s="30"/>
+      <c r="D101" s="30"/>
     </row>
     <row r="102" spans="3:4">
-      <c r="C102" s="31"/>
-      <c r="D102" s="31"/>
+      <c r="C102" s="30"/>
+      <c r="D102" s="30"/>
     </row>
     <row r="103" spans="3:4">
-      <c r="C103" s="31"/>
-      <c r="D103" s="31"/>
+      <c r="C103" s="30"/>
+      <c r="D103" s="30"/>
     </row>
     <row r="104" spans="3:4">
-      <c r="C104" s="31"/>
-      <c r="D104" s="31"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="30"/>
     </row>
     <row r="105" spans="3:4">
-      <c r="C105" s="31"/>
-      <c r="D105" s="31"/>
+      <c r="C105" s="30"/>
+      <c r="D105" s="30"/>
     </row>
     <row r="106" spans="3:4">
-      <c r="C106" s="31"/>
-      <c r="D106" s="31"/>
+      <c r="C106" s="30"/>
+      <c r="D106" s="30"/>
     </row>
     <row r="107" spans="3:4">
-      <c r="C107" s="31"/>
-      <c r="D107" s="31"/>
+      <c r="C107" s="30"/>
+      <c r="D107" s="30"/>
     </row>
     <row r="108" spans="3:4">
-      <c r="C108" s="31"/>
-      <c r="D108" s="31"/>
+      <c r="C108" s="30"/>
+      <c r="D108" s="30"/>
     </row>
     <row r="109" spans="3:4">
-      <c r="C109" s="31"/>
-      <c r="D109" s="31"/>
+      <c r="C109" s="30"/>
+      <c r="D109" s="30"/>
     </row>
     <row r="110" spans="3:4">
-      <c r="C110" s="31"/>
-      <c r="D110" s="31"/>
+      <c r="C110" s="30"/>
+      <c r="D110" s="30"/>
     </row>
     <row r="111" spans="3:4">
-      <c r="C111" s="31"/>
-      <c r="D111" s="31"/>
+      <c r="C111" s="30"/>
+      <c r="D111" s="30"/>
     </row>
     <row r="112" spans="3:4">
-      <c r="C112" s="31"/>
-      <c r="D112" s="31"/>
+      <c r="C112" s="30"/>
+      <c r="D112" s="30"/>
     </row>
     <row r="113" spans="3:4">
-      <c r="C113" s="31"/>
-      <c r="D113" s="31"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
     </row>
     <row r="114" spans="3:4">
-      <c r="C114" s="31"/>
-      <c r="D114" s="31"/>
+      <c r="C114" s="30"/>
+      <c r="D114" s="30"/>
     </row>
     <row r="115" spans="3:4">
-      <c r="C115" s="31"/>
-      <c r="D115" s="31"/>
+      <c r="C115" s="30"/>
+      <c r="D115" s="30"/>
     </row>
     <row r="116" spans="3:4">
-      <c r="C116" s="31"/>
-      <c r="D116" s="31"/>
+      <c r="C116" s="30"/>
+      <c r="D116" s="30"/>
     </row>
     <row r="117" spans="3:4">
-      <c r="C117" s="31"/>
-      <c r="D117" s="31"/>
+      <c r="C117" s="30"/>
+      <c r="D117" s="30"/>
     </row>
     <row r="118" spans="3:4">
-      <c r="C118" s="31"/>
-      <c r="D118" s="31"/>
+      <c r="C118" s="30"/>
+      <c r="D118" s="30"/>
     </row>
     <row r="119" spans="3:4">
-      <c r="C119" s="31"/>
-      <c r="D119" s="31"/>
+      <c r="C119" s="30"/>
+      <c r="D119" s="30"/>
     </row>
     <row r="120" spans="3:4">
-      <c r="C120" s="31"/>
-      <c r="D120" s="31"/>
+      <c r="C120" s="30"/>
+      <c r="D120" s="30"/>
     </row>
     <row r="121" spans="3:4">
-      <c r="C121" s="31"/>
-      <c r="D121" s="31"/>
+      <c r="C121" s="30"/>
+      <c r="D121" s="30"/>
     </row>
     <row r="122" spans="3:4">
-      <c r="C122" s="31"/>
-      <c r="D122" s="31"/>
+      <c r="C122" s="30"/>
+      <c r="D122" s="30"/>
     </row>
     <row r="123" spans="3:4">
-      <c r="C123" s="31"/>
-      <c r="D123" s="31"/>
+      <c r="C123" s="30"/>
+      <c r="D123" s="30"/>
     </row>
     <row r="124" spans="3:4">
-      <c r="C124" s="31"/>
-      <c r="D124" s="31"/>
+      <c r="C124" s="30"/>
+      <c r="D124" s="30"/>
     </row>
     <row r="125" spans="3:4">
-      <c r="C125" s="31"/>
-      <c r="D125" s="31"/>
+      <c r="C125" s="30"/>
+      <c r="D125" s="30"/>
     </row>
     <row r="126" spans="3:4">
-      <c r="C126" s="31"/>
-      <c r="D126" s="31"/>
+      <c r="C126" s="30"/>
+      <c r="D126" s="30"/>
     </row>
     <row r="127" spans="3:4">
-      <c r="C127" s="31"/>
-      <c r="D127" s="31"/>
+      <c r="C127" s="30"/>
+      <c r="D127" s="30"/>
     </row>
     <row r="128" spans="3:4">
-      <c r="C128" s="31"/>
-      <c r="D128" s="31"/>
+      <c r="C128" s="30"/>
+      <c r="D128" s="30"/>
     </row>
     <row r="129" spans="3:4">
-      <c r="C129" s="31"/>
-      <c r="D129" s="31"/>
+      <c r="C129" s="30"/>
+      <c r="D129" s="30"/>
     </row>
     <row r="130" spans="3:4">
-      <c r="C130" s="31"/>
-      <c r="D130" s="31"/>
+      <c r="C130" s="30"/>
+      <c r="D130" s="30"/>
     </row>
     <row r="131" spans="3:4">
-      <c r="C131" s="31"/>
-      <c r="D131" s="31"/>
+      <c r="C131" s="30"/>
+      <c r="D131" s="30"/>
     </row>
     <row r="132" spans="3:4">
-      <c r="C132" s="31"/>
-      <c r="D132" s="31"/>
+      <c r="C132" s="30"/>
+      <c r="D132" s="30"/>
     </row>
     <row r="133" spans="3:4">
-      <c r="C133" s="31"/>
-      <c r="D133" s="31"/>
+      <c r="C133" s="30"/>
+      <c r="D133" s="30"/>
     </row>
     <row r="134" spans="3:4">
-      <c r="C134" s="31"/>
-      <c r="D134" s="31"/>
+      <c r="C134" s="30"/>
+      <c r="D134" s="30"/>
     </row>
     <row r="135" spans="3:4">
-      <c r="C135" s="31"/>
-      <c r="D135" s="31"/>
+      <c r="C135" s="30"/>
+      <c r="D135" s="30"/>
     </row>
     <row r="136" spans="3:4">
-      <c r="C136" s="31"/>
-      <c r="D136" s="31"/>
+      <c r="C136" s="30"/>
+      <c r="D136" s="30"/>
     </row>
     <row r="137" spans="3:4">
-      <c r="C137" s="31"/>
-      <c r="D137" s="31"/>
+      <c r="C137" s="30"/>
+      <c r="D137" s="30"/>
     </row>
     <row r="138" spans="3:4">
-      <c r="C138" s="31"/>
-      <c r="D138" s="31"/>
+      <c r="C138" s="30"/>
+      <c r="D138" s="30"/>
     </row>
     <row r="139" spans="3:4">
-      <c r="C139" s="31"/>
-      <c r="D139" s="31"/>
+      <c r="C139" s="30"/>
+      <c r="D139" s="30"/>
     </row>
     <row r="140" spans="3:4">
-      <c r="C140" s="31"/>
-      <c r="D140" s="31"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="30"/>
     </row>
     <row r="141" spans="3:4">
-      <c r="C141" s="31"/>
-      <c r="D141" s="31"/>
+      <c r="C141" s="30"/>
+      <c r="D141" s="30"/>
     </row>
     <row r="142" spans="3:4">
-      <c r="C142" s="31"/>
-      <c r="D142" s="31"/>
+      <c r="C142" s="30"/>
+      <c r="D142" s="30"/>
     </row>
     <row r="143" spans="3:4">
-      <c r="C143" s="31"/>
-      <c r="D143" s="31"/>
+      <c r="C143" s="30"/>
+      <c r="D143" s="30"/>
     </row>
     <row r="144" spans="3:4">
-      <c r="C144" s="31"/>
-      <c r="D144" s="31"/>
+      <c r="C144" s="30"/>
+      <c r="D144" s="30"/>
     </row>
     <row r="145" spans="3:4">
-      <c r="C145" s="31"/>
-      <c r="D145" s="31"/>
+      <c r="C145" s="30"/>
+      <c r="D145" s="30"/>
     </row>
     <row r="146" spans="3:4">
-      <c r="C146" s="31"/>
-      <c r="D146" s="31"/>
+      <c r="C146" s="30"/>
+      <c r="D146" s="30"/>
     </row>
     <row r="147" spans="3:4">
-      <c r="C147" s="31"/>
-      <c r="D147" s="31"/>
+      <c r="C147" s="30"/>
+      <c r="D147" s="30"/>
     </row>
     <row r="148" spans="3:4">
-      <c r="C148" s="31"/>
-      <c r="D148" s="31"/>
+      <c r="C148" s="30"/>
+      <c r="D148" s="30"/>
     </row>
     <row r="149" spans="3:4">
-      <c r="C149" s="31"/>
-      <c r="D149" s="31"/>
+      <c r="C149" s="30"/>
+      <c r="D149" s="30"/>
     </row>
     <row r="150" spans="3:4">
-      <c r="C150" s="31"/>
-      <c r="D150" s="31"/>
+      <c r="C150" s="30"/>
+      <c r="D150" s="30"/>
     </row>
     <row r="151" spans="3:4">
-      <c r="C151" s="31"/>
-      <c r="D151" s="31"/>
+      <c r="C151" s="30"/>
+      <c r="D151" s="30"/>
     </row>
     <row r="152" spans="3:4">
-      <c r="C152" s="31"/>
-      <c r="D152" s="31"/>
+      <c r="C152" s="30"/>
+      <c r="D152" s="30"/>
     </row>
     <row r="153" spans="3:4">
-      <c r="C153" s="31"/>
-      <c r="D153" s="31"/>
+      <c r="C153" s="30"/>
+      <c r="D153" s="30"/>
     </row>
     <row r="154" spans="3:4">
-      <c r="C154" s="31"/>
-      <c r="D154" s="31"/>
+      <c r="C154" s="30"/>
+      <c r="D154" s="30"/>
     </row>
     <row r="155" spans="3:4">
-      <c r="C155" s="31"/>
-      <c r="D155" s="31"/>
+      <c r="C155" s="30"/>
+      <c r="D155" s="30"/>
     </row>
     <row r="156" spans="3:4">
-      <c r="C156" s="31"/>
-      <c r="D156" s="31"/>
+      <c r="C156" s="30"/>
+      <c r="D156" s="30"/>
     </row>
     <row r="157" spans="3:4">
-      <c r="C157" s="31"/>
-      <c r="D157" s="31"/>
+      <c r="C157" s="30"/>
+      <c r="D157" s="30"/>
     </row>
     <row r="158" spans="3:4">
-      <c r="C158" s="31"/>
-      <c r="D158" s="31"/>
+      <c r="C158" s="30"/>
+      <c r="D158" s="30"/>
     </row>
     <row r="159" spans="3:4">
-      <c r="C159" s="31"/>
-      <c r="D159" s="31"/>
+      <c r="C159" s="30"/>
+      <c r="D159" s="30"/>
     </row>
     <row r="160" spans="3:4">
-      <c r="C160" s="31"/>
-      <c r="D160" s="31"/>
+      <c r="C160" s="30"/>
+      <c r="D160" s="30"/>
     </row>
     <row r="161" spans="3:4">
-      <c r="C161" s="31"/>
-      <c r="D161" s="31"/>
+      <c r="C161" s="30"/>
+      <c r="D161" s="30"/>
     </row>
     <row r="162" spans="3:4">
-      <c r="C162" s="31"/>
-      <c r="D162" s="31"/>
+      <c r="C162" s="30"/>
+      <c r="D162" s="30"/>
     </row>
     <row r="163" spans="3:4">
-      <c r="C163" s="31"/>
-      <c r="D163" s="31"/>
+      <c r="C163" s="30"/>
+      <c r="D163" s="30"/>
     </row>
     <row r="164" spans="3:4">
-      <c r="C164" s="31"/>
-      <c r="D164" s="31"/>
+      <c r="C164" s="30"/>
+      <c r="D164" s="30"/>
     </row>
     <row r="165" spans="3:4">
-      <c r="C165" s="31"/>
-      <c r="D165" s="31"/>
+      <c r="C165" s="30"/>
+      <c r="D165" s="30"/>
     </row>
     <row r="166" spans="3:4">
-      <c r="C166" s="31"/>
-      <c r="D166" s="31"/>
+      <c r="C166" s="30"/>
+      <c r="D166" s="30"/>
     </row>
     <row r="167" spans="3:4">
-      <c r="C167" s="31"/>
-      <c r="D167" s="31"/>
+      <c r="C167" s="30"/>
+      <c r="D167" s="30"/>
     </row>
     <row r="168" spans="3:4">
-      <c r="C168" s="31"/>
-      <c r="D168" s="31"/>
+      <c r="C168" s="30"/>
+      <c r="D168" s="30"/>
     </row>
     <row r="169" spans="3:4">
-      <c r="C169" s="31"/>
-      <c r="D169" s="31"/>
+      <c r="C169" s="30"/>
+      <c r="D169" s="30"/>
     </row>
     <row r="170" spans="3:4">
-      <c r="C170" s="31"/>
-      <c r="D170" s="31"/>
+      <c r="C170" s="30"/>
+      <c r="D170" s="30"/>
     </row>
     <row r="171" spans="3:4">
-      <c r="C171" s="31"/>
-      <c r="D171" s="31"/>
+      <c r="C171" s="30"/>
+      <c r="D171" s="30"/>
     </row>
     <row r="172" spans="3:4">
-      <c r="C172" s="31"/>
-      <c r="D172" s="31"/>
+      <c r="C172" s="30"/>
+      <c r="D172" s="30"/>
     </row>
     <row r="173" spans="3:4">
-      <c r="C173" s="31"/>
-      <c r="D173" s="31"/>
+      <c r="C173" s="30"/>
+      <c r="D173" s="30"/>
     </row>
     <row r="174" spans="3:4">
-      <c r="C174" s="31"/>
-      <c r="D174" s="31"/>
+      <c r="C174" s="30"/>
+      <c r="D174" s="30"/>
     </row>
     <row r="175" spans="3:4">
-      <c r="C175" s="31"/>
-      <c r="D175" s="31"/>
+      <c r="C175" s="30"/>
+      <c r="D175" s="30"/>
     </row>
     <row r="176" spans="3:4">
-      <c r="C176" s="31"/>
-      <c r="D176" s="31"/>
+      <c r="C176" s="30"/>
+      <c r="D176" s="30"/>
     </row>
     <row r="177" spans="3:4">
-      <c r="C177" s="31"/>
-      <c r="D177" s="31"/>
+      <c r="C177" s="30"/>
+      <c r="D177" s="30"/>
     </row>
     <row r="178" spans="3:4">
-      <c r="C178" s="31"/>
-      <c r="D178" s="31"/>
+      <c r="C178" s="30"/>
+      <c r="D178" s="30"/>
     </row>
     <row r="179" spans="3:4">
-      <c r="C179" s="31"/>
-      <c r="D179" s="31"/>
+      <c r="C179" s="30"/>
+      <c r="D179" s="30"/>
     </row>
     <row r="180" spans="3:4">
-      <c r="C180" s="31"/>
-      <c r="D180" s="31"/>
+      <c r="C180" s="30"/>
+      <c r="D180" s="30"/>
     </row>
     <row r="181" spans="3:4">
-      <c r="C181" s="31"/>
-      <c r="D181" s="31"/>
+      <c r="C181" s="30"/>
+      <c r="D181" s="30"/>
     </row>
     <row r="182" spans="3:4">
-      <c r="C182" s="31"/>
-      <c r="D182" s="31"/>
+      <c r="C182" s="30"/>
+      <c r="D182" s="30"/>
     </row>
     <row r="183" spans="3:4">
-      <c r="C183" s="31"/>
-      <c r="D183" s="31"/>
+      <c r="C183" s="30"/>
+      <c r="D183" s="30"/>
     </row>
     <row r="184" spans="3:4">
-      <c r="C184" s="31"/>
-      <c r="D184" s="31"/>
+      <c r="C184" s="30"/>
+      <c r="D184" s="30"/>
     </row>
     <row r="185" spans="3:4">
-      <c r="C185" s="31"/>
-      <c r="D185" s="31"/>
+      <c r="C185" s="30"/>
+      <c r="D185" s="30"/>
     </row>
     <row r="186" spans="3:4">
-      <c r="C186" s="31"/>
-      <c r="D186" s="31"/>
+      <c r="C186" s="30"/>
+      <c r="D186" s="30"/>
     </row>
     <row r="187" spans="3:4">
-      <c r="C187" s="31"/>
-      <c r="D187" s="31"/>
+      <c r="C187" s="30"/>
+      <c r="D187" s="30"/>
     </row>
     <row r="188" spans="3:4">
-      <c r="C188" s="31"/>
-      <c r="D188" s="31"/>
+      <c r="C188" s="30"/>
+      <c r="D188" s="30"/>
     </row>
     <row r="189" spans="3:4">
-      <c r="C189" s="31"/>
-      <c r="D189" s="31"/>
+      <c r="C189" s="30"/>
+      <c r="D189" s="30"/>
     </row>
     <row r="190" spans="3:4">
-      <c r="C190" s="31"/>
-      <c r="D190" s="31"/>
+      <c r="C190" s="30"/>
+      <c r="D190" s="30"/>
     </row>
     <row r="191" spans="3:4">
-      <c r="C191" s="31"/>
-      <c r="D191" s="31"/>
+      <c r="C191" s="30"/>
+      <c r="D191" s="30"/>
     </row>
     <row r="192" spans="3:4">
-      <c r="C192" s="31"/>
-      <c r="D192" s="31"/>
+      <c r="C192" s="30"/>
+      <c r="D192" s="30"/>
     </row>
     <row r="193" spans="3:4">
-      <c r="C193" s="31"/>
-      <c r="D193" s="31"/>
+      <c r="C193" s="30"/>
+      <c r="D193" s="30"/>
     </row>
     <row r="194" spans="3:4">
-      <c r="C194" s="31"/>
-      <c r="D194" s="31"/>
+      <c r="C194" s="30"/>
+      <c r="D194" s="30"/>
     </row>
     <row r="195" spans="3:4">
-      <c r="C195" s="31"/>
-      <c r="D195" s="31"/>
+      <c r="C195" s="30"/>
+      <c r="D195" s="30"/>
     </row>
     <row r="196" spans="3:4">
-      <c r="C196" s="31"/>
-      <c r="D196" s="31"/>
+      <c r="C196" s="30"/>
+      <c r="D196" s="30"/>
     </row>
     <row r="197" spans="3:4">
-      <c r="C197" s="31"/>
-      <c r="D197" s="31"/>
+      <c r="C197" s="30"/>
+      <c r="D197" s="30"/>
     </row>
     <row r="198" spans="3:4">
-      <c r="C198" s="31"/>
-      <c r="D198" s="31"/>
+      <c r="C198" s="30"/>
+      <c r="D198" s="30"/>
     </row>
     <row r="199" spans="3:4">
-      <c r="C199" s="31"/>
-      <c r="D199" s="31"/>
+      <c r="C199" s="30"/>
+      <c r="D199" s="30"/>
     </row>
     <row r="200" spans="3:4">
-      <c r="C200" s="31"/>
-      <c r="D200" s="31"/>
+      <c r="C200" s="30"/>
+      <c r="D200" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E200" xr:uid="{0ABCEF69-CFAC-437F-9DF5-474C398D3B95}">
       <formula1>"In Progress,Completed,Planning,On Hold"</formula1>
     </dataValidation>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -939,39 +939,39 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1369,34 +1369,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1434,34 +1434,34 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="71">
+      <c r="C5" s="60">
         <v>46084</v>
       </c>
-      <c r="D5" s="71">
+      <c r="D5" s="60">
         <v>46127</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="72">
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61">
         <v>1</v>
       </c>
-      <c r="H5" s="70" t="s">
+      <c r="H5" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="69">
+      <c r="I5" s="64">
         <v>46213</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="64"/>
       <c r="K5" s="48"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="62"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="45" t="s">
         <v>13</v>
       </c>
@@ -1479,12 +1479,12 @@
       <c r="H6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="62"/>
-      <c r="J6" s="64"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="63"/>
       <c r="K6" s="49"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="66" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="39" t="s">
@@ -1504,14 +1504,14 @@
       <c r="H7" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="63" t="s">
+      <c r="I7" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="63"/>
+      <c r="J7" s="62"/>
       <c r="K7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="62"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="36" t="s">
         <v>13</v>
       </c>
@@ -1529,12 +1529,12 @@
       <c r="H8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="62"/>
-      <c r="J8" s="64"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="63"/>
       <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="66" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="39" t="s">
@@ -1554,14 +1554,14 @@
       <c r="H9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="63">
+      <c r="I9" s="62">
         <v>46218</v>
       </c>
-      <c r="J9" s="63"/>
+      <c r="J9" s="62"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="62"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="36" t="s">
         <v>13</v>
       </c>
@@ -1579,12 +1579,12 @@
       <c r="H10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="64"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="63"/>
       <c r="K10" s="49"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="66" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="42" t="s">
@@ -1604,14 +1604,14 @@
       <c r="H11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="63">
+      <c r="I11" s="62">
         <v>46171</v>
       </c>
-      <c r="J11" s="63"/>
+      <c r="J11" s="62"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="62"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="45" t="s">
         <v>13</v>
       </c>
@@ -1629,12 +1629,12 @@
       <c r="H12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="62"/>
-      <c r="J12" s="64"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="63"/>
       <c r="K12" s="49"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="66" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="39" t="s">
@@ -1654,14 +1654,14 @@
       <c r="H13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="63" t="s">
+      <c r="I13" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="63"/>
+      <c r="J13" s="62"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="62"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="36" t="s">
         <v>13</v>
       </c>
@@ -1679,12 +1679,12 @@
       <c r="H14" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="62"/>
-      <c r="J14" s="64"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="63"/>
       <c r="K14" s="49"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="66" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="42" t="s">
@@ -1704,14 +1704,14 @@
       <c r="H15" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="63">
+      <c r="I15" s="62">
         <v>46199</v>
       </c>
-      <c r="J15" s="63"/>
+      <c r="J15" s="62"/>
       <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="62"/>
+      <c r="A16" s="67"/>
       <c r="B16" s="45" t="s">
         <v>13</v>
       </c>
@@ -1729,12 +1729,12 @@
       <c r="H16" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="62"/>
-      <c r="J16" s="64"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="63"/>
       <c r="K16" s="49"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="68" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="33" t="s">
@@ -1754,14 +1754,14 @@
       <c r="H17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="66">
+      <c r="I17" s="65">
         <v>46305</v>
       </c>
-      <c r="J17" s="66"/>
+      <c r="J17" s="65"/>
       <c r="K17" s="51"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="62"/>
+      <c r="A18" s="67"/>
       <c r="B18" s="36" t="s">
         <v>13</v>
       </c>
@@ -1779,12 +1779,12 @@
       <c r="H18" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="62"/>
-      <c r="J18" s="64"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="63"/>
       <c r="K18" s="49"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="68" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="33" t="s">
@@ -1804,14 +1804,14 @@
       <c r="H19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="66">
+      <c r="I19" s="65">
         <v>46336</v>
       </c>
-      <c r="J19" s="66"/>
+      <c r="J19" s="65"/>
       <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="62"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
@@ -1829,12 +1829,12 @@
       <c r="H20" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="62"/>
-      <c r="J20" s="64"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="63"/>
       <c r="K20" s="49"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="61" t="s">
+      <c r="A21" s="66" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="39" t="s">
@@ -1854,14 +1854,14 @@
       <c r="H21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="63">
+      <c r="I21" s="62">
         <v>46336</v>
       </c>
-      <c r="J21" s="63"/>
+      <c r="J21" s="62"/>
       <c r="K21" s="52"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="62"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="36" t="s">
         <v>13</v>
       </c>
@@ -1879,12 +1879,12 @@
       <c r="H22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="62"/>
-      <c r="J22" s="64"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="63"/>
       <c r="K22" s="53"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="42" t="s">
@@ -1904,14 +1904,14 @@
       <c r="H23" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="63">
+      <c r="I23" s="62">
         <v>46237</v>
       </c>
-      <c r="J23" s="63"/>
+      <c r="J23" s="62"/>
       <c r="K23" s="52"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="62"/>
+      <c r="A24" s="67"/>
       <c r="B24" s="45" t="s">
         <v>13</v>
       </c>
@@ -1929,12 +1929,12 @@
       <c r="H24" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="62"/>
-      <c r="J24" s="64"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="63"/>
       <c r="K24" s="53"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="66" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="42" t="s">
@@ -1954,14 +1954,14 @@
       <c r="H25" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="63">
+      <c r="I25" s="62">
         <v>46188</v>
       </c>
-      <c r="J25" s="63"/>
+      <c r="J25" s="62"/>
       <c r="K25" s="52"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="62"/>
+      <c r="A26" s="67"/>
       <c r="B26" s="45" t="s">
         <v>13</v>
       </c>
@@ -1979,12 +1979,12 @@
       <c r="H26" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="62"/>
-      <c r="J26" s="64"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="63"/>
       <c r="K26" s="53"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="61" t="s">
+      <c r="A27" s="66" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="39" t="s">
@@ -2004,14 +2004,14 @@
       <c r="H27" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="63">
+      <c r="I27" s="62">
         <v>46321</v>
       </c>
-      <c r="J27" s="63"/>
+      <c r="J27" s="62"/>
       <c r="K27" s="52"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="62"/>
+      <c r="A28" s="67"/>
       <c r="B28" s="36" t="s">
         <v>13</v>
       </c>
@@ -2029,12 +2029,12 @@
       <c r="H28" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="62"/>
-      <c r="J28" s="64"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="63"/>
       <c r="K28" s="53"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="61" t="s">
+      <c r="A29" s="66" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
@@ -2054,14 +2054,14 @@
       <c r="H29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="63">
+      <c r="I29" s="62">
         <v>46139</v>
       </c>
-      <c r="J29" s="63"/>
+      <c r="J29" s="62"/>
       <c r="K29" s="52"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="62"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="45" t="s">
         <v>13</v>
       </c>
@@ -2079,12 +2079,12 @@
       <c r="H30" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="62"/>
-      <c r="J30" s="64"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="63"/>
       <c r="K30" s="53"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="66" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="42" t="s">
@@ -2104,14 +2104,14 @@
       <c r="H31" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="63">
+      <c r="I31" s="62">
         <v>46133</v>
       </c>
-      <c r="J31" s="63"/>
+      <c r="J31" s="62"/>
       <c r="K31" s="52"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="62"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="45" t="s">
         <v>13</v>
       </c>
@@ -2129,12 +2129,12 @@
       <c r="H32" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="62"/>
-      <c r="J32" s="64"/>
+      <c r="I32" s="67"/>
+      <c r="J32" s="63"/>
       <c r="K32" s="53"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="61" t="s">
+      <c r="A33" s="66" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="39" t="s">
@@ -2154,14 +2154,14 @@
       <c r="H33" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="63">
+      <c r="I33" s="62">
         <v>46295</v>
       </c>
-      <c r="J33" s="63"/>
+      <c r="J33" s="62"/>
       <c r="K33" s="52"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="62"/>
+      <c r="A34" s="67"/>
       <c r="B34" s="36" t="s">
         <v>13</v>
       </c>
@@ -2179,12 +2179,12 @@
       <c r="H34" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="62"/>
-      <c r="J34" s="64"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="63"/>
       <c r="K34" s="53"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="61" t="s">
+      <c r="A35" s="66" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="39" t="s">
@@ -2204,14 +2204,14 @@
       <c r="H35" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="63">
+      <c r="I35" s="62">
         <v>45884</v>
       </c>
-      <c r="J35" s="63"/>
+      <c r="J35" s="62"/>
       <c r="K35" s="52"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="62"/>
+      <c r="A36" s="67"/>
       <c r="B36" s="36" t="s">
         <v>13</v>
       </c>
@@ -2229,12 +2229,12 @@
       <c r="H36" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="62"/>
-      <c r="J36" s="64"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="63"/>
       <c r="K36" s="53"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="61" t="s">
+      <c r="A37" s="66" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="39" t="s">
@@ -2254,14 +2254,14 @@
       <c r="H37" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="63">
+      <c r="I37" s="62">
         <v>45915</v>
       </c>
-      <c r="J37" s="63"/>
+      <c r="J37" s="62"/>
       <c r="K37" s="52"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="62"/>
+      <c r="A38" s="67"/>
       <c r="B38" s="36" t="s">
         <v>13</v>
       </c>
@@ -2279,12 +2279,12 @@
       <c r="H38" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="62"/>
-      <c r="J38" s="64"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="63"/>
       <c r="K38" s="53"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="61" t="s">
+      <c r="A39" s="66" t="s">
         <v>131</v>
       </c>
       <c r="B39" s="39" t="s">
@@ -2300,12 +2300,12 @@
       <c r="H39" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="63"/>
-      <c r="J39" s="63"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="62"/>
       <c r="K39" s="52"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="62"/>
+      <c r="A40" s="67"/>
       <c r="B40" s="56" t="s">
         <v>13</v>
       </c>
@@ -2319,12 +2319,12 @@
       <c r="H40" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="62"/>
-      <c r="J40" s="64"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="63"/>
       <c r="K40" s="53"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="61" t="s">
+      <c r="A41" s="66" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="39" t="s">
@@ -2344,14 +2344,14 @@
       <c r="H41" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="63">
+      <c r="I41" s="62">
         <v>46230</v>
       </c>
-      <c r="J41" s="63"/>
+      <c r="J41" s="62"/>
       <c r="K41" s="52"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="62"/>
+      <c r="A42" s="67"/>
       <c r="B42" s="56" t="s">
         <v>13</v>
       </c>
@@ -2361,26 +2361,41 @@
       <c r="F42" s="57"/>
       <c r="G42" s="58"/>
       <c r="H42" s="56"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="64"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="63"/>
       <c r="K42" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2397,35 +2412,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2461,56 +2461,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
+      <c r="V2" s="71"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -4190,20 +4190,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4596,22 +4596,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5774,15 +5774,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5793,6 +5784,15 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5815,14 +5815,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5831,4 +5823,12 @@
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFD760CD-EEE6-4E9E-ACC2-376EC4F5F17F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="135">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -444,6 +444,9 @@
   </si>
   <si>
     <t>ทำราคาขั้นต่ำ ในกรณีงานเล็กเป็นงานเหมา</t>
+  </si>
+  <si>
+    <t>Data Actual  Plan</t>
   </si>
 </sst>
 </file>
@@ -456,7 +459,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,6 +559,12 @@
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -775,7 +784,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -972,6 +981,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2140,10 +2155,10 @@
       <c r="B33" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="40">
+      <c r="C33" s="73">
         <v>46091</v>
       </c>
-      <c r="D33" s="40">
+      <c r="D33" s="73">
         <v>46094</v>
       </c>
       <c r="E33" s="40"/>
@@ -2165,10 +2180,10 @@
       <c r="B34" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="74">
         <v>46091</v>
       </c>
-      <c r="D34" s="37">
+      <c r="D34" s="74">
         <v>46094</v>
       </c>
       <c r="E34" s="37"/>
@@ -2269,7 +2284,7 @@
         <v>45729</v>
       </c>
       <c r="D38" s="37">
-        <v>45732</v>
+        <v>45862</v>
       </c>
       <c r="E38" s="37"/>
       <c r="F38" s="37"/>
@@ -2433,6 +2448,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4699,10 +4715,19 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="6"/>
+      <c r="A9" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="C9" s="6">
+        <v>46217</v>
+      </c>
+      <c r="D9" s="6">
+        <v>46224</v>
+      </c>
+      <c r="E9" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6"/>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFD760CD-EEE6-4E9E-ACC2-376EC4F5F17F}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA7C2CBC-69B9-4AA1-9D0F-52034DD4022A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -459,7 +459,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,12 +559,6 @@
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -957,36 +951,36 @@
     <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1384,34 +1378,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1449,7 +1443,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="73" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="59" t="s">
@@ -1469,14 +1463,14 @@
       <c r="H5" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="64">
+      <c r="I5" s="74">
         <v>46213</v>
       </c>
-      <c r="J5" s="64"/>
+      <c r="J5" s="74"/>
       <c r="K5" s="48"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="67"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="45" t="s">
         <v>13</v>
       </c>
@@ -1494,12 +1488,12 @@
       <c r="H6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="67"/>
-      <c r="J6" s="63"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="67"/>
       <c r="K6" s="49"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="64" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="39" t="s">
@@ -1519,14 +1513,14 @@
       <c r="H7" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="62" t="s">
+      <c r="I7" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="62"/>
+      <c r="J7" s="66"/>
       <c r="K7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="67"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="36" t="s">
         <v>13</v>
       </c>
@@ -1544,12 +1538,12 @@
       <c r="H8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="67"/>
-      <c r="J8" s="63"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="67"/>
       <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="64" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="39" t="s">
@@ -1569,14 +1563,14 @@
       <c r="H9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="66">
         <v>46218</v>
       </c>
-      <c r="J9" s="62"/>
+      <c r="J9" s="66"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="67"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="36" t="s">
         <v>13</v>
       </c>
@@ -1594,12 +1588,12 @@
       <c r="H10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="67"/>
-      <c r="J10" s="63"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="67"/>
       <c r="K10" s="49"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="42" t="s">
@@ -1619,14 +1613,14 @@
       <c r="H11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="66">
         <v>46171</v>
       </c>
-      <c r="J11" s="62"/>
+      <c r="J11" s="66"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="67"/>
+      <c r="A12" s="65"/>
       <c r="B12" s="45" t="s">
         <v>13</v>
       </c>
@@ -1644,12 +1638,12 @@
       <c r="H12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="67"/>
-      <c r="J12" s="63"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="67"/>
       <c r="K12" s="49"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="64" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="39" t="s">
@@ -1669,14 +1663,14 @@
       <c r="H13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="62" t="s">
+      <c r="I13" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="62"/>
+      <c r="J13" s="66"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="67"/>
+      <c r="A14" s="65"/>
       <c r="B14" s="36" t="s">
         <v>13</v>
       </c>
@@ -1694,12 +1688,12 @@
       <c r="H14" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="67"/>
-      <c r="J14" s="63"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="67"/>
       <c r="K14" s="49"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="64" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="42" t="s">
@@ -1719,14 +1713,14 @@
       <c r="H15" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="62">
+      <c r="I15" s="66">
         <v>46199</v>
       </c>
-      <c r="J15" s="62"/>
+      <c r="J15" s="66"/>
       <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="67"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="45" t="s">
         <v>13</v>
       </c>
@@ -1744,12 +1738,12 @@
       <c r="H16" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="67"/>
-      <c r="J16" s="63"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="67"/>
       <c r="K16" s="49"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="71" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="33" t="s">
@@ -1769,14 +1763,14 @@
       <c r="H17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="65">
+      <c r="I17" s="70">
         <v>46305</v>
       </c>
-      <c r="J17" s="65"/>
+      <c r="J17" s="70"/>
       <c r="K17" s="51"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="67"/>
+      <c r="A18" s="65"/>
       <c r="B18" s="36" t="s">
         <v>13</v>
       </c>
@@ -1794,12 +1788,12 @@
       <c r="H18" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="67"/>
-      <c r="J18" s="63"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="67"/>
       <c r="K18" s="49"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="71" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="33" t="s">
@@ -1819,14 +1813,14 @@
       <c r="H19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="65">
+      <c r="I19" s="70">
         <v>46336</v>
       </c>
-      <c r="J19" s="65"/>
+      <c r="J19" s="70"/>
       <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="67"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
@@ -1844,12 +1838,12 @@
       <c r="H20" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="67"/>
-      <c r="J20" s="63"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="67"/>
       <c r="K20" s="49"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="64" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="39" t="s">
@@ -1869,14 +1863,14 @@
       <c r="H21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="62">
+      <c r="I21" s="66">
         <v>46336</v>
       </c>
-      <c r="J21" s="62"/>
+      <c r="J21" s="66"/>
       <c r="K21" s="52"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="67"/>
+      <c r="A22" s="65"/>
       <c r="B22" s="36" t="s">
         <v>13</v>
       </c>
@@ -1894,12 +1888,12 @@
       <c r="H22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="67"/>
-      <c r="J22" s="63"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="67"/>
       <c r="K22" s="53"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="64" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="42" t="s">
@@ -1919,14 +1913,14 @@
       <c r="H23" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="62">
+      <c r="I23" s="66">
         <v>46237</v>
       </c>
-      <c r="J23" s="62"/>
+      <c r="J23" s="66"/>
       <c r="K23" s="52"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="67"/>
+      <c r="A24" s="65"/>
       <c r="B24" s="45" t="s">
         <v>13</v>
       </c>
@@ -1944,12 +1938,12 @@
       <c r="H24" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="67"/>
-      <c r="J24" s="63"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="67"/>
       <c r="K24" s="53"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="64" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="42" t="s">
@@ -1969,14 +1963,14 @@
       <c r="H25" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="62">
+      <c r="I25" s="66">
         <v>46188</v>
       </c>
-      <c r="J25" s="62"/>
+      <c r="J25" s="66"/>
       <c r="K25" s="52"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="67"/>
+      <c r="A26" s="65"/>
       <c r="B26" s="45" t="s">
         <v>13</v>
       </c>
@@ -1994,12 +1988,12 @@
       <c r="H26" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="67"/>
-      <c r="J26" s="63"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="67"/>
       <c r="K26" s="53"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="64" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="39" t="s">
@@ -2019,14 +2013,14 @@
       <c r="H27" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="62">
+      <c r="I27" s="66">
         <v>46321</v>
       </c>
-      <c r="J27" s="62"/>
+      <c r="J27" s="66"/>
       <c r="K27" s="52"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="67"/>
+      <c r="A28" s="65"/>
       <c r="B28" s="36" t="s">
         <v>13</v>
       </c>
@@ -2044,12 +2038,12 @@
       <c r="H28" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="67"/>
-      <c r="J28" s="63"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="67"/>
       <c r="K28" s="53"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="66" t="s">
+      <c r="A29" s="64" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
@@ -2069,14 +2063,14 @@
       <c r="H29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="62">
+      <c r="I29" s="66">
         <v>46139</v>
       </c>
-      <c r="J29" s="62"/>
+      <c r="J29" s="66"/>
       <c r="K29" s="52"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="67"/>
+      <c r="A30" s="65"/>
       <c r="B30" s="45" t="s">
         <v>13</v>
       </c>
@@ -2094,12 +2088,12 @@
       <c r="H30" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="67"/>
-      <c r="J30" s="63"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="67"/>
       <c r="K30" s="53"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="64" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="42" t="s">
@@ -2119,14 +2113,14 @@
       <c r="H31" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="62">
+      <c r="I31" s="66">
         <v>46133</v>
       </c>
-      <c r="J31" s="62"/>
+      <c r="J31" s="66"/>
       <c r="K31" s="52"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="67"/>
+      <c r="A32" s="65"/>
       <c r="B32" s="45" t="s">
         <v>13</v>
       </c>
@@ -2144,22 +2138,22 @@
       <c r="H32" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="67"/>
-      <c r="J32" s="63"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="67"/>
       <c r="K32" s="53"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="64" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="73">
-        <v>46091</v>
-      </c>
-      <c r="D33" s="73">
-        <v>46094</v>
+      <c r="C33" s="62">
+        <v>46237</v>
+      </c>
+      <c r="D33" s="62">
+        <v>46248</v>
       </c>
       <c r="E33" s="40"/>
       <c r="F33" s="40"/>
@@ -2169,22 +2163,22 @@
       <c r="H33" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="62">
+      <c r="I33" s="66">
         <v>46295</v>
       </c>
-      <c r="J33" s="62"/>
+      <c r="J33" s="66"/>
       <c r="K33" s="52"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="67"/>
+      <c r="A34" s="65"/>
       <c r="B34" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="74">
-        <v>46091</v>
-      </c>
-      <c r="D34" s="74">
-        <v>46094</v>
+      <c r="C34" s="63">
+        <v>46296</v>
+      </c>
+      <c r="D34" s="63">
+        <v>46303</v>
       </c>
       <c r="E34" s="37"/>
       <c r="F34" s="37"/>
@@ -2194,12 +2188,12 @@
       <c r="H34" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="67"/>
-      <c r="J34" s="63"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="67"/>
       <c r="K34" s="53"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="64" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="39" t="s">
@@ -2219,14 +2213,14 @@
       <c r="H35" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="62">
+      <c r="I35" s="66">
         <v>45884</v>
       </c>
-      <c r="J35" s="62"/>
+      <c r="J35" s="66"/>
       <c r="K35" s="52"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="67"/>
+      <c r="A36" s="65"/>
       <c r="B36" s="36" t="s">
         <v>13</v>
       </c>
@@ -2244,12 +2238,12 @@
       <c r="H36" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="67"/>
-      <c r="J36" s="63"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="67"/>
       <c r="K36" s="53"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="66" t="s">
+      <c r="A37" s="64" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="39" t="s">
@@ -2269,14 +2263,14 @@
       <c r="H37" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="62">
+      <c r="I37" s="66">
         <v>45915</v>
       </c>
-      <c r="J37" s="62"/>
+      <c r="J37" s="66"/>
       <c r="K37" s="52"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="67"/>
+      <c r="A38" s="65"/>
       <c r="B38" s="36" t="s">
         <v>13</v>
       </c>
@@ -2294,12 +2288,12 @@
       <c r="H38" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="67"/>
-      <c r="J38" s="63"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="67"/>
       <c r="K38" s="53"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="64" t="s">
         <v>131</v>
       </c>
       <c r="B39" s="39" t="s">
@@ -2315,12 +2309,12 @@
       <c r="H39" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
+      <c r="I39" s="66"/>
+      <c r="J39" s="66"/>
       <c r="K39" s="52"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="67"/>
+      <c r="A40" s="65"/>
       <c r="B40" s="56" t="s">
         <v>13</v>
       </c>
@@ -2334,12 +2328,12 @@
       <c r="H40" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="67"/>
-      <c r="J40" s="63"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="67"/>
       <c r="K40" s="53"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="64" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="39" t="s">
@@ -2359,14 +2353,14 @@
       <c r="H41" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="62">
+      <c r="I41" s="66">
         <v>46230</v>
       </c>
-      <c r="J41" s="62"/>
+      <c r="J41" s="66"/>
       <c r="K41" s="52"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="67"/>
+      <c r="A42" s="65"/>
       <c r="B42" s="56" t="s">
         <v>13</v>
       </c>
@@ -2376,18 +2370,49 @@
       <c r="F42" s="57"/>
       <c r="G42" s="58"/>
       <c r="H42" s="56"/>
-      <c r="I42" s="67"/>
-      <c r="J42" s="63"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="67"/>
       <c r="K42" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2404,43 +2429,12 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2477,56 +2471,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="69"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -3447,7 +3441,7 @@
       </c>
       <c r="Q19" s="19">
         <f>'Master Schedule'!C33</f>
-        <v>46091</v>
+        <v>46237</v>
       </c>
       <c r="R19" s="11">
         <v>46295</v>
@@ -4206,20 +4200,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4612,22 +4606,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5799,6 +5793,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5809,15 +5812,6 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5840,6 +5834,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5848,12 +5850,4 @@
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA7C2CBC-69B9-4AA1-9D0F-52034DD4022A}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17342736-9A5A-4BE9-A360-14E602BF2838}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="324" yWindow="108" windowWidth="14988" windowHeight="11484" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -957,30 +957,30 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1378,34 +1378,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1443,7 +1443,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="74" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="59" t="s">
@@ -1463,14 +1463,14 @@
       <c r="H5" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="74">
-        <v>46213</v>
-      </c>
-      <c r="J5" s="74"/>
+      <c r="I5" s="66">
+        <v>46244</v>
+      </c>
+      <c r="J5" s="66"/>
       <c r="K5" s="48"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="65"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="45" t="s">
         <v>13</v>
       </c>
@@ -1488,12 +1488,12 @@
       <c r="H6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="65"/>
-      <c r="J6" s="67"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="65"/>
       <c r="K6" s="49"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="68" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="39" t="s">
@@ -1513,14 +1513,14 @@
       <c r="H7" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="66" t="s">
+      <c r="I7" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="66"/>
+      <c r="J7" s="64"/>
       <c r="K7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="65"/>
+      <c r="A8" s="69"/>
       <c r="B8" s="36" t="s">
         <v>13</v>
       </c>
@@ -1538,12 +1538,12 @@
       <c r="H8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="65"/>
-      <c r="J8" s="67"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="65"/>
       <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="68" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="39" t="s">
@@ -1563,14 +1563,14 @@
       <c r="H9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="66">
+      <c r="I9" s="64">
         <v>46218</v>
       </c>
-      <c r="J9" s="66"/>
+      <c r="J9" s="64"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="65"/>
+      <c r="A10" s="69"/>
       <c r="B10" s="36" t="s">
         <v>13</v>
       </c>
@@ -1588,12 +1588,12 @@
       <c r="H10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="65"/>
-      <c r="J10" s="67"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="65"/>
       <c r="K10" s="49"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="68" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="42" t="s">
@@ -1613,14 +1613,14 @@
       <c r="H11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="66">
+      <c r="I11" s="64">
         <v>46171</v>
       </c>
-      <c r="J11" s="66"/>
+      <c r="J11" s="64"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="65"/>
+      <c r="A12" s="69"/>
       <c r="B12" s="45" t="s">
         <v>13</v>
       </c>
@@ -1638,12 +1638,12 @@
       <c r="H12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="65"/>
-      <c r="J12" s="67"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="65"/>
       <c r="K12" s="49"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="68" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="39" t="s">
@@ -1663,14 +1663,14 @@
       <c r="H13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="66" t="s">
+      <c r="I13" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="66"/>
+      <c r="J13" s="64"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="65"/>
+      <c r="A14" s="69"/>
       <c r="B14" s="36" t="s">
         <v>13</v>
       </c>
@@ -1688,12 +1688,12 @@
       <c r="H14" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="65"/>
-      <c r="J14" s="67"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="65"/>
       <c r="K14" s="49"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="68" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="42" t="s">
@@ -1713,14 +1713,14 @@
       <c r="H15" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="66">
+      <c r="I15" s="64">
         <v>46199</v>
       </c>
-      <c r="J15" s="66"/>
+      <c r="J15" s="64"/>
       <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="65"/>
+      <c r="A16" s="69"/>
       <c r="B16" s="45" t="s">
         <v>13</v>
       </c>
@@ -1738,12 +1738,12 @@
       <c r="H16" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="65"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="65"/>
       <c r="K16" s="49"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="71" t="s">
+      <c r="A17" s="70" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="33" t="s">
@@ -1763,14 +1763,14 @@
       <c r="H17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="70">
+      <c r="I17" s="67">
         <v>46305</v>
       </c>
-      <c r="J17" s="70"/>
+      <c r="J17" s="67"/>
       <c r="K17" s="51"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="65"/>
+      <c r="A18" s="69"/>
       <c r="B18" s="36" t="s">
         <v>13</v>
       </c>
@@ -1788,12 +1788,12 @@
       <c r="H18" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="65"/>
-      <c r="J18" s="67"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="65"/>
       <c r="K18" s="49"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="71" t="s">
+      <c r="A19" s="70" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="33" t="s">
@@ -1813,14 +1813,14 @@
       <c r="H19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="70">
+      <c r="I19" s="67">
         <v>46336</v>
       </c>
-      <c r="J19" s="70"/>
+      <c r="J19" s="67"/>
       <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="65"/>
+      <c r="A20" s="69"/>
       <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
@@ -1838,12 +1838,12 @@
       <c r="H20" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="65"/>
-      <c r="J20" s="67"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="65"/>
       <c r="K20" s="49"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="68" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="39" t="s">
@@ -1863,14 +1863,14 @@
       <c r="H21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="66">
+      <c r="I21" s="64">
         <v>46336</v>
       </c>
-      <c r="J21" s="66"/>
+      <c r="J21" s="64"/>
       <c r="K21" s="52"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="65"/>
+      <c r="A22" s="69"/>
       <c r="B22" s="36" t="s">
         <v>13</v>
       </c>
@@ -1888,12 +1888,12 @@
       <c r="H22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="65"/>
-      <c r="J22" s="67"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="65"/>
       <c r="K22" s="53"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="68" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="42" t="s">
@@ -1913,14 +1913,14 @@
       <c r="H23" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="66">
+      <c r="I23" s="64">
         <v>46237</v>
       </c>
-      <c r="J23" s="66"/>
+      <c r="J23" s="64"/>
       <c r="K23" s="52"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="65"/>
+      <c r="A24" s="69"/>
       <c r="B24" s="45" t="s">
         <v>13</v>
       </c>
@@ -1938,12 +1938,12 @@
       <c r="H24" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="65"/>
-      <c r="J24" s="67"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="65"/>
       <c r="K24" s="53"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="68" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="42" t="s">
@@ -1963,14 +1963,14 @@
       <c r="H25" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="66">
+      <c r="I25" s="64">
         <v>46188</v>
       </c>
-      <c r="J25" s="66"/>
+      <c r="J25" s="64"/>
       <c r="K25" s="52"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="65"/>
+      <c r="A26" s="69"/>
       <c r="B26" s="45" t="s">
         <v>13</v>
       </c>
@@ -1988,12 +1988,12 @@
       <c r="H26" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="65"/>
-      <c r="J26" s="67"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="65"/>
       <c r="K26" s="53"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="64" t="s">
+      <c r="A27" s="68" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="39" t="s">
@@ -2013,14 +2013,14 @@
       <c r="H27" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="66">
+      <c r="I27" s="64">
         <v>46321</v>
       </c>
-      <c r="J27" s="66"/>
+      <c r="J27" s="64"/>
       <c r="K27" s="52"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="65"/>
+      <c r="A28" s="69"/>
       <c r="B28" s="36" t="s">
         <v>13</v>
       </c>
@@ -2038,12 +2038,12 @@
       <c r="H28" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="65"/>
-      <c r="J28" s="67"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="65"/>
       <c r="K28" s="53"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="64" t="s">
+      <c r="A29" s="68" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
@@ -2063,14 +2063,14 @@
       <c r="H29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="66">
+      <c r="I29" s="64">
         <v>46139</v>
       </c>
-      <c r="J29" s="66"/>
+      <c r="J29" s="64"/>
       <c r="K29" s="52"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="65"/>
+      <c r="A30" s="69"/>
       <c r="B30" s="45" t="s">
         <v>13</v>
       </c>
@@ -2088,12 +2088,12 @@
       <c r="H30" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="65"/>
-      <c r="J30" s="67"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="65"/>
       <c r="K30" s="53"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="64" t="s">
+      <c r="A31" s="68" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="42" t="s">
@@ -2113,14 +2113,14 @@
       <c r="H31" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="66">
+      <c r="I31" s="64">
         <v>46133</v>
       </c>
-      <c r="J31" s="66"/>
+      <c r="J31" s="64"/>
       <c r="K31" s="52"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="65"/>
+      <c r="A32" s="69"/>
       <c r="B32" s="45" t="s">
         <v>13</v>
       </c>
@@ -2138,12 +2138,12 @@
       <c r="H32" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="65"/>
-      <c r="J32" s="67"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="65"/>
       <c r="K32" s="53"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="64" t="s">
+      <c r="A33" s="68" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="39" t="s">
@@ -2163,14 +2163,14 @@
       <c r="H33" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="66">
+      <c r="I33" s="64">
         <v>46295</v>
       </c>
-      <c r="J33" s="66"/>
+      <c r="J33" s="64"/>
       <c r="K33" s="52"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="65"/>
+      <c r="A34" s="69"/>
       <c r="B34" s="36" t="s">
         <v>13</v>
       </c>
@@ -2188,12 +2188,12 @@
       <c r="H34" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="65"/>
-      <c r="J34" s="67"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="65"/>
       <c r="K34" s="53"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="64" t="s">
+      <c r="A35" s="68" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="39" t="s">
@@ -2213,14 +2213,14 @@
       <c r="H35" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="66">
+      <c r="I35" s="64">
         <v>45884</v>
       </c>
-      <c r="J35" s="66"/>
+      <c r="J35" s="64"/>
       <c r="K35" s="52"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="65"/>
+      <c r="A36" s="69"/>
       <c r="B36" s="36" t="s">
         <v>13</v>
       </c>
@@ -2238,12 +2238,12 @@
       <c r="H36" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="65"/>
-      <c r="J36" s="67"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="65"/>
       <c r="K36" s="53"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="64" t="s">
+      <c r="A37" s="68" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="39" t="s">
@@ -2263,14 +2263,14 @@
       <c r="H37" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="66">
+      <c r="I37" s="64">
         <v>45915</v>
       </c>
-      <c r="J37" s="66"/>
+      <c r="J37" s="64"/>
       <c r="K37" s="52"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="65"/>
+      <c r="A38" s="69"/>
       <c r="B38" s="36" t="s">
         <v>13</v>
       </c>
@@ -2288,12 +2288,12 @@
       <c r="H38" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="65"/>
-      <c r="J38" s="67"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="65"/>
       <c r="K38" s="53"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="64" t="s">
+      <c r="A39" s="68" t="s">
         <v>131</v>
       </c>
       <c r="B39" s="39" t="s">
@@ -2309,12 +2309,12 @@
       <c r="H39" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="66"/>
-      <c r="J39" s="66"/>
+      <c r="I39" s="64"/>
+      <c r="J39" s="64"/>
       <c r="K39" s="52"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="65"/>
+      <c r="A40" s="69"/>
       <c r="B40" s="56" t="s">
         <v>13</v>
       </c>
@@ -2328,12 +2328,12 @@
       <c r="H40" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="65"/>
-      <c r="J40" s="67"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="65"/>
       <c r="K40" s="53"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="64" t="s">
+      <c r="A41" s="68" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="39" t="s">
@@ -2353,14 +2353,14 @@
       <c r="H41" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="66">
+      <c r="I41" s="64">
         <v>46230</v>
       </c>
-      <c r="J41" s="66"/>
+      <c r="J41" s="64"/>
       <c r="K41" s="52"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="65"/>
+      <c r="A42" s="69"/>
       <c r="B42" s="56" t="s">
         <v>13</v>
       </c>
@@ -2370,26 +2370,41 @@
       <c r="F42" s="57"/>
       <c r="G42" s="58"/>
       <c r="H42" s="56"/>
-      <c r="I42" s="65"/>
-      <c r="J42" s="67"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="65"/>
       <c r="K42" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2406,37 +2421,22 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -2471,56 +2471,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
-      <c r="V1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -4200,20 +4200,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4606,22 +4606,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5540,6 +5540,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5792,15 +5801,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5815,6 +5815,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5833,14 +5841,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17342736-9A5A-4BE9-A360-14E602BF2838}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CBFAFF0-4937-4D65-B797-338A352C1D17}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="324" yWindow="108" windowWidth="14988" windowHeight="11484" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -3127,7 +3127,7 @@
         <v>67</v>
       </c>
       <c r="D14" s="21">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E14" s="16">
         <v>1707089</v>
@@ -3612,7 +3612,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="15">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E24" s="16">
         <v>203880</v>
@@ -4160,7 +4160,7 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CBFAFF0-4937-4D65-B797-338A352C1D17}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{937C9C92-53BB-40B4-B11F-C97B1CC6D74C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="141">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -447,6 +447,24 @@
   </si>
   <si>
     <t>Data Actual  Plan</t>
+  </si>
+  <si>
+    <t>ประชุมไซต์ก่อนเริ่มงาน</t>
+  </si>
+  <si>
+    <t>ประชุม,คุยงานแก้ไขหลัง Corring</t>
+  </si>
+  <si>
+    <t>เข้าเคลียร์ติดตั้งหน้างานวันแรก</t>
+  </si>
+  <si>
+    <t>Achalaboon Residence</t>
+  </si>
+  <si>
+    <t>รอข้อมูลจาก Main con</t>
+  </si>
+  <si>
+    <t>Planning</t>
   </si>
 </sst>
 </file>
@@ -459,7 +477,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,6 +577,10 @@
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="7">
@@ -778,7 +800,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -981,6 +1003,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1076,6 +1110,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1363,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="41.33203125" bestFit="1" customWidth="1"/>
@@ -2374,8 +2412,51 @@
       <c r="J42" s="65"/>
       <c r="K42" s="53"/>
     </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="41">
+        <v>0</v>
+      </c>
+      <c r="H43" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="64"/>
+      <c r="J43" s="64"/>
+      <c r="K43" s="52"/>
+    </row>
+    <row r="44" spans="1:11" ht="15" thickBot="1">
+      <c r="A44" s="69"/>
+      <c r="B44" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="58">
+        <v>0</v>
+      </c>
+      <c r="H44" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="69"/>
+      <c r="J44" s="65"/>
+      <c r="K44" s="53"/>
+    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="62">
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="I39:I40"/>
     <mergeCell ref="J39:J40"/>
@@ -2436,7 +2517,7 @@
     <mergeCell ref="J33:J34"/>
     <mergeCell ref="J35:J36"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -3661,6 +3742,43 @@
       </c>
     </row>
     <row r="25" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
+      <c r="A25" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="78">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13">
+        <v>799875</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
+        <f>E25*0.4</f>
+        <v>319950</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="N25" s="13">
+        <v>0</v>
+      </c>
+      <c r="P25" s="13">
+        <v>384843</v>
+      </c>
+      <c r="T25" s="13" t="s">
+        <v>139</v>
+      </c>
       <c r="V25" s="19"/>
     </row>
     <row r="26" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
@@ -4160,7 +4278,7 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -4568,22 +4686,55 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="4"/>
+      <c r="A26" s="77">
+        <v>46219</v>
+      </c>
+      <c r="B26" s="76" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="75">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="4"/>
+      <c r="A27" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B27" s="76" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="76" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="4"/>
+      <c r="A28" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="4">
+        <v>4</v>
+      </c>
+      <c r="E28" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{D6F423AA-70F0-48D1-99A3-0E79A49440FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{937C9C92-53BB-40B4-B11F-C97B1CC6D74C}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{F9904DBD-7032-4B5C-8FB6-1CDB90EC0AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E5C768D-E1C7-46E4-B8C8-9A8A6DDB9C8B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="141">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -979,6 +979,20 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -998,23 +1012,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1110,10 +1110,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1416,34 +1412,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1481,7 +1477,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="78" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="59" t="s">
@@ -1501,14 +1497,14 @@
       <c r="H5" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="72">
         <v>46244</v>
       </c>
-      <c r="J5" s="66"/>
+      <c r="J5" s="72"/>
       <c r="K5" s="48"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="69"/>
+      <c r="A6" s="75"/>
       <c r="B6" s="45" t="s">
         <v>13</v>
       </c>
@@ -1526,12 +1522,12 @@
       <c r="H6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="65"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="71"/>
       <c r="K6" s="49"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="74" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="39" t="s">
@@ -1551,14 +1547,14 @@
       <c r="H7" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="64"/>
+      <c r="J7" s="70"/>
       <c r="K7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="69"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="36" t="s">
         <v>13</v>
       </c>
@@ -1576,12 +1572,12 @@
       <c r="H8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="69"/>
-      <c r="J8" s="65"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="71"/>
       <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="74" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="39" t="s">
@@ -1601,14 +1597,14 @@
       <c r="H9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="64">
+      <c r="I9" s="70">
         <v>46218</v>
       </c>
-      <c r="J9" s="64"/>
+      <c r="J9" s="70"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="69"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="36" t="s">
         <v>13</v>
       </c>
@@ -1626,12 +1622,12 @@
       <c r="H10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="69"/>
-      <c r="J10" s="65"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="71"/>
       <c r="K10" s="49"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="74" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="42" t="s">
@@ -1651,14 +1647,14 @@
       <c r="H11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="64">
+      <c r="I11" s="70">
         <v>46171</v>
       </c>
-      <c r="J11" s="64"/>
+      <c r="J11" s="70"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="69"/>
+      <c r="A12" s="75"/>
       <c r="B12" s="45" t="s">
         <v>13</v>
       </c>
@@ -1676,12 +1672,12 @@
       <c r="H12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="69"/>
-      <c r="J12" s="65"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="71"/>
       <c r="K12" s="49"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="74" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="39" t="s">
@@ -1701,14 +1697,14 @@
       <c r="H13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="64"/>
+      <c r="J13" s="70"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="69"/>
+      <c r="A14" s="75"/>
       <c r="B14" s="36" t="s">
         <v>13</v>
       </c>
@@ -1726,12 +1722,12 @@
       <c r="H14" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="69"/>
-      <c r="J14" s="65"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="71"/>
       <c r="K14" s="49"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="74" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="42" t="s">
@@ -1751,14 +1747,14 @@
       <c r="H15" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="64">
+      <c r="I15" s="70">
         <v>46199</v>
       </c>
-      <c r="J15" s="64"/>
+      <c r="J15" s="70"/>
       <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="69"/>
+      <c r="A16" s="75"/>
       <c r="B16" s="45" t="s">
         <v>13</v>
       </c>
@@ -1776,12 +1772,12 @@
       <c r="H16" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="69"/>
-      <c r="J16" s="65"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="71"/>
       <c r="K16" s="49"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="70" t="s">
+      <c r="A17" s="76" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="33" t="s">
@@ -1801,14 +1797,14 @@
       <c r="H17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="67">
+      <c r="I17" s="73">
         <v>46305</v>
       </c>
-      <c r="J17" s="67"/>
+      <c r="J17" s="73"/>
       <c r="K17" s="51"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="69"/>
+      <c r="A18" s="75"/>
       <c r="B18" s="36" t="s">
         <v>13</v>
       </c>
@@ -1826,12 +1822,12 @@
       <c r="H18" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="69"/>
-      <c r="J18" s="65"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="71"/>
       <c r="K18" s="49"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="76" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="33" t="s">
@@ -1851,14 +1847,14 @@
       <c r="H19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="67">
+      <c r="I19" s="73">
         <v>46336</v>
       </c>
-      <c r="J19" s="67"/>
+      <c r="J19" s="73"/>
       <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="69"/>
+      <c r="A20" s="75"/>
       <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
@@ -1876,12 +1872,12 @@
       <c r="H20" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="69"/>
-      <c r="J20" s="65"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="71"/>
       <c r="K20" s="49"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="74" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="39" t="s">
@@ -1901,14 +1897,14 @@
       <c r="H21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="64">
+      <c r="I21" s="70">
         <v>46336</v>
       </c>
-      <c r="J21" s="64"/>
+      <c r="J21" s="70"/>
       <c r="K21" s="52"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="69"/>
+      <c r="A22" s="75"/>
       <c r="B22" s="36" t="s">
         <v>13</v>
       </c>
@@ -1926,12 +1922,12 @@
       <c r="H22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="69"/>
-      <c r="J22" s="65"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="71"/>
       <c r="K22" s="53"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="74" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="42" t="s">
@@ -1951,14 +1947,14 @@
       <c r="H23" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="64">
+      <c r="I23" s="70">
         <v>46237</v>
       </c>
-      <c r="J23" s="64"/>
+      <c r="J23" s="70"/>
       <c r="K23" s="52"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="69"/>
+      <c r="A24" s="75"/>
       <c r="B24" s="45" t="s">
         <v>13</v>
       </c>
@@ -1976,12 +1972,12 @@
       <c r="H24" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="69"/>
-      <c r="J24" s="65"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="71"/>
       <c r="K24" s="53"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="68" t="s">
+      <c r="A25" s="74" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="42" t="s">
@@ -2001,14 +1997,14 @@
       <c r="H25" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="64">
+      <c r="I25" s="70">
         <v>46188</v>
       </c>
-      <c r="J25" s="64"/>
+      <c r="J25" s="70"/>
       <c r="K25" s="52"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="69"/>
+      <c r="A26" s="75"/>
       <c r="B26" s="45" t="s">
         <v>13</v>
       </c>
@@ -2026,12 +2022,12 @@
       <c r="H26" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="69"/>
-      <c r="J26" s="65"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="71"/>
       <c r="K26" s="53"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="68" t="s">
+      <c r="A27" s="74" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="39" t="s">
@@ -2051,14 +2047,14 @@
       <c r="H27" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="64">
+      <c r="I27" s="70">
         <v>46321</v>
       </c>
-      <c r="J27" s="64"/>
+      <c r="J27" s="70"/>
       <c r="K27" s="52"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="69"/>
+      <c r="A28" s="75"/>
       <c r="B28" s="36" t="s">
         <v>13</v>
       </c>
@@ -2076,12 +2072,12 @@
       <c r="H28" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="69"/>
-      <c r="J28" s="65"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="71"/>
       <c r="K28" s="53"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="68" t="s">
+      <c r="A29" s="74" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
@@ -2101,14 +2097,14 @@
       <c r="H29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="64">
+      <c r="I29" s="70">
         <v>46139</v>
       </c>
-      <c r="J29" s="64"/>
+      <c r="J29" s="70"/>
       <c r="K29" s="52"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="69"/>
+      <c r="A30" s="75"/>
       <c r="B30" s="45" t="s">
         <v>13</v>
       </c>
@@ -2126,12 +2122,12 @@
       <c r="H30" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="69"/>
-      <c r="J30" s="65"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="71"/>
       <c r="K30" s="53"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="74" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="42" t="s">
@@ -2151,14 +2147,14 @@
       <c r="H31" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="64">
+      <c r="I31" s="70">
         <v>46133</v>
       </c>
-      <c r="J31" s="64"/>
+      <c r="J31" s="70"/>
       <c r="K31" s="52"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="69"/>
+      <c r="A32" s="75"/>
       <c r="B32" s="45" t="s">
         <v>13</v>
       </c>
@@ -2176,12 +2172,12 @@
       <c r="H32" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="69"/>
-      <c r="J32" s="65"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="71"/>
       <c r="K32" s="53"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="68" t="s">
+      <c r="A33" s="74" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="39" t="s">
@@ -2201,14 +2197,14 @@
       <c r="H33" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="64">
+      <c r="I33" s="70">
         <v>46295</v>
       </c>
-      <c r="J33" s="64"/>
+      <c r="J33" s="70"/>
       <c r="K33" s="52"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="69"/>
+      <c r="A34" s="75"/>
       <c r="B34" s="36" t="s">
         <v>13</v>
       </c>
@@ -2226,12 +2222,12 @@
       <c r="H34" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="69"/>
-      <c r="J34" s="65"/>
+      <c r="I34" s="75"/>
+      <c r="J34" s="71"/>
       <c r="K34" s="53"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="68" t="s">
+      <c r="A35" s="74" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="39" t="s">
@@ -2251,14 +2247,14 @@
       <c r="H35" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="64">
+      <c r="I35" s="70">
         <v>45884</v>
       </c>
-      <c r="J35" s="64"/>
+      <c r="J35" s="70"/>
       <c r="K35" s="52"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="69"/>
+      <c r="A36" s="75"/>
       <c r="B36" s="36" t="s">
         <v>13</v>
       </c>
@@ -2276,12 +2272,12 @@
       <c r="H36" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="69"/>
-      <c r="J36" s="65"/>
+      <c r="I36" s="75"/>
+      <c r="J36" s="71"/>
       <c r="K36" s="53"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="68" t="s">
+      <c r="A37" s="74" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="39" t="s">
@@ -2301,14 +2297,14 @@
       <c r="H37" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="64">
+      <c r="I37" s="70">
         <v>45915</v>
       </c>
-      <c r="J37" s="64"/>
+      <c r="J37" s="70"/>
       <c r="K37" s="52"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="69"/>
+      <c r="A38" s="75"/>
       <c r="B38" s="36" t="s">
         <v>13</v>
       </c>
@@ -2326,12 +2322,12 @@
       <c r="H38" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="69"/>
-      <c r="J38" s="65"/>
+      <c r="I38" s="75"/>
+      <c r="J38" s="71"/>
       <c r="K38" s="53"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="68" t="s">
+      <c r="A39" s="74" t="s">
         <v>131</v>
       </c>
       <c r="B39" s="39" t="s">
@@ -2345,14 +2341,14 @@
         <v>0</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
+        <v>140</v>
+      </c>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
       <c r="K39" s="52"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="69"/>
+      <c r="A40" s="75"/>
       <c r="B40" s="56" t="s">
         <v>13</v>
       </c>
@@ -2364,14 +2360,14 @@
         <v>0</v>
       </c>
       <c r="H40" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="69"/>
-      <c r="J40" s="65"/>
+        <v>140</v>
+      </c>
+      <c r="I40" s="75"/>
+      <c r="J40" s="71"/>
       <c r="K40" s="53"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="74" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="39" t="s">
@@ -2391,14 +2387,14 @@
       <c r="H41" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="64">
+      <c r="I41" s="70">
         <v>46230</v>
       </c>
-      <c r="J41" s="64"/>
+      <c r="J41" s="70"/>
       <c r="K41" s="52"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="69"/>
+      <c r="A42" s="75"/>
       <c r="B42" s="56" t="s">
         <v>13</v>
       </c>
@@ -2408,12 +2404,12 @@
       <c r="F42" s="57"/>
       <c r="G42" s="58"/>
       <c r="H42" s="56"/>
-      <c r="I42" s="69"/>
-      <c r="J42" s="65"/>
+      <c r="I42" s="75"/>
+      <c r="J42" s="71"/>
       <c r="K42" s="53"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="68" t="s">
+      <c r="A43" s="74" t="s">
         <v>138</v>
       </c>
       <c r="B43" s="39" t="s">
@@ -2427,14 +2423,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="64"/>
-      <c r="J43" s="64"/>
+        <v>140</v>
+      </c>
+      <c r="I43" s="70"/>
+      <c r="J43" s="70"/>
       <c r="K43" s="52"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="69"/>
+      <c r="A44" s="75"/>
       <c r="B44" s="56" t="s">
         <v>13</v>
       </c>
@@ -2446,10 +2442,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="69"/>
-      <c r="J44" s="65"/>
+        <v>140</v>
+      </c>
+      <c r="I44" s="75"/>
+      <c r="J44" s="71"/>
       <c r="K44" s="53"/>
     </row>
   </sheetData>
@@ -2552,56 +2548,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="71"/>
-      <c r="T1" s="71"/>
-      <c r="U1" s="71"/>
-      <c r="V1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+      <c r="V2" s="69"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -3644,7 +3640,7 @@
         <v>91</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>67</v>
@@ -3741,42 +3737,45 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="13" customFormat="1" ht="18.600000000000001">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
+      <c r="A25" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="78">
+      <c r="D25" s="67">
         <v>0</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="12">
         <v>799875</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="9">
         <v>0</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="9">
         <v>0</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="9">
         <f>E25*0.4</f>
         <v>319950</v>
       </c>
-      <c r="L25" s="13">
+      <c r="L25" s="9">
+        <v>22399</v>
+      </c>
+      <c r="N25" s="9">
         <v>0</v>
       </c>
-      <c r="N25" s="13">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
+      <c r="O25" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="P25" s="12">
         <v>384843</v>
       </c>
-      <c r="T25" s="13" t="s">
+      <c r="T25" s="9" t="s">
         <v>139</v>
       </c>
       <c r="V25" s="19"/>
@@ -4278,7 +4277,7 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -4302,6 +4301,7 @@
     <hyperlink ref="U24" r:id="rId10" xr:uid="{DFFF659B-3A50-4FD0-AA9F-289AE4EB0963}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId11"/>
 </worksheet>
 </file>
 
@@ -4318,20 +4318,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4686,16 +4686,16 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="77">
+      <c r="A26" s="66">
         <v>46219</v>
       </c>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="75">
+      <c r="D26" s="64">
         <v>3</v>
       </c>
       <c r="E26" t="s">
@@ -4706,10 +4706,10 @@
       <c r="A27" s="3">
         <v>46224</v>
       </c>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="76" t="s">
+      <c r="C27" s="65" t="s">
         <v>61</v>
       </c>
       <c r="D27" s="4">
@@ -4726,7 +4726,7 @@
       <c r="B28" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="77" t="s">
+      <c r="C28" s="66" t="s">
         <v>61</v>
       </c>
       <c r="D28" s="4">
@@ -4757,22 +4757,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5691,15 +5691,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5952,7 +5943,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5965,15 +5956,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5992,7 +5984,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -6001,4 +5993,12 @@
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{F9904DBD-7032-4B5C-8FB6-1CDB90EC0AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E5C768D-E1C7-46E4-B8C8-9A8A6DDB9C8B}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{F9904DBD-7032-4B5C-8FB6-1CDB90EC0AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{787C0A91-B15D-439A-A808-661A8A7411B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="143">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -465,6 +465,12 @@
   </si>
   <si>
     <t>Planning</t>
+  </si>
+  <si>
+    <t>Huaykwang residence</t>
+  </si>
+  <si>
+    <t>ส่งมอบงานงวดสุดท้าย</t>
   </si>
 </sst>
 </file>
@@ -581,6 +587,7 @@
     <font>
       <sz val="10.5"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1018,10 +1025,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2 2 3 2" xfId="3" xr:uid="{10CA6883-C0B4-442D-A7D0-FF27A9ED468E}"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1110,6 +1117,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4277,7 +4288,7 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -4307,7 +4318,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4734,6 +4745,40 @@
       </c>
       <c r="E28" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="4">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="4">
+        <v>4</v>
+      </c>
+      <c r="E30" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{F9904DBD-7032-4B5C-8FB6-1CDB90EC0AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{787C0A91-B15D-439A-A808-661A8A7411B0}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{996805BD-2E1C-4C06-8112-A048AB4BF4BE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="142">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -435,9 +435,6 @@
   </si>
   <si>
     <t>ส่งงาน 100% วันที่ 07/24/2026</t>
-  </si>
-  <si>
-    <t>บ้านคุณทวีชัย สมุทปราการ</t>
   </si>
   <si>
     <t>ราคา Minimum ของผู้รับเหมา</t>
@@ -999,6 +996,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1019,16 +1017,15 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma 2 2 3 2" xfId="3" xr:uid="{10CA6883-C0B4-442D-A7D0-FF27A9ED468E}"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1066,16 +1063,6 @@
             <v>46189</v>
           </cell>
         </row>
-        <row r="7">
-          <cell r="C7">
-            <v>46219</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8">
-            <v>46244</v>
-          </cell>
-        </row>
         <row r="10">
           <cell r="C10">
             <v>46168</v>
@@ -1101,26 +1088,12 @@
             <v>46198</v>
           </cell>
         </row>
-        <row r="17">
-          <cell r="C17">
-            <v>46188</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="C18">
-            <v>46200</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1426,31 +1399,31 @@
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1508,14 +1481,14 @@
       <c r="H5" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="72">
+      <c r="I5" s="73">
         <v>46244</v>
       </c>
-      <c r="J5" s="72"/>
+      <c r="J5" s="73"/>
       <c r="K5" s="48"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="75"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="45" t="s">
         <v>13</v>
       </c>
@@ -1533,12 +1506,12 @@
       <c r="H6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="75"/>
-      <c r="J6" s="71"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="72"/>
       <c r="K6" s="49"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="75" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="39" t="s">
@@ -1558,14 +1531,14 @@
       <c r="H7" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="70" t="s">
+      <c r="I7" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="70"/>
+      <c r="J7" s="71"/>
       <c r="K7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="75"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="36" t="s">
         <v>13</v>
       </c>
@@ -1583,12 +1556,12 @@
       <c r="H8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="75"/>
-      <c r="J8" s="71"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="72"/>
       <c r="K8" s="49"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="75" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="39" t="s">
@@ -1608,14 +1581,14 @@
       <c r="H9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="70">
+      <c r="I9" s="71">
         <v>46218</v>
       </c>
-      <c r="J9" s="70"/>
+      <c r="J9" s="71"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="75"/>
+      <c r="A10" s="76"/>
       <c r="B10" s="36" t="s">
         <v>13</v>
       </c>
@@ -1633,12 +1606,12 @@
       <c r="H10" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="75"/>
-      <c r="J10" s="71"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="72"/>
       <c r="K10" s="49"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="75" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="42" t="s">
@@ -1658,14 +1631,14 @@
       <c r="H11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="70">
+      <c r="I11" s="71">
         <v>46171</v>
       </c>
-      <c r="J11" s="70"/>
+      <c r="J11" s="71"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="75"/>
+      <c r="A12" s="76"/>
       <c r="B12" s="45" t="s">
         <v>13</v>
       </c>
@@ -1683,12 +1656,12 @@
       <c r="H12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="75"/>
-      <c r="J12" s="71"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="72"/>
       <c r="K12" s="49"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="75" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="39" t="s">
@@ -1708,14 +1681,14 @@
       <c r="H13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="70" t="s">
+      <c r="I13" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="70"/>
+      <c r="J13" s="71"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="75"/>
+      <c r="A14" s="76"/>
       <c r="B14" s="36" t="s">
         <v>13</v>
       </c>
@@ -1733,12 +1706,12 @@
       <c r="H14" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="75"/>
-      <c r="J14" s="71"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="72"/>
       <c r="K14" s="49"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="75" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="42" t="s">
@@ -1758,14 +1731,14 @@
       <c r="H15" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="70">
+      <c r="I15" s="71">
         <v>46199</v>
       </c>
-      <c r="J15" s="70"/>
+      <c r="J15" s="71"/>
       <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="75"/>
+      <c r="A16" s="76"/>
       <c r="B16" s="45" t="s">
         <v>13</v>
       </c>
@@ -1783,12 +1756,12 @@
       <c r="H16" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="75"/>
-      <c r="J16" s="71"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="72"/>
       <c r="K16" s="49"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="76" t="s">
+      <c r="A17" s="77" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="33" t="s">
@@ -1808,14 +1781,14 @@
       <c r="H17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="73">
+      <c r="I17" s="74">
         <v>46305</v>
       </c>
-      <c r="J17" s="73"/>
+      <c r="J17" s="74"/>
       <c r="K17" s="51"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="75"/>
+      <c r="A18" s="76"/>
       <c r="B18" s="36" t="s">
         <v>13</v>
       </c>
@@ -1833,12 +1806,12 @@
       <c r="H18" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="75"/>
-      <c r="J18" s="71"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="72"/>
       <c r="K18" s="49"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="77" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="33" t="s">
@@ -1858,14 +1831,14 @@
       <c r="H19" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="73">
+      <c r="I19" s="74">
         <v>46336</v>
       </c>
-      <c r="J19" s="73"/>
+      <c r="J19" s="74"/>
       <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="75"/>
+      <c r="A20" s="76"/>
       <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
@@ -1883,12 +1856,12 @@
       <c r="H20" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="75"/>
-      <c r="J20" s="71"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="72"/>
       <c r="K20" s="49"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="74" t="s">
+      <c r="A21" s="75" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="39" t="s">
@@ -1908,14 +1881,14 @@
       <c r="H21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="70">
+      <c r="I21" s="71">
         <v>46336</v>
       </c>
-      <c r="J21" s="70"/>
+      <c r="J21" s="71"/>
       <c r="K21" s="52"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="75"/>
+      <c r="A22" s="76"/>
       <c r="B22" s="36" t="s">
         <v>13</v>
       </c>
@@ -1933,12 +1906,12 @@
       <c r="H22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="75"/>
-      <c r="J22" s="71"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="72"/>
       <c r="K22" s="53"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="75" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="42" t="s">
@@ -1958,14 +1931,14 @@
       <c r="H23" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="70">
+      <c r="I23" s="71">
         <v>46237</v>
       </c>
-      <c r="J23" s="70"/>
+      <c r="J23" s="71"/>
       <c r="K23" s="52"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="75"/>
+      <c r="A24" s="76"/>
       <c r="B24" s="45" t="s">
         <v>13</v>
       </c>
@@ -1983,12 +1956,12 @@
       <c r="H24" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="75"/>
-      <c r="J24" s="71"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="72"/>
       <c r="K24" s="53"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="74" t="s">
+      <c r="A25" s="75" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="42" t="s">
@@ -2008,14 +1981,14 @@
       <c r="H25" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="70">
+      <c r="I25" s="71">
         <v>46188</v>
       </c>
-      <c r="J25" s="70"/>
+      <c r="J25" s="71"/>
       <c r="K25" s="52"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="75"/>
+      <c r="A26" s="76"/>
       <c r="B26" s="45" t="s">
         <v>13</v>
       </c>
@@ -2033,12 +2006,12 @@
       <c r="H26" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="75"/>
-      <c r="J26" s="71"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="72"/>
       <c r="K26" s="53"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="74" t="s">
+      <c r="A27" s="75" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="39" t="s">
@@ -2058,14 +2031,14 @@
       <c r="H27" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="70">
+      <c r="I27" s="71">
         <v>46321</v>
       </c>
-      <c r="J27" s="70"/>
+      <c r="J27" s="71"/>
       <c r="K27" s="52"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="75"/>
+      <c r="A28" s="76"/>
       <c r="B28" s="36" t="s">
         <v>13</v>
       </c>
@@ -2083,12 +2056,12 @@
       <c r="H28" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="75"/>
-      <c r="J28" s="71"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="72"/>
       <c r="K28" s="53"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="74" t="s">
+      <c r="A29" s="75" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="42" t="s">
@@ -2108,14 +2081,14 @@
       <c r="H29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="70">
+      <c r="I29" s="71">
         <v>46139</v>
       </c>
-      <c r="J29" s="70"/>
+      <c r="J29" s="71"/>
       <c r="K29" s="52"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="75"/>
+      <c r="A30" s="76"/>
       <c r="B30" s="45" t="s">
         <v>13</v>
       </c>
@@ -2133,12 +2106,12 @@
       <c r="H30" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="75"/>
-      <c r="J30" s="71"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="72"/>
       <c r="K30" s="53"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="74" t="s">
+      <c r="A31" s="75" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="42" t="s">
@@ -2158,14 +2131,14 @@
       <c r="H31" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="70">
+      <c r="I31" s="71">
         <v>46133</v>
       </c>
-      <c r="J31" s="70"/>
+      <c r="J31" s="71"/>
       <c r="K31" s="52"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="75"/>
+      <c r="A32" s="76"/>
       <c r="B32" s="45" t="s">
         <v>13</v>
       </c>
@@ -2183,12 +2156,12 @@
       <c r="H32" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="75"/>
-      <c r="J32" s="71"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="72"/>
       <c r="K32" s="53"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="74" t="s">
+      <c r="A33" s="75" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="39" t="s">
@@ -2208,14 +2181,14 @@
       <c r="H33" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="70">
+      <c r="I33" s="71">
         <v>46295</v>
       </c>
-      <c r="J33" s="70"/>
+      <c r="J33" s="71"/>
       <c r="K33" s="52"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="75"/>
+      <c r="A34" s="76"/>
       <c r="B34" s="36" t="s">
         <v>13</v>
       </c>
@@ -2233,12 +2206,12 @@
       <c r="H34" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="75"/>
-      <c r="J34" s="71"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="72"/>
       <c r="K34" s="53"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="74" t="s">
+      <c r="A35" s="75" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="39" t="s">
@@ -2258,14 +2231,14 @@
       <c r="H35" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="70">
+      <c r="I35" s="71">
         <v>45884</v>
       </c>
-      <c r="J35" s="70"/>
+      <c r="J35" s="71"/>
       <c r="K35" s="52"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="75"/>
+      <c r="A36" s="76"/>
       <c r="B36" s="36" t="s">
         <v>13</v>
       </c>
@@ -2283,12 +2256,12 @@
       <c r="H36" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="75"/>
-      <c r="J36" s="71"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="72"/>
       <c r="K36" s="53"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="74" t="s">
+      <c r="A37" s="75" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="39" t="s">
@@ -2308,14 +2281,14 @@
       <c r="H37" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="70">
+      <c r="I37" s="71">
         <v>45915</v>
       </c>
-      <c r="J37" s="70"/>
+      <c r="J37" s="71"/>
       <c r="K37" s="52"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="75"/>
+      <c r="A38" s="76"/>
       <c r="B38" s="36" t="s">
         <v>13</v>
       </c>
@@ -2333,13 +2306,13 @@
       <c r="H38" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="75"/>
-      <c r="J38" s="71"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="72"/>
       <c r="K38" s="53"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="74" t="s">
-        <v>131</v>
+      <c r="A39" s="75" t="s">
+        <v>91</v>
       </c>
       <c r="B39" s="39" t="s">
         <v>11</v>
@@ -2352,14 +2325,14 @@
         <v>0</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="I39" s="70"/>
-      <c r="J39" s="70"/>
+        <v>139</v>
+      </c>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
       <c r="K39" s="52"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="75"/>
+      <c r="A40" s="76"/>
       <c r="B40" s="56" t="s">
         <v>13</v>
       </c>
@@ -2371,14 +2344,14 @@
         <v>0</v>
       </c>
       <c r="H40" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="I40" s="75"/>
-      <c r="J40" s="71"/>
+        <v>139</v>
+      </c>
+      <c r="I40" s="76"/>
+      <c r="J40" s="72"/>
       <c r="K40" s="53"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="74" t="s">
+      <c r="A41" s="75" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="39" t="s">
@@ -2398,14 +2371,14 @@
       <c r="H41" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="70">
+      <c r="I41" s="71">
         <v>46230</v>
       </c>
-      <c r="J41" s="70"/>
+      <c r="J41" s="71"/>
       <c r="K41" s="52"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="75"/>
+      <c r="A42" s="76"/>
       <c r="B42" s="56" t="s">
         <v>13</v>
       </c>
@@ -2415,13 +2388,13 @@
       <c r="F42" s="57"/>
       <c r="G42" s="58"/>
       <c r="H42" s="56"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="71"/>
+      <c r="I42" s="76"/>
+      <c r="J42" s="72"/>
       <c r="K42" s="53"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="74" t="s">
-        <v>138</v>
+      <c r="A43" s="75" t="s">
+        <v>137</v>
       </c>
       <c r="B43" s="39" t="s">
         <v>11</v>
@@ -2434,14 +2407,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="I43" s="70"/>
-      <c r="J43" s="70"/>
+        <v>139</v>
+      </c>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
       <c r="K43" s="52"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="75"/>
+      <c r="A44" s="76"/>
       <c r="B44" s="56" t="s">
         <v>13</v>
       </c>
@@ -2453,10 +2426,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="I44" s="75"/>
-      <c r="J44" s="71"/>
+        <v>139</v>
+      </c>
+      <c r="I44" s="76"/>
+      <c r="J44" s="72"/>
       <c r="K44" s="53"/>
     </row>
   </sheetData>
@@ -2585,30 +2558,30 @@
       <c r="V1" s="68"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
+      <c r="V2" s="70"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -2840,11 +2813,10 @@
         <v>280000</v>
       </c>
       <c r="Q7" s="19">
-        <f>'[1]Master Schedule'!C7</f>
+        <v>46102</v>
+      </c>
+      <c r="R7" s="19">
         <v>46219</v>
-      </c>
-      <c r="R7" s="19">
-        <v>46102</v>
       </c>
       <c r="S7" s="14"/>
       <c r="T7" s="26" t="s">
@@ -2901,11 +2873,10 @@
         <v>89000</v>
       </c>
       <c r="Q8" s="19">
-        <f>'[1]Master Schedule'!C8</f>
+        <v>46171</v>
+      </c>
+      <c r="R8" s="19">
         <v>46244</v>
-      </c>
-      <c r="R8" s="19">
-        <v>46171</v>
       </c>
       <c r="S8" s="14"/>
       <c r="T8" s="26"/>
@@ -3420,11 +3391,10 @@
         <v>234861</v>
       </c>
       <c r="Q17" s="19">
-        <f>'[1]Master Schedule'!C17</f>
+        <v>46139</v>
+      </c>
+      <c r="R17" s="11">
         <v>46188</v>
-      </c>
-      <c r="R17" s="11">
-        <v>46139</v>
       </c>
       <c r="T17" s="28"/>
       <c r="U17" s="26"/>
@@ -3474,11 +3444,10 @@
         <v>119980</v>
       </c>
       <c r="Q18" s="19">
-        <f>'[1]Master Schedule'!C18</f>
+        <v>46133</v>
+      </c>
+      <c r="R18" s="11">
         <v>46200</v>
-      </c>
-      <c r="R18" s="11">
-        <v>46133</v>
       </c>
       <c r="T18" s="28"/>
       <c r="U18" s="26"/>
@@ -3651,7 +3620,7 @@
         <v>91</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>67</v>
@@ -3750,10 +3719,10 @@
     </row>
     <row r="25" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="A25" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>67</v>
@@ -3787,7 +3756,7 @@
         <v>384843</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="V25" s="19"/>
     </row>
@@ -4333,16 +4302,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="68"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4710,7 +4679,7 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4727,7 +4696,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -4744,7 +4713,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4752,7 +4721,7 @@
         <v>46227</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C29" s="66" t="s">
         <v>61</v>
@@ -4778,7 +4747,7 @@
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4811,13 +4780,13 @@
       <c r="E1" s="68"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4889,10 +4858,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="C8" s="6">
         <v>46226</v>
@@ -4906,7 +4875,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="6">
@@ -5736,6 +5705,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5988,29 +5979,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6027,23 +6015,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{996805BD-2E1C-4C06-8112-A048AB4BF4BE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5E2E3CC-A260-4216-891E-591C22F5C5DB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -434,9 +434,6 @@
     <t>https://corallife806.sharepoint.com/:b:/s/CoralLife2/IQB85P7JtoSZT6532Il6VakbAcqfI6xy5EwPf0pgbRJpT3Y?e=Qwe5V0</t>
   </si>
   <si>
-    <t>ส่งงาน 100% วันที่ 07/24/2026</t>
-  </si>
-  <si>
     <t>ราคา Minimum ของผู้รับเหมา</t>
   </si>
   <si>
@@ -468,6 +465,9 @@
   </si>
   <si>
     <t>ส่งมอบงานงวดสุดท้าย</t>
+  </si>
+  <si>
+    <t>คิดงานเพิ่ม 3000 บาท ค่ากล่องพรีนัม ส่งงานวันที่ 07/31/2026</t>
   </si>
 </sst>
 </file>
@@ -804,7 +804,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -862,9 +862,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -998,27 +995,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1396,34 +1393,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1461,988 +1458,1016 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="59">
         <v>46084</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="59">
         <v>46127</v>
       </c>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="61">
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="60">
         <v>1</v>
       </c>
-      <c r="H5" s="59" t="s">
+      <c r="H5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="73">
+      <c r="I5" s="77">
         <v>46244</v>
       </c>
-      <c r="J5" s="73"/>
-      <c r="K5" s="48"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="47"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="76"/>
-      <c r="B6" s="45" t="s">
+      <c r="A6" s="71"/>
+      <c r="B6" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="45">
         <v>46189</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="45">
         <v>46189</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="47">
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46">
         <v>1</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="76"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="49"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="48"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="39">
         <v>46219</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="39">
         <v>46233</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41">
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40">
         <v>0</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="H7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="71" t="s">
+      <c r="I7" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="71"/>
-      <c r="K7" s="50"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="36" t="s">
+      <c r="A8" s="71"/>
+      <c r="B8" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="36">
         <v>46244</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="36">
         <v>46247</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38">
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="37">
         <v>0</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="76"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="49"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="48"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="39">
         <v>46082</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="39">
         <v>46096</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41">
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40">
         <v>1</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="H9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="71">
+      <c r="I9" s="72">
         <v>46218</v>
       </c>
-      <c r="J9" s="71"/>
-      <c r="K9" s="50"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="76"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="71"/>
+      <c r="B10" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="36">
         <v>46168</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="36">
         <v>46213</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="38">
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="37">
         <v>1</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="76"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="49"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="48"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="42">
         <v>46184</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="42">
         <v>46191</v>
       </c>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44">
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="43">
         <v>1</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="71">
+      <c r="I11" s="72">
         <v>46171</v>
       </c>
-      <c r="J11" s="71"/>
-      <c r="K11" s="50"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="49"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="76"/>
-      <c r="B12" s="45" t="s">
+      <c r="A12" s="71"/>
+      <c r="B12" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="45">
         <v>46200</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="45">
         <v>46202</v>
       </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47">
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="46">
         <v>1</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="76"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="49"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="48"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="39">
         <v>46392</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="39">
         <v>46402</v>
       </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41">
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40">
         <v>0</v>
       </c>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="71" t="s">
+      <c r="I13" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="71"/>
-      <c r="K13" s="50"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="49"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="76"/>
-      <c r="B14" s="36" t="s">
+      <c r="A14" s="71"/>
+      <c r="B14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="36">
         <v>46042</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="36">
         <v>46042</v>
       </c>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38">
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="37">
         <v>0</v>
       </c>
-      <c r="H14" s="36" t="s">
+      <c r="H14" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="76"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="49"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="48"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="42">
         <v>46168</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="42">
         <v>46188</v>
       </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44">
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43">
         <v>1</v>
       </c>
-      <c r="H15" s="42" t="s">
+      <c r="H15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="71">
+      <c r="I15" s="72">
         <v>46199</v>
       </c>
-      <c r="J15" s="71"/>
-      <c r="K15" s="50"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="49"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="76"/>
-      <c r="B16" s="45" t="s">
+      <c r="A16" s="71"/>
+      <c r="B16" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="45">
         <v>46198</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="45">
         <v>46199</v>
       </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="47">
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46">
         <v>1</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="76"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="49"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="48"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="77" t="s">
+      <c r="A17" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>46188</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>46198</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="35">
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="34">
         <v>0.8</v>
       </c>
-      <c r="H17" s="33" t="s">
+      <c r="H17" s="32" t="s">
         <v>12</v>
       </c>
       <c r="I17" s="74">
         <v>46305</v>
       </c>
       <c r="J17" s="74"/>
-      <c r="K17" s="51"/>
+      <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="76"/>
-      <c r="B18" s="36" t="s">
+      <c r="A18" s="71"/>
+      <c r="B18" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="36">
         <v>46296</v>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="36">
         <v>46298</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38">
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37">
         <v>0.4</v>
       </c>
-      <c r="H18" s="36" t="s">
+      <c r="H18" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="76"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="49"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="48"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="33">
         <v>46275</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="33">
         <v>46290</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="35">
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="34">
         <v>0</v>
       </c>
-      <c r="H19" s="33" t="s">
+      <c r="H19" s="32" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="74">
         <v>46336</v>
       </c>
       <c r="J19" s="74"/>
-      <c r="K19" s="51"/>
+      <c r="K19" s="50"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="76"/>
-      <c r="B20" s="36" t="s">
+      <c r="A20" s="71"/>
+      <c r="B20" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="37">
+      <c r="C20" s="36">
         <v>46327</v>
       </c>
-      <c r="D20" s="37">
+      <c r="D20" s="36">
         <v>46329</v>
       </c>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38">
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37">
         <v>0</v>
       </c>
-      <c r="H20" s="36" t="s">
+      <c r="H20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="76"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="49"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="73"/>
+      <c r="K20" s="48"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="39">
         <v>46240</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="39">
         <v>46249</v>
       </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41">
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40">
         <v>0</v>
       </c>
-      <c r="H21" s="39" t="s">
+      <c r="H21" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="71">
+      <c r="I21" s="72">
         <v>46336</v>
       </c>
-      <c r="J21" s="71"/>
-      <c r="K21" s="52"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="51"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="76"/>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="71"/>
+      <c r="B22" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="36">
         <v>46327</v>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="36">
         <v>46329</v>
       </c>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38">
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="37">
         <v>0</v>
       </c>
-      <c r="H22" s="36" t="s">
+      <c r="H22" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="76"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="53"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="52"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="42">
         <v>46190</v>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="42">
         <v>46206</v>
       </c>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="44">
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="43">
         <v>1</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="H23" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="71">
+      <c r="I23" s="72">
         <v>46237</v>
       </c>
-      <c r="J23" s="71"/>
-      <c r="K23" s="52"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="51"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="76"/>
-      <c r="B24" s="45" t="s">
+      <c r="A24" s="71"/>
+      <c r="B24" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="45">
         <v>46216</v>
       </c>
-      <c r="D24" s="46">
+      <c r="D24" s="45">
         <v>46220</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47">
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="46">
         <v>1</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="76"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="53"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="52"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="75" t="s">
+      <c r="A25" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="42">
         <v>46185</v>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="42">
         <v>46188</v>
       </c>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="44">
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43">
         <v>1</v>
       </c>
-      <c r="H25" s="42" t="s">
+      <c r="H25" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="71">
+      <c r="I25" s="72">
         <v>46188</v>
       </c>
-      <c r="J25" s="71"/>
-      <c r="K25" s="52"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="51"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="76"/>
-      <c r="B26" s="45" t="s">
+      <c r="A26" s="71"/>
+      <c r="B26" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="46">
+      <c r="C26" s="45">
         <v>46185</v>
       </c>
-      <c r="D26" s="46">
+      <c r="D26" s="45">
         <v>46188</v>
       </c>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47">
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46">
         <v>1</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="76"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="53"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="52"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="75" t="s">
+      <c r="A27" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="40">
+      <c r="C27" s="39">
         <v>46234</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="39">
         <v>46247</v>
       </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41">
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40">
         <v>0</v>
       </c>
-      <c r="H27" s="39" t="s">
+      <c r="H27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="71">
+      <c r="I27" s="72">
         <v>46321</v>
       </c>
-      <c r="J27" s="71"/>
-      <c r="K27" s="52"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="51"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="76"/>
-      <c r="B28" s="36" t="s">
+      <c r="A28" s="71"/>
+      <c r="B28" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="36">
         <v>46314</v>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="36">
         <v>46316</v>
       </c>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38">
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="37">
         <v>0</v>
       </c>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="76"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="53"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="52"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="75" t="s">
+      <c r="A29" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="43">
+      <c r="C29" s="42">
         <v>46091</v>
       </c>
-      <c r="D29" s="43">
+      <c r="D29" s="42">
         <v>46100</v>
       </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44">
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43">
         <v>1</v>
       </c>
-      <c r="H29" s="42" t="s">
+      <c r="H29" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="71">
+      <c r="I29" s="72">
         <v>46139</v>
       </c>
-      <c r="J29" s="71"/>
-      <c r="K29" s="52"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="51"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="76"/>
-      <c r="B30" s="45" t="s">
+      <c r="A30" s="71"/>
+      <c r="B30" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="46">
+      <c r="C30" s="45">
         <v>46120</v>
       </c>
-      <c r="D30" s="46">
+      <c r="D30" s="45">
         <v>46124</v>
       </c>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="47">
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="46">
         <v>1</v>
       </c>
-      <c r="H30" s="45" t="s">
+      <c r="H30" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="76"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="53"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="52"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="43">
+      <c r="C31" s="42">
         <v>46091</v>
       </c>
-      <c r="D31" s="43">
+      <c r="D31" s="42">
         <v>46094</v>
       </c>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44">
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43">
         <v>1</v>
       </c>
-      <c r="H31" s="42" t="s">
+      <c r="H31" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="71">
+      <c r="I31" s="72">
         <v>46133</v>
       </c>
-      <c r="J31" s="71"/>
-      <c r="K31" s="52"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="51"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="76"/>
-      <c r="B32" s="45" t="s">
+      <c r="A32" s="71"/>
+      <c r="B32" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="46">
+      <c r="C32" s="45">
         <v>46091</v>
       </c>
-      <c r="D32" s="46">
+      <c r="D32" s="45">
         <v>46094</v>
       </c>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="47">
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="46">
         <v>1</v>
       </c>
-      <c r="H32" s="45" t="s">
+      <c r="H32" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="76"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="53"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="52"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="75" t="s">
+      <c r="A33" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="62">
+      <c r="C33" s="61">
         <v>46237</v>
       </c>
-      <c r="D33" s="62">
+      <c r="D33" s="61">
         <v>46248</v>
       </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41">
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40">
         <v>0</v>
       </c>
-      <c r="H33" s="39" t="s">
+      <c r="H33" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="71">
+      <c r="I33" s="72">
         <v>46295</v>
       </c>
-      <c r="J33" s="71"/>
-      <c r="K33" s="52"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="51"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="76"/>
-      <c r="B34" s="36" t="s">
+      <c r="A34" s="71"/>
+      <c r="B34" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="63">
+      <c r="C34" s="62">
         <v>46296</v>
       </c>
-      <c r="D34" s="63">
+      <c r="D34" s="62">
         <v>46303</v>
       </c>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="38">
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="37">
         <v>0</v>
       </c>
-      <c r="H34" s="36" t="s">
+      <c r="H34" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="76"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="53"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="73"/>
+      <c r="K34" s="52"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="40">
+      <c r="C35" s="39">
         <v>45723</v>
       </c>
-      <c r="D35" s="40">
+      <c r="D35" s="39">
         <v>45729</v>
       </c>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="41">
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="40">
         <v>1</v>
       </c>
-      <c r="H35" s="39" t="s">
+      <c r="H35" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="71">
+      <c r="I35" s="72">
         <v>45884</v>
       </c>
-      <c r="J35" s="71"/>
-      <c r="K35" s="52"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="51"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="76"/>
-      <c r="B36" s="36" t="s">
+      <c r="A36" s="71"/>
+      <c r="B36" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="36">
         <v>45729</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="36">
         <v>45732</v>
       </c>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="38">
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="37">
         <v>0.9</v>
       </c>
-      <c r="H36" s="36" t="s">
+      <c r="H36" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="76"/>
-      <c r="J36" s="72"/>
-      <c r="K36" s="53"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="73"/>
+      <c r="K36" s="52"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="75" t="s">
+      <c r="A37" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="39">
         <v>45723</v>
       </c>
-      <c r="D37" s="40">
+      <c r="D37" s="39">
         <v>45729</v>
       </c>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="41">
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="40">
         <v>1</v>
       </c>
-      <c r="H37" s="39" t="s">
+      <c r="H37" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="71">
+      <c r="I37" s="72">
         <v>45915</v>
       </c>
-      <c r="J37" s="71"/>
-      <c r="K37" s="52"/>
+      <c r="J37" s="72"/>
+      <c r="K37" s="51"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="76"/>
-      <c r="B38" s="36" t="s">
+      <c r="A38" s="71"/>
+      <c r="B38" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="37">
+      <c r="C38" s="36">
         <v>45729</v>
       </c>
-      <c r="D38" s="37">
+      <c r="D38" s="36">
         <v>45862</v>
       </c>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="38">
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="37">
         <v>0.9</v>
       </c>
-      <c r="H38" s="36" t="s">
+      <c r="H38" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="76"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="53"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="73"/>
+      <c r="K38" s="52"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="75" t="s">
+      <c r="A39" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="41">
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="40">
         <v>0</v>
       </c>
-      <c r="H39" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="52"/>
+      <c r="H39" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="I39" s="72"/>
+      <c r="J39" s="72"/>
+      <c r="K39" s="51"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="76"/>
-      <c r="B40" s="56" t="s">
+      <c r="A40" s="71"/>
+      <c r="B40" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="57"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="58">
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="57">
         <v>0</v>
       </c>
-      <c r="H40" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="I40" s="76"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="53"/>
+      <c r="H40" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="I40" s="71"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="52"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="75" t="s">
+      <c r="A41" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="40">
+      <c r="C41" s="39">
         <v>46226</v>
       </c>
-      <c r="D41" s="40">
+      <c r="D41" s="39">
         <v>46228</v>
       </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="41">
-        <v>0.35</v>
-      </c>
-      <c r="H41" s="39" t="s">
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="40">
+        <v>1</v>
+      </c>
+      <c r="H41" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="71">
-        <v>46230</v>
-      </c>
-      <c r="J41" s="71"/>
-      <c r="K41" s="52"/>
+      <c r="I41" s="72">
+        <v>46234</v>
+      </c>
+      <c r="J41" s="72"/>
+      <c r="K41" s="51"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="76"/>
-      <c r="B42" s="56" t="s">
+      <c r="A42" s="71"/>
+      <c r="B42" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="76"/>
-      <c r="J42" s="72"/>
-      <c r="K42" s="53"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="73"/>
+      <c r="K42" s="52"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="B43" s="39" t="s">
+      <c r="A43" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="41">
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="40">
         <v>0</v>
       </c>
-      <c r="H43" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
-      <c r="K43" s="52"/>
+      <c r="H43" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="I43" s="72"/>
+      <c r="J43" s="72"/>
+      <c r="K43" s="51"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="76"/>
-      <c r="B44" s="56" t="s">
+      <c r="A44" s="71"/>
+      <c r="B44" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="58">
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="57">
         <v>0</v>
       </c>
-      <c r="H44" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="I44" s="76"/>
-      <c r="J44" s="72"/>
-      <c r="K44" s="53"/>
+      <c r="H44" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="I44" s="71"/>
+      <c r="J44" s="73"/>
+      <c r="K44" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2459,43 +2484,15 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -2532,56 +2529,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
-      <c r="V1" s="68"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="70"/>
-      <c r="V2" s="70"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
+      <c r="U2" s="69"/>
+      <c r="V2" s="69"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -2702,10 +2699,10 @@
         <v>46106</v>
       </c>
       <c r="S5" s="14"/>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="U5" s="29" t="s">
+      <c r="U5" s="28" t="s">
         <v>80</v>
       </c>
       <c r="V5" s="19"/>
@@ -2761,10 +2758,10 @@
         <v>46264</v>
       </c>
       <c r="S6" s="14"/>
-      <c r="T6" s="26" t="s">
+      <c r="T6" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="U6" s="26"/>
+      <c r="U6" s="25"/>
       <c r="V6" s="19"/>
     </row>
     <row r="7" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
@@ -2819,10 +2816,10 @@
         <v>46219</v>
       </c>
       <c r="S7" s="14"/>
-      <c r="T7" s="26" t="s">
+      <c r="T7" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="U7" s="29" t="s">
+      <c r="U7" s="28" t="s">
         <v>81</v>
       </c>
       <c r="V7" s="19"/>
@@ -2879,8 +2876,8 @@
         <v>46244</v>
       </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="31" t="s">
+      <c r="T8" s="25"/>
+      <c r="U8" s="30" t="s">
         <v>82</v>
       </c>
       <c r="V8" s="19">
@@ -2933,8 +2930,8 @@
         <v>46447</v>
       </c>
       <c r="S9" s="14"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
       <c r="V9" s="19"/>
     </row>
     <row r="10" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
@@ -2990,8 +2987,8 @@
         <v>46199</v>
       </c>
       <c r="S10" s="14"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="31" t="s">
+      <c r="T10" s="26"/>
+      <c r="U10" s="30" t="s">
         <v>82</v>
       </c>
       <c r="V10" s="19">
@@ -3050,10 +3047,10 @@
         <v>46305</v>
       </c>
       <c r="S11" s="14"/>
-      <c r="T11" s="27" t="s">
+      <c r="T11" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="U11" s="31" t="s">
+      <c r="U11" s="30" t="s">
         <v>83</v>
       </c>
       <c r="V11" s="19">
@@ -3111,10 +3108,10 @@
         <v>46336</v>
       </c>
       <c r="S12" s="14"/>
-      <c r="T12" s="27" t="s">
+      <c r="T12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="U12" s="26"/>
+      <c r="U12" s="25"/>
       <c r="V12" s="19">
         <v>46331</v>
       </c>
@@ -3165,10 +3162,10 @@
       <c r="R13" s="11">
         <v>46336</v>
       </c>
-      <c r="T13" s="26" t="s">
+      <c r="T13" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="U13" s="31" t="s">
+      <c r="U13" s="30" t="s">
         <v>84</v>
       </c>
       <c r="V13" s="19">
@@ -3185,7 +3182,7 @@
       <c r="C14" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="15">
         <v>1</v>
       </c>
       <c r="E14" s="16">
@@ -3224,10 +3221,10 @@
       <c r="R14" s="11">
         <v>46237</v>
       </c>
-      <c r="T14" s="27" t="s">
+      <c r="T14" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="U14" s="29" t="s">
+      <c r="U14" s="28" t="s">
         <v>70</v>
       </c>
       <c r="V14" s="19">
@@ -3284,8 +3281,8 @@
       <c r="R15" s="11">
         <v>46188</v>
       </c>
-      <c r="T15" s="28"/>
-      <c r="U15" s="26"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="25"/>
       <c r="V15" s="19">
         <v>46169</v>
       </c>
@@ -3337,10 +3334,10 @@
       <c r="R16" s="11">
         <v>46321</v>
       </c>
-      <c r="T16" s="26" t="s">
+      <c r="T16" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="29" t="s">
+      <c r="U16" s="28" t="s">
         <v>85</v>
       </c>
       <c r="V16" s="19">
@@ -3374,7 +3371,7 @@
         <f>E17*1</f>
         <v>600000</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="21">
         <v>10</v>
       </c>
       <c r="K17" s="14"/>
@@ -3396,8 +3393,8 @@
       <c r="R17" s="11">
         <v>46188</v>
       </c>
-      <c r="T17" s="28"/>
-      <c r="U17" s="26"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="25"/>
       <c r="V17" s="19">
         <v>46079</v>
       </c>
@@ -3427,7 +3424,7 @@
         <f>E18*1</f>
         <v>317648</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="21">
         <v>10</v>
       </c>
       <c r="K18" s="14"/>
@@ -3449,8 +3446,8 @@
       <c r="R18" s="11">
         <v>46200</v>
       </c>
-      <c r="T18" s="28"/>
-      <c r="U18" s="26"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="25"/>
       <c r="V18" s="19"/>
     </row>
     <row r="19" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
@@ -3480,7 +3477,7 @@
         <f>455555</f>
         <v>455555</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="21">
         <v>3</v>
       </c>
       <c r="K19" s="14"/>
@@ -3503,10 +3500,10 @@
       <c r="R19" s="11">
         <v>46295</v>
       </c>
-      <c r="T19" s="27" t="s">
+      <c r="T19" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="U19" s="32" t="s">
+      <c r="U19" s="31" t="s">
         <v>86</v>
       </c>
       <c r="V19" s="19">
@@ -3517,7 +3514,7 @@
       <c r="A20" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="22" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="14" t="s">
@@ -3526,8 +3523,8 @@
       <c r="D20" s="15">
         <v>0.9</v>
       </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="24"/>
       <c r="G20" s="9">
         <v>255</v>
       </c>
@@ -3548,17 +3545,17 @@
       <c r="R20" s="19">
         <v>45737</v>
       </c>
-      <c r="T20" s="27" t="s">
+      <c r="T20" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="U20" s="26"/>
+      <c r="U20" s="25"/>
       <c r="V20" s="19"/>
     </row>
     <row r="21" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="A21" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="22" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="14" t="s">
@@ -3567,7 +3564,7 @@
       <c r="D21" s="15">
         <v>0.9</v>
       </c>
-      <c r="F21" s="25"/>
+      <c r="F21" s="24"/>
       <c r="I21" s="9">
         <v>6</v>
       </c>
@@ -3584,7 +3581,7 @@
       <c r="R21" s="19">
         <v>45737</v>
       </c>
-      <c r="T21" s="27" t="s">
+      <c r="T21" s="26" t="s">
         <v>126</v>
       </c>
       <c r="V21" s="19"/>
@@ -3593,14 +3590,14 @@
       <c r="A22" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="15"/>
-      <c r="F22" s="25"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="9">
         <v>2484</v>
       </c>
@@ -3610,7 +3607,7 @@
       <c r="P22" s="10"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="19"/>
-      <c r="T22" s="27" t="s">
+      <c r="T22" s="26" t="s">
         <v>88</v>
       </c>
       <c r="V22" s="19"/>
@@ -3620,7 +3617,7 @@
         <v>91</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>67</v>
@@ -3639,7 +3636,7 @@
         <f>E23*0.5</f>
         <v>230000</v>
       </c>
-      <c r="I23" s="22"/>
+      <c r="I23" s="21"/>
       <c r="K23" s="14"/>
       <c r="L23" s="16">
         <v>15000</v>
@@ -3652,8 +3649,8 @@
       </c>
       <c r="Q23" s="19"/>
       <c r="R23" s="11"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="32"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="31"/>
       <c r="V23" s="19">
         <v>46209</v>
       </c>
@@ -3669,7 +3666,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="15">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="E24" s="16">
         <v>203880</v>
@@ -3685,14 +3682,14 @@
         <f>E24*0.4</f>
         <v>81552</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="21">
         <v>6</v>
       </c>
       <c r="K24" s="14"/>
       <c r="L24" s="16">
         <v>13500</v>
       </c>
-      <c r="N24" s="55">
+      <c r="N24" s="54">
         <v>497</v>
       </c>
       <c r="O24" s="9" t="s">
@@ -3705,12 +3702,12 @@
         <v>46225</v>
       </c>
       <c r="R24" s="11">
-        <v>46227</v>
-      </c>
-      <c r="T24" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="U24" s="32" t="s">
+        <v>46234</v>
+      </c>
+      <c r="T24" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="U24" s="31" t="s">
         <v>129</v>
       </c>
       <c r="V24" s="19">
@@ -3719,15 +3716,15 @@
     </row>
     <row r="25" spans="1:22" s="9" customFormat="1" ht="18.600000000000001">
       <c r="A25" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="67">
+      <c r="D25" s="66">
         <v>0</v>
       </c>
       <c r="E25" s="12">
@@ -3756,7 +3753,7 @@
         <v>384843</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="V25" s="19"/>
     </row>
@@ -4257,7 +4254,7 @@
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -4298,20 +4295,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4326,7 +4323,7 @@
       <c r="D4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="53" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4666,37 +4663,37 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="66">
+      <c r="A26" s="65">
         <v>46219</v>
       </c>
-      <c r="B26" s="65" t="s">
+      <c r="B26" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="64">
+      <c r="D26" s="63">
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3">
         <v>46224</v>
       </c>
-      <c r="B27" s="65" t="s">
+      <c r="B27" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="64" t="s">
         <v>61</v>
       </c>
       <c r="D27" s="4">
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -4706,14 +4703,14 @@
       <c r="B28" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="65" t="s">
         <v>61</v>
       </c>
       <c r="D28" s="4">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4721,9 +4718,9 @@
         <v>46227</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="65" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="4">
@@ -4740,14 +4737,14 @@
       <c r="B30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="66" t="s">
+      <c r="C30" s="65" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="4">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -4771,22 +4768,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4858,10 +4855,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="C8" s="6">
         <v>46226</v>
@@ -4875,7 +4872,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="6">
@@ -5003,692 +5000,692 @@
       <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
     </row>
     <row r="33" spans="3:4">
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
     </row>
     <row r="34" spans="3:4">
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
     </row>
     <row r="35" spans="3:4">
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
     </row>
     <row r="36" spans="3:4">
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
     </row>
     <row r="37" spans="3:4">
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
     </row>
     <row r="38" spans="3:4">
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
     </row>
     <row r="39" spans="3:4">
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
     </row>
     <row r="40" spans="3:4">
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
     </row>
     <row r="42" spans="3:4">
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
     </row>
     <row r="43" spans="3:4">
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
     </row>
     <row r="44" spans="3:4">
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
     </row>
     <row r="45" spans="3:4">
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
     </row>
     <row r="46" spans="3:4">
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
     </row>
     <row r="47" spans="3:4">
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
     </row>
     <row r="48" spans="3:4">
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
     </row>
     <row r="49" spans="3:4">
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
     </row>
     <row r="50" spans="3:4">
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
     </row>
     <row r="51" spans="3:4">
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
     </row>
     <row r="52" spans="3:4">
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
     </row>
     <row r="53" spans="3:4">
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
     </row>
     <row r="54" spans="3:4">
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
     </row>
     <row r="55" spans="3:4">
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
     </row>
     <row r="56" spans="3:4">
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
     </row>
     <row r="57" spans="3:4">
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
     </row>
     <row r="58" spans="3:4">
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
     </row>
     <row r="59" spans="3:4">
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
     </row>
     <row r="60" spans="3:4">
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
     </row>
     <row r="61" spans="3:4">
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
     </row>
     <row r="62" spans="3:4">
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
     </row>
     <row r="63" spans="3:4">
-      <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
     </row>
     <row r="64" spans="3:4">
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
     </row>
     <row r="65" spans="3:4">
-      <c r="C65" s="30"/>
-      <c r="D65" s="30"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="29"/>
     </row>
     <row r="66" spans="3:4">
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
     </row>
     <row r="67" spans="3:4">
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
     </row>
     <row r="68" spans="3:4">
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
     </row>
     <row r="69" spans="3:4">
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
     </row>
     <row r="70" spans="3:4">
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
     </row>
     <row r="71" spans="3:4">
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
     </row>
     <row r="72" spans="3:4">
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
     </row>
     <row r="73" spans="3:4">
-      <c r="C73" s="30"/>
-      <c r="D73" s="30"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="29"/>
     </row>
     <row r="74" spans="3:4">
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
     </row>
     <row r="75" spans="3:4">
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="29"/>
     </row>
     <row r="76" spans="3:4">
-      <c r="C76" s="30"/>
-      <c r="D76" s="30"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
     </row>
     <row r="77" spans="3:4">
-      <c r="C77" s="30"/>
-      <c r="D77" s="30"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="29"/>
     </row>
     <row r="78" spans="3:4">
-      <c r="C78" s="30"/>
-      <c r="D78" s="30"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="29"/>
     </row>
     <row r="79" spans="3:4">
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
+      <c r="C79" s="29"/>
+      <c r="D79" s="29"/>
     </row>
     <row r="80" spans="3:4">
-      <c r="C80" s="30"/>
-      <c r="D80" s="30"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="29"/>
     </row>
     <row r="81" spans="3:4">
-      <c r="C81" s="30"/>
-      <c r="D81" s="30"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="29"/>
     </row>
     <row r="82" spans="3:4">
-      <c r="C82" s="30"/>
-      <c r="D82" s="30"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="29"/>
     </row>
     <row r="83" spans="3:4">
-      <c r="C83" s="30"/>
-      <c r="D83" s="30"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="29"/>
     </row>
     <row r="84" spans="3:4">
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
     </row>
     <row r="85" spans="3:4">
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="29"/>
     </row>
     <row r="86" spans="3:4">
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
+      <c r="C86" s="29"/>
+      <c r="D86" s="29"/>
     </row>
     <row r="87" spans="3:4">
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
+      <c r="C87" s="29"/>
+      <c r="D87" s="29"/>
     </row>
     <row r="88" spans="3:4">
-      <c r="C88" s="30"/>
-      <c r="D88" s="30"/>
+      <c r="C88" s="29"/>
+      <c r="D88" s="29"/>
     </row>
     <row r="89" spans="3:4">
-      <c r="C89" s="30"/>
-      <c r="D89" s="30"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="29"/>
     </row>
     <row r="90" spans="3:4">
-      <c r="C90" s="30"/>
-      <c r="D90" s="30"/>
+      <c r="C90" s="29"/>
+      <c r="D90" s="29"/>
     </row>
     <row r="91" spans="3:4">
-      <c r="C91" s="30"/>
-      <c r="D91" s="30"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="29"/>
     </row>
     <row r="92" spans="3:4">
-      <c r="C92" s="30"/>
-      <c r="D92" s="30"/>
+      <c r="C92" s="29"/>
+      <c r="D92" s="29"/>
     </row>
     <row r="93" spans="3:4">
-      <c r="C93" s="30"/>
-      <c r="D93" s="30"/>
+      <c r="C93" s="29"/>
+      <c r="D93" s="29"/>
     </row>
     <row r="94" spans="3:4">
-      <c r="C94" s="30"/>
-      <c r="D94" s="30"/>
+      <c r="C94" s="29"/>
+      <c r="D94" s="29"/>
     </row>
     <row r="95" spans="3:4">
-      <c r="C95" s="30"/>
-      <c r="D95" s="30"/>
+      <c r="C95" s="29"/>
+      <c r="D95" s="29"/>
     </row>
     <row r="96" spans="3:4">
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
+      <c r="C96" s="29"/>
+      <c r="D96" s="29"/>
     </row>
     <row r="97" spans="3:4">
-      <c r="C97" s="30"/>
-      <c r="D97" s="30"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="29"/>
     </row>
     <row r="98" spans="3:4">
-      <c r="C98" s="30"/>
-      <c r="D98" s="30"/>
+      <c r="C98" s="29"/>
+      <c r="D98" s="29"/>
     </row>
     <row r="99" spans="3:4">
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="29"/>
     </row>
     <row r="100" spans="3:4">
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
+      <c r="C100" s="29"/>
+      <c r="D100" s="29"/>
     </row>
     <row r="101" spans="3:4">
-      <c r="C101" s="30"/>
-      <c r="D101" s="30"/>
+      <c r="C101" s="29"/>
+      <c r="D101" s="29"/>
     </row>
     <row r="102" spans="3:4">
-      <c r="C102" s="30"/>
-      <c r="D102" s="30"/>
+      <c r="C102" s="29"/>
+      <c r="D102" s="29"/>
     </row>
     <row r="103" spans="3:4">
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="29"/>
     </row>
     <row r="104" spans="3:4">
-      <c r="C104" s="30"/>
-      <c r="D104" s="30"/>
+      <c r="C104" s="29"/>
+      <c r="D104" s="29"/>
     </row>
     <row r="105" spans="3:4">
-      <c r="C105" s="30"/>
-      <c r="D105" s="30"/>
+      <c r="C105" s="29"/>
+      <c r="D105" s="29"/>
     </row>
     <row r="106" spans="3:4">
-      <c r="C106" s="30"/>
-      <c r="D106" s="30"/>
+      <c r="C106" s="29"/>
+      <c r="D106" s="29"/>
     </row>
     <row r="107" spans="3:4">
-      <c r="C107" s="30"/>
-      <c r="D107" s="30"/>
+      <c r="C107" s="29"/>
+      <c r="D107" s="29"/>
     </row>
     <row r="108" spans="3:4">
-      <c r="C108" s="30"/>
-      <c r="D108" s="30"/>
+      <c r="C108" s="29"/>
+      <c r="D108" s="29"/>
     </row>
     <row r="109" spans="3:4">
-      <c r="C109" s="30"/>
-      <c r="D109" s="30"/>
+      <c r="C109" s="29"/>
+      <c r="D109" s="29"/>
     </row>
     <row r="110" spans="3:4">
-      <c r="C110" s="30"/>
-      <c r="D110" s="30"/>
+      <c r="C110" s="29"/>
+      <c r="D110" s="29"/>
     </row>
     <row r="111" spans="3:4">
-      <c r="C111" s="30"/>
-      <c r="D111" s="30"/>
+      <c r="C111" s="29"/>
+      <c r="D111" s="29"/>
     </row>
     <row r="112" spans="3:4">
-      <c r="C112" s="30"/>
-      <c r="D112" s="30"/>
+      <c r="C112" s="29"/>
+      <c r="D112" s="29"/>
     </row>
     <row r="113" spans="3:4">
-      <c r="C113" s="30"/>
-      <c r="D113" s="30"/>
+      <c r="C113" s="29"/>
+      <c r="D113" s="29"/>
     </row>
     <row r="114" spans="3:4">
-      <c r="C114" s="30"/>
-      <c r="D114" s="30"/>
+      <c r="C114" s="29"/>
+      <c r="D114" s="29"/>
     </row>
     <row r="115" spans="3:4">
-      <c r="C115" s="30"/>
-      <c r="D115" s="30"/>
+      <c r="C115" s="29"/>
+      <c r="D115" s="29"/>
     </row>
     <row r="116" spans="3:4">
-      <c r="C116" s="30"/>
-      <c r="D116" s="30"/>
+      <c r="C116" s="29"/>
+      <c r="D116" s="29"/>
     </row>
     <row r="117" spans="3:4">
-      <c r="C117" s="30"/>
-      <c r="D117" s="30"/>
+      <c r="C117" s="29"/>
+      <c r="D117" s="29"/>
     </row>
     <row r="118" spans="3:4">
-      <c r="C118" s="30"/>
-      <c r="D118" s="30"/>
+      <c r="C118" s="29"/>
+      <c r="D118" s="29"/>
     </row>
     <row r="119" spans="3:4">
-      <c r="C119" s="30"/>
-      <c r="D119" s="30"/>
+      <c r="C119" s="29"/>
+      <c r="D119" s="29"/>
     </row>
     <row r="120" spans="3:4">
-      <c r="C120" s="30"/>
-      <c r="D120" s="30"/>
+      <c r="C120" s="29"/>
+      <c r="D120" s="29"/>
     </row>
     <row r="121" spans="3:4">
-      <c r="C121" s="30"/>
-      <c r="D121" s="30"/>
+      <c r="C121" s="29"/>
+      <c r="D121" s="29"/>
     </row>
     <row r="122" spans="3:4">
-      <c r="C122" s="30"/>
-      <c r="D122" s="30"/>
+      <c r="C122" s="29"/>
+      <c r="D122" s="29"/>
     </row>
     <row r="123" spans="3:4">
-      <c r="C123" s="30"/>
-      <c r="D123" s="30"/>
+      <c r="C123" s="29"/>
+      <c r="D123" s="29"/>
     </row>
     <row r="124" spans="3:4">
-      <c r="C124" s="30"/>
-      <c r="D124" s="30"/>
+      <c r="C124" s="29"/>
+      <c r="D124" s="29"/>
     </row>
     <row r="125" spans="3:4">
-      <c r="C125" s="30"/>
-      <c r="D125" s="30"/>
+      <c r="C125" s="29"/>
+      <c r="D125" s="29"/>
     </row>
     <row r="126" spans="3:4">
-      <c r="C126" s="30"/>
-      <c r="D126" s="30"/>
+      <c r="C126" s="29"/>
+      <c r="D126" s="29"/>
     </row>
     <row r="127" spans="3:4">
-      <c r="C127" s="30"/>
-      <c r="D127" s="30"/>
+      <c r="C127" s="29"/>
+      <c r="D127" s="29"/>
     </row>
     <row r="128" spans="3:4">
-      <c r="C128" s="30"/>
-      <c r="D128" s="30"/>
+      <c r="C128" s="29"/>
+      <c r="D128" s="29"/>
     </row>
     <row r="129" spans="3:4">
-      <c r="C129" s="30"/>
-      <c r="D129" s="30"/>
+      <c r="C129" s="29"/>
+      <c r="D129" s="29"/>
     </row>
     <row r="130" spans="3:4">
-      <c r="C130" s="30"/>
-      <c r="D130" s="30"/>
+      <c r="C130" s="29"/>
+      <c r="D130" s="29"/>
     </row>
     <row r="131" spans="3:4">
-      <c r="C131" s="30"/>
-      <c r="D131" s="30"/>
+      <c r="C131" s="29"/>
+      <c r="D131" s="29"/>
     </row>
     <row r="132" spans="3:4">
-      <c r="C132" s="30"/>
-      <c r="D132" s="30"/>
+      <c r="C132" s="29"/>
+      <c r="D132" s="29"/>
     </row>
     <row r="133" spans="3:4">
-      <c r="C133" s="30"/>
-      <c r="D133" s="30"/>
+      <c r="C133" s="29"/>
+      <c r="D133" s="29"/>
     </row>
     <row r="134" spans="3:4">
-      <c r="C134" s="30"/>
-      <c r="D134" s="30"/>
+      <c r="C134" s="29"/>
+      <c r="D134" s="29"/>
     </row>
     <row r="135" spans="3:4">
-      <c r="C135" s="30"/>
-      <c r="D135" s="30"/>
+      <c r="C135" s="29"/>
+      <c r="D135" s="29"/>
     </row>
     <row r="136" spans="3:4">
-      <c r="C136" s="30"/>
-      <c r="D136" s="30"/>
+      <c r="C136" s="29"/>
+      <c r="D136" s="29"/>
     </row>
     <row r="137" spans="3:4">
-      <c r="C137" s="30"/>
-      <c r="D137" s="30"/>
+      <c r="C137" s="29"/>
+      <c r="D137" s="29"/>
     </row>
     <row r="138" spans="3:4">
-      <c r="C138" s="30"/>
-      <c r="D138" s="30"/>
+      <c r="C138" s="29"/>
+      <c r="D138" s="29"/>
     </row>
     <row r="139" spans="3:4">
-      <c r="C139" s="30"/>
-      <c r="D139" s="30"/>
+      <c r="C139" s="29"/>
+      <c r="D139" s="29"/>
     </row>
     <row r="140" spans="3:4">
-      <c r="C140" s="30"/>
-      <c r="D140" s="30"/>
+      <c r="C140" s="29"/>
+      <c r="D140" s="29"/>
     </row>
     <row r="141" spans="3:4">
-      <c r="C141" s="30"/>
-      <c r="D141" s="30"/>
+      <c r="C141" s="29"/>
+      <c r="D141" s="29"/>
     </row>
     <row r="142" spans="3:4">
-      <c r="C142" s="30"/>
-      <c r="D142" s="30"/>
+      <c r="C142" s="29"/>
+      <c r="D142" s="29"/>
     </row>
     <row r="143" spans="3:4">
-      <c r="C143" s="30"/>
-      <c r="D143" s="30"/>
+      <c r="C143" s="29"/>
+      <c r="D143" s="29"/>
     </row>
     <row r="144" spans="3:4">
-      <c r="C144" s="30"/>
-      <c r="D144" s="30"/>
+      <c r="C144" s="29"/>
+      <c r="D144" s="29"/>
     </row>
     <row r="145" spans="3:4">
-      <c r="C145" s="30"/>
-      <c r="D145" s="30"/>
+      <c r="C145" s="29"/>
+      <c r="D145" s="29"/>
     </row>
     <row r="146" spans="3:4">
-      <c r="C146" s="30"/>
-      <c r="D146" s="30"/>
+      <c r="C146" s="29"/>
+      <c r="D146" s="29"/>
     </row>
     <row r="147" spans="3:4">
-      <c r="C147" s="30"/>
-      <c r="D147" s="30"/>
+      <c r="C147" s="29"/>
+      <c r="D147" s="29"/>
     </row>
     <row r="148" spans="3:4">
-      <c r="C148" s="30"/>
-      <c r="D148" s="30"/>
+      <c r="C148" s="29"/>
+      <c r="D148" s="29"/>
     </row>
     <row r="149" spans="3:4">
-      <c r="C149" s="30"/>
-      <c r="D149" s="30"/>
+      <c r="C149" s="29"/>
+      <c r="D149" s="29"/>
     </row>
     <row r="150" spans="3:4">
-      <c r="C150" s="30"/>
-      <c r="D150" s="30"/>
+      <c r="C150" s="29"/>
+      <c r="D150" s="29"/>
     </row>
     <row r="151" spans="3:4">
-      <c r="C151" s="30"/>
-      <c r="D151" s="30"/>
+      <c r="C151" s="29"/>
+      <c r="D151" s="29"/>
     </row>
     <row r="152" spans="3:4">
-      <c r="C152" s="30"/>
-      <c r="D152" s="30"/>
+      <c r="C152" s="29"/>
+      <c r="D152" s="29"/>
     </row>
     <row r="153" spans="3:4">
-      <c r="C153" s="30"/>
-      <c r="D153" s="30"/>
+      <c r="C153" s="29"/>
+      <c r="D153" s="29"/>
     </row>
     <row r="154" spans="3:4">
-      <c r="C154" s="30"/>
-      <c r="D154" s="30"/>
+      <c r="C154" s="29"/>
+      <c r="D154" s="29"/>
     </row>
     <row r="155" spans="3:4">
-      <c r="C155" s="30"/>
-      <c r="D155" s="30"/>
+      <c r="C155" s="29"/>
+      <c r="D155" s="29"/>
     </row>
     <row r="156" spans="3:4">
-      <c r="C156" s="30"/>
-      <c r="D156" s="30"/>
+      <c r="C156" s="29"/>
+      <c r="D156" s="29"/>
     </row>
     <row r="157" spans="3:4">
-      <c r="C157" s="30"/>
-      <c r="D157" s="30"/>
+      <c r="C157" s="29"/>
+      <c r="D157" s="29"/>
     </row>
     <row r="158" spans="3:4">
-      <c r="C158" s="30"/>
-      <c r="D158" s="30"/>
+      <c r="C158" s="29"/>
+      <c r="D158" s="29"/>
     </row>
     <row r="159" spans="3:4">
-      <c r="C159" s="30"/>
-      <c r="D159" s="30"/>
+      <c r="C159" s="29"/>
+      <c r="D159" s="29"/>
     </row>
     <row r="160" spans="3:4">
-      <c r="C160" s="30"/>
-      <c r="D160" s="30"/>
+      <c r="C160" s="29"/>
+      <c r="D160" s="29"/>
     </row>
     <row r="161" spans="3:4">
-      <c r="C161" s="30"/>
-      <c r="D161" s="30"/>
+      <c r="C161" s="29"/>
+      <c r="D161" s="29"/>
     </row>
     <row r="162" spans="3:4">
-      <c r="C162" s="30"/>
-      <c r="D162" s="30"/>
+      <c r="C162" s="29"/>
+      <c r="D162" s="29"/>
     </row>
     <row r="163" spans="3:4">
-      <c r="C163" s="30"/>
-      <c r="D163" s="30"/>
+      <c r="C163" s="29"/>
+      <c r="D163" s="29"/>
     </row>
     <row r="164" spans="3:4">
-      <c r="C164" s="30"/>
-      <c r="D164" s="30"/>
+      <c r="C164" s="29"/>
+      <c r="D164" s="29"/>
     </row>
     <row r="165" spans="3:4">
-      <c r="C165" s="30"/>
-      <c r="D165" s="30"/>
+      <c r="C165" s="29"/>
+      <c r="D165" s="29"/>
     </row>
     <row r="166" spans="3:4">
-      <c r="C166" s="30"/>
-      <c r="D166" s="30"/>
+      <c r="C166" s="29"/>
+      <c r="D166" s="29"/>
     </row>
     <row r="167" spans="3:4">
-      <c r="C167" s="30"/>
-      <c r="D167" s="30"/>
+      <c r="C167" s="29"/>
+      <c r="D167" s="29"/>
     </row>
     <row r="168" spans="3:4">
-      <c r="C168" s="30"/>
-      <c r="D168" s="30"/>
+      <c r="C168" s="29"/>
+      <c r="D168" s="29"/>
     </row>
     <row r="169" spans="3:4">
-      <c r="C169" s="30"/>
-      <c r="D169" s="30"/>
+      <c r="C169" s="29"/>
+      <c r="D169" s="29"/>
     </row>
     <row r="170" spans="3:4">
-      <c r="C170" s="30"/>
-      <c r="D170" s="30"/>
+      <c r="C170" s="29"/>
+      <c r="D170" s="29"/>
     </row>
     <row r="171" spans="3:4">
-      <c r="C171" s="30"/>
-      <c r="D171" s="30"/>
+      <c r="C171" s="29"/>
+      <c r="D171" s="29"/>
     </row>
     <row r="172" spans="3:4">
-      <c r="C172" s="30"/>
-      <c r="D172" s="30"/>
+      <c r="C172" s="29"/>
+      <c r="D172" s="29"/>
     </row>
     <row r="173" spans="3:4">
-      <c r="C173" s="30"/>
-      <c r="D173" s="30"/>
+      <c r="C173" s="29"/>
+      <c r="D173" s="29"/>
     </row>
     <row r="174" spans="3:4">
-      <c r="C174" s="30"/>
-      <c r="D174" s="30"/>
+      <c r="C174" s="29"/>
+      <c r="D174" s="29"/>
     </row>
     <row r="175" spans="3:4">
-      <c r="C175" s="30"/>
-      <c r="D175" s="30"/>
+      <c r="C175" s="29"/>
+      <c r="D175" s="29"/>
     </row>
     <row r="176" spans="3:4">
-      <c r="C176" s="30"/>
-      <c r="D176" s="30"/>
+      <c r="C176" s="29"/>
+      <c r="D176" s="29"/>
     </row>
     <row r="177" spans="3:4">
-      <c r="C177" s="30"/>
-      <c r="D177" s="30"/>
+      <c r="C177" s="29"/>
+      <c r="D177" s="29"/>
     </row>
     <row r="178" spans="3:4">
-      <c r="C178" s="30"/>
-      <c r="D178" s="30"/>
+      <c r="C178" s="29"/>
+      <c r="D178" s="29"/>
     </row>
     <row r="179" spans="3:4">
-      <c r="C179" s="30"/>
-      <c r="D179" s="30"/>
+      <c r="C179" s="29"/>
+      <c r="D179" s="29"/>
     </row>
     <row r="180" spans="3:4">
-      <c r="C180" s="30"/>
-      <c r="D180" s="30"/>
+      <c r="C180" s="29"/>
+      <c r="D180" s="29"/>
     </row>
     <row r="181" spans="3:4">
-      <c r="C181" s="30"/>
-      <c r="D181" s="30"/>
+      <c r="C181" s="29"/>
+      <c r="D181" s="29"/>
     </row>
     <row r="182" spans="3:4">
-      <c r="C182" s="30"/>
-      <c r="D182" s="30"/>
+      <c r="C182" s="29"/>
+      <c r="D182" s="29"/>
     </row>
     <row r="183" spans="3:4">
-      <c r="C183" s="30"/>
-      <c r="D183" s="30"/>
+      <c r="C183" s="29"/>
+      <c r="D183" s="29"/>
     </row>
     <row r="184" spans="3:4">
-      <c r="C184" s="30"/>
-      <c r="D184" s="30"/>
+      <c r="C184" s="29"/>
+      <c r="D184" s="29"/>
     </row>
     <row r="185" spans="3:4">
-      <c r="C185" s="30"/>
-      <c r="D185" s="30"/>
+      <c r="C185" s="29"/>
+      <c r="D185" s="29"/>
     </row>
     <row r="186" spans="3:4">
-      <c r="C186" s="30"/>
-      <c r="D186" s="30"/>
+      <c r="C186" s="29"/>
+      <c r="D186" s="29"/>
     </row>
     <row r="187" spans="3:4">
-      <c r="C187" s="30"/>
-      <c r="D187" s="30"/>
+      <c r="C187" s="29"/>
+      <c r="D187" s="29"/>
     </row>
     <row r="188" spans="3:4">
-      <c r="C188" s="30"/>
-      <c r="D188" s="30"/>
+      <c r="C188" s="29"/>
+      <c r="D188" s="29"/>
     </row>
     <row r="189" spans="3:4">
-      <c r="C189" s="30"/>
-      <c r="D189" s="30"/>
+      <c r="C189" s="29"/>
+      <c r="D189" s="29"/>
     </row>
     <row r="190" spans="3:4">
-      <c r="C190" s="30"/>
-      <c r="D190" s="30"/>
+      <c r="C190" s="29"/>
+      <c r="D190" s="29"/>
     </row>
     <row r="191" spans="3:4">
-      <c r="C191" s="30"/>
-      <c r="D191" s="30"/>
+      <c r="C191" s="29"/>
+      <c r="D191" s="29"/>
     </row>
     <row r="192" spans="3:4">
-      <c r="C192" s="30"/>
-      <c r="D192" s="30"/>
+      <c r="C192" s="29"/>
+      <c r="D192" s="29"/>
     </row>
     <row r="193" spans="3:4">
-      <c r="C193" s="30"/>
-      <c r="D193" s="30"/>
+      <c r="C193" s="29"/>
+      <c r="D193" s="29"/>
     </row>
     <row r="194" spans="3:4">
-      <c r="C194" s="30"/>
-      <c r="D194" s="30"/>
+      <c r="C194" s="29"/>
+      <c r="D194" s="29"/>
     </row>
     <row r="195" spans="3:4">
-      <c r="C195" s="30"/>
-      <c r="D195" s="30"/>
+      <c r="C195" s="29"/>
+      <c r="D195" s="29"/>
     </row>
     <row r="196" spans="3:4">
-      <c r="C196" s="30"/>
-      <c r="D196" s="30"/>
+      <c r="C196" s="29"/>
+      <c r="D196" s="29"/>
     </row>
     <row r="197" spans="3:4">
-      <c r="C197" s="30"/>
-      <c r="D197" s="30"/>
+      <c r="C197" s="29"/>
+      <c r="D197" s="29"/>
     </row>
     <row r="198" spans="3:4">
-      <c r="C198" s="30"/>
-      <c r="D198" s="30"/>
+      <c r="C198" s="29"/>
+      <c r="D198" s="29"/>
     </row>
     <row r="199" spans="3:4">
-      <c r="C199" s="30"/>
-      <c r="D199" s="30"/>
+      <c r="C199" s="29"/>
+      <c r="D199" s="29"/>
     </row>
     <row r="200" spans="3:4">
-      <c r="C200" s="30"/>
-      <c r="D200" s="30"/>
+      <c r="C200" s="29"/>
+      <c r="D200" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5705,6 +5702,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5715,15 +5721,6 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5980,20 +5977,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5E2E3CC-A260-4216-891E-591C22F5C5DB}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E6AC9C9-F318-4838-B7C2-7323EB448754}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -993,29 +993,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1396,31 +1396,31 @@
       <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1458,7 +1458,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="77" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="58" t="s">
@@ -1478,14 +1478,14 @@
       <c r="H5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="77">
+      <c r="I5" s="71">
         <v>46244</v>
       </c>
-      <c r="J5" s="77"/>
+      <c r="J5" s="71"/>
       <c r="K5" s="47"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="71"/>
+      <c r="A6" s="74"/>
       <c r="B6" s="44" t="s">
         <v>13</v>
       </c>
@@ -1503,12 +1503,12 @@
       <c r="H6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="73"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="70"/>
       <c r="K6" s="48"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="73" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="38" t="s">
@@ -1528,14 +1528,14 @@
       <c r="H7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="72" t="s">
+      <c r="I7" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="72"/>
+      <c r="J7" s="69"/>
       <c r="K7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="71"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="35" t="s">
         <v>13</v>
       </c>
@@ -1553,12 +1553,12 @@
       <c r="H8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="71"/>
-      <c r="J8" s="73"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="70"/>
       <c r="K8" s="48"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="73" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="38" t="s">
@@ -1578,14 +1578,14 @@
       <c r="H9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="72">
+      <c r="I9" s="69">
         <v>46218</v>
       </c>
-      <c r="J9" s="72"/>
+      <c r="J9" s="69"/>
       <c r="K9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="71"/>
+      <c r="A10" s="74"/>
       <c r="B10" s="35" t="s">
         <v>13</v>
       </c>
@@ -1603,12 +1603,12 @@
       <c r="H10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="71"/>
-      <c r="J10" s="73"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="70"/>
       <c r="K10" s="48"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="73" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="41" t="s">
@@ -1628,14 +1628,14 @@
       <c r="H11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="72">
+      <c r="I11" s="69">
         <v>46171</v>
       </c>
-      <c r="J11" s="72"/>
+      <c r="J11" s="69"/>
       <c r="K11" s="49"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="71"/>
+      <c r="A12" s="74"/>
       <c r="B12" s="44" t="s">
         <v>13</v>
       </c>
@@ -1653,12 +1653,12 @@
       <c r="H12" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="71"/>
-      <c r="J12" s="73"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="70"/>
       <c r="K12" s="48"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="73" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="38" t="s">
@@ -1678,14 +1678,14 @@
       <c r="H13" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="72" t="s">
+      <c r="I13" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="72"/>
+      <c r="J13" s="69"/>
       <c r="K13" s="49"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="71"/>
+      <c r="A14" s="74"/>
       <c r="B14" s="35" t="s">
         <v>13</v>
       </c>
@@ -1703,12 +1703,12 @@
       <c r="H14" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="71"/>
-      <c r="J14" s="73"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="70"/>
       <c r="K14" s="48"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="73" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="41" t="s">
@@ -1728,14 +1728,14 @@
       <c r="H15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="72">
+      <c r="I15" s="69">
         <v>46199</v>
       </c>
-      <c r="J15" s="72"/>
+      <c r="J15" s="69"/>
       <c r="K15" s="49"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="71"/>
+      <c r="A16" s="74"/>
       <c r="B16" s="44" t="s">
         <v>13</v>
       </c>
@@ -1753,8 +1753,8 @@
       <c r="H16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="71"/>
-      <c r="J16" s="73"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="70"/>
       <c r="K16" s="48"/>
     </row>
     <row r="17" spans="1:11">
@@ -1778,14 +1778,14 @@
       <c r="H17" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="74">
+      <c r="I17" s="72">
         <v>46305</v>
       </c>
-      <c r="J17" s="74"/>
+      <c r="J17" s="72"/>
       <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="71"/>
+      <c r="A18" s="74"/>
       <c r="B18" s="35" t="s">
         <v>13</v>
       </c>
@@ -1803,8 +1803,8 @@
       <c r="H18" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="71"/>
-      <c r="J18" s="73"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="70"/>
       <c r="K18" s="48"/>
     </row>
     <row r="19" spans="1:11">
@@ -1828,14 +1828,14 @@
       <c r="H19" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="74">
+      <c r="I19" s="72">
         <v>46336</v>
       </c>
-      <c r="J19" s="74"/>
+      <c r="J19" s="72"/>
       <c r="K19" s="50"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="71"/>
+      <c r="A20" s="74"/>
       <c r="B20" s="35" t="s">
         <v>13</v>
       </c>
@@ -1853,12 +1853,12 @@
       <c r="H20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="71"/>
-      <c r="J20" s="73"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="70"/>
       <c r="K20" s="48"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="73" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="38" t="s">
@@ -1878,14 +1878,14 @@
       <c r="H21" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="72">
+      <c r="I21" s="69">
         <v>46336</v>
       </c>
-      <c r="J21" s="72"/>
+      <c r="J21" s="69"/>
       <c r="K21" s="51"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="71"/>
+      <c r="A22" s="74"/>
       <c r="B22" s="35" t="s">
         <v>13</v>
       </c>
@@ -1903,12 +1903,12 @@
       <c r="H22" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="71"/>
-      <c r="J22" s="73"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="70"/>
       <c r="K22" s="52"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="70" t="s">
+      <c r="A23" s="73" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="41" t="s">
@@ -1928,14 +1928,14 @@
       <c r="H23" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="72">
+      <c r="I23" s="69">
         <v>46237</v>
       </c>
-      <c r="J23" s="72"/>
+      <c r="J23" s="69"/>
       <c r="K23" s="51"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="71"/>
+      <c r="A24" s="74"/>
       <c r="B24" s="44" t="s">
         <v>13</v>
       </c>
@@ -1953,12 +1953,12 @@
       <c r="H24" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="71"/>
-      <c r="J24" s="73"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="70"/>
       <c r="K24" s="52"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="70" t="s">
+      <c r="A25" s="73" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="41" t="s">
@@ -1978,14 +1978,14 @@
       <c r="H25" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="72">
+      <c r="I25" s="69">
         <v>46188</v>
       </c>
-      <c r="J25" s="72"/>
+      <c r="J25" s="69"/>
       <c r="K25" s="51"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="71"/>
+      <c r="A26" s="74"/>
       <c r="B26" s="44" t="s">
         <v>13</v>
       </c>
@@ -2003,12 +2003,12 @@
       <c r="H26" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="71"/>
-      <c r="J26" s="73"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="70"/>
       <c r="K26" s="52"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="73" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="38" t="s">
@@ -2028,14 +2028,14 @@
       <c r="H27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="72">
+      <c r="I27" s="69">
         <v>46321</v>
       </c>
-      <c r="J27" s="72"/>
+      <c r="J27" s="69"/>
       <c r="K27" s="51"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="71"/>
+      <c r="A28" s="74"/>
       <c r="B28" s="35" t="s">
         <v>13</v>
       </c>
@@ -2053,12 +2053,12 @@
       <c r="H28" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="71"/>
-      <c r="J28" s="73"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="70"/>
       <c r="K28" s="52"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="73" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="41" t="s">
@@ -2078,14 +2078,14 @@
       <c r="H29" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="72">
+      <c r="I29" s="69">
         <v>46139</v>
       </c>
-      <c r="J29" s="72"/>
+      <c r="J29" s="69"/>
       <c r="K29" s="51"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="71"/>
+      <c r="A30" s="74"/>
       <c r="B30" s="44" t="s">
         <v>13</v>
       </c>
@@ -2103,12 +2103,12 @@
       <c r="H30" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="71"/>
-      <c r="J30" s="73"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="70"/>
       <c r="K30" s="52"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="70" t="s">
+      <c r="A31" s="73" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="41" t="s">
@@ -2128,14 +2128,14 @@
       <c r="H31" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="72">
+      <c r="I31" s="69">
         <v>46133</v>
       </c>
-      <c r="J31" s="72"/>
+      <c r="J31" s="69"/>
       <c r="K31" s="51"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="71"/>
+      <c r="A32" s="74"/>
       <c r="B32" s="44" t="s">
         <v>13</v>
       </c>
@@ -2153,12 +2153,12 @@
       <c r="H32" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="71"/>
-      <c r="J32" s="73"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="70"/>
       <c r="K32" s="52"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="70" t="s">
+      <c r="A33" s="73" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="38" t="s">
@@ -2178,14 +2178,14 @@
       <c r="H33" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="72">
+      <c r="I33" s="69">
         <v>46295</v>
       </c>
-      <c r="J33" s="72"/>
+      <c r="J33" s="69"/>
       <c r="K33" s="51"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="71"/>
+      <c r="A34" s="74"/>
       <c r="B34" s="35" t="s">
         <v>13</v>
       </c>
@@ -2203,12 +2203,12 @@
       <c r="H34" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="71"/>
-      <c r="J34" s="73"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="70"/>
       <c r="K34" s="52"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="73" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="38" t="s">
@@ -2228,14 +2228,14 @@
       <c r="H35" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="72">
+      <c r="I35" s="69">
         <v>45884</v>
       </c>
-      <c r="J35" s="72"/>
+      <c r="J35" s="69"/>
       <c r="K35" s="51"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="71"/>
+      <c r="A36" s="74"/>
       <c r="B36" s="35" t="s">
         <v>13</v>
       </c>
@@ -2253,12 +2253,12 @@
       <c r="H36" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="71"/>
-      <c r="J36" s="73"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="70"/>
       <c r="K36" s="52"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="70" t="s">
+      <c r="A37" s="73" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="38" t="s">
@@ -2278,14 +2278,14 @@
       <c r="H37" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="72">
+      <c r="I37" s="69">
         <v>45915</v>
       </c>
-      <c r="J37" s="72"/>
+      <c r="J37" s="69"/>
       <c r="K37" s="51"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="71"/>
+      <c r="A38" s="74"/>
       <c r="B38" s="35" t="s">
         <v>13</v>
       </c>
@@ -2303,12 +2303,12 @@
       <c r="H38" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="71"/>
-      <c r="J38" s="73"/>
+      <c r="I38" s="74"/>
+      <c r="J38" s="70"/>
       <c r="K38" s="52"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="73" t="s">
         <v>91</v>
       </c>
       <c r="B39" s="38" t="s">
@@ -2324,12 +2324,12 @@
       <c r="H39" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="72"/>
-      <c r="J39" s="72"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
       <c r="K39" s="51"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="71"/>
+      <c r="A40" s="74"/>
       <c r="B40" s="55" t="s">
         <v>13</v>
       </c>
@@ -2343,12 +2343,12 @@
       <c r="H40" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="I40" s="71"/>
-      <c r="J40" s="73"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="70"/>
       <c r="K40" s="52"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="73" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="38" t="s">
@@ -2368,14 +2368,14 @@
       <c r="H41" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="72">
+      <c r="I41" s="69">
         <v>46234</v>
       </c>
-      <c r="J41" s="72"/>
+      <c r="J41" s="69"/>
       <c r="K41" s="51"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="71"/>
+      <c r="A42" s="74"/>
       <c r="B42" s="55" t="s">
         <v>13</v>
       </c>
@@ -2385,12 +2385,12 @@
       <c r="F42" s="56"/>
       <c r="G42" s="57"/>
       <c r="H42" s="55"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="73"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="70"/>
       <c r="K42" s="52"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="70" t="s">
+      <c r="A43" s="73" t="s">
         <v>136</v>
       </c>
       <c r="B43" s="38" t="s">
@@ -2404,14 +2404,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="I43" s="72"/>
-      <c r="J43" s="72"/>
+        <v>22</v>
+      </c>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
       <c r="K43" s="51"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="71"/>
+      <c r="A44" s="74"/>
       <c r="B44" s="55" t="s">
         <v>13</v>
       </c>
@@ -2423,28 +2423,46 @@
         <v>0</v>
       </c>
       <c r="H44" s="55" t="s">
-        <v>138</v>
-      </c>
-      <c r="I44" s="71"/>
-      <c r="J44" s="73"/>
+        <v>22</v>
+      </c>
+      <c r="I44" s="74"/>
+      <c r="J44" s="70"/>
       <c r="K44" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2461,40 +2479,22 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -2555,30 +2555,30 @@
       <c r="V1" s="67"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -3617,7 +3617,7 @@
         <v>91</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>67</v>
@@ -3719,7 +3719,7 @@
         <v>136</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>67</v>
@@ -4299,16 +4299,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="67"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4777,13 +4777,13 @@
       <c r="E1" s="67"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5702,15 +5702,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -5721,6 +5712,15 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5977,20 +5977,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E6AC9C9-F318-4838-B7C2-7323EB448754}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD90073-5B89-4B92-979D-15C2FE4D8674}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,12 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Internal Work'!$A$4:$E$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Schedule'!$A$4:$K$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Site Visit Log'!$A$4:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary Report'!$A$4:$V$189</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="143">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -464,10 +470,13 @@
     <t>Huaykwang residence</t>
   </si>
   <si>
-    <t>ส่งมอบงานงวดสุดท้าย</t>
-  </si>
-  <si>
     <t>คิดงานเพิ่ม 3000 บาท ค่ากล่องพรีนัม ส่งงานวันที่ 07/31/2026</t>
+  </si>
+  <si>
+    <t>ประชุม,คุยงานนัด Owner เข้า Pretest</t>
+  </si>
+  <si>
+    <t>บริษัท อีโค่คูล ไครลเมท เทคโนโลยี จำกัด</t>
   </si>
 </sst>
 </file>
@@ -994,28 +1003,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1396,31 +1405,31 @@
       <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1458,7 +1467,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="76" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="58" t="s">
@@ -1478,14 +1487,14 @@
       <c r="H5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="71">
+      <c r="I5" s="77">
         <v>46244</v>
       </c>
-      <c r="J5" s="71"/>
+      <c r="J5" s="77"/>
       <c r="K5" s="47"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="74"/>
+      <c r="A6" s="70"/>
       <c r="B6" s="44" t="s">
         <v>13</v>
       </c>
@@ -1503,12 +1512,12 @@
       <c r="H6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="72"/>
       <c r="K6" s="48"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="69" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="38" t="s">
@@ -1528,14 +1537,14 @@
       <c r="H7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="69" t="s">
+      <c r="I7" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="71"/>
       <c r="K7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="74"/>
+      <c r="A8" s="70"/>
       <c r="B8" s="35" t="s">
         <v>13</v>
       </c>
@@ -1553,12 +1562,12 @@
       <c r="H8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="74"/>
-      <c r="J8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="72"/>
       <c r="K8" s="48"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="69" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="38" t="s">
@@ -1578,14 +1587,14 @@
       <c r="H9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="69">
+      <c r="I9" s="71">
         <v>46218</v>
       </c>
-      <c r="J9" s="69"/>
+      <c r="J9" s="71"/>
       <c r="K9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="74"/>
+      <c r="A10" s="70"/>
       <c r="B10" s="35" t="s">
         <v>13</v>
       </c>
@@ -1603,12 +1612,12 @@
       <c r="H10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="74"/>
-      <c r="J10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="72"/>
       <c r="K10" s="48"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="69" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="41" t="s">
@@ -1628,14 +1637,14 @@
       <c r="H11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="69">
+      <c r="I11" s="71">
         <v>46171</v>
       </c>
-      <c r="J11" s="69"/>
+      <c r="J11" s="71"/>
       <c r="K11" s="49"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="74"/>
+      <c r="A12" s="70"/>
       <c r="B12" s="44" t="s">
         <v>13</v>
       </c>
@@ -1653,12 +1662,12 @@
       <c r="H12" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="74"/>
-      <c r="J12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="72"/>
       <c r="K12" s="48"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="69" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="38" t="s">
@@ -1678,14 +1687,14 @@
       <c r="H13" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="69" t="s">
+      <c r="I13" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="69"/>
+      <c r="J13" s="71"/>
       <c r="K13" s="49"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="74"/>
+      <c r="A14" s="70"/>
       <c r="B14" s="35" t="s">
         <v>13</v>
       </c>
@@ -1703,12 +1712,12 @@
       <c r="H14" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="74"/>
-      <c r="J14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="72"/>
       <c r="K14" s="48"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="69" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="41" t="s">
@@ -1728,14 +1737,14 @@
       <c r="H15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="69">
+      <c r="I15" s="71">
         <v>46199</v>
       </c>
-      <c r="J15" s="69"/>
+      <c r="J15" s="71"/>
       <c r="K15" s="49"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="74"/>
+      <c r="A16" s="70"/>
       <c r="B16" s="44" t="s">
         <v>13</v>
       </c>
@@ -1753,8 +1762,8 @@
       <c r="H16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="74"/>
-      <c r="J16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="72"/>
       <c r="K16" s="48"/>
     </row>
     <row r="17" spans="1:11">
@@ -1778,14 +1787,14 @@
       <c r="H17" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="72">
+      <c r="I17" s="74">
         <v>46305</v>
       </c>
-      <c r="J17" s="72"/>
+      <c r="J17" s="74"/>
       <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="74"/>
+      <c r="A18" s="70"/>
       <c r="B18" s="35" t="s">
         <v>13</v>
       </c>
@@ -1803,8 +1812,8 @@
       <c r="H18" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="74"/>
-      <c r="J18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="72"/>
       <c r="K18" s="48"/>
     </row>
     <row r="19" spans="1:11">
@@ -1828,14 +1837,14 @@
       <c r="H19" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="72">
+      <c r="I19" s="74">
         <v>46336</v>
       </c>
-      <c r="J19" s="72"/>
+      <c r="J19" s="74"/>
       <c r="K19" s="50"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="74"/>
+      <c r="A20" s="70"/>
       <c r="B20" s="35" t="s">
         <v>13</v>
       </c>
@@ -1853,12 +1862,12 @@
       <c r="H20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="74"/>
-      <c r="J20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="72"/>
       <c r="K20" s="48"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="69" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="38" t="s">
@@ -1878,14 +1887,14 @@
       <c r="H21" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="69">
+      <c r="I21" s="71">
         <v>46336</v>
       </c>
-      <c r="J21" s="69"/>
+      <c r="J21" s="71"/>
       <c r="K21" s="51"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="74"/>
+      <c r="A22" s="70"/>
       <c r="B22" s="35" t="s">
         <v>13</v>
       </c>
@@ -1903,12 +1912,12 @@
       <c r="H22" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="74"/>
-      <c r="J22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="72"/>
       <c r="K22" s="52"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="69" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="41" t="s">
@@ -1928,14 +1937,14 @@
       <c r="H23" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="69">
+      <c r="I23" s="71">
         <v>46237</v>
       </c>
-      <c r="J23" s="69"/>
+      <c r="J23" s="71"/>
       <c r="K23" s="51"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="74"/>
+      <c r="A24" s="70"/>
       <c r="B24" s="44" t="s">
         <v>13</v>
       </c>
@@ -1953,12 +1962,12 @@
       <c r="H24" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="74"/>
-      <c r="J24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="72"/>
       <c r="K24" s="52"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="69" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="41" t="s">
@@ -1978,14 +1987,14 @@
       <c r="H25" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="69">
+      <c r="I25" s="71">
         <v>46188</v>
       </c>
-      <c r="J25" s="69"/>
+      <c r="J25" s="71"/>
       <c r="K25" s="51"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="74"/>
+      <c r="A26" s="70"/>
       <c r="B26" s="44" t="s">
         <v>13</v>
       </c>
@@ -2003,12 +2012,12 @@
       <c r="H26" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="74"/>
-      <c r="J26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="72"/>
       <c r="K26" s="52"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="73" t="s">
+      <c r="A27" s="69" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="38" t="s">
@@ -2028,14 +2037,14 @@
       <c r="H27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="69">
+      <c r="I27" s="71">
         <v>46321</v>
       </c>
-      <c r="J27" s="69"/>
+      <c r="J27" s="71"/>
       <c r="K27" s="51"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="74"/>
+      <c r="A28" s="70"/>
       <c r="B28" s="35" t="s">
         <v>13</v>
       </c>
@@ -2053,12 +2062,12 @@
       <c r="H28" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="74"/>
-      <c r="J28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="72"/>
       <c r="K28" s="52"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="73" t="s">
+      <c r="A29" s="69" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="41" t="s">
@@ -2078,14 +2087,14 @@
       <c r="H29" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="69">
+      <c r="I29" s="71">
         <v>46139</v>
       </c>
-      <c r="J29" s="69"/>
+      <c r="J29" s="71"/>
       <c r="K29" s="51"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="74"/>
+      <c r="A30" s="70"/>
       <c r="B30" s="44" t="s">
         <v>13</v>
       </c>
@@ -2103,12 +2112,12 @@
       <c r="H30" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="74"/>
-      <c r="J30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="72"/>
       <c r="K30" s="52"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="73" t="s">
+      <c r="A31" s="69" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="41" t="s">
@@ -2128,14 +2137,14 @@
       <c r="H31" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="69">
+      <c r="I31" s="71">
         <v>46133</v>
       </c>
-      <c r="J31" s="69"/>
+      <c r="J31" s="71"/>
       <c r="K31" s="51"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="74"/>
+      <c r="A32" s="70"/>
       <c r="B32" s="44" t="s">
         <v>13</v>
       </c>
@@ -2153,12 +2162,12 @@
       <c r="H32" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="74"/>
-      <c r="J32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="72"/>
       <c r="K32" s="52"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="69" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="38" t="s">
@@ -2178,14 +2187,14 @@
       <c r="H33" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="69">
+      <c r="I33" s="71">
         <v>46295</v>
       </c>
-      <c r="J33" s="69"/>
+      <c r="J33" s="71"/>
       <c r="K33" s="51"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="74"/>
+      <c r="A34" s="70"/>
       <c r="B34" s="35" t="s">
         <v>13</v>
       </c>
@@ -2203,12 +2212,12 @@
       <c r="H34" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="74"/>
-      <c r="J34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="72"/>
       <c r="K34" s="52"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="69" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="38" t="s">
@@ -2228,14 +2237,14 @@
       <c r="H35" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="69">
+      <c r="I35" s="71">
         <v>45884</v>
       </c>
-      <c r="J35" s="69"/>
+      <c r="J35" s="71"/>
       <c r="K35" s="51"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="74"/>
+      <c r="A36" s="70"/>
       <c r="B36" s="35" t="s">
         <v>13</v>
       </c>
@@ -2253,12 +2262,12 @@
       <c r="H36" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="74"/>
-      <c r="J36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="72"/>
       <c r="K36" s="52"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="69" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="38" t="s">
@@ -2278,14 +2287,14 @@
       <c r="H37" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="69">
+      <c r="I37" s="71">
         <v>45915</v>
       </c>
-      <c r="J37" s="69"/>
+      <c r="J37" s="71"/>
       <c r="K37" s="51"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="74"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="35" t="s">
         <v>13</v>
       </c>
@@ -2303,12 +2312,12 @@
       <c r="H38" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="74"/>
-      <c r="J38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="72"/>
       <c r="K38" s="52"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="69" t="s">
         <v>91</v>
       </c>
       <c r="B39" s="38" t="s">
@@ -2324,12 +2333,12 @@
       <c r="H39" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
       <c r="K39" s="51"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="74"/>
+      <c r="A40" s="70"/>
       <c r="B40" s="55" t="s">
         <v>13</v>
       </c>
@@ -2343,12 +2352,12 @@
       <c r="H40" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="I40" s="74"/>
-      <c r="J40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="72"/>
       <c r="K40" s="52"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="73" t="s">
+      <c r="A41" s="69" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="38" t="s">
@@ -2368,14 +2377,14 @@
       <c r="H41" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="69">
+      <c r="I41" s="71">
         <v>46234</v>
       </c>
-      <c r="J41" s="69"/>
+      <c r="J41" s="71"/>
       <c r="K41" s="51"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="74"/>
+      <c r="A42" s="70"/>
       <c r="B42" s="55" t="s">
         <v>13</v>
       </c>
@@ -2385,12 +2394,12 @@
       <c r="F42" s="56"/>
       <c r="G42" s="57"/>
       <c r="H42" s="55"/>
-      <c r="I42" s="74"/>
-      <c r="J42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="72"/>
       <c r="K42" s="52"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="69" t="s">
         <v>136</v>
       </c>
       <c r="B43" s="38" t="s">
@@ -2406,12 +2415,12 @@
       <c r="H43" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I43" s="69"/>
-      <c r="J43" s="69"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
       <c r="K43" s="51"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="74"/>
+      <c r="A44" s="70"/>
       <c r="B44" s="55" t="s">
         <v>13</v>
       </c>
@@ -2425,21 +2434,50 @@
       <c r="H44" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="74"/>
-      <c r="J44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="72"/>
       <c r="K44" s="52"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:K44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="62">
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2456,43 +2494,15 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3523,7 +3533,9 @@
       <c r="D20" s="15">
         <v>0.9</v>
       </c>
-      <c r="E20" s="23"/>
+      <c r="E20" s="23">
+        <v>341236.34</v>
+      </c>
       <c r="F20" s="24"/>
       <c r="G20" s="9">
         <v>255</v>
@@ -3538,7 +3550,12 @@
       <c r="N20" s="9">
         <v>0</v>
       </c>
-      <c r="P20" s="10"/>
+      <c r="O20" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="P20" s="10">
+        <v>228548</v>
+      </c>
       <c r="Q20" s="19">
         <v>45717</v>
       </c>
@@ -3564,6 +3581,9 @@
       <c r="D21" s="15">
         <v>0.9</v>
       </c>
+      <c r="E21" s="16">
+        <v>666700</v>
+      </c>
       <c r="F21" s="24"/>
       <c r="I21" s="9">
         <v>6</v>
@@ -3574,7 +3594,12 @@
       <c r="N21" s="9">
         <v>0</v>
       </c>
-      <c r="P21" s="10"/>
+      <c r="O21" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="P21" s="10">
+        <v>224227</v>
+      </c>
       <c r="Q21" s="19">
         <v>45717</v>
       </c>
@@ -3705,7 +3730,7 @@
         <v>46234</v>
       </c>
       <c r="T24" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U24" s="31" t="s">
         <v>129</v>
@@ -4250,11 +4275,12 @@
       <c r="V189" s="19"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:V189" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="B5:B40" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -4299,16 +4325,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="67"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="68" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="68"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4724,7 +4750,7 @@
         <v>61</v>
       </c>
       <c r="D29" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="s">
         <v>124</v>
@@ -4734,20 +4760,21 @@
       <c r="A30" s="3">
         <v>46230</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>100</v>
+      <c r="B30" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="C30" s="65" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E30" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -5688,6 +5715,7 @@
       <c r="D200" s="29"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E200" xr:uid="{0CACF7FE-A4AF-4302-B8F5-800998C4C21C}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -5715,15 +5743,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5976,6 +5995,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
   <ds:schemaRefs>
@@ -5988,14 +6016,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6012,4 +6032,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD90073-5B89-4B92-979D-15C2FE4D8674}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3108" yWindow="756" windowWidth="14988" windowHeight="11484" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD90073-5B89-4B92-979D-15C2FE4D8674}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA74708-4782-4A89-80A6-2A2930F6DA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3108" yWindow="756" windowWidth="14988" windowHeight="11484" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -1003,28 +1003,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1405,31 +1405,31 @@
       <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
     </row>
     <row r="4" spans="1:11" ht="27.6">
       <c r="A4" s="1" t="s">
@@ -1467,7 +1467,7 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="77" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="58" t="s">
@@ -1487,14 +1487,14 @@
       <c r="H5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="77">
+      <c r="I5" s="71">
         <v>46244</v>
       </c>
-      <c r="J5" s="77"/>
+      <c r="J5" s="71"/>
       <c r="K5" s="47"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="70"/>
+      <c r="A6" s="74"/>
       <c r="B6" s="44" t="s">
         <v>13</v>
       </c>
@@ -1512,12 +1512,12 @@
       <c r="H6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="72"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="70"/>
       <c r="K6" s="48"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="73" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="38" t="s">
@@ -1537,14 +1537,14 @@
       <c r="H7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="71" t="s">
+      <c r="I7" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="71"/>
+      <c r="J7" s="69"/>
       <c r="K7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="70"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="35" t="s">
         <v>13</v>
       </c>
@@ -1562,12 +1562,12 @@
       <c r="H8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="70"/>
-      <c r="J8" s="72"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="70"/>
       <c r="K8" s="48"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="73" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="38" t="s">
@@ -1587,14 +1587,14 @@
       <c r="H9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="71">
+      <c r="I9" s="69">
         <v>46218</v>
       </c>
-      <c r="J9" s="71"/>
+      <c r="J9" s="69"/>
       <c r="K9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="70"/>
+      <c r="A10" s="74"/>
       <c r="B10" s="35" t="s">
         <v>13</v>
       </c>
@@ -1612,12 +1612,12 @@
       <c r="H10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="70"/>
-      <c r="J10" s="72"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="70"/>
       <c r="K10" s="48"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="73" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="41" t="s">
@@ -1637,14 +1637,14 @@
       <c r="H11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="71">
+      <c r="I11" s="69">
         <v>46171</v>
       </c>
-      <c r="J11" s="71"/>
+      <c r="J11" s="69"/>
       <c r="K11" s="49"/>
     </row>
     <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="70"/>
+      <c r="A12" s="74"/>
       <c r="B12" s="44" t="s">
         <v>13</v>
       </c>
@@ -1662,12 +1662,12 @@
       <c r="H12" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="70"/>
-      <c r="J12" s="72"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="70"/>
       <c r="K12" s="48"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="69" t="s">
+      <c r="A13" s="73" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="38" t="s">
@@ -1687,14 +1687,14 @@
       <c r="H13" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="71" t="s">
+      <c r="I13" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="71"/>
+      <c r="J13" s="69"/>
       <c r="K13" s="49"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="70"/>
+      <c r="A14" s="74"/>
       <c r="B14" s="35" t="s">
         <v>13</v>
       </c>
@@ -1712,12 +1712,12 @@
       <c r="H14" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="72"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="70"/>
       <c r="K14" s="48"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="69" t="s">
+      <c r="A15" s="73" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="41" t="s">
@@ -1737,14 +1737,14 @@
       <c r="H15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="71">
+      <c r="I15" s="69">
         <v>46199</v>
       </c>
-      <c r="J15" s="71"/>
+      <c r="J15" s="69"/>
       <c r="K15" s="49"/>
     </row>
     <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="70"/>
+      <c r="A16" s="74"/>
       <c r="B16" s="44" t="s">
         <v>13</v>
       </c>
@@ -1762,8 +1762,8 @@
       <c r="H16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="70"/>
-      <c r="J16" s="72"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="70"/>
       <c r="K16" s="48"/>
     </row>
     <row r="17" spans="1:11">
@@ -1787,14 +1787,14 @@
       <c r="H17" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="74">
+      <c r="I17" s="72">
         <v>46305</v>
       </c>
-      <c r="J17" s="74"/>
+      <c r="J17" s="72"/>
       <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="70"/>
+      <c r="A18" s="74"/>
       <c r="B18" s="35" t="s">
         <v>13</v>
       </c>
@@ -1812,8 +1812,8 @@
       <c r="H18" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="70"/>
-      <c r="J18" s="72"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="70"/>
       <c r="K18" s="48"/>
     </row>
     <row r="19" spans="1:11">
@@ -1837,14 +1837,14 @@
       <c r="H19" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="74">
+      <c r="I19" s="72">
         <v>46336</v>
       </c>
-      <c r="J19" s="74"/>
+      <c r="J19" s="72"/>
       <c r="K19" s="50"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="70"/>
+      <c r="A20" s="74"/>
       <c r="B20" s="35" t="s">
         <v>13</v>
       </c>
@@ -1862,12 +1862,12 @@
       <c r="H20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="70"/>
-      <c r="J20" s="72"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="70"/>
       <c r="K20" s="48"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="69" t="s">
+      <c r="A21" s="73" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="38" t="s">
@@ -1887,14 +1887,14 @@
       <c r="H21" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="71">
+      <c r="I21" s="69">
         <v>46336</v>
       </c>
-      <c r="J21" s="71"/>
+      <c r="J21" s="69"/>
       <c r="K21" s="51"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="70"/>
+      <c r="A22" s="74"/>
       <c r="B22" s="35" t="s">
         <v>13</v>
       </c>
@@ -1912,12 +1912,12 @@
       <c r="H22" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="70"/>
-      <c r="J22" s="72"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="70"/>
       <c r="K22" s="52"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="69" t="s">
+      <c r="A23" s="73" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="41" t="s">
@@ -1937,14 +1937,14 @@
       <c r="H23" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="71">
+      <c r="I23" s="69">
         <v>46237</v>
       </c>
-      <c r="J23" s="71"/>
+      <c r="J23" s="69"/>
       <c r="K23" s="51"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="70"/>
+      <c r="A24" s="74"/>
       <c r="B24" s="44" t="s">
         <v>13</v>
       </c>
@@ -1962,12 +1962,12 @@
       <c r="H24" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="70"/>
-      <c r="J24" s="72"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="70"/>
       <c r="K24" s="52"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="69" t="s">
+      <c r="A25" s="73" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="41" t="s">
@@ -1987,14 +1987,14 @@
       <c r="H25" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="71">
+      <c r="I25" s="69">
         <v>46188</v>
       </c>
-      <c r="J25" s="71"/>
+      <c r="J25" s="69"/>
       <c r="K25" s="51"/>
     </row>
     <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="70"/>
+      <c r="A26" s="74"/>
       <c r="B26" s="44" t="s">
         <v>13</v>
       </c>
@@ -2012,12 +2012,12 @@
       <c r="H26" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="70"/>
-      <c r="J26" s="72"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="70"/>
       <c r="K26" s="52"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="69" t="s">
+      <c r="A27" s="73" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="38" t="s">
@@ -2037,14 +2037,14 @@
       <c r="H27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="71">
+      <c r="I27" s="69">
         <v>46321</v>
       </c>
-      <c r="J27" s="71"/>
+      <c r="J27" s="69"/>
       <c r="K27" s="51"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="70"/>
+      <c r="A28" s="74"/>
       <c r="B28" s="35" t="s">
         <v>13</v>
       </c>
@@ -2062,12 +2062,12 @@
       <c r="H28" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="70"/>
-      <c r="J28" s="72"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="70"/>
       <c r="K28" s="52"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="69" t="s">
+      <c r="A29" s="73" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="41" t="s">
@@ -2087,14 +2087,14 @@
       <c r="H29" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="71">
+      <c r="I29" s="69">
         <v>46139</v>
       </c>
-      <c r="J29" s="71"/>
+      <c r="J29" s="69"/>
       <c r="K29" s="51"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="70"/>
+      <c r="A30" s="74"/>
       <c r="B30" s="44" t="s">
         <v>13</v>
       </c>
@@ -2112,12 +2112,12 @@
       <c r="H30" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="70"/>
-      <c r="J30" s="72"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="70"/>
       <c r="K30" s="52"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="69" t="s">
+      <c r="A31" s="73" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="41" t="s">
@@ -2137,14 +2137,14 @@
       <c r="H31" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="71">
+      <c r="I31" s="69">
         <v>46133</v>
       </c>
-      <c r="J31" s="71"/>
+      <c r="J31" s="69"/>
       <c r="K31" s="51"/>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="70"/>
+      <c r="A32" s="74"/>
       <c r="B32" s="44" t="s">
         <v>13</v>
       </c>
@@ -2162,12 +2162,12 @@
       <c r="H32" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="70"/>
-      <c r="J32" s="72"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="70"/>
       <c r="K32" s="52"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="69" t="s">
+      <c r="A33" s="73" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="38" t="s">
@@ -2187,14 +2187,14 @@
       <c r="H33" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="71">
+      <c r="I33" s="69">
         <v>46295</v>
       </c>
-      <c r="J33" s="71"/>
+      <c r="J33" s="69"/>
       <c r="K33" s="51"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="70"/>
+      <c r="A34" s="74"/>
       <c r="B34" s="35" t="s">
         <v>13</v>
       </c>
@@ -2212,12 +2212,12 @@
       <c r="H34" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="70"/>
-      <c r="J34" s="72"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="70"/>
       <c r="K34" s="52"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="69" t="s">
+      <c r="A35" s="73" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="38" t="s">
@@ -2237,14 +2237,14 @@
       <c r="H35" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="71">
+      <c r="I35" s="69">
         <v>45884</v>
       </c>
-      <c r="J35" s="71"/>
+      <c r="J35" s="69"/>
       <c r="K35" s="51"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="70"/>
+      <c r="A36" s="74"/>
       <c r="B36" s="35" t="s">
         <v>13</v>
       </c>
@@ -2262,12 +2262,12 @@
       <c r="H36" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="70"/>
-      <c r="J36" s="72"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="70"/>
       <c r="K36" s="52"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="69" t="s">
+      <c r="A37" s="73" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="38" t="s">
@@ -2287,14 +2287,14 @@
       <c r="H37" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="71">
+      <c r="I37" s="69">
         <v>45915</v>
       </c>
-      <c r="J37" s="71"/>
+      <c r="J37" s="69"/>
       <c r="K37" s="51"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="70"/>
+      <c r="A38" s="74"/>
       <c r="B38" s="35" t="s">
         <v>13</v>
       </c>
@@ -2312,12 +2312,12 @@
       <c r="H38" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="70"/>
-      <c r="J38" s="72"/>
+      <c r="I38" s="74"/>
+      <c r="J38" s="70"/>
       <c r="K38" s="52"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="73" t="s">
         <v>91</v>
       </c>
       <c r="B39" s="38" t="s">
@@ -2333,12 +2333,12 @@
       <c r="H39" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
       <c r="K39" s="51"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="70"/>
+      <c r="A40" s="74"/>
       <c r="B40" s="55" t="s">
         <v>13</v>
       </c>
@@ -2352,12 +2352,12 @@
       <c r="H40" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="I40" s="70"/>
-      <c r="J40" s="72"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="70"/>
       <c r="K40" s="52"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="69" t="s">
+      <c r="A41" s="73" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="38" t="s">
@@ -2377,14 +2377,14 @@
       <c r="H41" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="71">
+      <c r="I41" s="69">
         <v>46234</v>
       </c>
-      <c r="J41" s="71"/>
+      <c r="J41" s="69"/>
       <c r="K41" s="51"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="70"/>
+      <c r="A42" s="74"/>
       <c r="B42" s="55" t="s">
         <v>13</v>
       </c>
@@ -2394,12 +2394,12 @@
       <c r="F42" s="56"/>
       <c r="G42" s="57"/>
       <c r="H42" s="55"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="72"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="70"/>
       <c r="K42" s="52"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="69" t="s">
+      <c r="A43" s="73" t="s">
         <v>136</v>
       </c>
       <c r="B43" s="38" t="s">
@@ -2415,12 +2415,12 @@
       <c r="H43" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
       <c r="K43" s="51"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="70"/>
+      <c r="A44" s="74"/>
       <c r="B44" s="55" t="s">
         <v>13</v>
       </c>
@@ -2434,27 +2434,45 @@
       <c r="H44" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="70"/>
-      <c r="J44" s="72"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="70"/>
       <c r="K44" s="52"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:K44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="62">
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="J19:J20"/>
@@ -2471,38 +2489,20 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -4325,16 +4325,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="67"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="68" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="68"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4843,7 +4843,7 @@
         <v>46224</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4877,7 +4877,7 @@
         <v>46224</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5730,19 +5730,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5995,6 +5982,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6005,17 +6005,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6034,6 +6023,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
   <ds:schemaRefs>

--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA74708-4782-4A89-80A6-2A2930F6DA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1678C19D-7701-4479-84E8-EB3188F027EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -489,7 +489,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,6 +592,20 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -813,7 +827,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1003,28 +1017,38 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1387,6 +1411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -1405,33 +1430,33 @@
       <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-    </row>
-    <row r="4" spans="1:11" ht="27.6">
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+    </row>
+    <row r="4" spans="1:11" ht="28.2" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1466,8 +1491,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="77" t="s">
+    <row r="5" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A5" s="76" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="58" t="s">
@@ -1487,14 +1512,14 @@
       <c r="H5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="71">
+      <c r="I5" s="77">
         <v>46244</v>
       </c>
-      <c r="J5" s="71"/>
+      <c r="J5" s="77"/>
       <c r="K5" s="47"/>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1">
-      <c r="A6" s="74"/>
+    <row r="6" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A6" s="70"/>
       <c r="B6" s="44" t="s">
         <v>13</v>
       </c>
@@ -1512,12 +1537,12 @@
       <c r="H6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="72"/>
       <c r="K6" s="48"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="69" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="38" t="s">
@@ -1537,14 +1562,14 @@
       <c r="H7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="69" t="s">
+      <c r="I7" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="71"/>
       <c r="K7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="74"/>
+      <c r="A8" s="70"/>
       <c r="B8" s="35" t="s">
         <v>13</v>
       </c>
@@ -1562,12 +1587,12 @@
       <c r="H8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="74"/>
-      <c r="J8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="72"/>
       <c r="K8" s="48"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="73" t="s">
+    <row r="9" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A9" s="69" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="38" t="s">
@@ -1587,14 +1612,14 @@
       <c r="H9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="69">
+      <c r="I9" s="71">
         <v>46218</v>
       </c>
-      <c r="J9" s="69"/>
+      <c r="J9" s="71"/>
       <c r="K9" s="49"/>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1">
-      <c r="A10" s="74"/>
+    <row r="10" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A10" s="70"/>
       <c r="B10" s="35" t="s">
         <v>13</v>
       </c>
@@ -1612,12 +1637,12 @@
       <c r="H10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="74"/>
-      <c r="J10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="72"/>
       <c r="K10" s="48"/>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="73" t="s">
+    <row r="11" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A11" s="69" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="41" t="s">
@@ -1637,14 +1662,14 @@
       <c r="H11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="69">
+      <c r="I11" s="71">
         <v>46171</v>
       </c>
-      <c r="J11" s="69"/>
+      <c r="J11" s="71"/>
       <c r="K11" s="49"/>
     </row>
-    <row r="12" spans="1:11" ht="15" thickBot="1">
-      <c r="A12" s="74"/>
+    <row r="12" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A12" s="70"/>
       <c r="B12" s="44" t="s">
         <v>13</v>
       </c>
@@ -1662,12 +1687,12 @@
       <c r="H12" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="74"/>
-      <c r="J12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="72"/>
       <c r="K12" s="48"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="69" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="38" t="s">
@@ -1687,14 +1712,14 @@
       <c r="H13" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="69" t="s">
+      <c r="I13" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="69"/>
+      <c r="J13" s="71"/>
       <c r="K13" s="49"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="74"/>
+      <c r="A14" s="70"/>
       <c r="B14" s="35" t="s">
         <v>13</v>
       </c>
@@ -1712,12 +1737,12 @@
       <c r="H14" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="74"/>
-      <c r="J14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="72"/>
       <c r="K14" s="48"/>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="73" t="s">
+    <row r="15" spans="1:11" hidden="1">
+      <c r="A15" s="69" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="41" t="s">
@@ -1737,14 +1762,14 @@
       <c r="H15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="69">
+      <c r="I15" s="71">
         <v>46199</v>
       </c>
-      <c r="J15" s="69"/>
+      <c r="J15" s="71"/>
       <c r="K15" s="49"/>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1">
-      <c r="A16" s="74"/>
+    <row r="16" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A16" s="70"/>
       <c r="B16" s="44" t="s">
         <v>13</v>
       </c>
@@ -1762,11 +1787,11 @@
       <c r="H16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="74"/>
-      <c r="J16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="72"/>
       <c r="K16" s="48"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" hidden="1">
       <c r="A17" s="75" t="s">
         <v>21</v>
       </c>
@@ -1787,14 +1812,14 @@
       <c r="H17" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="72">
+      <c r="I17" s="74">
         <v>46305</v>
       </c>
-      <c r="J17" s="72"/>
+      <c r="J17" s="74"/>
       <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="74"/>
+      <c r="A18" s="70"/>
       <c r="B18" s="35" t="s">
         <v>13</v>
       </c>
@@ -1812,8 +1837,8 @@
       <c r="H18" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="74"/>
-      <c r="J18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="72"/>
       <c r="K18" s="48"/>
     </row>
     <row r="19" spans="1:11">
@@ -1837,14 +1862,14 @@
       <c r="H19" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="72">
-        <v>46336</v>
-      </c>
-      <c r="J19" s="72"/>
+      <c r="I19" s="78">
+        <v>46419</v>
+      </c>
+      <c r="J19" s="74"/>
       <c r="K19" s="50"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="74"/>
+      <c r="A20" s="70"/>
       <c r="B20" s="35" t="s">
         <v>13</v>
       </c>
@@ -1862,12 +1887,12 @@
       <c r="H20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="74"/>
-      <c r="J20" s="70"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="72"/>
       <c r="K20" s="48"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="69" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="38" t="s">
@@ -1887,14 +1912,14 @@
       <c r="H21" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="69">
-        <v>46336</v>
-      </c>
-      <c r="J21" s="69"/>
+      <c r="I21" s="80">
+        <v>46397</v>
+      </c>
+      <c r="J21" s="71"/>
       <c r="K21" s="51"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="74"/>
+      <c r="A22" s="70"/>
       <c r="B22" s="35" t="s">
         <v>13</v>
       </c>
@@ -1912,12 +1937,12 @@
       <c r="H22" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="74"/>
-      <c r="J22" s="70"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="72"/>
       <c r="K22" s="52"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="73" t="s">
+      <c r="A23" s="69" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="41" t="s">
@@ -1937,14 +1962,14 @@
       <c r="H23" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="69">
+      <c r="I23" s="71">
         <v>46237</v>
       </c>
-      <c r="J23" s="69"/>
+      <c r="J23" s="71"/>
       <c r="K23" s="51"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="74"/>
+      <c r="A24" s="70"/>
       <c r="B24" s="44" t="s">
         <v>13</v>
       </c>
@@ -1962,12 +1987,12 @@
       <c r="H24" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="74"/>
-      <c r="J24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="72"/>
       <c r="K24" s="52"/>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="73" t="s">
+    <row r="25" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A25" s="69" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="41" t="s">
@@ -1987,14 +2012,14 @@
       <c r="H25" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="69">
+      <c r="I25" s="71">
         <v>46188</v>
       </c>
-      <c r="J25" s="69"/>
+      <c r="J25" s="71"/>
       <c r="K25" s="51"/>
     </row>
-    <row r="26" spans="1:11" ht="15" thickBot="1">
-      <c r="A26" s="74"/>
+    <row r="26" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A26" s="70"/>
       <c r="B26" s="44" t="s">
         <v>13</v>
       </c>
@@ -2012,12 +2037,12 @@
       <c r="H26" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="74"/>
-      <c r="J26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="72"/>
       <c r="K26" s="52"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="73" t="s">
+      <c r="A27" s="69" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="38" t="s">
@@ -2037,14 +2062,14 @@
       <c r="H27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="69">
+      <c r="I27" s="71">
         <v>46321</v>
       </c>
-      <c r="J27" s="69"/>
+      <c r="J27" s="71"/>
       <c r="K27" s="51"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="74"/>
+      <c r="A28" s="70"/>
       <c r="B28" s="35" t="s">
         <v>13</v>
       </c>
@@ -2062,12 +2087,12 @@
       <c r="H28" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="74"/>
-      <c r="J28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="72"/>
       <c r="K28" s="52"/>
     </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="73" t="s">
+    <row r="29" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A29" s="69" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="41" t="s">
@@ -2087,14 +2112,14 @@
       <c r="H29" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="69">
+      <c r="I29" s="71">
         <v>46139</v>
       </c>
-      <c r="J29" s="69"/>
+      <c r="J29" s="71"/>
       <c r="K29" s="51"/>
     </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1">
-      <c r="A30" s="74"/>
+    <row r="30" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A30" s="70"/>
       <c r="B30" s="44" t="s">
         <v>13</v>
       </c>
@@ -2112,12 +2137,12 @@
       <c r="H30" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="74"/>
-      <c r="J30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="72"/>
       <c r="K30" s="52"/>
     </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="73" t="s">
+    <row r="31" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A31" s="69" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="41" t="s">
@@ -2137,14 +2162,14 @@
       <c r="H31" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="69">
+      <c r="I31" s="71">
         <v>46133</v>
       </c>
-      <c r="J31" s="69"/>
+      <c r="J31" s="71"/>
       <c r="K31" s="51"/>
     </row>
-    <row r="32" spans="1:11" ht="15" thickBot="1">
-      <c r="A32" s="74"/>
+    <row r="32" spans="1:11" ht="15" hidden="1" thickBot="1">
+      <c r="A32" s="70"/>
       <c r="B32" s="44" t="s">
         <v>13</v>
       </c>
@@ -2162,12 +2187,12 @@
       <c r="H32" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="74"/>
-      <c r="J32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="72"/>
       <c r="K32" s="52"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="69" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="38" t="s">
@@ -2187,14 +2212,14 @@
       <c r="H33" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="69">
+      <c r="I33" s="71">
         <v>46295</v>
       </c>
-      <c r="J33" s="69"/>
+      <c r="J33" s="71"/>
       <c r="K33" s="51"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="74"/>
+      <c r="A34" s="70"/>
       <c r="B34" s="35" t="s">
         <v>13</v>
       </c>
@@ -2212,12 +2237,12 @@
       <c r="H34" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="74"/>
-      <c r="J34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="72"/>
       <c r="K34" s="52"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="73" t="s">
+      <c r="A35" s="69" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="38" t="s">
@@ -2237,14 +2262,14 @@
       <c r="H35" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="69">
-        <v>45884</v>
-      </c>
-      <c r="J35" s="69"/>
+      <c r="I35" s="71">
+        <v>45899</v>
+      </c>
+      <c r="J35" s="71"/>
       <c r="K35" s="51"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="74"/>
+      <c r="A36" s="70"/>
       <c r="B36" s="35" t="s">
         <v>13</v>
       </c>
@@ -2262,12 +2287,12 @@
       <c r="H36" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="74"/>
-      <c r="J36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="72"/>
       <c r="K36" s="52"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="69" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="38" t="s">
@@ -2287,14 +2312,14 @@
       <c r="H37" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="69">
-        <v>45915</v>
-      </c>
-      <c r="J37" s="69"/>
+      <c r="I37" s="71">
+        <v>45910</v>
+      </c>
+      <c r="J37" s="71"/>
       <c r="K37" s="51"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="74"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="35" t="s">
         <v>13</v>
       </c>
@@ -2312,12 +2337,12 @@
       <c r="H38" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="74"/>
-      <c r="J38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="72"/>
       <c r="K38" s="52"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="69" t="s">
         <v>91</v>
       </c>
       <c r="B39" s="38" t="s">
@@ -2333,12 +2358,12 @@
       <c r="H39" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
       <c r="K39" s="51"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="74"/>
+      <c r="A40" s="70"/>
       <c r="B40" s="55" t="s">
         <v>13</v>
       </c>
@@ -2352,12 +2377,12 @@
       <c r="H40" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="I40" s="74"/>
-      <c r="J40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="72"/>
       <c r="K40" s="52"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="73" t="s">
+      <c r="A41" s="69" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="38" t="s">
@@ -2377,14 +2402,14 @@
       <c r="H41" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="69">
-        <v>46234</v>
-      </c>
-      <c r="J41" s="69"/>
+      <c r="I41" s="71">
+        <v>46237</v>
+      </c>
+      <c r="J41" s="71"/>
       <c r="K41" s="51"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="74"/>
+      <c r="A42" s="70"/>
       <c r="B42" s="55" t="s">
         <v>13</v>
       </c>
@@ -2394,12 +2419,12 @@
       <c r="F42" s="56"/>
       <c r="G42" s="57"/>
       <c r="H42" s="55"/>
-      <c r="I42" s="74"/>
-      <c r="J42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="72"/>
       <c r="K42" s="52"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="69" t="s">
         <v>136</v>
       </c>
       <c r="B43" s="38" t="s">
@@ -2415,12 +2440,12 @@
       <c r="H43" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I43" s="69"/>
-      <c r="J43" s="69"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
       <c r="K43" s="51"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="74"/>
+      <c r="A44" s="70"/>
       <c r="B44" s="55" t="s">
         <v>13</v>
       </c>
@@ -2434,22 +2459,58 @@
       <c r="H44" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="74"/>
-      <c r="J44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="72"/>
       <c r="K44" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:K44" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="7">
+      <filters blank="1">
+        <filter val="Construction"/>
+        <filter val="On Hold"/>
+        <filter val="Planning"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="62">
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A1:K1"/>
@@ -2466,45 +2527,17 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -2705,8 +2738,8 @@
         <f>'[1]Master Schedule'!C5</f>
         <v>46084</v>
       </c>
-      <c r="R5" s="19">
-        <v>46106</v>
+      <c r="R5" s="81">
+        <v>46248</v>
       </c>
       <c r="S5" s="14"/>
       <c r="T5" s="25" t="s">
@@ -3560,7 +3593,7 @@
         <v>45717</v>
       </c>
       <c r="R20" s="19">
-        <v>45737</v>
+        <v>45899</v>
       </c>
       <c r="T20" s="26" t="s">
         <v>65</v>
@@ -3604,7 +3637,7 @@
         <v>45717</v>
       </c>
       <c r="R21" s="19">
-        <v>45737</v>
+        <v>45910</v>
       </c>
       <c r="T21" s="26" t="s">
         <v>126</v>
@@ -3727,7 +3760,7 @@
         <v>46225</v>
       </c>
       <c r="R24" s="11">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="T24" s="26" t="s">
         <v>140</v>
@@ -4325,16 +4358,16 @@
         <v>57</v>
       </c>
       <c r="B1" s="67"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="68" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="68"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -5730,6 +5763,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -5982,29 +6037,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CD2A335-1DEC-4C21-977A-9ED57024A196}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6021,23 +6073,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B14C1EB-02DF-450B-8928-EA02D20EAB49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{235994A7-6E6B-494E-A465-C3E876960F00}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Construction_Portfolio_Template.xlsx
+++ b/Construction_Portfolio_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1678C19D-7701-4479-84E8-EB3188F027EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{F600DE45-4501-465C-9806-A81742F36D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6683723C-A3B6-44E3-855E-63C92E5D4C5A}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Schedule" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="144">
   <si>
     <t>MASTER SCHEDULE</t>
   </si>
@@ -477,6 +477,9 @@
   </si>
   <si>
     <t>บริษัท อีโค่คูล ไครลเมท เทคโนโลยี จำกัด</t>
+  </si>
+  <si>
+    <t>เทสและวัดลม</t>
   </si>
 </sst>
 </file>
@@ -489,7 +492,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,6 +606,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.5"/>
       <color rgb="FFFF0000"/>
@@ -610,7 +623,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,8 +658,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -820,6 +845,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -827,7 +867,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -997,12 +1037,6 @@
     <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1040,16 +1074,32 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2 2 3 2" xfId="3" xr:uid="{10CA6883-C0B4-442D-A7D0-FF27A9ED468E}"/>
@@ -1411,7 +1461,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -1427,34 +1476,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="4" spans="1:11" ht="28.2" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -1491,17 +1540,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A5" s="76" t="s">
+    <row r="5" spans="1:11" ht="15" thickBot="1">
+      <c r="A5" s="74" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="59">
+      <c r="C5" s="76">
         <v>46084</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="76">
         <v>46127</v>
       </c>
       <c r="E5" s="59"/>
@@ -1512,21 +1561,21 @@
       <c r="H5" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="77">
+      <c r="I5" s="82">
         <v>46244</v>
       </c>
-      <c r="J5" s="77"/>
+      <c r="J5" s="75"/>
       <c r="K5" s="47"/>
     </row>
-    <row r="6" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A6" s="70"/>
+    <row r="6" spans="1:11" ht="15" thickBot="1">
+      <c r="A6" s="68"/>
       <c r="B6" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="76">
         <v>46189</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="76">
         <v>46189</v>
       </c>
       <c r="E6" s="45"/>
@@ -1537,22 +1586,22 @@
       <c r="H6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="72"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="70"/>
       <c r="K6" s="48"/>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="69" t="s">
+    <row r="7" spans="1:11" ht="15" thickBot="1">
+      <c r="A7" s="67" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="39">
-        <v>46219</v>
-      </c>
-      <c r="D7" s="39">
-        <v>46233</v>
+      <c r="C7" s="77">
+        <v>46266</v>
+      </c>
+      <c r="D7" s="77">
+        <v>46275</v>
       </c>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
@@ -1562,22 +1611,22 @@
       <c r="H7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="71"/>
+      <c r="I7" s="82">
+        <v>46366</v>
+      </c>
+      <c r="J7" s="69"/>
       <c r="K7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="15" thickBot="1">
-      <c r="A8" s="70"/>
+      <c r="A8" s="68"/>
       <c r="B8" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="36">
-        <v>46244</v>
-      </c>
-      <c r="D8" s="36">
-        <v>46247</v>
+      <c r="C8" s="77">
+        <v>46305</v>
+      </c>
+      <c r="D8" s="77">
+        <v>46308</v>
       </c>
       <c r="E8" s="36"/>
       <c r="F8" s="36"/>
@@ -1587,21 +1636,21 @@
       <c r="H8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="70"/>
-      <c r="J8" s="72"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="70"/>
       <c r="K8" s="48"/>
     </row>
-    <row r="9" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A9" s="69" t="s">
+    <row r="9" spans="1:11" ht="15" thickBot="1">
+      <c r="A9" s="67" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="76">
         <v>46082</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="76">
         <v>46096</v>
       </c>
       <c r="E9" s="39"/>
@@ -1612,21 +1661,21 @@
       <c r="H9" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="71">
+      <c r="I9" s="82">
         <v>46218</v>
       </c>
-      <c r="J9" s="71"/>
+      <c r="J9" s="69"/>
       <c r="K9" s="49"/>
     </row>
-    <row r="10" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A10" s="70"/>
+    <row r="10" spans="1:11" ht="15" thickBot="1">
+      <c r="A10" s="68"/>
       <c r="B10" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="76">
         <v>46168</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="76">
         <v>46213</v>
       </c>
       <c r="E10" s="36"/>
@@ -1637,21 +1686,21 @@
       <c r="H10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="70"/>
-      <c r="J10" s="72"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="70"/>
       <c r="K10" s="48"/>
     </row>
-    <row r="11" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A11" s="69" t="s">
+    <row r="11" spans="1:11" ht="15" thickBot="1">
+      <c r="A11" s="67" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="76">
         <v>46184</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="76">
         <v>46191</v>
       </c>
       <c r="E11" s="42"/>
@@ -1662,21 +1711,21 @@
       <c r="H11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="71">
+      <c r="I11" s="82">
         <v>46171</v>
       </c>
-      <c r="J11" s="71"/>
+      <c r="J11" s="69"/>
       <c r="K11" s="49"/>
     </row>
-    <row r="12" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A12" s="70"/>
+    <row r="12" spans="1:11" ht="15" thickBot="1">
+      <c r="A12" s="68"/>
       <c r="B12" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="45">
+      <c r="C12" s="76">
         <v>46200</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="76">
         <v>46202</v>
       </c>
       <c r="E12" s="45"/>
@@ -1687,21 +1736,21 @@
       <c r="H12" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="70"/>
-      <c r="J12" s="72"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="70"/>
       <c r="K12" s="48"/>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="69" t="s">
+    <row r="13" spans="1:11" ht="15" thickBot="1">
+      <c r="A13" s="67" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="77">
         <v>46392</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="77">
         <v>46402</v>
       </c>
       <c r="E13" s="39"/>
@@ -1712,22 +1761,22 @@
       <c r="H13" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="71"/>
+      <c r="I13" s="84">
+        <v>46419</v>
+      </c>
+      <c r="J13" s="69"/>
       <c r="K13" s="49"/>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="A14" s="70"/>
+      <c r="A14" s="68"/>
       <c r="B14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="36">
-        <v>46042</v>
-      </c>
-      <c r="D14" s="36">
-        <v>46042</v>
+      <c r="C14" s="77">
+        <v>46423</v>
+      </c>
+      <c r="D14" s="77">
+        <v>46428</v>
       </c>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
@@ -1737,21 +1786,21 @@
       <c r="H14" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="72"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="70"/>
       <c r="K14" s="48"/>
     </row>
-    <row r="15" spans="1:11" hidden="1">
-      <c r="A15" s="69" t="s">
+    <row r="15" spans="1:11" ht="15" thickBot="1">
+      <c r="A15" s="67" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="42">
+      <c r="C15" s="76">
         <v>46168</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="76">
         <v>46188</v>
       </c>
       <c r="E15" s="42"/>
@@ -1762,21 +1811,21 @@
       <c r="H15" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="71">
+      <c r="I15" s="82">
         <v>46199</v>
       </c>
-      <c r="J15" s="71"/>
+      <c r="J15" s="69"/>
       <c r="K15" s="49"/>
     </row>
-    <row r="16" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A16" s="70"/>
+    <row r="16" spans="1:11" ht="15" thickBot="1">
+      <c r="A16" s="68"/>
       <c r="B16" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="45">
+      <c r="C16" s="76">
         <v>46198</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="76">
         <v>46199</v>
       </c>
       <c r="E16" s="45"/>
@@ -1787,21 +1836,21 @@
       <c r="H16" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="70"/>
-      <c r="J16" s="72"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="70"/>
       <c r="K16" s="48"/>
     </row>
-    <row r="17" spans="1:11" hidden="1">
-      <c r="A17" s="75" t="s">
+    <row r="17" spans="1:11" ht="15" thickBot="1">
+      <c r="A17" s="73" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="76">
         <v>46188</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="76">
         <v>46198</v>
       </c>
       <c r="E17" s="33"/>
@@ -1812,21 +1861,21 @@
       <c r="H17" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="74">
+      <c r="I17" s="82">
         <v>46305</v>
       </c>
-      <c r="J17" s="74"/>
+      <c r="J17" s="72"/>
       <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:11" ht="15" thickBot="1">
-      <c r="A18" s="70"/>
+      <c r="A18" s="68"/>
       <c r="B18" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="78">
         <v>46296</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="78">
         <v>46298</v>
       </c>
       <c r="E18" s="36"/>
@@ -1837,22 +1886,22 @@
       <c r="H18" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="70"/>
-      <c r="J18" s="72"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="70"/>
       <c r="K18" s="48"/>
     </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="75" t="s">
+    <row r="19" spans="1:11" ht="15" thickBot="1">
+      <c r="A19" s="73" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="33">
-        <v>46275</v>
-      </c>
-      <c r="D19" s="33">
-        <v>46290</v>
+      <c r="C19" s="77">
+        <v>46366</v>
+      </c>
+      <c r="D19" s="77">
+        <v>46381</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="33"/>
@@ -1862,22 +1911,22 @@
       <c r="H19" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="78">
+      <c r="I19" s="84">
         <v>46419</v>
       </c>
-      <c r="J19" s="74"/>
+      <c r="J19" s="72"/>
       <c r="K19" s="50"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1">
-      <c r="A20" s="70"/>
+      <c r="A20" s="68"/>
       <c r="B20" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="36">
-        <v>46327</v>
-      </c>
-      <c r="D20" s="36">
-        <v>46329</v>
+      <c r="C20" s="77">
+        <v>46388</v>
+      </c>
+      <c r="D20" s="77">
+        <v>46390</v>
       </c>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
@@ -1887,21 +1936,21 @@
       <c r="H20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="79"/>
-      <c r="J20" s="72"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="70"/>
       <c r="K20" s="48"/>
     </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="69" t="s">
+    <row r="21" spans="1:11" ht="15" thickBot="1">
+      <c r="A21" s="67" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="39">
+      <c r="C21" s="77">
         <v>46240</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="77">
         <v>46249</v>
       </c>
       <c r="E21" s="39"/>
@@ -1912,21 +1961,21 @@
       <c r="H21" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="80">
+      <c r="I21" s="84">
         <v>46397</v>
       </c>
-      <c r="J21" s="71"/>
+      <c r="J21" s="69"/>
       <c r="K21" s="51"/>
     </row>
     <row r="22" spans="1:11" ht="15" thickBot="1">
-      <c r="A22" s="70"/>
+      <c r="A22" s="68"/>
       <c r="B22" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="77">
         <v>46327</v>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="77">
         <v>46329</v>
       </c>
       <c r="E22" s="36"/>
@@ -1937,22 +1986,22 @@
       <c r="H22" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="79"/>
-      <c r="J22" s="72"/>
+      <c r="I22" s="85"/>
+      <c r="J22" s="70"/>
       <c r="K22" s="52"/>
     </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="69" t="s">
+    <row r="23" spans="1:11" ht="15" thickBot="1">
+      <c r="A23" s="67" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="42">
-        <v>46190</v>
-      </c>
-      <c r="D23" s="42">
-        <v>46206</v>
+      <c r="C23" s="76">
+        <v>46197</v>
+      </c>
+      <c r="D23" s="76">
+        <v>46209</v>
       </c>
       <c r="E23" s="42"/>
       <c r="F23" s="42"/>
@@ -1962,22 +2011,22 @@
       <c r="H23" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="71">
+      <c r="I23" s="82">
         <v>46237</v>
       </c>
-      <c r="J23" s="71"/>
+      <c r="J23" s="69"/>
       <c r="K23" s="51"/>
     </row>
     <row r="24" spans="1:11" ht="15" thickBot="1">
-      <c r="A24" s="70"/>
+      <c r="A24" s="68"/>
       <c r="B24" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="45">
-        <v>46216</v>
-      </c>
-      <c r="D24" s="45">
-        <v>46220</v>
+      <c r="C24" s="76">
+        <v>46209</v>
+      </c>
+      <c r="D24" s="76">
+        <v>46211</v>
       </c>
       <c r="E24" s="45"/>
       <c r="F24" s="45"/>
@@ -1987,21 +2036,21 @@
       <c r="H24" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="70"/>
-      <c r="J24" s="72"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="70"/>
       <c r="K24" s="52"/>
     </row>
-    <row r="25" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A25" s="69" t="s">
+    <row r="25" spans="1:11" ht="15" thickBot="1">
+      <c r="A25" s="67" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="42">
+      <c r="C25" s="76">
         <v>46185</v>
       </c>
-      <c r="D25" s="42">
+      <c r="D25" s="76">
         <v>46188</v>
       </c>
       <c r="E25" s="42"/>
@@ -2012,21 +2061,21 @@
       <c r="H25" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="71">
+      <c r="I25" s="82">
         <v>46188</v>
       </c>
-      <c r="J25" s="71"/>
+      <c r="J25" s="69"/>
       <c r="K25" s="51"/>
     </row>
-    <row r="26" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A26" s="70"/>
+    <row r="26" spans="1:11" ht="15" thickBot="1">
+      <c r="A26" s="68"/>
       <c r="B26" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="45">
+      <c r="C26" s="76">
         <v>46185</v>
       </c>
-      <c r="D26" s="45">
+      <c r="D26" s="76">
         <v>46188</v>
       </c>
       <c r="E26" s="45"/>
@@ -2037,22 +2086,22 @@
       <c r="H26" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="70"/>
-      <c r="J26" s="72"/>
+      <c r="I26" s="83"/>
+      <c r="J26" s="70"/>
       <c r="K26" s="52"/>
     </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="69" t="s">
+    <row r="27" spans="1:11" ht="15" thickBot="1">
+      <c r="A27" s="67" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="39">
-        <v>46234</v>
-      </c>
-      <c r="D27" s="39">
-        <v>46247</v>
+      <c r="C27" s="79">
+        <v>46275</v>
+      </c>
+      <c r="D27" s="79">
+        <v>46295</v>
       </c>
       <c r="E27" s="39"/>
       <c r="F27" s="39"/>
@@ -2062,22 +2111,22 @@
       <c r="H27" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="71">
-        <v>46321</v>
-      </c>
-      <c r="J27" s="71"/>
+      <c r="I27" s="84">
+        <v>46382</v>
+      </c>
+      <c r="J27" s="69"/>
       <c r="K27" s="51"/>
     </row>
     <row r="28" spans="1:11" ht="15" thickBot="1">
-      <c r="A28" s="70"/>
+      <c r="A28" s="68"/>
       <c r="B28" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="36">
-        <v>46314</v>
-      </c>
-      <c r="D28" s="36">
-        <v>46316</v>
+      <c r="C28" s="79">
+        <v>46345</v>
+      </c>
+      <c r="D28" s="79">
+        <v>46347</v>
       </c>
       <c r="E28" s="36"/>
       <c r="F28" s="36"/>
@@ -2087,21 +2136,21 @@
       <c r="H28" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="70"/>
-      <c r="J28" s="72"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="70"/>
       <c r="K28" s="52"/>
     </row>
-    <row r="29" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A29" s="69" t="s">
+    <row r="29" spans="1:11" ht="15" thickBot="1">
+      <c r="A29" s="67" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="42">
+      <c r="C29" s="76">
         <v>46091</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="76">
         <v>46100</v>
       </c>
       <c r="E29" s="42"/>
@@ -2112,21 +2161,21 @@
       <c r="H29" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I29" s="71">
+      <c r="I29" s="82">
         <v>46139</v>
       </c>
-      <c r="J29" s="71"/>
+      <c r="J29" s="69"/>
       <c r="K29" s="51"/>
     </row>
-    <row r="30" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A30" s="70"/>
+    <row r="30" spans="1:11" ht="15" thickBot="1">
+      <c r="A30" s="68"/>
       <c r="B30" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="45">
+      <c r="C30" s="76">
         <v>46120</v>
       </c>
-      <c r="D30" s="45">
+      <c r="D30" s="76">
         <v>46124</v>
       </c>
       <c r="E30" s="45"/>
@@ -2137,21 +2186,21 @@
       <c r="H30" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="70"/>
-      <c r="J30" s="72"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="70"/>
       <c r="K30" s="52"/>
     </row>
-    <row r="31" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A31" s="69" t="s">
+    <row r="31" spans="1:11" ht="15" thickBot="1">
+      <c r="A31" s="67" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="42">
+      <c r="C31" s="76">
         <v>46091</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="76">
         <v>46094</v>
       </c>
       <c r="E31" s="42"/>
@@ -2162,21 +2211,21 @@
       <c r="H31" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I31" s="71">
+      <c r="I31" s="82">
         <v>46133</v>
       </c>
-      <c r="J31" s="71"/>
+      <c r="J31" s="69"/>
       <c r="K31" s="51"/>
     </row>
-    <row r="32" spans="1:11" ht="15" hidden="1" thickBot="1">
-      <c r="A32" s="70"/>
+    <row r="32" spans="1:11" ht="15" thickBot="1">
+      <c r="A32" s="68"/>
       <c r="B32" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="45">
+      <c r="C32" s="76">
         <v>46091</v>
       </c>
-      <c r="D32" s="45">
+      <c r="D32" s="76">
         <v>46094</v>
       </c>
       <c r="E32" s="45"/>
@@ -2187,21 +2236,21 @@
       <c r="H32" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="70"/>
-      <c r="J32" s="72"/>
+      <c r="I32" s="83"/>
+      <c r="J32" s="70"/>
       <c r="K32" s="52"/>
     </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="69" t="s">
+    <row r="33" spans="1:11" ht="15" thickBot="1">
+      <c r="A33" s="67" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="61">
+      <c r="C33" s="77">
         <v>46237</v>
       </c>
-      <c r="D33" s="61">
+      <c r="D33" s="77">
         <v>46248</v>
       </c>
       <c r="E33" s="39"/>
@@ -2212,21 +2261,21 @@
       <c r="H33" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="71">
-        <v>46295</v>
-      </c>
-      <c r="J33" s="71"/>
+      <c r="I33" s="82">
+        <v>46342</v>
+      </c>
+      <c r="J33" s="69"/>
       <c r="K33" s="51"/>
     </row>
     <row r="34" spans="1:11" ht="15" thickBot="1">
-      <c r="A34" s="70"/>
+      <c r="A34" s="68"/>
       <c r="B34" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="62">
+      <c r="C34" s="77">
         <v>46296</v>
       </c>
-      <c r="D34" s="62">
+      <c r="D34" s="77">
         <v>46303</v>
       </c>
       <c r="E34" s="36"/>
@@ -2237,21 +2286,21 @@
       <c r="H34" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="70"/>
-      <c r="J34" s="72"/>
+      <c r="I34" s="83"/>
+      <c r="J34" s="70"/>
       <c r="K34" s="52"/>
     </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="69" t="s">
+    <row r="35" spans="1:11" ht="15" thickBot="1">
+      <c r="A35" s="67" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="76">
         <v>45723</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="76">
         <v>45729</v>
       </c>
       <c r="E35" s="39"/>
@@ -2262,22 +2311,22 @@
       <c r="H35" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="71">
-        <v>45899</v>
-      </c>
-      <c r="J35" s="71"/>
+      <c r="I35" s="82">
+        <v>46264</v>
+      </c>
+      <c r="J35" s="69"/>
       <c r="K35" s="51"/>
     </row>
     <row r="36" spans="1:11" ht="15" thickBot="1">
-      <c r="A36" s="70"/>
+      <c r="A36" s="68"/>
       <c r="B36" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="36">
-        <v>45729</v>
-      </c>
-      <c r="D36" s="36">
-        <v>45732</v>
+      <c r="C36" s="78">
+        <v>46259</v>
+      </c>
+      <c r="D36" s="78">
+        <v>46264</v>
       </c>
       <c r="E36" s="36"/>
       <c r="F36" s="36"/>
@@ -2287,21 +2336,21 @@
       <c r="H36" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="70"/>
-      <c r="J36" s="72"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="70"/>
       <c r="K36" s="52"/>
     </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="69" t="s">
+    <row r="37" spans="1:11" ht="15" thickBot="1">
+      <c r="A37" s="67" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="76">
         <v>45723</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="76">
         <v>45729</v>
       </c>
       <c r="E37" s="39"/>
@@ -2312,22 +2361,22 @@
       <c r="H37" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="71">
-        <v>45910</v>
-      </c>
-      <c r="J37" s="71"/>
+      <c r="I37" s="82">
+        <v>46295</v>
+      </c>
+      <c r="J37" s="69"/>
       <c r="K37" s="51"/>
     </row>
     <row r="38" spans="1:11" ht="15" thickBot="1">
-      <c r="A38" s="70"/>
+      <c r="A38" s="68"/>
       <c r="B38" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="36">
-        <v>45729</v>
-      </c>
-      <c r="D38" s="36">
-        <v>45862</v>
+      <c r="C38" s="77">
+        <v>46264</v>
+      </c>
+      <c r="D38" s="77">
+        <v>46275</v>
       </c>
       <c r="E38" s="36"/>
       <c r="F38" s="36"/>
@@ -2337,19 +2386,23 @@
       <c r="H38" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="I38" s="70"/>
-      <c r="J38" s="72"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="70"/>
       <c r="K38" s="52"/>
     </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="69" t="s">
+    <row r="39" spans="1:11" ht="15" thickBot="1">
+      <c r="A39" s="67" t="s">
         <v>91</v>
       </c>
       <c r="B39" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
+      <c r="C39" s="80">
+        <v>46280</v>
+      </c>
+      <c r="D39" s="80">
+        <v>46290</v>
+      </c>
       <c r="E39" s="39"/>
       <c r="F39" s="39"/>
       <c r="G39" s="40">
@@ -2358,17 +2411,23 @@
       <c r="H39" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
+      <c r="I39" s="82">
+        <v>46539</v>
+      </c>
+      <c r="J39" s="69"/>
       <c r="K39" s="51"/>
     </row>
     <row r="40" spans="1:11" ht="15" thickBot="1">
-      <c r="A40" s="70"/>
+      <c r="A40" s="68"/>
       <c r="B40" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
+      <c r="C40" s="80">
+        <v>46510</v>
+      </c>
+      <c r="D40" s="80">
+        <v>46517</v>
+      </c>
       <c r="E40" s="56"/>
       <c r="F40" s="56"/>
       <c r="G40" s="57">
@@ -2377,22 +2436,22 @@
       <c r="H40" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="I40" s="70"/>
-      <c r="J40" s="72"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="70"/>
       <c r="K40" s="52"/>
     </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="69" t="s">
+    <row r="41" spans="1:11" ht="15" thickBot="1">
+      <c r="A41" s="67" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="39">
-        <v>46226</v>
-      </c>
-      <c r="D41" s="39">
-        <v>46228</v>
+      <c r="C41" s="81">
+        <v>46225</v>
+      </c>
+      <c r="D41" s="81">
+        <v>46237</v>
       </c>
       <c r="E41" s="39"/>
       <c r="F41" s="39"/>
@@ -2402,36 +2461,40 @@
       <c r="H41" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I41" s="71">
+      <c r="I41" s="82">
         <v>46237</v>
       </c>
-      <c r="J41" s="71"/>
+      <c r="J41" s="69"/>
       <c r="K41" s="51"/>
     </row>
     <row r="42" spans="1:11" ht="15" thickBot="1">
-      <c r="A42" s="70"/>
+      <c r="A42" s="68"/>
       <c r="B42" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
       <c r="E42" s="56"/>
       <c r="F42" s="56"/>
       <c r="G42" s="57"/>
       <c r="H42" s="55"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="72"/>
+      <c r="I42" s="83"/>
+      <c r="J42" s="70"/>
       <c r="K42" s="52"/>
     </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="69" t="s">
+    <row r="43" spans="1:11" ht="15" thickBot="1">
+      <c r="A43" s="67" t="s">
         <v>136</v>
       </c>
       <c r="B43" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
+      <c r="C43" s="80">
+        <v>46290</v>
+      </c>
+      <c r="D43" s="80">
+        <v>46305</v>
+      </c>
       <c r="E43" s="39"/>
       <c r="F43" s="39"/>
       <c r="G43" s="40">
@@ -2440,17 +2503,23 @@
       <c r="H43" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
+      <c r="I43" s="82">
+        <v>46447</v>
+      </c>
+      <c r="J43" s="69"/>
       <c r="K43" s="51"/>
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1">
-      <c r="A44" s="70"/>
+      <c r="A44" s="68"/>
       <c r="B44" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
+      <c r="C44" s="80">
+        <v>46419</v>
+      </c>
+      <c r="D44" s="80">
+        <v>46428</v>
+      </c>
       <c r="E44" s="56"/>
       <c r="F44" s="56"/>
       <c r="G44" s="57">
@@ -2459,20 +2528,12 @@
       <c r="H44" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="70"/>
-      <c r="J44" s="72"/>
+      <c r="I44" s="83"/>
+      <c r="J44" s="70"/>
       <c r="K44" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K44" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="7">
-      <filters blank="1">
-        <filter val="Construction"/>
-        <filter val="On Hold"/>
-        <filter val="Planning"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:K44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="62">
     <mergeCell ref="J37:J38"/>
     <mergeCell ref="J21:J22"/>
@@ -2537,7 +2598,7 @@
     <mergeCell ref="I41:I42"/>
     <mergeCell ref="J41:J42"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="H5:H48" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Construction,Completed,Planning,On Hold"</formula1>
     </dataValidation>
@@ -2572,56 +2633,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.399999999999999">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
     </row>
     <row r="4" spans="1:22" ht="41.4">
       <c r="A4" s="1" t="s">
@@ -2738,8 +2799,8 @@
         <f>'[1]Master Schedule'!C5</f>
         <v>46084</v>
       </c>
-      <c r="R5" s="81">
-        <v>46248</v>
+      <c r="R5" s="19">
+        <v>46106</v>
       </c>
       <c r="S5" s="14"/>
       <c r="T5" s="25" t="s">
@@ -2998,7 +3059,7 @@
         <v>138000</v>
       </c>
       <c r="G10" s="16">
-        <v>370</v>
+        <v>470</v>
       </c>
       <c r="H10" s="16">
         <f>E10*1</f>
@@ -3236,7 +3297,8 @@
         <v>525343.22400000005</v>
       </c>
       <c r="G14" s="16">
-        <v>215</v>
+        <f>215+146.7</f>
+        <v>361.7</v>
       </c>
       <c r="H14" s="16">
         <f>E14*0.8</f>
@@ -3593,7 +3655,7 @@
         <v>45717</v>
       </c>
       <c r="R20" s="19">
-        <v>45899</v>
+        <v>45737</v>
       </c>
       <c r="T20" s="26" t="s">
         <v>65</v>
@@ -3637,7 +3699,7 @@
         <v>45717</v>
       </c>
       <c r="R21" s="19">
-        <v>45910</v>
+        <v>45737</v>
       </c>
       <c r="T21" s="26" t="s">
         <v>126</v>
@@ -3657,7 +3719,8 @@
       <c r="D22" s="15"/>
       <c r="F22" s="24"/>
       <c r="G22" s="9">
-        <v>2484</v>
+        <f>2484+107</f>
+        <v>2591</v>
       </c>
       <c r="M22" s="9">
         <v>10000</v>
@@ -3760,7 +3823,7 @@
         <v>46225</v>
       </c>
       <c r="R24" s="11">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="T24" s="26" t="s">
         <v>140</v>
@@ -3782,7 +3845,7 @@
       <c r="C25" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="66">
+      <c r="D25" s="64">
         <v>0</v>
       </c>
       <c r="E25" s="12">
@@ -4343,7 +4406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4354,20 +4417,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4722,16 +4785,16 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="65">
+      <c r="A26" s="63">
         <v>46219</v>
       </c>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="64" t="s">
+      <c r="C26" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="63">
+      <c r="D26" s="61">
         <v>3</v>
       </c>
       <c r="E26" t="s">
@@ -4742,10 +4805,10 @@
       <c r="A27" s="3">
         <v>46224</v>
       </c>
-      <c r="B27" s="64" t="s">
+      <c r="B27" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="62" t="s">
         <v>61</v>
       </c>
       <c r="D27" s="4">
@@ -4762,7 +4825,7 @@
       <c r="B28" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="63" t="s">
         <v>61</v>
       </c>
       <c r="D28" s="4">
@@ -4779,7 +4842,7 @@
       <c r="B29" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C29" s="65" t="s">
+      <c r="C29" s="63" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="4">
@@ -4796,7 +4859,7 @@
       <c r="B30" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="65" t="s">
+      <c r="C30" s="63" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="4">
@@ -4804,6 +4867,23 @@
       </c>
       <c r="E30" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="4">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4828,22 +4908,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4876,7 +4956,7 @@
         <v>46224</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4910,7 +4990,7 @@
         <v>46224</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
     </row>
     <row 